--- a/admin/EIS-Compass-events.xlsx
+++ b/admin/EIS-Compass-events.xlsx
@@ -2007,7 +2007,7 @@
       </c>
       <c r="J24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC・初等部カリキュラム説明会</t>
+          <t xml:space="preserve">幼稚部・小学部カリキュラム説明会</t>
         </is>
       </c>
       <c r="K24" t="inlineStr" s="2">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="J33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC運動会リハーサル #1</t>
+          <t xml:space="preserve">幼稚部運動会リハーサル #1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr" s="2">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="J38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC運動会リハーサル #2</t>
+          <t xml:space="preserve">幼稚部運動会リハーサル #2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr" s="2">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="J39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC運動会</t>
+          <t xml:space="preserve">幼稚部運動会</t>
         </is>
       </c>
       <c r="K39" t="inlineStr" s="2">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="L44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC・初等部の保護者の皆様をお招きし、朝の授業をご参観いただき、お子様と一緒に朝の日課を体験していただきます。</t>
+          <t xml:space="preserve">幼稚部・小学部の保護者の皆様をお招きし、朝の授業をご参観いただき、お子様と一緒に朝の日課を体験していただきます。</t>
         </is>
       </c>
       <c r="M44" t="inlineStr" s="2">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="L50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ご家族や地域の皆様が寄付された品物や体験に入札し、初等部生徒会が選んだ取り組みを支援します。</t>
+          <t xml:space="preserve">ご家族や地域の皆様が寄付された品物や体験に入札し、小学部生徒会が選んだ取り組みを支援します。</t>
         </is>
       </c>
       <c r="M50" t="inlineStr" s="2">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="L52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">イーグルネストごとに、楽しい活動やゲームを通して仲間と交流し、季節を祝います。初等部生徒会が主催します。</t>
+          <t xml:space="preserve">イーグルネストごとに、楽しい活動やゲームを通して仲間と交流し、季節を祝います。小学部生徒会が主催します。</t>
         </is>
       </c>
       <c r="M52" t="inlineStr" s="2">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="J69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">初等部運動会リハーサル #1</t>
+          <t xml:space="preserve">小学部運動会リハーサル #1</t>
         </is>
       </c>
       <c r="K69" t="inlineStr" s="2">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="L70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC・初等部の保護者の皆様をお招きし、朝の授業をご参観いただき、お子様と一緒に朝の日課を体験していただきます。</t>
+          <t xml:space="preserve">幼稚部・小学部の保護者の皆様をお招きし、朝の授業をご参観いただき、お子様と一緒に朝の日課を体験していただきます。</t>
         </is>
       </c>
       <c r="M70" t="inlineStr" s="2">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="J75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">初等部運動会リハーサル #2</t>
+          <t xml:space="preserve">小学部運動会リハーサル #2</t>
         </is>
       </c>
       <c r="K75" t="inlineStr" s="2">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="J84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">初等部運動会リハーサル #3</t>
+          <t xml:space="preserve">小学部運動会リハーサル #3</t>
         </is>
       </c>
       <c r="K84" t="inlineStr" s="2">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="J86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">初等部運動会 2027</t>
+          <t xml:space="preserve">小学部運動会 2027</t>
         </is>
       </c>
       <c r="K86" t="inlineStr" s="2">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="J107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">初等部・ELC 年度末発表会</t>
+          <t xml:space="preserve">小学部・幼稚部 年度末発表会</t>
         </is>
       </c>
       <c r="K107" t="inlineStr" s="2">

--- a/admin/EIS-Compass-events.xlsx
+++ b/admin/EIS-Compass-events.xlsx
@@ -367,7 +367,7 @@
       </c>
       <c r="J4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">オリエンテーション週間・生活指導説明会</t>
+          <t xml:space="preserve">オリエンテーション週間・学校生活説明会</t>
         </is>
       </c>
       <c r="K4" t="inlineStr" s="2">
@@ -777,7 +777,7 @@
       </c>
       <c r="J9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お気に入りの本を持ってくる日</t>
+          <t xml:space="preserve">お気に入りの本を持ってこよう！</t>
         </is>
       </c>
       <c r="K9" t="inlineStr" s="2">
@@ -951,7 +951,7 @@
       </c>
       <c r="L11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">キーボード操作のスキル、正確さ、自信を高めることを目的とした、親善タイピング大会に参加します。</t>
+          <t xml:space="preserve">キーボード操作のスキル、正確さ、自信を高めることを目的とした、校内タイピング大会に参加します。</t>
         </is>
       </c>
       <c r="M11" t="inlineStr" s="2">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="J13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内バスケットボール親善大会</t>
+          <t xml:space="preserve">校内バスケットボール大会</t>
         </is>
       </c>
       <c r="K13" t="inlineStr" s="2">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="L13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内でのバスケットボール親善大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
+          <t xml:space="preserve">校内バスケットボール大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
         </is>
       </c>
       <c r="M13" t="inlineStr" s="2">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="J14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">コンセプト・コン（グローバルな視野）</t>
+          <t xml:space="preserve">コンセプト・コン（国際的な視野）</t>
         </is>
       </c>
       <c r="K14" t="inlineStr" s="2">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DPラフティング</t>
+          <t xml:space="preserve">DPラフティング体験</t>
         </is>
       </c>
       <c r="K20" t="inlineStr" s="2">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="J21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">進路支援・メンタルヘルス座談会</t>
+          <t xml:space="preserve">進路・メンタルヘルス座談会</t>
         </is>
       </c>
       <c r="K21" t="inlineStr" s="2">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="J27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">大学フェア</t>
+          <t xml:space="preserve">大学進学フェア</t>
         </is>
       </c>
       <c r="K27" t="inlineStr" s="2">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="J30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">豊田高専 見学</t>
+          <t xml:space="preserve">豊田高専見学</t>
         </is>
       </c>
       <c r="K30" t="inlineStr" s="2">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="J32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">インターナショナル・マインドネス・フェスティバル</t>
+          <t xml:space="preserve">国際理解フェスティバル</t>
         </is>
       </c>
       <c r="K32" t="inlineStr" s="2">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="J34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">トヨタ博物館 校外学習</t>
+          <t xml:space="preserve">トヨタ博物館校外学習</t>
         </is>
       </c>
       <c r="K34" t="inlineStr" s="2">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="J35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">課外活動：秋のCAS・プロジェクト支援フェア</t>
+          <t xml:space="preserve">課外活動：秋のCAS・プロジェクトサポートフェア</t>
         </is>
       </c>
       <c r="K35" t="inlineStr" s="2">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="J40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内サッカー親善大会</t>
+          <t xml:space="preserve">校内サッカー大会</t>
         </is>
       </c>
       <c r="K40" t="inlineStr" s="2">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="L40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内でのサッカー親善大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
+          <t xml:space="preserve">校内サッカー大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
         </is>
       </c>
       <c r="M40" t="inlineStr" s="2">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="J44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者モーニング参観 #1</t>
+          <t xml:space="preserve">朝の授業参観 #1</t>
         </is>
       </c>
       <c r="K44" t="inlineStr" s="2">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="J45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">教員感謝デー</t>
+          <t xml:space="preserve">教職員感謝デー</t>
         </is>
       </c>
       <c r="K45" t="inlineStr" s="2">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="J54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ティーパーティー／PTA（どなたでも）</t>
+          <t xml:space="preserve">PTAティーパーティー（どなたでも参加できます）</t>
         </is>
       </c>
       <c r="K54" t="inlineStr" s="2">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="J56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第1学期末行事 お泊まりプログラム：G6–10</t>
+          <t xml:space="preserve">第1学期末行事：宿泊プログラム（G6–10）</t>
         </is>
       </c>
       <c r="K56" t="inlineStr" s="2">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="L56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">6～10年生が学校でのお泊まりプログラムに参加し、共に活動しながら仲間づくりを行い、第1学期の終わりを祝います。</t>
+          <t xml:space="preserve">6～10年生が校内での宿泊プログラムに参加し、共に活動しながら仲間づくりを行い、第1学期の終わりを祝います。</t>
         </is>
       </c>
       <c r="M56" t="inlineStr" s="2">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="J58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G10保護者説明会（高等部の科目選択）</t>
+          <t xml:space="preserve">G10保護者向け説明会（高等部科目選択）</t>
         </is>
       </c>
       <c r="K58" t="inlineStr" s="2">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="J60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">卒業生講話</t>
+          <t xml:space="preserve">卒業生トーク</t>
         </is>
       </c>
       <c r="K60" t="inlineStr" s="2">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="J63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内バレーボール親善大会</t>
+          <t xml:space="preserve">校内バレーボール大会</t>
         </is>
       </c>
       <c r="K63" t="inlineStr" s="2">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="L63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内でのバレーボール親善大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
+          <t xml:space="preserve">校内バレーボール大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
         </is>
       </c>
       <c r="M63" t="inlineStr" s="2">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="J65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">進路支援：セカンドキャリア座談会・キャリアフェア</t>
+          <t xml:space="preserve">進路支援：第2回キャリア座談会・キャリアフェア</t>
         </is>
       </c>
       <c r="K65" t="inlineStr" s="2">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="J70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者モーニング参観 #2</t>
+          <t xml:space="preserve">朝の授業参観 #2</t>
         </is>
       </c>
       <c r="K70" t="inlineStr" s="2">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="J79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ティーパーティー／PTA（どなたでも）</t>
+          <t xml:space="preserve">PTAティーパーティー（どなたでも参加できます）</t>
         </is>
       </c>
       <c r="K79" t="inlineStr" s="2">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="J90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">生物IA準備 校外学習：海岸の生態系</t>
+          <t xml:space="preserve">生物IA準備校外学習：海岸生態系調査</t>
         </is>
       </c>
       <c r="K90" t="inlineStr" s="2">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="J91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G12お祝い行事</t>
+          <t xml:space="preserve">G12修了記念イベント</t>
         </is>
       </c>
       <c r="K91" t="inlineStr" s="2">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="J95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内バスケットボール親善大会</t>
+          <t xml:space="preserve">校内バスケットボール大会</t>
         </is>
       </c>
       <c r="K95" t="inlineStr" s="2">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="L95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内でのバスケットボール親善大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
+          <t xml:space="preserve">校内バスケットボール大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
         </is>
       </c>
       <c r="M95" t="inlineStr" s="2">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="J96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">起業家デー</t>
+          <t xml:space="preserve">アントレプレナーシップ・デー</t>
         </is>
       </c>
       <c r="K96" t="inlineStr" s="2">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="J98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">土曜校 最終日イベント</t>
+          <t xml:space="preserve">土曜校最終日イベント</t>
         </is>
       </c>
       <c r="K98" t="inlineStr" s="2">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="J99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">コンセプト・コン（未来への視点）</t>
+          <t xml:space="preserve">コンセプト・コン（未来を考える）</t>
         </is>
       </c>
       <c r="K99" t="inlineStr" s="2">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="J100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G12卒業式（パフォーマンス付き）</t>
+          <t xml:space="preserve">G12卒業式・記念パフォーマンス</t>
         </is>
       </c>
       <c r="K100" t="inlineStr" s="2">
@@ -8321,7 +8321,7 @@
       </c>
       <c r="J101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学びの発表会 準備</t>
+          <t xml:space="preserve">学びの発表会準備</t>
         </is>
       </c>
       <c r="K101" t="inlineStr" s="2">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="J106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部・5年生 卒業式</t>
+          <t xml:space="preserve">幼稚部・5年生卒業式</t>
         </is>
       </c>
       <c r="K106" t="inlineStr" s="2">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="J107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小学部・幼稚部 年度末発表会</t>
+          <t xml:space="preserve">小学部・幼稚部年度末発表会</t>
         </is>
       </c>
       <c r="K107" t="inlineStr" s="2">

--- a/admin/EIS-Compass-events.xlsx
+++ b/admin/EIS-Compass-events.xlsx
@@ -42,11 +42,14 @@
   <cellStyleXfs count="1">
     <xf/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf/>
     <xf fontId="1" fillId="2" applyFont="1" applyFill="1"/>
     <xf applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
 </styleSheet>
@@ -56,9 +59,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1" style="3"/>
+    <col min="3" max="3" width="12" customWidth="1" style="3"/>
+    <col min="4" max="4" width="13" customWidth="1" style="3"/>
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
@@ -161,17 +164,17 @@
           <t xml:space="preserve">2026-08-12-book-drive</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr" s="2">
+      <c r="B2" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-08-12</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr" s="2">
+      <c r="C2" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-08-12</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr" s="2">
+      <c r="D2" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -243,17 +246,17 @@
           <t xml:space="preserve">2026-08-17-student-orientation-program</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr" s="2">
+      <c r="B3" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-08-17</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr" s="2">
+      <c r="C3" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-08-17</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr" s="2">
+      <c r="D3" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -325,17 +328,17 @@
           <t xml:space="preserve">2026-08-17-orientation-week-welfare-briefing</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr" s="2">
+      <c r="B4" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-08-17</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr" s="2">
+      <c r="C4" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-08-21</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr" s="2">
+      <c r="D4" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -407,17 +410,17 @@
           <t xml:space="preserve">2026-08-22-sat-test-1</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr" s="2">
+      <c r="B5" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-08-22</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr" s="2">
+      <c r="C5" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-08-22</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr" s="2">
+      <c r="D5" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -489,17 +492,17 @@
           <t xml:space="preserve">2026-08-24-book-drive</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr" s="2">
+      <c r="B6" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-08-24</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr" s="2">
+      <c r="C6" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-08-24</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr" s="2">
+      <c r="D6" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -571,17 +574,17 @@
           <t xml:space="preserve">2026-08-24-jigsaw-competition</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr" s="2">
+      <c r="B7" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-08-24</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr" s="2">
+      <c r="C7" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-08-24</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr" s="2">
+      <c r="D7" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -653,17 +656,17 @@
           <t xml:space="preserve">2026-08-28-movie-night</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr" s="2">
+      <c r="B8" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-08-28</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr" s="2">
+      <c r="C8" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-08-28</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr" s="2">
+      <c r="D8" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -735,17 +738,17 @@
           <t xml:space="preserve">2026-09-01-bring-your-favourite-book-day</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr" s="2">
+      <c r="B9" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr" s="2">
+      <c r="C9" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-09-01</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr" s="2">
+      <c r="D9" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -817,17 +820,17 @@
           <t xml:space="preserve">2026-09-04-art-workshop</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr" s="2">
+      <c r="B10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr" s="2">
+      <c r="C10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-09-04</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr" s="2">
+      <c r="D10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -899,17 +902,17 @@
           <t xml:space="preserve">2026-09-09-speed-typing-competition</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr" s="2">
+      <c r="B11" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr" s="2">
+      <c r="C11" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr" s="2">
+      <c r="D11" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -981,17 +984,17 @@
           <t xml:space="preserve">2026-09-12-sat-test-2</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr" s="2">
+      <c r="B12" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr" s="2">
+      <c r="C12" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr" s="2">
+      <c r="D12" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1063,17 +1066,17 @@
           <t xml:space="preserve">2026-09-14-friendly-basketball-tournament-internal</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr" s="2">
+      <c r="B13" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-09-14</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr" s="2">
+      <c r="C13" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-09-18</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr" s="2">
+      <c r="D13" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1145,17 +1148,17 @@
           <t xml:space="preserve">2026-09-14-concept-con-global-mindedness</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr" s="2">
+      <c r="B14" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-09-14</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr" s="2">
+      <c r="C14" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-09-18</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr" s="2">
+      <c r="D14" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1227,17 +1230,17 @@
           <t xml:space="preserve">2026-09-18-coffee-hour</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr" s="2">
+      <c r="B15" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-09-18</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr" s="2">
+      <c r="C15" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-09-18</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr" s="2">
+      <c r="D15" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1309,17 +1312,17 @@
           <t xml:space="preserve">2026-09-25-open-campus</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr" s="2">
+      <c r="B16" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-09-25</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr" s="2">
+      <c r="C16" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-09-25</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr" s="2">
+      <c r="D16" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1391,17 +1394,17 @@
           <t xml:space="preserve">2026-09-28-spirit-week</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr" s="2">
+      <c r="B17" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-09-28</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr" s="2">
+      <c r="C17" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-09-30</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr" s="2">
+      <c r="D17" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1473,17 +1476,17 @@
           <t xml:space="preserve">2026-10-03-world-tea-party</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr" s="2">
+      <c r="B18" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-03</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr" s="2">
+      <c r="C18" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-03</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr" s="2">
+      <c r="D18" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1555,17 +1558,17 @@
           <t xml:space="preserve">2026-10-03-sat-test-3</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr" s="2">
+      <c r="B19" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-03</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr" s="2">
+      <c r="C19" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-03</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr" s="2">
+      <c r="D19" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1637,17 +1640,17 @@
           <t xml:space="preserve">2026-10-03-dp-rafting-trip</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr" s="2">
+      <c r="B20" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-03</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr" s="2">
+      <c r="C20" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-03</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr" s="2">
+      <c r="D20" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1719,17 +1722,17 @@
           <t xml:space="preserve">2026-10-07-career-support-and-mental-health-round-table</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr" s="2">
+      <c r="B21" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-07</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr" s="2">
+      <c r="C21" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-07</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr" s="2">
+      <c r="D21" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1801,17 +1804,17 @@
           <t xml:space="preserve">2026-10-09-high-school-curriculum-night</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr" s="2">
+      <c r="B22" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-09</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr" s="2">
+      <c r="C22" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-09</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr" s="2">
+      <c r="D22" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1883,17 +1886,17 @@
           <t xml:space="preserve">2026-10-09-eagle-bucks-store</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr" s="2">
+      <c r="B23" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-09</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr" s="2">
+      <c r="C23" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-09</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr" s="2">
+      <c r="D23" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1965,17 +1968,17 @@
           <t xml:space="preserve">2026-10-19-elc-primary-curriculum-night</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr" s="2">
+      <c r="B24" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-19</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr" s="2">
+      <c r="C24" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-19</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr" s="2">
+      <c r="D24" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2047,17 +2050,17 @@
           <t xml:space="preserve">2026-10-19-parent-teacher-conferences</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr" s="2">
+      <c r="B25" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-19</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr" s="2">
+      <c r="C25" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-19</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr" s="2">
+      <c r="D25" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2129,17 +2132,17 @@
           <t xml:space="preserve">2026-10-20-secondary-curriculum-night</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr" s="2">
+      <c r="B26" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr" s="2">
+      <c r="C26" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr" s="2">
+      <c r="D26" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2211,17 +2214,17 @@
           <t xml:space="preserve">2026-10-21-college-fair</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr" s="2">
+      <c r="B27" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr" s="2">
+      <c r="C27" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr" s="2">
+      <c r="D27" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2293,17 +2296,17 @@
           <t xml:space="preserve">2026-10-23-nagoya-university-biology-laboratory-visit</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr" s="2">
+      <c r="B28" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr" s="2">
+      <c r="C28" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr" s="2">
+      <c r="D28" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2375,17 +2378,17 @@
           <t xml:space="preserve">2026-10-25-pta-picnic</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr" s="2">
+      <c r="B29" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-25</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr" s="2">
+      <c r="C29" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-25</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr" s="2">
+      <c r="D29" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2457,17 +2460,17 @@
           <t xml:space="preserve">2026-10-26-toyota-college-trip</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr" s="2">
+      <c r="B30" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-26</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr" s="2">
+      <c r="C30" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-26</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr" s="2">
+      <c r="D30" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2539,17 +2542,17 @@
           <t xml:space="preserve">2026-10-30-sensory-wonderland</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr" s="2">
+      <c r="B31" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-30</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr" s="2">
+      <c r="C31" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-30</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr" s="2">
+      <c r="D31" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2621,17 +2624,17 @@
           <t xml:space="preserve">2026-10-31-international-mindedness-festival</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr" s="2">
+      <c r="B32" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr" s="2">
+      <c r="C32" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr" s="2">
+      <c r="D32" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2703,17 +2706,17 @@
           <t xml:space="preserve">2026-11-04-elc-sports-day-rehearsal-1</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr" s="2">
+      <c r="B33" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-04</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr" s="2">
+      <c r="C33" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-04</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr" s="2">
+      <c r="D33" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2785,17 +2788,17 @@
           <t xml:space="preserve">2026-11-05-toyota-museum-field-trip</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr" s="2">
+      <c r="B34" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-05</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr" s="2">
+      <c r="C34" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-05</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr" s="2">
+      <c r="D34" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2867,17 +2870,17 @@
           <t xml:space="preserve">2026-11-06-extracurricular-activities-autumn-cas-project-su</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr" s="2">
+      <c r="B35" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-06</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr" s="2">
+      <c r="C35" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-06</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr" s="2">
+      <c r="D35" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -2949,17 +2952,17 @@
           <t xml:space="preserve">2026-11-07-sat-test-4</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr" s="2">
+      <c r="B36" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr" s="2">
+      <c r="C36" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr" s="2">
+      <c r="D36" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3031,17 +3034,17 @@
           <t xml:space="preserve">2026-11-09-wellbeing-week</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr" s="2">
+      <c r="B37" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-09</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr" s="2">
+      <c r="C37" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-13</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr" s="2">
+      <c r="D37" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3113,17 +3116,17 @@
           <t xml:space="preserve">2026-11-11-elc-sports-day-rehearsal-2</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr" s="2">
+      <c r="B38" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr" s="2">
+      <c r="C38" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr" s="2">
+      <c r="D38" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3195,17 +3198,17 @@
           <t xml:space="preserve">2026-11-14-elc-sports-day</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr" s="2">
+      <c r="B39" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-14</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr" s="2">
+      <c r="C39" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-14</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr" s="2">
+      <c r="D39" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3277,17 +3280,17 @@
           <t xml:space="preserve">2026-11-16-friendly-soccer-tournament-internal</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr" s="2">
+      <c r="B40" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr" s="2">
+      <c r="C40" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-20</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr" s="2">
+      <c r="D40" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3359,17 +3362,17 @@
           <t xml:space="preserve">2026-11-17-foundation-field-trip</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr" s="2">
+      <c r="B41" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr" s="2">
+      <c r="C41" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr" s="2">
+      <c r="D41" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3441,17 +3444,17 @@
           <t xml:space="preserve">2026-11-20-gifu-kakamigahara-air-and-space-museum</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr" s="2">
+      <c r="B42" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-20</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr" s="2">
+      <c r="C42" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-20</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr" s="2">
+      <c r="D42" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3523,17 +3526,17 @@
           <t xml:space="preserve">2026-11-24-winter-art-contest</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr" s="2">
+      <c r="B43" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr" s="2">
+      <c r="C43" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-25</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr" s="2">
+      <c r="D43" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3605,17 +3608,17 @@
           <t xml:space="preserve">2026-11-27-parents-morning-1</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr" s="2">
+      <c r="B44" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr" s="2">
+      <c r="C44" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr" s="2">
+      <c r="D44" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3687,17 +3690,17 @@
           <t xml:space="preserve">2026-11-27-teacher-appreciation-day</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr" s="2">
+      <c r="B45" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr" s="2">
+      <c r="C45" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr" s="2">
+      <c r="D45" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3769,17 +3772,17 @@
           <t xml:space="preserve">2026-11-28-2026-enishi-futsal-tournament</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr" s="2">
+      <c r="B46" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-28</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr" s="2">
+      <c r="C46" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-28</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr" s="2">
+      <c r="D46" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3851,17 +3854,17 @@
           <t xml:space="preserve">2026-12-03-grade-3-4-musical</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr" s="2">
+      <c r="B47" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-12-03</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr" s="2">
+      <c r="C47" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-12-04</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr" s="2">
+      <c r="D47" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3933,17 +3936,17 @@
           <t xml:space="preserve">2026-12-05-sat-test-5</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr" s="2">
+      <c r="B48" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-12-05</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr" s="2">
+      <c r="C48" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-12-05</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr" s="2">
+      <c r="D48" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4015,17 +4018,17 @@
           <t xml:space="preserve">2026-12-10-choir-and-orchestra-concert</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr" s="2">
+      <c r="B49" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-12-10</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr" s="2">
+      <c r="C49" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-12-10</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr" s="2">
+      <c r="D49" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4097,17 +4100,17 @@
           <t xml:space="preserve">2026-12-11-silent-auction</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr" s="2">
+      <c r="B50" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-12-11</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr" s="2">
+      <c r="C50" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-12-11</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr" s="2">
+      <c r="D50" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4179,17 +4182,17 @@
           <t xml:space="preserve">2026-12-16-industry-visit-tech-company</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr" s="2">
+      <c r="B51" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr" s="2">
+      <c r="C51" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr" s="2">
+      <c r="D51" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4261,17 +4264,17 @@
           <t xml:space="preserve">2026-12-16-winter-party-eagle-nest</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr" s="2">
+      <c r="B52" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr" s="2">
+      <c r="C52" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr" s="2">
+      <c r="D52" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4343,17 +4346,17 @@
           <t xml:space="preserve">2026-12-17-talent-day</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr" s="2">
+      <c r="B53" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-12-17</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr" s="2">
+      <c r="C53" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-12-17</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr" s="2">
+      <c r="D53" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4425,17 +4428,17 @@
           <t xml:space="preserve">2026-12-18-tea-party-pta-for-all</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr" s="2">
+      <c r="B54" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-12-18</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr" s="2">
+      <c r="C54" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-12-18</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr" s="2">
+      <c r="D54" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4507,17 +4510,17 @@
           <t xml:space="preserve">2026-12-18-eagle-bucks-store</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr" s="2">
+      <c r="B55" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-12-18</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr" s="2">
+      <c r="C55" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-12-18</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr" s="2">
+      <c r="D55" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4589,17 +4592,17 @@
           <t xml:space="preserve">2026-12-19-end-of-term-1-activity-sleep-over-program-g6-10</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr" s="2">
+      <c r="B56" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-12-19</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr" s="2">
+      <c r="C56" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-12-19</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr" s="2">
+      <c r="D56" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4671,17 +4674,17 @@
           <t xml:space="preserve">2026-12-21-winter-study-camp-g11-12</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr" s="2">
+      <c r="B57" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-12-21</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr" s="2">
+      <c r="C57" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-12-23</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr" s="2">
+      <c r="D57" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4753,17 +4756,17 @@
           <t xml:space="preserve">2027-01-14-g10-parent-info-session-high-school-subject-choi</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr" s="2">
+      <c r="B58" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-01-14</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr" s="2">
+      <c r="C58" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-01-14</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr" s="2">
+      <c r="D58" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4835,17 +4838,17 @@
           <t xml:space="preserve">2027-01-22-open-campus</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr" s="2">
+      <c r="B59" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-01-22</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr" s="2">
+      <c r="C59" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-01-22</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr" s="2">
+      <c r="D59" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4917,17 +4920,17 @@
           <t xml:space="preserve">2027-01-23-alumni-talk</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr" s="2">
+      <c r="B60" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-01-23</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr" s="2">
+      <c r="C60" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-01-23</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr" s="2">
+      <c r="D60" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -4999,17 +5002,17 @@
           <t xml:space="preserve">2027-01-27-natural-disaster-field-trip</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr" s="2">
+      <c r="B61" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-01-27</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr" s="2">
+      <c r="C61" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-01-27</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr" s="2">
+      <c r="D61" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5081,17 +5084,17 @@
           <t xml:space="preserve">2027-01-30-model-united-nations-event-mun</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr" s="2">
+      <c r="B62" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr" s="2">
+      <c r="C62" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr" s="2">
+      <c r="D62" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5163,17 +5166,17 @@
           <t xml:space="preserve">2027-02-01-friendly-volleyball-tournament-internal</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr" s="2">
+      <c r="B63" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-02-01</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr" s="2">
+      <c r="C63" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-02-05</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr" s="2">
+      <c r="D63" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5245,17 +5248,17 @@
           <t xml:space="preserve">2027-02-01-concept-con-language</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr" s="2">
+      <c r="B64" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-02-01</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr" s="2">
+      <c r="C64" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-02-05</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr" s="2">
+      <c r="D64" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5327,17 +5330,17 @@
           <t xml:space="preserve">2027-02-18-career-support-second-career-roundtable-and-care</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr" s="2">
+      <c r="B65" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-02-18</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr" s="2">
+      <c r="C65" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-02-18</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr" s="2">
+      <c r="D65" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5409,17 +5412,17 @@
           <t xml:space="preserve">2027-02-19-collective-field-trip</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr" s="2">
+      <c r="B66" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-02-19</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr" s="2">
+      <c r="C66" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-02-19</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr" s="2">
+      <c r="D66" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5491,17 +5494,17 @@
           <t xml:space="preserve">2027-02-22-world-thinking-day</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr" s="2">
+      <c r="B67" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr" s="2">
+      <c r="C67" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr" s="2">
+      <c r="D67" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5573,17 +5576,17 @@
           <t xml:space="preserve">2027-02-22-secondary-sports-day-rehearsal-1</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr" s="2">
+      <c r="B68" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr" s="2">
+      <c r="C68" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr" s="2">
+      <c r="D68" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5655,17 +5658,17 @@
           <t xml:space="preserve">2027-02-25-primary-sports-day-rehearsal-1</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr" s="2">
+      <c r="B69" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-02-25</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr" s="2">
+      <c r="C69" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-02-25</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr" s="2">
+      <c r="D69" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5737,17 +5740,17 @@
           <t xml:space="preserve">2027-02-26-parents-morning-2</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr" s="2">
+      <c r="B70" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-02-26</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr" s="2">
+      <c r="C70" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-02-26</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr" s="2">
+      <c r="D70" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5819,17 +5822,17 @@
           <t xml:space="preserve">2027-02-26-eagle-talks</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr" s="2">
+      <c r="B71" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-02-26</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr" s="2">
+      <c r="C71" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-02-26</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr" s="2">
+      <c r="D71" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5901,17 +5904,17 @@
           <t xml:space="preserve">2027-03-04-grade-1-2-musical</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr" s="2">
+      <c r="B72" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-04</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr" s="2">
+      <c r="C72" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-05</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr" s="2">
+      <c r="D72" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -5983,17 +5986,17 @@
           <t xml:space="preserve">2027-03-05-higashiyama-zoo-botanical-garden</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr" s="2">
+      <c r="B73" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-05</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr" s="2">
+      <c r="C73" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-05</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr" s="2">
+      <c r="D73" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6065,17 +6068,17 @@
           <t xml:space="preserve">2027-03-06-sat-test-6</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr" s="2">
+      <c r="B74" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-06</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr" s="2">
+      <c r="C74" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-06</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr" s="2">
+      <c r="D74" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6147,17 +6150,17 @@
           <t xml:space="preserve">2027-03-09-primary-sports-day-rehearsal-2</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr" s="2">
+      <c r="B75" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-09</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr" s="2">
+      <c r="C75" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-09</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr" s="2">
+      <c r="D75" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6229,17 +6232,17 @@
           <t xml:space="preserve">2027-03-12-secondary-sports-day-rehearsal-2</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr" s="2">
+      <c r="B76" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-12</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr" s="2">
+      <c r="C76" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-12</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr" s="2">
+      <c r="D76" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6311,17 +6314,17 @@
           <t xml:space="preserve">2027-03-18-japanese-culture-day</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr" s="2">
+      <c r="B77" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-18</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr" s="2">
+      <c r="C77" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-18</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr" s="2">
+      <c r="D77" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6393,17 +6396,17 @@
           <t xml:space="preserve">2027-03-19-eagle-bucks-store</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr" s="2">
+      <c r="B78" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-19</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr" s="2">
+      <c r="C78" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-19</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr" s="2">
+      <c r="D78" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6475,17 +6478,17 @@
           <t xml:space="preserve">2027-03-19-tea-party-pta-for-all</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr" s="2">
+      <c r="B79" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-19</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr" s="2">
+      <c r="C79" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-19</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr" s="2">
+      <c r="D79" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6557,17 +6560,17 @@
           <t xml:space="preserve">2027-03-19-end-of-term-2-activity-g9-12</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr" s="2">
+      <c r="B80" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-19</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr" s="2">
+      <c r="C80" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-20</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr" s="2">
+      <c r="D80" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6639,17 +6642,17 @@
           <t xml:space="preserve">2027-03-20-end-of-term-2-activity-g6-8</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr" s="2">
+      <c r="B81" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-20</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr" s="2">
+      <c r="C81" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-21</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr" s="2">
+      <c r="D81" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6721,17 +6724,17 @@
           <t xml:space="preserve">2027-03-30-parent-teacher-conferences</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr" s="2">
+      <c r="B82" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-30</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr" s="2">
+      <c r="C82" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-30</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr" s="2">
+      <c r="D82" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6803,17 +6806,17 @@
           <t xml:space="preserve">2027-03-31-secondary-sports-day-rehearsal-3</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr" s="2">
+      <c r="B83" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-31</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr" s="2">
+      <c r="C83" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-31</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr" s="2">
+      <c r="D83" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6885,17 +6888,17 @@
           <t xml:space="preserve">2027-04-01-primary-sports-day-rehearsal-3</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr" s="2">
+      <c r="B84" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-04-01</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr" s="2">
+      <c r="C84" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-04-01</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr" s="2">
+      <c r="D84" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -6967,17 +6970,17 @@
           <t xml:space="preserve">2027-04-03-sports-day</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr" s="2">
+      <c r="B85" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr" s="2">
+      <c r="C85" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr" s="2">
+      <c r="D85" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -7049,17 +7052,17 @@
           <t xml:space="preserve">2027-04-03-primary-sports-day-2027</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr" s="2">
+      <c r="B86" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr" s="2">
+      <c r="C86" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr" s="2">
+      <c r="D86" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -7131,17 +7134,17 @@
           <t xml:space="preserve">2027-04-15-world-art-day</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr" s="2">
+      <c r="B87" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-04-15</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr" s="2">
+      <c r="C87" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-04-15</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr" s="2">
+      <c r="D87" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -7213,17 +7216,17 @@
           <t xml:space="preserve">2027-04-16-foundation-field-trip</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr" s="2">
+      <c r="B88" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-04-16</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr" s="2">
+      <c r="C88" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-04-16</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr" s="2">
+      <c r="D88" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -7295,17 +7298,17 @@
           <t xml:space="preserve">2027-04-21-hackathon-hour-of-code</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr" s="2">
+      <c r="B89" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-04-21</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr" s="2">
+      <c r="C89" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-04-21</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr" s="2">
+      <c r="D89" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -7377,17 +7380,17 @@
           <t xml:space="preserve">2027-04-22-biology-ia-prep-field-trip-shore-ecosystem</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr" s="2">
+      <c r="B90" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-04-22</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr" s="2">
+      <c r="C90" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-04-22</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr" s="2">
+      <c r="D90" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -7459,17 +7462,17 @@
           <t xml:space="preserve">2027-04-23-g12-celebration</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr" s="2">
+      <c r="B91" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-04-23</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr" s="2">
+      <c r="C91" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-04-23</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr" s="2">
+      <c r="D91" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -7541,17 +7544,17 @@
           <t xml:space="preserve">2027-04-26-grade-4-5-camping-trip</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr" s="2">
+      <c r="B92" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-04-26</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr" s="2">
+      <c r="C92" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr" s="2">
+      <c r="D92" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -7623,17 +7626,17 @@
           <t xml:space="preserve">2027-04-27-choir-and-orchestra-concert</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr" s="2">
+      <c r="B93" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr" s="2">
+      <c r="C93" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr" s="2">
+      <c r="D93" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -7705,17 +7708,17 @@
           <t xml:space="preserve">2027-04-30-science-fair</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr" s="2">
+      <c r="B94" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-04-30</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr" s="2">
+      <c r="C94" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-04-30</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr" s="2">
+      <c r="D94" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -7787,17 +7790,17 @@
           <t xml:space="preserve">2027-05-17-friendly-basketball-tournament-internal</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr" s="2">
+      <c r="B95" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-05-17</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr" s="2">
+      <c r="C95" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr" s="2">
+      <c r="D95" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -7869,17 +7872,17 @@
           <t xml:space="preserve">2027-05-19-entrepreneurs-day</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr" s="2">
+      <c r="B96" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-05-19</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr" s="2">
+      <c r="C96" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-05-20</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr" s="2">
+      <c r="D96" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -7951,17 +7954,17 @@
           <t xml:space="preserve">2027-05-21-collective-field-trip</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr" s="2">
+      <c r="B97" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr" s="2">
+      <c r="C97" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr" s="2">
+      <c r="D97" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -8033,17 +8036,17 @@
           <t xml:space="preserve">2027-05-22-saturday-school-last-day-event</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr" s="2">
+      <c r="B98" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr" s="2">
+      <c r="C98" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr" s="2">
+      <c r="D98" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -8115,17 +8118,17 @@
           <t xml:space="preserve">2027-05-24-concept-con-future-focus</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr" s="2">
+      <c r="B99" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-05-24</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr" s="2">
+      <c r="C99" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-05-28</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr" s="2">
+      <c r="D99" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -8197,17 +8200,17 @@
           <t xml:space="preserve">2027-05-28-g12-graduation-with-performances</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr" s="2">
+      <c r="B100" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-05-28</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr" s="2">
+      <c r="C100" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-05-28</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr" s="2">
+      <c r="D100" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -8279,17 +8282,17 @@
           <t xml:space="preserve">2027-06-03-celebration-of-learning-prep</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr" s="2">
+      <c r="B101" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr" s="2">
+      <c r="C101" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr" s="2">
+      <c r="D101" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -8361,17 +8364,17 @@
           <t xml:space="preserve">2027-06-03-ukulele-concert</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr" s="2">
+      <c r="B102" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr" s="2">
+      <c r="C102" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-06-04</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr" s="2">
+      <c r="D102" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -8443,17 +8446,17 @@
           <t xml:space="preserve">2027-06-04-celebration-of-learning</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr" s="2">
+      <c r="B103" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-06-04</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr" s="2">
+      <c r="C103" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-06-04</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr" s="2">
+      <c r="D103" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -8525,17 +8528,17 @@
           <t xml:space="preserve">2027-06-05-sat-test-7</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr" s="2">
+      <c r="B104" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-06-05</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr" s="2">
+      <c r="C104" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-06-05</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr" s="2">
+      <c r="D104" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -8607,17 +8610,17 @@
           <t xml:space="preserve">2027-06-17-eagle-bucks-store</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr" s="2">
+      <c r="B105" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-06-17</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr" s="2">
+      <c r="C105" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-06-17</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr" s="2">
+      <c r="D105" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -8689,17 +8692,17 @@
           <t xml:space="preserve">2027-06-18-kindergarten-and-grade-5-graduation</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr" s="2">
+      <c r="B106" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-06-18</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr" s="2">
+      <c r="C106" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-06-18</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr" s="2">
+      <c r="D106" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -8771,17 +8774,17 @@
           <t xml:space="preserve">2027-06-18-primary-elc-year-end-performance</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr" s="2">
+      <c r="B107" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-06-18</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr" s="2">
+      <c r="C107" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-06-18</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr" s="2">
+      <c r="D107" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -8853,17 +8856,17 @@
           <t xml:space="preserve">2027-06-19-end-of-term-3-activity-g6-10</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr" s="2">
+      <c r="B108" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-06-19</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr" s="2">
+      <c r="C108" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-06-19</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr" s="2">
+      <c r="D108" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -8935,17 +8938,17 @@
           <t xml:space="preserve">2027-06-22-parent-teacher-conferences</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr" s="2">
+      <c r="B109" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-06-22</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr" s="2">
+      <c r="C109" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-06-23</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr" s="2">
+      <c r="D109" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -9017,17 +9020,17 @@
           <t xml:space="preserve">2027-06-28-summer-school</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr" s="2">
+      <c r="B110" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-06-28</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr" s="2">
+      <c r="C110" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-07-24</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr" s="2">
+      <c r="D110" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -9100,8 +9103,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1" style="3"/>
+    <col min="2" max="2" width="12" customWidth="1" style="3"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="32" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
@@ -9135,12 +9138,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr" s="2">
+      <c r="A2" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-09-21</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr" s="2">
+      <c r="B2" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-09-21</t>
         </is>
@@ -9162,12 +9165,12 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr" s="2">
+      <c r="A3" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-09-22</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr" s="2">
+      <c r="B3" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-09-22</t>
         </is>
@@ -9189,12 +9192,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr" s="2">
+      <c r="A4" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-12</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr" s="2">
+      <c r="B4" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-12</t>
         </is>
@@ -9216,12 +9219,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr" s="2">
+      <c r="A5" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-13</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr" s="2">
+      <c r="B5" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-10-16</t>
         </is>
@@ -9243,12 +9246,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr" s="2">
+      <c r="A6" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-03</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr" s="2">
+      <c r="B6" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-03</t>
         </is>
@@ -9270,12 +9273,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr" s="2">
+      <c r="A7" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-23</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr" s="2">
+      <c r="B7" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-11-23</t>
         </is>
@@ -9297,12 +9300,12 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr" s="2">
+      <c r="A8" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-12-21</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr" s="2">
+      <c r="B8" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-12-25</t>
         </is>
@@ -9324,12 +9327,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr" s="2">
+      <c r="A9" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-12-28</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr" s="2">
+      <c r="B9" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2026-12-31</t>
         </is>
@@ -9351,12 +9354,12 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr" s="2">
+      <c r="A10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-01-01</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr" s="2">
+      <c r="B10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-01-01</t>
         </is>
@@ -9378,12 +9381,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr" s="2">
+      <c r="A11" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-01-04</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr" s="2">
+      <c r="B11" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-01-06</t>
         </is>
@@ -9405,12 +9408,12 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr" s="2">
+      <c r="A12" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-02-11</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr" s="2">
+      <c r="B12" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-02-11</t>
         </is>
@@ -9432,12 +9435,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr" s="2">
+      <c r="A13" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-02-23</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr" s="2">
+      <c r="B13" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-02-23</t>
         </is>
@@ -9459,12 +9462,12 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr" s="2">
+      <c r="A14" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-21</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr" s="2">
+      <c r="B14" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-21</t>
         </is>
@@ -9486,12 +9489,12 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr" s="2">
+      <c r="A15" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-22</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr" s="2">
+      <c r="B15" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-26</t>
         </is>
@@ -9513,12 +9516,12 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr" s="2">
+      <c r="A16" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-29</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr" s="2">
+      <c r="B16" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-03-29</t>
         </is>
@@ -9540,12 +9543,12 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr" s="2">
+      <c r="A17" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-05-03</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr" s="2">
+      <c r="B17" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-05-03</t>
         </is>
@@ -9567,12 +9570,12 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr" s="2">
+      <c r="A18" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-05-04</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr" s="2">
+      <c r="B18" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-05-04</t>
         </is>
@@ -9594,12 +9597,12 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr" s="2">
+      <c r="A19" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-05-05</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr" s="2">
+      <c r="B19" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-05-05</t>
         </is>
@@ -9621,12 +9624,12 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr" s="2">
+      <c r="A20" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-05-06</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr" s="2">
+      <c r="B20" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-05-07</t>
         </is>
@@ -9648,12 +9651,12 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr" s="2">
+      <c r="A21" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-06-06</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr" s="2">
+      <c r="B21" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-06-07</t>
         </is>
@@ -9675,12 +9678,12 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr" s="2">
+      <c r="A22" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-06-21</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr" s="2">
+      <c r="B22" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-06-21</t>
         </is>
@@ -9702,12 +9705,12 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr" s="2">
+      <c r="A23" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-06-24</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr" s="2">
+      <c r="B23" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-06-25</t>
         </is>
@@ -9729,12 +9732,12 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr" s="2">
+      <c r="A24" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-07-19</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr" s="2">
+      <c r="B24" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-07-19</t>
         </is>
@@ -9756,12 +9759,12 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr" s="2">
+      <c r="A25" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-07-26</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr" s="2">
+      <c r="B25" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-07-30</t>
         </is>
@@ -9837,7 +9840,7 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Optional, e.g. 15:00 or 15:00-17:00. Empty = all day.</t>
+          <t xml:space="preserve">Optional. 24-hour time: 15:00 for a start time, or 15:00-17:00 for start and end. Leave empty for all-day events (most events). Shown on the website and in subscribed calendars.</t>
         </is>
       </c>
     </row>

--- a/admin/EIS-Compass-events.xlsx
+++ b/admin/EIS-Compass-events.xlsx
@@ -73,7 +73,10 @@
     <col min="13" max="13" width="20" customWidth="1"/>
     <col min="14" max="14" width="20" customWidth="1"/>
     <col min="15" max="15" width="30" customWidth="1"/>
-    <col min="16" max="16" width="8" customWidth="1"/>
+    <col min="16" max="16" width="40" customWidth="1"/>
+    <col min="17" max="17" width="40" customWidth="1"/>
+    <col min="18" max="18" width="40" customWidth="1"/>
+    <col min="19" max="19" width="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -154,6 +157,21 @@
       </c>
       <c r="P1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">link_1</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">link_2</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">link_3</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">hidden</t>
         </is>
       </c>
@@ -239,6 +257,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr" s="2">
@@ -321,6 +354,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr" s="2">
@@ -403,6 +451,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr" s="2">
@@ -485,6 +548,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr" s="2">
@@ -567,6 +645,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr" s="2">
@@ -649,6 +742,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr" s="2">
@@ -731,6 +839,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr" s="2">
@@ -813,6 +936,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr" s="2">
@@ -895,6 +1033,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr" s="2">
@@ -977,6 +1130,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr" s="2">
@@ -1059,6 +1227,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr" s="2">
@@ -1141,6 +1324,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr" s="2">
@@ -1223,6 +1421,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr" s="2">
@@ -1305,6 +1518,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr" s="2">
@@ -1387,6 +1615,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr" s="2">
@@ -1469,6 +1712,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr" s="2">
@@ -1551,6 +1809,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr" s="2">
@@ -1633,6 +1906,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr" s="2">
@@ -1715,6 +2003,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr" s="2">
@@ -1797,6 +2100,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr" s="2">
@@ -1879,6 +2197,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
@@ -1961,6 +2294,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
@@ -2043,6 +2391,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
@@ -2125,6 +2488,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
@@ -2207,6 +2585,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr" s="2">
@@ -2289,6 +2682,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr" s="2">
@@ -2371,6 +2779,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr" s="2">
@@ -2453,6 +2876,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr" s="2">
@@ -2535,6 +2973,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q30" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr" s="2">
@@ -2617,6 +3070,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q31" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr" s="2">
@@ -2699,6 +3167,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q32" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr" s="2">
@@ -2781,6 +3264,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr" s="2">
@@ -2863,6 +3361,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr" s="2">
@@ -2945,6 +3458,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr" s="2">
@@ -3027,6 +3555,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr" s="2">
@@ -3109,6 +3652,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr" s="2">
@@ -3191,6 +3749,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr" s="2">
@@ -3273,6 +3846,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr" s="2">
@@ -3355,6 +3943,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr" s="2">
@@ -3437,6 +4040,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr" s="2">
@@ -3519,6 +4137,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr" s="2">
@@ -3601,6 +4234,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr" s="2">
@@ -3683,6 +4331,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr" s="2">
@@ -3765,6 +4428,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr" s="2">
@@ -3847,6 +4525,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr" s="2">
@@ -3929,6 +4622,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr" s="2">
@@ -4011,6 +4719,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr" s="2">
@@ -4093,6 +4816,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr" s="2">
@@ -4175,6 +4913,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr" s="2">
@@ -4257,6 +5010,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr" s="2">
@@ -4339,6 +5107,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr" s="2">
@@ -4421,6 +5204,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr" s="2">
@@ -4503,6 +5301,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr" s="2">
@@ -4585,6 +5398,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr" s="2">
@@ -4667,6 +5495,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr" s="2">
@@ -4749,6 +5592,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr" s="2">
@@ -4831,6 +5689,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr" s="2">
@@ -4913,6 +5786,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr" s="2">
@@ -4995,6 +5883,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr" s="2">
@@ -5077,6 +5980,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr" s="2">
@@ -5159,6 +6077,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr" s="2">
@@ -5241,6 +6174,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr" s="2">
@@ -5323,6 +6271,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr" s="2">
@@ -5405,6 +6368,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr" s="2">
@@ -5487,6 +6465,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr" s="2">
@@ -5569,6 +6562,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr" s="2">
@@ -5651,6 +6659,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr" s="2">
@@ -5733,6 +6756,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr" s="2">
@@ -5815,6 +6853,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr" s="2">
@@ -5897,6 +6950,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr" s="2">
@@ -5979,6 +7047,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr" s="2">
@@ -6061,6 +7144,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr" s="2">
@@ -6143,6 +7241,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr" s="2">
@@ -6225,6 +7338,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr" s="2">
@@ -6307,6 +7435,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr" s="2">
@@ -6389,6 +7532,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr" s="2">
@@ -6471,6 +7629,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr" s="2">
@@ -6553,6 +7726,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr" s="2">
@@ -6635,6 +7823,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr" s="2">
@@ -6717,6 +7920,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr" s="2">
@@ -6799,6 +8017,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr" s="2">
@@ -6881,6 +8114,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr" s="2">
@@ -6963,6 +8211,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr" s="2">
@@ -7045,6 +8308,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr" s="2">
@@ -7127,6 +8405,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr" s="2">
@@ -7209,6 +8502,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr" s="2">
@@ -7291,6 +8599,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr" s="2">
@@ -7373,6 +8696,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr" s="2">
@@ -7455,6 +8793,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr" s="2">
@@ -7537,6 +8890,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr" s="2">
@@ -7619,6 +8987,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr" s="2">
@@ -7701,6 +9084,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr" s="2">
@@ -7783,6 +9181,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr" s="2">
@@ -7865,6 +9278,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr" s="2">
@@ -7947,6 +9375,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr" s="2">
@@ -8029,6 +9472,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr" s="2">
@@ -8111,6 +9569,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr" s="2">
@@ -8193,6 +9666,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr" s="2">
@@ -8275,6 +9763,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr" s="2">
@@ -8357,6 +9860,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr" s="2">
@@ -8439,6 +9957,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr" s="2">
@@ -8521,6 +10054,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr" s="2">
@@ -8603,6 +10151,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr" s="2">
@@ -8685,6 +10248,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr" s="2">
@@ -8767,6 +10345,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr" s="2">
@@ -8849,6 +10442,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr" s="2">
@@ -8931,6 +10539,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr" s="2">
@@ -9013,6 +10636,21 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="Q109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr" s="2">
@@ -9091,6 +10729,21 @@
         </is>
       </c>
       <c r="P110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -9919,10 +11572,22 @@
     <row r="11">
       <c r="A11" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">link_1 / link_2 / link_3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Optional links shown as buttons in the event window (flyers, sign-up forms, more information). Enter just the address (https://…), or add a label: Flyer | https://…  or  Flyer | チラシ | https://…  Without a label the button is named automatically (PDF flyer, Sign-up form, View document…). Excel hyperlinks (Insert &gt; Link) also work. Flyers uploaded to the website can use a path such as compass/files/sports-day.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">Holidays sheet: type</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr" s="2">
+      <c r="B12" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">national, school or noclass</t>
         </is>

--- a/admin/EIS-Compass-events.xlsx
+++ b/admin/EIS-Compass-events.xlsx
@@ -2022,17 +2022,17 @@
     <row r="21">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-07-career-support-and-mental-health-round-table</t>
+          <t xml:space="preserve">2026-10-09-high-school-curriculum-night</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-07</t>
+          <t xml:space="preserve">2026-10-09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-07</t>
+          <t xml:space="preserve">2026-10-09</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="3">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="F21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G21" t="inlineStr" s="2">
@@ -2062,22 +2062,22 @@
       </c>
       <c r="I21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Career Support and Mental Health Round Table</t>
+          <t xml:space="preserve">High School Curriculum Night</t>
         </is>
       </c>
       <c r="J21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">進路・メンタルヘルス座談会</t>
+          <t xml:space="preserve">高等部カリキュラム説明会</t>
         </is>
       </c>
       <c r="K21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An informative event where students can learn about IB university admissions, holistic admissions strategies in Japan and abroad, and explore future academic and career opportunities through discussions with experts and representatives.</t>
+          <t xml:space="preserve">An information session for students to learn about the IB Diploma Programme, course choices, academic expectations, and pathways to university.</t>
         </is>
       </c>
       <c r="L21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">専門家や関係者との対話を通して、IBでの大学入試、国内外の総合型選抜の戦略について学び、将来の進学やキャリアの可能性を探る説明会です。</t>
+          <t xml:space="preserve">IBディプロマ・プログラム、科目選択、学業面で求められること、大学への進路について学ぶ説明会です。</t>
         </is>
       </c>
       <c r="M21" t="inlineStr" s="2">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="O21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-07-career-support-and-mental-health-round-table.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-09-high-school-curriculum-night.webp</t>
         </is>
       </c>
       <c r="P21" t="inlineStr" s="2">
@@ -2119,7 +2119,7 @@
     <row r="22">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-09-high-school-curriculum-night</t>
+          <t xml:space="preserve">2026-10-09-eagle-bucks-store</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="3">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="E22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="2">
@@ -2159,22 +2159,22 @@
       </c>
       <c r="I22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School Curriculum Night</t>
+          <t xml:space="preserve">Eagle Bucks Store</t>
         </is>
       </c>
       <c r="J22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">高等部カリキュラム説明会</t>
+          <t xml:space="preserve">イーグルバックス・ストア</t>
         </is>
       </c>
       <c r="K22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An information session for students to learn about the IB Diploma Programme, course choices, academic expectations, and pathways to university.</t>
+          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
         </is>
       </c>
       <c r="L22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">IBディプロマ・プログラム、科目選択、学業面で求められること、大学への進路について学ぶ説明会です。</t>
+          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
         </is>
       </c>
       <c r="M22" t="inlineStr" s="2">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="O22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-09-high-school-curriculum-night.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-09-eagle-bucks-store.webp</t>
         </is>
       </c>
       <c r="P22" t="inlineStr" s="2">
@@ -2216,32 +2216,32 @@
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-09-eagle-bucks-store</t>
+          <t xml:space="preserve">2026-10-19-elc-primary-curriculum-night</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-09</t>
+          <t xml:space="preserve">2026-10-19</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-09</t>
+          <t xml:space="preserve">2026-10-19</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">17:30-20:30</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G23" t="inlineStr" s="2">
@@ -2256,37 +2256,37 @@
       </c>
       <c r="I23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Eagle Bucks Store</t>
+          <t xml:space="preserve">ELC &amp; Primary Curriculum Night</t>
         </is>
       </c>
       <c r="J23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">イーグルバックス・ストア</t>
+          <t xml:space="preserve">幼稚部・小学部カリキュラム説明会</t>
         </is>
       </c>
       <c r="K23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
+          <t xml:space="preserve">An evening to help families understand what children learn, how they learn, how progress is assessed, and how learning can be supported at home. Families will experience classroom activities, explore topics of interest, and ask questions. The evening begins with a welcome in the Community Room, followed by two breakout sessions and a panel Q&amp;A. Please complete the attendance and session selection form; sessions with limited interest may be cancelled.</t>
         </is>
       </c>
       <c r="L23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
+          <t xml:space="preserve">お子さまが何を、どのように学んでいるのか、学習の進歩をどのように評価しているのか、ご家庭でどのように学びを支えられるのかについて理解を深めていただく会です。教室での活動を体験し、関心のあるテーマについて学び、質問していただけます。コミュニティルームでの開会の後、2つの分科会とパネル質疑応答を行います。参加確認・セッション選択フォームへのご回答をお願いいたします（参加希望者が少ないセッションは中止となる場合があります）。</t>
         </is>
       </c>
       <c r="M23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Community Room</t>
         </is>
       </c>
       <c r="N23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">コミュニティルーム</t>
         </is>
       </c>
       <c r="O23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-09-eagle-bucks-store.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-19-elc-primary-curriculum-night.webp</t>
         </is>
       </c>
       <c r="P23" t="inlineStr" s="2">
@@ -2313,7 +2313,7 @@
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-19-elc-primary-curriculum-night</t>
+          <t xml:space="preserve">2026-10-19-parent-teacher-conferences</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="3">
@@ -2333,17 +2333,17 @@
       </c>
       <c r="E24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="H24" t="inlineStr" s="2">
@@ -2353,22 +2353,22 @@
       </c>
       <c r="I24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC &amp; Primary Curriculum Night</t>
+          <t xml:space="preserve">Parent Teacher Conferences</t>
         </is>
       </c>
       <c r="J24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部・小学部カリキュラム説明会</t>
+          <t xml:space="preserve">保護者面談</t>
         </is>
       </c>
       <c r="K24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Families are invited to learn about the curriculum, classroom routines, and learning goals for the year. This event helps strengthen the home-school partnership.</t>
+          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on this day.</t>
         </is>
       </c>
       <c r="L24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">カリキュラム、教室での日課、今年度の学習目標についてご紹介します。家庭と学校の連携を深める行事です。</t>
+          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。当日、生徒は登校しません。</t>
         </is>
       </c>
       <c r="M24" t="inlineStr" s="2">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="O24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-19-elc-primary-curriculum-night.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-19-parent-teacher-conferences.webp</t>
         </is>
       </c>
       <c r="P24" t="inlineStr" s="2">
@@ -2410,17 +2410,17 @@
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-19-parent-teacher-conferences</t>
+          <t xml:space="preserve">2026-10-20-secondary-curriculum-night</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-19</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-19</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="3">
@@ -2430,17 +2430,17 @@
       </c>
       <c r="E25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H25" t="inlineStr" s="2">
@@ -2450,22 +2450,22 @@
       </c>
       <c r="I25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parent Teacher Conferences</t>
+          <t xml:space="preserve">Secondary Curriculum Night</t>
         </is>
       </c>
       <c r="J25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者面談</t>
+          <t xml:space="preserve">中等部カリキュラム説明会</t>
         </is>
       </c>
       <c r="K25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on this day.</t>
+          <t xml:space="preserve">Secondary parents are invited to Curriculum Night to learn more about subject expectations, learning goals, assessment, and support for students in Grades 6 to 10.</t>
         </is>
       </c>
       <c r="L25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。当日、生徒は登校しません。</t>
+          <t xml:space="preserve">中等部の保護者の皆様を対象に、6～10年生の各教科で求められること、学習目標、評価、生徒への支援についてご説明します。</t>
         </is>
       </c>
       <c r="M25" t="inlineStr" s="2">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="O25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-19-parent-teacher-conferences.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-20-secondary-curriculum-night.webp</t>
         </is>
       </c>
       <c r="P25" t="inlineStr" s="2">
@@ -2507,17 +2507,17 @@
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-20-secondary-curriculum-night</t>
+          <t xml:space="preserve">2026-10-21-college-fair</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="3">
@@ -2527,12 +2527,12 @@
       </c>
       <c r="E26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G26" t="inlineStr" s="2">
@@ -2547,22 +2547,22 @@
       </c>
       <c r="I26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary Curriculum Night</t>
+          <t xml:space="preserve">College Fair</t>
         </is>
       </c>
       <c r="J26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部カリキュラム説明会</t>
+          <t xml:space="preserve">大学進学フェア</t>
         </is>
       </c>
       <c r="K26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary parents are invited to Curriculum Night to learn more about subject expectations, learning goals, assessment, and support for students in Grades 6 to 10.</t>
+          <t xml:space="preserve">A special event where representatives from several international and Japanese universities visit our school to introduce their programs and admission opportunities. The fair is open to all students and parents, and students from other international schools in the area are also invited to attend.</t>
         </is>
       </c>
       <c r="L26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部の保護者の皆様を対象に、6～10年生の各教科で求められること、学習目標、評価、生徒への支援についてご説明します。</t>
+          <t xml:space="preserve">国内外の複数の大学の担当者が来校し、各大学のプログラムや入学機会を紹介する特別イベントです。全生徒・保護者が参加でき、近隣のインターナショナルスクールの生徒もご招待しています。</t>
         </is>
       </c>
       <c r="M26" t="inlineStr" s="2">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="O26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-20-secondary-curriculum-night.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-21-college-fair.webp</t>
         </is>
       </c>
       <c r="P26" t="inlineStr" s="2">
@@ -2604,17 +2604,17 @@
     <row r="27">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-21-college-fair</t>
+          <t xml:space="preserve">2026-10-23-nagoya-university-biology-laboratory-visit</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="3">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="F27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G27" t="inlineStr" s="2">
@@ -2644,22 +2644,22 @@
       </c>
       <c r="I27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">College Fair</t>
+          <t xml:space="preserve">Nagoya University Biology Laboratory Visit</t>
         </is>
       </c>
       <c r="J27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">大学進学フェア</t>
+          <t xml:space="preserve">名古屋大学 生物学研究室訪問</t>
         </is>
       </c>
       <c r="K27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A special event where representatives from several international and Japanese universities visit our school to introduce their programs and admission opportunities. The fair is open to all students and parents, and students from other international schools in the area are also invited to attend.</t>
+          <t xml:space="preserve">Grade 11 and 12 Biology students will visit Nagoya University for a guided laboratory experience, connecting classroom learning with real-world scientific research.</t>
         </is>
       </c>
       <c r="L27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国内外の複数の大学の担当者が来校し、各大学のプログラムや入学機会を紹介する特別イベントです。全生徒・保護者が参加でき、近隣のインターナショナルスクールの生徒もご招待しています。</t>
+          <t xml:space="preserve">11・12年生の生物履修者が名古屋大学を訪問し、研究室での体験を通して授業での学びと実際の科学研究を結びつけます。</t>
         </is>
       </c>
       <c r="M27" t="inlineStr" s="2">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="O27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-21-college-fair.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-23-nagoya-university-biology-laboratory-visit.webp</t>
         </is>
       </c>
       <c r="P27" t="inlineStr" s="2">
@@ -2701,17 +2701,17 @@
     <row r="28">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-23-nagoya-university-biology-laboratory-visit</t>
+          <t xml:space="preserve">2026-10-25-pta-picnic</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-23</t>
+          <t xml:space="preserve">2026-10-25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-23</t>
+          <t xml:space="preserve">2026-10-25</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="3">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="E28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">PTA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="2">
@@ -2741,22 +2741,22 @@
       </c>
       <c r="I28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Nagoya University Biology Laboratory Visit</t>
+          <t xml:space="preserve">PTA Picnic</t>
         </is>
       </c>
       <c r="J28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">名古屋大学 生物学研究室訪問</t>
+          <t xml:space="preserve">PTAピクニック</t>
         </is>
       </c>
       <c r="K28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 11 and 12 Biology students will visit Nagoya University for a guided laboratory experience, connecting classroom learning with real-world scientific research.</t>
+          <t xml:space="preserve">Families, students, and staff come together for a fun outdoor gathering that strengthens relationships and builds school community.</t>
         </is>
       </c>
       <c r="L28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11・12年生の生物履修者が名古屋大学を訪問し、研究室での体験を通して授業での学びと実際の科学研究を結びつけます。</t>
+          <t xml:space="preserve">ご家族、生徒、教職員が集まり、屋外で楽しく交流しながら絆を深め、学校コミュニティを育みます。</t>
         </is>
       </c>
       <c r="M28" t="inlineStr" s="2">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="O28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-23-nagoya-university-biology-laboratory-visit.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-25-pta-picnic.webp</t>
         </is>
       </c>
       <c r="P28" t="inlineStr" s="2">
@@ -2798,17 +2798,17 @@
     <row r="29">
       <c r="A29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-25-pta-picnic</t>
+          <t xml:space="preserve">2026-10-26-toyota-college-trip</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-25</t>
+          <t xml:space="preserve">2026-10-26</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-25</t>
+          <t xml:space="preserve">2026-10-26</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="3">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="E29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTA</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="2">
@@ -2838,22 +2838,22 @@
       </c>
       <c r="I29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTA Picnic</t>
+          <t xml:space="preserve">Toyota College Trip</t>
         </is>
       </c>
       <c r="J29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTAピクニック</t>
+          <t xml:space="preserve">豊田高専見学</t>
         </is>
       </c>
       <c r="K29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Families, students, and staff come together for a fun outdoor gathering that strengthens relationships and builds school community.</t>
+          <t xml:space="preserve">Grade 8 Science students will visit Toyota College for a curriculum-based learning experience connected to their science studies.</t>
         </is>
       </c>
       <c r="L29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ご家族、生徒、教職員が集まり、屋外で楽しく交流しながら絆を深め、学校コミュニティを育みます。</t>
+          <t xml:space="preserve">8年生が理科の授業と関連したカリキュラムに基づく学習として、豊田高専を訪問します。</t>
         </is>
       </c>
       <c r="M29" t="inlineStr" s="2">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="O29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-25-pta-picnic.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-26-toyota-college-trip.webp</t>
         </is>
       </c>
       <c r="P29" t="inlineStr" s="2">
@@ -2895,17 +2895,17 @@
     <row r="30">
       <c r="A30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-26-toyota-college-trip</t>
+          <t xml:space="preserve">2026-10-30-sensory-wonderland</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-26</t>
+          <t xml:space="preserve">2026-10-30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-26</t>
+          <t xml:space="preserve">2026-10-30</t>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="3">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="E30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">ELC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr" s="2">
@@ -2935,22 +2935,22 @@
       </c>
       <c r="I30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Toyota College Trip</t>
+          <t xml:space="preserve">Sensory Wonderland</t>
         </is>
       </c>
       <c r="J30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">豊田高専見学</t>
+          <t xml:space="preserve">センサリー・ワンダーランド</t>
         </is>
       </c>
       <c r="K30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 8 Science students will visit Toyota College for a curriculum-based learning experience connected to their science studies.</t>
+          <t xml:space="preserve">Students explore a variety of interactive sensory experiences designed to engage curiosity, creativity, and learning through play.</t>
         </is>
       </c>
       <c r="L30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8年生が理科の授業と関連したカリキュラムに基づく学習として、豊田高専を訪問します。</t>
+          <t xml:space="preserve">好奇心と創造性を刺激し、遊びを通して学ぶ、さまざまな体験型の感覚活動を楽しみます。</t>
         </is>
       </c>
       <c r="M30" t="inlineStr" s="2">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="O30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-26-toyota-college-trip.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P30" t="inlineStr" s="2">
@@ -2992,32 +2992,32 @@
     <row r="31">
       <c r="A31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-30-sensory-wonderland</t>
+          <t xml:space="preserve">2026-10-31-international-mindedness-festival</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-30</t>
+          <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-30</t>
+          <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">10:00-14:00</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G31" t="inlineStr" s="2">
@@ -3032,22 +3032,22 @@
       </c>
       <c r="I31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sensory Wonderland</t>
+          <t xml:space="preserve">International Mindedness Festival</t>
         </is>
       </c>
       <c r="J31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">センサリー・ワンダーランド</t>
+          <t xml:space="preserve">インターナショナル・マインデッドネス・フェスティバル</t>
         </is>
       </c>
       <c r="K31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students explore a variety of interactive sensory experiences designed to engage curiosity, creativity, and learning through play.</t>
+          <t xml:space="preserve">This year’s theme is “Festivals and Holidays Around the World”. A Saturday family event celebrating traditions, cultures, stories, arts, music and celebrations from around the world, with student activities, cultural displays, performances, arts and crafts, and interactive booths. Clean-up runs from 14:00 to 15:00, and community members are welcome to help. ELC and Primary students must attend with a parent or guardian and may not be dropped off. School buses will not operate. More details will be shared soon.</t>
         </is>
       </c>
       <c r="L31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">好奇心と創造性を刺激し、遊びを通して学ぶ、さまざまな体験型の感覚活動を楽しみます。</t>
+          <t xml:space="preserve">今年のテーマは「世界の祭りと祝日」です。世界各地の伝統、文化、物語、芸術、音楽、お祝いを紹介する、土曜日のご家族参加型イベントです。児童・生徒の活動、文化展示、パフォーマンス、工作、体験型ブースをお楽しみいただけます。午後2時～3時に片付けを行います（学校コミュニティの皆さまのご協力も歓迎します）。幼稚部・小学部の児童は必ず保護者同伴でご参加ください（お子さまだけを送り届けることはできません）。当日はスクールバスの運行はありません。詳細は近日中にお知らせします。</t>
         </is>
       </c>
       <c r="M31" t="inlineStr" s="2">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="O31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">compass/images/events/2026-10-31-international-mindedness-festival.webp</t>
         </is>
       </c>
       <c r="P31" t="inlineStr" s="2">
@@ -3089,17 +3089,17 @@
     <row r="32">
       <c r="A32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-31-international-mindedness-festival</t>
+          <t xml:space="preserve">2026-11-04-elc-sports-day-rehearsal-1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-31</t>
+          <t xml:space="preserve">2026-11-04</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-31</t>
+          <t xml:space="preserve">2026-11-04</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="3">
@@ -3109,12 +3109,12 @@
       </c>
       <c r="E32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">ELC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G32" t="inlineStr" s="2">
@@ -3129,22 +3129,22 @@
       </c>
       <c r="I32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">International Mindedness Festival</t>
+          <t xml:space="preserve">ELC Sports Day Rehearsal #1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国際理解フェスティバル</t>
+          <t xml:space="preserve">幼稚部運動会リハーサル #1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The whole school community, including parents, will take part in IMF, a full-day event celebrating community, culture, and shared school experiences.</t>
+          <t xml:space="preserve">During Sports Day practice, students participate in a variety of physical activities, team games, relays, and event rehearsals in preparation for Sports Day. They develop teamwork, cooperation, sportsmanship, and physical fitness while learning event procedures, safety expectations, and cheering routines. Practice sessions help students build confidence and ensure they are prepared to participate successfully in the Sports Day celebration.</t>
         </is>
       </c>
       <c r="L32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者の皆様を含む学校コミュニティ全体で、コミュニティと文化、そして共に過ごす学校生活を祝う終日行事「IMF」に参加します。</t>
+          <t xml:space="preserve">運動会に向けた練習では、さまざまな運動、チームゲーム、リレー、種目のリハーサルに取り組みます。進行の流れ、安全面のルール、応援の仕方を学びながら、チームワーク、協調性、スポーツマンシップ、体力を養います。練習を通して自信をつけ、運動会当日に力を発揮できるよう準備します。</t>
         </is>
       </c>
       <c r="M32" t="inlineStr" s="2">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="O32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-31-international-mindedness-festival.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-04-elc-sports-day-rehearsal-1.webp</t>
         </is>
       </c>
       <c r="P32" t="inlineStr" s="2">
@@ -3186,17 +3186,17 @@
     <row r="33">
       <c r="A33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-04-elc-sports-day-rehearsal-1</t>
+          <t xml:space="preserve">2026-11-05-toyota-museum-field-trip</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-04</t>
+          <t xml:space="preserve">2026-11-05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-04</t>
+          <t xml:space="preserve">2026-11-05</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="3">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="E33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F33" t="inlineStr" s="2">
@@ -3226,22 +3226,22 @@
       </c>
       <c r="I33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC Sports Day Rehearsal #1</t>
+          <t xml:space="preserve">Toyota Museum Field Trip</t>
         </is>
       </c>
       <c r="J33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部運動会リハーサル #1</t>
+          <t xml:space="preserve">トヨタ博物館校外学習</t>
         </is>
       </c>
       <c r="K33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">During Sports Day practice, students participate in a variety of physical activities, team games, relays, and event rehearsals in preparation for Sports Day. They develop teamwork, cooperation, sportsmanship, and physical fitness while learning event procedures, safety expectations, and cheering routines. Practice sessions help students build confidence and ensure they are prepared to participate successfully in the Sports Day celebration.</t>
+          <t xml:space="preserve">Grade 9 students go to the Toyota museum down the road and view the exhibits taking some notes on machines they learned about.</t>
         </is>
       </c>
       <c r="L33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会に向けた練習では、さまざまな運動、チームゲーム、リレー、種目のリハーサルに取り組みます。進行の流れ、安全面のルール、応援の仕方を学びながら、チームワーク、協調性、スポーツマンシップ、体力を養います。練習を通して自信をつけ、運動会当日に力を発揮できるよう準備します。</t>
+          <t xml:space="preserve">9年生が近くのトヨタの博物館を訪れ、授業で学んだ機械について展示を見学しながらメモを取ります。</t>
         </is>
       </c>
       <c r="M33" t="inlineStr" s="2">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="O33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-04-elc-sports-day-rehearsal-1.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-05-toyota-museum-field-trip.webp</t>
         </is>
       </c>
       <c r="P33" t="inlineStr" s="2">
@@ -3283,17 +3283,17 @@
     <row r="34">
       <c r="A34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-05-toyota-museum-field-trip</t>
+          <t xml:space="preserve">2026-11-06-extracurricular-activities-autumn-cas-project-su</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-05</t>
+          <t xml:space="preserve">2026-11-06</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-05</t>
+          <t xml:space="preserve">2026-11-06</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="3">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="F34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G34" t="inlineStr" s="2">
@@ -3323,22 +3323,22 @@
       </c>
       <c r="I34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Toyota Museum Field Trip</t>
+          <t xml:space="preserve">Extracurricular Activities: Autumn CAS &amp; Project Support Fair</t>
         </is>
       </c>
       <c r="J34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">トヨタ博物館校外学習</t>
+          <t xml:space="preserve">課外活動：秋のCAS・プロジェクトサポートフェア</t>
         </is>
       </c>
       <c r="K34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 9 students go to the Toyota museum down the road and view the exhibits taking some notes on machines they learned about.</t>
+          <t xml:space="preserve">Secondary PTA Supported Event to help students understand various volunteering and CAS project opportunities in the community. Open to MYP and DP Students.</t>
         </is>
       </c>
       <c r="L34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9年生が近くのトヨタの博物館を訪れ、授業で学んだ機械について展示を見学しながらメモを取ります。</t>
+          <t xml:space="preserve">中等部PTAの支援による行事で、地域でのさまざまなボランティアやCASプロジェクトの機会について知ることができます。MYP・DP生徒が対象です。</t>
         </is>
       </c>
       <c r="M34" t="inlineStr" s="2">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="O34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-05-toyota-museum-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-06-extracurricular-activities-autumn-cas-project-su.webp</t>
         </is>
       </c>
       <c r="P34" t="inlineStr" s="2">
@@ -3380,17 +3380,17 @@
     <row r="35">
       <c r="A35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-06-extracurricular-activities-autumn-cas-project-su</t>
+          <t xml:space="preserve">2026-11-07-sat-test-4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-06</t>
+          <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-06</t>
+          <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="3">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="E35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G35" t="inlineStr" s="2">
@@ -3420,22 +3420,22 @@
       </c>
       <c r="I35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Extracurricular Activities: Autumn CAS &amp; Project Support Fair</t>
+          <t xml:space="preserve">SAT Test #4</t>
         </is>
       </c>
       <c r="J35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">課外活動：秋のCAS・プロジェクトサポートフェア</t>
+          <t xml:space="preserve">SAT試験 第4回</t>
         </is>
       </c>
       <c r="K35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary PTA Supported Event to help students understand various volunteering and CAS project opportunities in the community. Open to MYP and DP Students.</t>
+          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
         </is>
       </c>
       <c r="L35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部PTAの支援による行事で、地域でのさまざまなボランティアやCASプロジェクトの機会について知ることができます。MYP・DP生徒が対象です。</t>
+          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
         </is>
       </c>
       <c r="M35" t="inlineStr" s="2">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="O35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-06-extracurricular-activities-autumn-cas-project-su.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-07-sat-test-4.webp</t>
         </is>
       </c>
       <c r="P35" t="inlineStr" s="2">
@@ -3477,17 +3477,17 @@
     <row r="36">
       <c r="A36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-07-sat-test-4</t>
+          <t xml:space="preserve">2026-11-09-wellbeing-week</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-07</t>
+          <t xml:space="preserve">2026-11-09</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-07</t>
+          <t xml:space="preserve">2026-11-13</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="3">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="E36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F36" t="inlineStr" s="2">
@@ -3517,22 +3517,22 @@
       </c>
       <c r="I36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT Test #4</t>
+          <t xml:space="preserve">Wellbeing Week</t>
         </is>
       </c>
       <c r="J36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT試験 第4回</t>
+          <t xml:space="preserve">ウェルビーイング週間</t>
         </is>
       </c>
       <c r="K36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
+          <t xml:space="preserve">A school wide event focused on raising awareness for wellbeing.</t>
         </is>
       </c>
       <c r="L36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
+          <t xml:space="preserve">ウェルビーイング（心身の健康）への意識を高めることを目的とした全校行事です。</t>
         </is>
       </c>
       <c r="M36" t="inlineStr" s="2">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="O36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-07-sat-test-4.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-09-wellbeing-week.webp</t>
         </is>
       </c>
       <c r="P36" t="inlineStr" s="2">
@@ -3574,7 +3574,7 @@
     <row r="37">
       <c r="A37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-09-wellbeing-week</t>
+          <t xml:space="preserve">2026-11-09-concept-con-wellbeing</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="3">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="E37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F37" t="inlineStr" s="2">
@@ -3614,22 +3614,22 @@
       </c>
       <c r="I37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wellbeing Week</t>
+          <t xml:space="preserve">Concept Con (Wellbeing)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ウェルビーイング週間</t>
+          <t xml:space="preserve">コンセプト・コン（ウェルビーイング）</t>
         </is>
       </c>
       <c r="K37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A school wide event focused on raising awareness for wellbeing.</t>
+          <t xml:space="preserve">The Primary Concept Conference on the theme of wellbeing, held during Wellbeing Week.</t>
         </is>
       </c>
       <c r="L37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ウェルビーイング（心身の健康）への意識を高めることを目的とした全校行事です。</t>
+          <t xml:space="preserve">ウェルビーイング週間に合わせて行う、小学部のコンセプト・カンファレンス（テーマ：ウェルビーイング）です。</t>
         </is>
       </c>
       <c r="M37" t="inlineStr" s="2">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-09-wellbeing-week.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P37" t="inlineStr" s="2">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="C43" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-25</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">13:10-14:55</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -4196,32 +4196,32 @@
       </c>
       <c r="I43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Winter Art Contest</t>
+          <t xml:space="preserve">Gallery Day: ELC &amp; Primary Art Showcase</t>
         </is>
       </c>
       <c r="J43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">冬のアートコンテスト</t>
+          <t xml:space="preserve">ギャラリーデー：幼稚部・小学部アート展</t>
         </is>
       </c>
       <c r="K43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students showcase their art that they have been working on with the visual arts teacher at an art showcase. Selected pieces will be displayed and celebrated within the school community.</t>
+          <t xml:space="preserve">ELC and Primary students display the artwork they have created with the visual arts teacher. Parents are welcome to view the gallery from 13:10 to 14:55. Students vote for their favourite artworks, and the winners for each grade are announced.</t>
         </is>
       </c>
       <c r="L43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">美術の先生と取り組んできた作品を作品展で発表します。選ばれた作品は校内に展示され、学校コミュニティで共に称えます。</t>
+          <t xml:space="preserve">幼稚部・小学部の児童が美術の授業で制作した作品を展示します。保護者の皆さまは13:10～14:55にご鑑賞いただけます。児童による投票を行い、学年ごとの受賞作品を発表します。</t>
         </is>
       </c>
       <c r="M43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Gym</t>
         </is>
       </c>
       <c r="N43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">体育館</t>
         </is>
       </c>
       <c r="O43" t="inlineStr" s="2">
@@ -4554,12 +4554,12 @@
       </c>
       <c r="C47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-04</t>
+          <t xml:space="preserve">2026-12-03</t>
         </is>
       </c>
       <c r="D47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">17:30</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">

--- a/admin/EIS-Compass-events.xlsx
+++ b/admin/EIS-Compass-events.xlsx
@@ -2047,7 +2047,7 @@
       </c>
       <c r="F21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G21" t="inlineStr" s="2">

--- a/admin/EIS-Compass-events.xlsx
+++ b/admin/EIS-Compass-events.xlsx
@@ -2022,7 +2022,7 @@
     <row r="21">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-09-high-school-curriculum-night</t>
+          <t xml:space="preserve">2026-10-09-eagle-bucks-store</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="3">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="E21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G21" t="inlineStr" s="2">
@@ -2062,22 +2062,22 @@
       </c>
       <c r="I21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School Curriculum Night</t>
+          <t xml:space="preserve">Eagle Bucks Store</t>
         </is>
       </c>
       <c r="J21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">高等部カリキュラム説明会</t>
+          <t xml:space="preserve">イーグルバックス・ストア</t>
         </is>
       </c>
       <c r="K21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An information session for students to learn about the IB Diploma Programme, course choices, academic expectations, and pathways to university.</t>
+          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
         </is>
       </c>
       <c r="L21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">IBディプロマ・プログラム、科目選択、学業面で求められること、大学への進路について学ぶ説明会です。</t>
+          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
         </is>
       </c>
       <c r="M21" t="inlineStr" s="2">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="O21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-09-high-school-curriculum-night.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-09-eagle-bucks-store.webp</t>
         </is>
       </c>
       <c r="P21" t="inlineStr" s="2">
@@ -2119,32 +2119,32 @@
     <row r="22">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-09-eagle-bucks-store</t>
+          <t xml:space="preserve">2026-10-19-elc-primary-curriculum-night</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-09</t>
+          <t xml:space="preserve">2026-10-19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-09</t>
+          <t xml:space="preserve">2026-10-19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">17:30-20:30</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G22" t="inlineStr" s="2">
@@ -2159,37 +2159,37 @@
       </c>
       <c r="I22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Eagle Bucks Store</t>
+          <t xml:space="preserve">ELC &amp; Primary Curriculum Night</t>
         </is>
       </c>
       <c r="J22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">イーグルバックス・ストア</t>
+          <t xml:space="preserve">幼稚部・小学部カリキュラム説明会</t>
         </is>
       </c>
       <c r="K22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
+          <t xml:space="preserve">An evening to help families understand what children learn, how they learn, how progress is assessed, and how learning can be supported at home. Families will experience classroom activities, explore topics of interest, and ask questions. The evening begins with a welcome in the Community Room, followed by two breakout sessions and a panel Q&amp;A. Please complete the attendance and session selection form; sessions with limited interest may be cancelled.</t>
         </is>
       </c>
       <c r="L22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
+          <t xml:space="preserve">お子さまが何を、どのように学んでいるのか、学習の進歩をどのように評価しているのか、ご家庭でどのように学びを支えられるのかについて理解を深めていただく会です。教室での活動を体験し、関心のあるテーマについて学び、質問していただけます。コミュニティルームでの開会の後、2つの分科会とパネル質疑応答を行います。参加確認・セッション選択フォームへのご回答をお願いいたします（参加希望者が少ないセッションは中止となる場合があります）。</t>
         </is>
       </c>
       <c r="M22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Community Room</t>
         </is>
       </c>
       <c r="N22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">コミュニティルーム</t>
         </is>
       </c>
       <c r="O22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-09-eagle-bucks-store.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-19-elc-primary-curriculum-night.webp</t>
         </is>
       </c>
       <c r="P22" t="inlineStr" s="2">
@@ -2216,7 +2216,7 @@
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-19-elc-primary-curriculum-night</t>
+          <t xml:space="preserve">2026-10-19-parent-teacher-conferences</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="3">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="D23" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">17:30-20:30</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="2">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="H23" t="inlineStr" s="2">
@@ -2256,37 +2256,37 @@
       </c>
       <c r="I23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC &amp; Primary Curriculum Night</t>
+          <t xml:space="preserve">Parent Teacher Conferences</t>
         </is>
       </c>
       <c r="J23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部・小学部カリキュラム説明会</t>
+          <t xml:space="preserve">保護者面談</t>
         </is>
       </c>
       <c r="K23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An evening to help families understand what children learn, how they learn, how progress is assessed, and how learning can be supported at home. Families will experience classroom activities, explore topics of interest, and ask questions. The evening begins with a welcome in the Community Room, followed by two breakout sessions and a panel Q&amp;A. Please complete the attendance and session selection form; sessions with limited interest may be cancelled.</t>
+          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on this day.</t>
         </is>
       </c>
       <c r="L23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お子さまが何を、どのように学んでいるのか、学習の進歩をどのように評価しているのか、ご家庭でどのように学びを支えられるのかについて理解を深めていただく会です。教室での活動を体験し、関心のあるテーマについて学び、質問していただけます。コミュニティルームでの開会の後、2つの分科会とパネル質疑応答を行います。参加確認・セッション選択フォームへのご回答をお願いいたします（参加希望者が少ないセッションは中止となる場合があります）。</t>
+          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。当日、生徒は登校しません。</t>
         </is>
       </c>
       <c r="M23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Community Room</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="N23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">コミュニティルーム</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="O23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-19-elc-primary-curriculum-night.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-19-parent-teacher-conferences.webp</t>
         </is>
       </c>
       <c r="P23" t="inlineStr" s="2">
@@ -2313,17 +2313,17 @@
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-19-parent-teacher-conferences</t>
+          <t xml:space="preserve">2026-10-20-secondary-curriculum-night</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-19</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-19</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="3">
@@ -2333,17 +2333,17 @@
       </c>
       <c r="E24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H24" t="inlineStr" s="2">
@@ -2353,22 +2353,22 @@
       </c>
       <c r="I24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parent Teacher Conferences</t>
+          <t xml:space="preserve">Secondary Curriculum Night</t>
         </is>
       </c>
       <c r="J24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者面談</t>
+          <t xml:space="preserve">中等部カリキュラム説明会</t>
         </is>
       </c>
       <c r="K24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on this day.</t>
+          <t xml:space="preserve">Secondary parents are invited to Curriculum Night to learn more about subject expectations, learning goals, assessment, and support for students in Grades 6 to 10.</t>
         </is>
       </c>
       <c r="L24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。当日、生徒は登校しません。</t>
+          <t xml:space="preserve">中等部の保護者の皆様を対象に、6～10年生の各教科で求められること、学習目標、評価、生徒への支援についてご説明します。</t>
         </is>
       </c>
       <c r="M24" t="inlineStr" s="2">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="O24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-19-parent-teacher-conferences.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-20-secondary-curriculum-night.webp</t>
         </is>
       </c>
       <c r="P24" t="inlineStr" s="2">
@@ -2410,17 +2410,17 @@
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-20-secondary-curriculum-night</t>
+          <t xml:space="preserve">2026-10-21-college-fair</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="3">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="E25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G25" t="inlineStr" s="2">
@@ -2450,22 +2450,22 @@
       </c>
       <c r="I25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary Curriculum Night</t>
+          <t xml:space="preserve">College Fair</t>
         </is>
       </c>
       <c r="J25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部カリキュラム説明会</t>
+          <t xml:space="preserve">大学進学フェア</t>
         </is>
       </c>
       <c r="K25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary parents are invited to Curriculum Night to learn more about subject expectations, learning goals, assessment, and support for students in Grades 6 to 10.</t>
+          <t xml:space="preserve">A special event where representatives from several international and Japanese universities visit our school to introduce their programs and admission opportunities. The fair is open to all students and parents, and students from other international schools in the area are also invited to attend.</t>
         </is>
       </c>
       <c r="L25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部の保護者の皆様を対象に、6～10年生の各教科で求められること、学習目標、評価、生徒への支援についてご説明します。</t>
+          <t xml:space="preserve">国内外の複数の大学の担当者が来校し、各大学のプログラムや入学機会を紹介する特別イベントです。全生徒・保護者が参加でき、近隣のインターナショナルスクールの生徒もご招待しています。</t>
         </is>
       </c>
       <c r="M25" t="inlineStr" s="2">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="O25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-20-secondary-curriculum-night.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-21-college-fair.webp</t>
         </is>
       </c>
       <c r="P25" t="inlineStr" s="2">
@@ -2507,17 +2507,17 @@
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-21-college-fair</t>
+          <t xml:space="preserve">2026-10-23-nagoya-university-biology-laboratory-visit</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="3">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="F26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G26" t="inlineStr" s="2">
@@ -2547,22 +2547,22 @@
       </c>
       <c r="I26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">College Fair</t>
+          <t xml:space="preserve">Nagoya University Biology Laboratory Visit</t>
         </is>
       </c>
       <c r="J26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">大学進学フェア</t>
+          <t xml:space="preserve">名古屋大学 生物学研究室訪問</t>
         </is>
       </c>
       <c r="K26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A special event where representatives from several international and Japanese universities visit our school to introduce their programs and admission opportunities. The fair is open to all students and parents, and students from other international schools in the area are also invited to attend.</t>
+          <t xml:space="preserve">Grade 11 and 12 Biology students will visit Nagoya University for a guided laboratory experience, connecting classroom learning with real-world scientific research.</t>
         </is>
       </c>
       <c r="L26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国内外の複数の大学の担当者が来校し、各大学のプログラムや入学機会を紹介する特別イベントです。全生徒・保護者が参加でき、近隣のインターナショナルスクールの生徒もご招待しています。</t>
+          <t xml:space="preserve">11・12年生の生物履修者が名古屋大学を訪問し、研究室での体験を通して授業での学びと実際の科学研究を結びつけます。</t>
         </is>
       </c>
       <c r="M26" t="inlineStr" s="2">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="O26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-21-college-fair.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-23-nagoya-university-biology-laboratory-visit.webp</t>
         </is>
       </c>
       <c r="P26" t="inlineStr" s="2">
@@ -2604,17 +2604,17 @@
     <row r="27">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-23-nagoya-university-biology-laboratory-visit</t>
+          <t xml:space="preserve">2026-10-25-pta-picnic</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-23</t>
+          <t xml:space="preserve">2026-10-25</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-23</t>
+          <t xml:space="preserve">2026-10-25</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="3">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="E27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">PTA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr" s="2">
@@ -2644,22 +2644,22 @@
       </c>
       <c r="I27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Nagoya University Biology Laboratory Visit</t>
+          <t xml:space="preserve">PTA Picnic</t>
         </is>
       </c>
       <c r="J27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">名古屋大学 生物学研究室訪問</t>
+          <t xml:space="preserve">PTAピクニック</t>
         </is>
       </c>
       <c r="K27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 11 and 12 Biology students will visit Nagoya University for a guided laboratory experience, connecting classroom learning with real-world scientific research.</t>
+          <t xml:space="preserve">Families, students, and staff come together for a fun outdoor gathering that strengthens relationships and builds school community.</t>
         </is>
       </c>
       <c r="L27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11・12年生の生物履修者が名古屋大学を訪問し、研究室での体験を通して授業での学びと実際の科学研究を結びつけます。</t>
+          <t xml:space="preserve">ご家族、生徒、教職員が集まり、屋外で楽しく交流しながら絆を深め、学校コミュニティを育みます。</t>
         </is>
       </c>
       <c r="M27" t="inlineStr" s="2">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="O27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-23-nagoya-university-biology-laboratory-visit.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-25-pta-picnic.webp</t>
         </is>
       </c>
       <c r="P27" t="inlineStr" s="2">
@@ -2701,17 +2701,17 @@
     <row r="28">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-25-pta-picnic</t>
+          <t xml:space="preserve">2026-10-26-toyota-college-trip</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-25</t>
+          <t xml:space="preserve">2026-10-26</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-25</t>
+          <t xml:space="preserve">2026-10-26</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="3">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="E28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTA</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="2">
@@ -2741,22 +2741,22 @@
       </c>
       <c r="I28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTA Picnic</t>
+          <t xml:space="preserve">Toyota College Trip</t>
         </is>
       </c>
       <c r="J28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTAピクニック</t>
+          <t xml:space="preserve">豊田高専見学</t>
         </is>
       </c>
       <c r="K28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Families, students, and staff come together for a fun outdoor gathering that strengthens relationships and builds school community.</t>
+          <t xml:space="preserve">Grade 8 Science students will visit Toyota College for a curriculum-based learning experience connected to their science studies.</t>
         </is>
       </c>
       <c r="L28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ご家族、生徒、教職員が集まり、屋外で楽しく交流しながら絆を深め、学校コミュニティを育みます。</t>
+          <t xml:space="preserve">8年生が理科の授業と関連したカリキュラムに基づく学習として、豊田高専を訪問します。</t>
         </is>
       </c>
       <c r="M28" t="inlineStr" s="2">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="O28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-25-pta-picnic.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-26-toyota-college-trip.webp</t>
         </is>
       </c>
       <c r="P28" t="inlineStr" s="2">
@@ -2798,17 +2798,17 @@
     <row r="29">
       <c r="A29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-26-toyota-college-trip</t>
+          <t xml:space="preserve">2026-10-30-sensory-wonderland</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-26</t>
+          <t xml:space="preserve">2026-10-30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-26</t>
+          <t xml:space="preserve">2026-10-30</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="3">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="E29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">ELC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="2">
@@ -2838,22 +2838,22 @@
       </c>
       <c r="I29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Toyota College Trip</t>
+          <t xml:space="preserve">Sensory Wonderland</t>
         </is>
       </c>
       <c r="J29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">豊田高専見学</t>
+          <t xml:space="preserve">センサリー・ワンダーランド</t>
         </is>
       </c>
       <c r="K29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 8 Science students will visit Toyota College for a curriculum-based learning experience connected to their science studies.</t>
+          <t xml:space="preserve">Students explore a variety of interactive sensory experiences designed to engage curiosity, creativity, and learning through play.</t>
         </is>
       </c>
       <c r="L29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8年生が理科の授業と関連したカリキュラムに基づく学習として、豊田高専を訪問します。</t>
+          <t xml:space="preserve">好奇心と創造性を刺激し、遊びを通して学ぶ、さまざまな体験型の感覚活動を楽しみます。</t>
         </is>
       </c>
       <c r="M29" t="inlineStr" s="2">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="O29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-26-toyota-college-trip.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P29" t="inlineStr" s="2">
@@ -2895,32 +2895,32 @@
     <row r="30">
       <c r="A30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-30-sensory-wonderland</t>
+          <t xml:space="preserve">2026-10-31-international-mindedness-festival</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-30</t>
+          <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-30</t>
+          <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">10:00-14:00</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G30" t="inlineStr" s="2">
@@ -2935,22 +2935,22 @@
       </c>
       <c r="I30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sensory Wonderland</t>
+          <t xml:space="preserve">International Mindedness Festival</t>
         </is>
       </c>
       <c r="J30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">センサリー・ワンダーランド</t>
+          <t xml:space="preserve">インターナショナル・マインデッドネス・フェスティバル</t>
         </is>
       </c>
       <c r="K30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students explore a variety of interactive sensory experiences designed to engage curiosity, creativity, and learning through play.</t>
+          <t xml:space="preserve">This year’s theme is “Festivals and Holidays Around the World”. A Saturday family event celebrating traditions, cultures, stories, arts, music and celebrations from around the world, with student activities, cultural displays, performances, arts and crafts, and interactive booths. Clean-up runs from 14:00 to 15:00, and community members are welcome to help. ELC and Primary students must attend with a parent or guardian and may not be dropped off. School buses will not operate. More details will be shared soon.</t>
         </is>
       </c>
       <c r="L30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">好奇心と創造性を刺激し、遊びを通して学ぶ、さまざまな体験型の感覚活動を楽しみます。</t>
+          <t xml:space="preserve">今年のテーマは「世界の祭りと祝日」です。世界各地の伝統、文化、物語、芸術、音楽、お祝いを紹介する、土曜日のご家族参加型イベントです。児童・生徒の活動、文化展示、パフォーマンス、工作、体験型ブースをお楽しみいただけます。午後2時～3時に片付けを行います（学校コミュニティの皆さまのご協力も歓迎します）。幼稚部・小学部の児童は必ず保護者同伴でご参加ください（お子さまだけを送り届けることはできません）。当日はスクールバスの運行はありません。詳細は近日中にお知らせします。</t>
         </is>
       </c>
       <c r="M30" t="inlineStr" s="2">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="O30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">compass/images/events/2026-10-31-international-mindedness-festival.webp</t>
         </is>
       </c>
       <c r="P30" t="inlineStr" s="2">
@@ -2992,32 +2992,32 @@
     <row r="31">
       <c r="A31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-31-international-mindedness-festival</t>
+          <t xml:space="preserve">2026-11-04-elc-sports-day-rehearsal-1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-31</t>
+          <t xml:space="preserve">2026-11-04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-31</t>
+          <t xml:space="preserve">2026-11-04</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">10:00-14:00</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">ELC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G31" t="inlineStr" s="2">
@@ -3032,22 +3032,22 @@
       </c>
       <c r="I31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">International Mindedness Festival</t>
+          <t xml:space="preserve">ELC Sports Day Rehearsal #1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">インターナショナル・マインデッドネス・フェスティバル</t>
+          <t xml:space="preserve">幼稚部運動会リハーサル #1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This year’s theme is “Festivals and Holidays Around the World”. A Saturday family event celebrating traditions, cultures, stories, arts, music and celebrations from around the world, with student activities, cultural displays, performances, arts and crafts, and interactive booths. Clean-up runs from 14:00 to 15:00, and community members are welcome to help. ELC and Primary students must attend with a parent or guardian and may not be dropped off. School buses will not operate. More details will be shared soon.</t>
+          <t xml:space="preserve">During Sports Day practice, students participate in a variety of physical activities, team games, relays, and event rehearsals in preparation for Sports Day. They develop teamwork, cooperation, sportsmanship, and physical fitness while learning event procedures, safety expectations, and cheering routines. Practice sessions help students build confidence and ensure they are prepared to participate successfully in the Sports Day celebration.</t>
         </is>
       </c>
       <c r="L31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">今年のテーマは「世界の祭りと祝日」です。世界各地の伝統、文化、物語、芸術、音楽、お祝いを紹介する、土曜日のご家族参加型イベントです。児童・生徒の活動、文化展示、パフォーマンス、工作、体験型ブースをお楽しみいただけます。午後2時～3時に片付けを行います（学校コミュニティの皆さまのご協力も歓迎します）。幼稚部・小学部の児童は必ず保護者同伴でご参加ください（お子さまだけを送り届けることはできません）。当日はスクールバスの運行はありません。詳細は近日中にお知らせします。</t>
+          <t xml:space="preserve">運動会に向けた練習では、さまざまな運動、チームゲーム、リレー、種目のリハーサルに取り組みます。進行の流れ、安全面のルール、応援の仕方を学びながら、チームワーク、協調性、スポーツマンシップ、体力を養います。練習を通して自信をつけ、運動会当日に力を発揮できるよう準備します。</t>
         </is>
       </c>
       <c r="M31" t="inlineStr" s="2">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="O31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-31-international-mindedness-festival.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-04-elc-sports-day-rehearsal-1.webp</t>
         </is>
       </c>
       <c r="P31" t="inlineStr" s="2">
@@ -3089,17 +3089,17 @@
     <row r="32">
       <c r="A32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-04-elc-sports-day-rehearsal-1</t>
+          <t xml:space="preserve">2026-11-05-toyota-museum-field-trip</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-04</t>
+          <t xml:space="preserve">2026-11-05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-04</t>
+          <t xml:space="preserve">2026-11-05</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="3">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="E32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="2">
@@ -3129,22 +3129,22 @@
       </c>
       <c r="I32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC Sports Day Rehearsal #1</t>
+          <t xml:space="preserve">Toyota Museum Field Trip</t>
         </is>
       </c>
       <c r="J32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部運動会リハーサル #1</t>
+          <t xml:space="preserve">トヨタ博物館校外学習</t>
         </is>
       </c>
       <c r="K32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">During Sports Day practice, students participate in a variety of physical activities, team games, relays, and event rehearsals in preparation for Sports Day. They develop teamwork, cooperation, sportsmanship, and physical fitness while learning event procedures, safety expectations, and cheering routines. Practice sessions help students build confidence and ensure they are prepared to participate successfully in the Sports Day celebration.</t>
+          <t xml:space="preserve">Grade 9 students go to the Toyota museum down the road and view the exhibits taking some notes on machines they learned about.</t>
         </is>
       </c>
       <c r="L32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会に向けた練習では、さまざまな運動、チームゲーム、リレー、種目のリハーサルに取り組みます。進行の流れ、安全面のルール、応援の仕方を学びながら、チームワーク、協調性、スポーツマンシップ、体力を養います。練習を通して自信をつけ、運動会当日に力を発揮できるよう準備します。</t>
+          <t xml:space="preserve">9年生が近くのトヨタの博物館を訪れ、授業で学んだ機械について展示を見学しながらメモを取ります。</t>
         </is>
       </c>
       <c r="M32" t="inlineStr" s="2">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="O32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-04-elc-sports-day-rehearsal-1.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-05-toyota-museum-field-trip.webp</t>
         </is>
       </c>
       <c r="P32" t="inlineStr" s="2">
@@ -3186,17 +3186,17 @@
     <row r="33">
       <c r="A33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-05-toyota-museum-field-trip</t>
+          <t xml:space="preserve">2026-11-06-extracurricular-activities-autumn-cas-project-su</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-05</t>
+          <t xml:space="preserve">2026-11-06</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-05</t>
+          <t xml:space="preserve">2026-11-06</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="3">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="F33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G33" t="inlineStr" s="2">
@@ -3226,22 +3226,22 @@
       </c>
       <c r="I33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Toyota Museum Field Trip</t>
+          <t xml:space="preserve">Extracurricular Activities: Autumn CAS &amp; Project Support Fair</t>
         </is>
       </c>
       <c r="J33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">トヨタ博物館校外学習</t>
+          <t xml:space="preserve">課外活動：秋のCAS・プロジェクトサポートフェア</t>
         </is>
       </c>
       <c r="K33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 9 students go to the Toyota museum down the road and view the exhibits taking some notes on machines they learned about.</t>
+          <t xml:space="preserve">Secondary PTA Supported Event to help students understand various volunteering and CAS project opportunities in the community. Open to MYP and DP Students.</t>
         </is>
       </c>
       <c r="L33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9年生が近くのトヨタの博物館を訪れ、授業で学んだ機械について展示を見学しながらメモを取ります。</t>
+          <t xml:space="preserve">中等部PTAの支援による行事で、地域でのさまざまなボランティアやCASプロジェクトの機会について知ることができます。MYP・DP生徒が対象です。</t>
         </is>
       </c>
       <c r="M33" t="inlineStr" s="2">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="O33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-05-toyota-museum-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-06-extracurricular-activities-autumn-cas-project-su.webp</t>
         </is>
       </c>
       <c r="P33" t="inlineStr" s="2">
@@ -3283,17 +3283,17 @@
     <row r="34">
       <c r="A34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-06-extracurricular-activities-autumn-cas-project-su</t>
+          <t xml:space="preserve">2026-11-07-sat-test-4</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-06</t>
+          <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-06</t>
+          <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="3">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="E34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G34" t="inlineStr" s="2">
@@ -3323,22 +3323,22 @@
       </c>
       <c r="I34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Extracurricular Activities: Autumn CAS &amp; Project Support Fair</t>
+          <t xml:space="preserve">SAT Test #4</t>
         </is>
       </c>
       <c r="J34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">課外活動：秋のCAS・プロジェクトサポートフェア</t>
+          <t xml:space="preserve">SAT試験 第4回</t>
         </is>
       </c>
       <c r="K34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary PTA Supported Event to help students understand various volunteering and CAS project opportunities in the community. Open to MYP and DP Students.</t>
+          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
         </is>
       </c>
       <c r="L34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部PTAの支援による行事で、地域でのさまざまなボランティアやCASプロジェクトの機会について知ることができます。MYP・DP生徒が対象です。</t>
+          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
         </is>
       </c>
       <c r="M34" t="inlineStr" s="2">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="O34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-06-extracurricular-activities-autumn-cas-project-su.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-07-sat-test-4.webp</t>
         </is>
       </c>
       <c r="P34" t="inlineStr" s="2">
@@ -3380,17 +3380,17 @@
     <row r="35">
       <c r="A35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-07-sat-test-4</t>
+          <t xml:space="preserve">2026-11-09-wellbeing-week</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-07</t>
+          <t xml:space="preserve">2026-11-09</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-07</t>
+          <t xml:space="preserve">2026-11-13</t>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="3">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="E35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F35" t="inlineStr" s="2">
@@ -3420,22 +3420,22 @@
       </c>
       <c r="I35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT Test #4</t>
+          <t xml:space="preserve">Wellbeing Week</t>
         </is>
       </c>
       <c r="J35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT試験 第4回</t>
+          <t xml:space="preserve">ウェルビーイング週間</t>
         </is>
       </c>
       <c r="K35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
+          <t xml:space="preserve">A school wide event focused on raising awareness for wellbeing.</t>
         </is>
       </c>
       <c r="L35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
+          <t xml:space="preserve">ウェルビーイング（心身の健康）への意識を高めることを目的とした全校行事です。</t>
         </is>
       </c>
       <c r="M35" t="inlineStr" s="2">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="O35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-07-sat-test-4.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-09-wellbeing-week.webp</t>
         </is>
       </c>
       <c r="P35" t="inlineStr" s="2">
@@ -3477,7 +3477,7 @@
     <row r="36">
       <c r="A36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-09-wellbeing-week</t>
+          <t xml:space="preserve">2026-11-09-concept-con-wellbeing</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="3">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="E36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F36" t="inlineStr" s="2">
@@ -3517,22 +3517,22 @@
       </c>
       <c r="I36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wellbeing Week</t>
+          <t xml:space="preserve">Concept Con (Wellbeing)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ウェルビーイング週間</t>
+          <t xml:space="preserve">コンセプト・コン（ウェルビーイング）</t>
         </is>
       </c>
       <c r="K36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A school wide event focused on raising awareness for wellbeing.</t>
+          <t xml:space="preserve">The Primary Concept Conference on the theme of wellbeing, held during Wellbeing Week.</t>
         </is>
       </c>
       <c r="L36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ウェルビーイング（心身の健康）への意識を高めることを目的とした全校行事です。</t>
+          <t xml:space="preserve">ウェルビーイング週間に合わせて行う、小学部のコンセプト・カンファレンス（テーマ：ウェルビーイング）です。</t>
         </is>
       </c>
       <c r="M36" t="inlineStr" s="2">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="O36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-09-wellbeing-week.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P36" t="inlineStr" s="2">
@@ -3574,17 +3574,17 @@
     <row r="37">
       <c r="A37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-09-concept-con-wellbeing</t>
+          <t xml:space="preserve">2026-11-11-elc-sports-day-rehearsal-2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-09</t>
+          <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-13</t>
+          <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="3">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="E37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">ELC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr" s="2">
@@ -3614,22 +3614,22 @@
       </c>
       <c r="I37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Concept Con (Wellbeing)</t>
+          <t xml:space="preserve">ELC Sports Day Rehearsal #2</t>
         </is>
       </c>
       <c r="J37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">コンセプト・コン（ウェルビーイング）</t>
+          <t xml:space="preserve">幼稚部運動会リハーサル #2</t>
         </is>
       </c>
       <c r="K37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Primary Concept Conference on the theme of wellbeing, held during Wellbeing Week.</t>
+          <t xml:space="preserve">During Sports Day practice, students participate in a variety of physical activities, team games, relays, and event rehearsals in preparation for Sports Day. They develop teamwork, cooperation, sportsmanship, and physical fitness while learning event procedures, safety expectations, and cheering routines. Practice sessions help students build confidence and ensure they are prepared to participate successfully in the Sports Day celebration.</t>
         </is>
       </c>
       <c r="L37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ウェルビーイング週間に合わせて行う、小学部のコンセプト・カンファレンス（テーマ：ウェルビーイング）です。</t>
+          <t xml:space="preserve">運動会に向けた練習では、さまざまな運動、チームゲーム、リレー、種目のリハーサルに取り組みます。進行の流れ、安全面のルール、応援の仕方を学びながら、チームワーク、協調性、スポーツマンシップ、体力を養います。練習を通して自信をつけ、運動会当日に力を発揮できるよう準備します。</t>
         </is>
       </c>
       <c r="M37" t="inlineStr" s="2">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">compass/images/events/2026-11-11-elc-sports-day-rehearsal-2.webp</t>
         </is>
       </c>
       <c r="P37" t="inlineStr" s="2">
@@ -3671,17 +3671,17 @@
     <row r="38">
       <c r="A38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-11-elc-sports-day-rehearsal-2</t>
+          <t xml:space="preserve">2026-11-14-elc-sports-day</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-11</t>
+          <t xml:space="preserve">2026-11-14</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-11</t>
+          <t xml:space="preserve">2026-11-14</t>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="3">
@@ -3711,22 +3711,22 @@
       </c>
       <c r="I38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC Sports Day Rehearsal #2</t>
+          <t xml:space="preserve">ELC Sports Day</t>
         </is>
       </c>
       <c r="J38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部運動会リハーサル #2</t>
+          <t xml:space="preserve">幼稚部運動会</t>
         </is>
       </c>
       <c r="K38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">During Sports Day practice, students participate in a variety of physical activities, team games, relays, and event rehearsals in preparation for Sports Day. They develop teamwork, cooperation, sportsmanship, and physical fitness while learning event procedures, safety expectations, and cheering routines. Practice sessions help students build confidence and ensure they are prepared to participate successfully in the Sports Day celebration.</t>
+          <t xml:space="preserve">During Sports Day, students participate in a variety of athletic events, relay races, team challenges, and cooperative games. They demonstrate teamwork, perseverance, sportsmanship, and school spirit while celebrating physical activity and healthy competition. Sports Day provides an opportunity for students to challenge themselves, support their peers, and enjoy a fun day of community participation and achievement.</t>
         </is>
       </c>
       <c r="L38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会に向けた練習では、さまざまな運動、チームゲーム、リレー、種目のリハーサルに取り組みます。進行の流れ、安全面のルール、応援の仕方を学びながら、チームワーク、協調性、スポーツマンシップ、体力を養います。練習を通して自信をつけ、運動会当日に力を発揮できるよう準備します。</t>
+          <t xml:space="preserve">運動会では、さまざまな競技、リレー、チーム対抗戦、協力ゲームに参加します。体を動かすことと健全な競争を楽しみながら、チームワーク、粘り強さ、スポーツマンシップ、愛校心を発揮します。自分に挑戦し、仲間を応援し、コミュニティ全体で達成感を味わう楽しい一日です。</t>
         </is>
       </c>
       <c r="M38" t="inlineStr" s="2">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="O38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-11-elc-sports-day-rehearsal-2.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-14-elc-sports-day.webp</t>
         </is>
       </c>
       <c r="P38" t="inlineStr" s="2">
@@ -3768,17 +3768,17 @@
     <row r="39">
       <c r="A39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-14-elc-sports-day</t>
+          <t xml:space="preserve">2026-11-16-friendly-soccer-tournament-internal</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-14</t>
+          <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-14</t>
+          <t xml:space="preserve">2026-11-20</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="3">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="E39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F39" t="inlineStr" s="2">
@@ -3808,22 +3808,22 @@
       </c>
       <c r="I39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC Sports Day</t>
+          <t xml:space="preserve">Friendly Soccer Tournament (Internal)</t>
         </is>
       </c>
       <c r="J39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部運動会</t>
+          <t xml:space="preserve">校内サッカー大会</t>
         </is>
       </c>
       <c r="K39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">During Sports Day, students participate in a variety of athletic events, relay races, team challenges, and cooperative games. They demonstrate teamwork, perseverance, sportsmanship, and school spirit while celebrating physical activity and healthy competition. Sports Day provides an opportunity for students to challenge themselves, support their peers, and enjoy a fun day of community participation and achievement.</t>
+          <t xml:space="preserve">Students will take part in a friendly internal soccer tournament, promoting teamwork, sportsmanship, and school spirit.</t>
         </is>
       </c>
       <c r="L39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会では、さまざまな競技、リレー、チーム対抗戦、協力ゲームに参加します。体を動かすことと健全な競争を楽しみながら、チームワーク、粘り強さ、スポーツマンシップ、愛校心を発揮します。自分に挑戦し、仲間を応援し、コミュニティ全体で達成感を味わう楽しい一日です。</t>
+          <t xml:space="preserve">校内サッカー大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
         </is>
       </c>
       <c r="M39" t="inlineStr" s="2">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="O39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-14-elc-sports-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-16-friendly-soccer-tournament-internal.webp</t>
         </is>
       </c>
       <c r="P39" t="inlineStr" s="2">
@@ -3865,17 +3865,17 @@
     <row r="40">
       <c r="A40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-16-friendly-soccer-tournament-internal</t>
+          <t xml:space="preserve">2026-11-17-foundation-field-trip</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-16</t>
+          <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-20</t>
+          <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="3">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="E40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">ELC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G40" t="inlineStr" s="2">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="I40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Friendly Soccer Tournament (Internal)</t>
+          <t xml:space="preserve">Foundation Field Trip</t>
         </is>
       </c>
       <c r="J40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内サッカー大会</t>
+          <t xml:space="preserve">ファウンデーション校外学習</t>
         </is>
       </c>
       <c r="K40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in a friendly internal soccer tournament, promoting teamwork, sportsmanship, and school spirit.</t>
+          <t xml:space="preserve">Our youngest learners will enjoy an age-appropriate educational excursion that supports classroom learning through hands-on experiences.</t>
         </is>
       </c>
       <c r="L40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内サッカー大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
+          <t xml:space="preserve">年少の子どもたちが、年齢に合った校外学習に出かけ、体験を通して教室での学びを深めます。</t>
         </is>
       </c>
       <c r="M40" t="inlineStr" s="2">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="O40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-16-friendly-soccer-tournament-internal.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-17-foundation-field-trip.webp</t>
         </is>
       </c>
       <c r="P40" t="inlineStr" s="2">
@@ -3962,17 +3962,17 @@
     <row r="41">
       <c r="A41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-17-foundation-field-trip</t>
+          <t xml:space="preserve">2026-11-20-gifu-kakamigahara-air-and-space-museum</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-17</t>
+          <t xml:space="preserve">2026-11-20</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-17</t>
+          <t xml:space="preserve">2026-11-20</t>
         </is>
       </c>
       <c r="D41" t="inlineStr" s="3">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="E41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G41" t="inlineStr" s="2">
@@ -4002,22 +4002,22 @@
       </c>
       <c r="I41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Foundation Field Trip</t>
+          <t xml:space="preserve">Gifu Kakamigahara Air and Space Museum</t>
         </is>
       </c>
       <c r="J41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ファウンデーション校外学習</t>
+          <t xml:space="preserve">岐阜かかみがはら航空宇宙博物館</t>
         </is>
       </c>
       <c r="K41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Our youngest learners will enjoy an age-appropriate educational excursion that supports classroom learning through hands-on experiences.</t>
+          <t xml:space="preserve">Students will be going to the air and space museum to complete a practical where they will be analyzing plane design throughout history.</t>
         </is>
       </c>
       <c r="L41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">年少の子どもたちが、年齢に合った校外学習に出かけ、体験を通して教室での学びを深めます。</t>
+          <t xml:space="preserve">航空宇宙博物館を訪れ、歴史を通じた飛行機のデザインを分析する実習に取り組みます。</t>
         </is>
       </c>
       <c r="M41" t="inlineStr" s="2">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="O41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-17-foundation-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-20-gifu-kakamigahara-air-and-space-museum.webp</t>
         </is>
       </c>
       <c r="P41" t="inlineStr" s="2">
@@ -4059,32 +4059,32 @@
     <row r="42">
       <c r="A42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-20-gifu-kakamigahara-air-and-space-museum</t>
+          <t xml:space="preserve">2026-11-24-winter-art-contest</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-20</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-20</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">13:10-14:55</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G42" t="inlineStr" s="2">
@@ -4099,37 +4099,37 @@
       </c>
       <c r="I42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Gifu Kakamigahara Air and Space Museum</t>
+          <t xml:space="preserve">Gallery Day: ELC &amp; Primary Art Showcase</t>
         </is>
       </c>
       <c r="J42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">岐阜かかみがはら航空宇宙博物館</t>
+          <t xml:space="preserve">ギャラリーデー：幼稚部・小学部アート展</t>
         </is>
       </c>
       <c r="K42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will be going to the air and space museum to complete a practical where they will be analyzing plane design throughout history.</t>
+          <t xml:space="preserve">ELC and Primary students display the artwork they have created with the visual arts teacher. Parents are welcome to view the gallery from 13:10 to 14:55. Students vote for their favourite artworks, and the winners for each grade are announced.</t>
         </is>
       </c>
       <c r="L42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">航空宇宙博物館を訪れ、歴史を通じた飛行機のデザインを分析する実習に取り組みます。</t>
+          <t xml:space="preserve">幼稚部・小学部の児童が美術の授業で制作した作品を展示します。保護者の皆さまは13:10～14:55にご鑑賞いただけます。児童による投票を行い、学年ごとの受賞作品を発表します。</t>
         </is>
       </c>
       <c r="M42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Gym</t>
         </is>
       </c>
       <c r="N42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">体育館</t>
         </is>
       </c>
       <c r="O42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-20-gifu-kakamigahara-air-and-space-museum.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-24-winter-art-contest.webp</t>
         </is>
       </c>
       <c r="P42" t="inlineStr" s="2">
@@ -4156,22 +4156,22 @@
     <row r="43">
       <c r="A43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-24-winter-art-contest</t>
+          <t xml:space="preserve">2026-11-27-parents-morning-1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-24</t>
+          <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-24</t>
+          <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">13:10-14:55</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -4196,37 +4196,37 @@
       </c>
       <c r="I43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Gallery Day: ELC &amp; Primary Art Showcase</t>
+          <t xml:space="preserve">Parents Morning #1</t>
         </is>
       </c>
       <c r="J43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ギャラリーデー：幼稚部・小学部アート展</t>
+          <t xml:space="preserve">朝の授業参観 #1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC and Primary students display the artwork they have created with the visual arts teacher. Parents are welcome to view the gallery from 13:10 to 14:55. Students vote for their favourite artworks, and the winners for each grade are announced.</t>
+          <t xml:space="preserve">ELC and Primary Parents are invited to come and see the lessons in the morning and experience the morning routines with their child.</t>
         </is>
       </c>
       <c r="L43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部・小学部の児童が美術の授業で制作した作品を展示します。保護者の皆さまは13:10～14:55にご鑑賞いただけます。児童による投票を行い、学年ごとの受賞作品を発表します。</t>
+          <t xml:space="preserve">幼稚部・小学部の保護者の皆様をお招きし、朝の授業をご参観いただき、お子様と一緒に朝の日課を体験していただきます。</t>
         </is>
       </c>
       <c r="M43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Gym</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="N43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">体育館</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="O43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-24-winter-art-contest.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-27-parents-morning-1.webp</t>
         </is>
       </c>
       <c r="P43" t="inlineStr" s="2">
@@ -4253,7 +4253,7 @@
     <row r="44">
       <c r="A44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-27-parents-morning-1</t>
+          <t xml:space="preserve">2026-11-27-teacher-appreciation-day</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="3">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="E44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G44" t="inlineStr" s="2">
@@ -4293,22 +4293,22 @@
       </c>
       <c r="I44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parents Morning #1</t>
+          <t xml:space="preserve">Teacher Appreciation Day</t>
         </is>
       </c>
       <c r="J44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">朝の授業参観 #1</t>
+          <t xml:space="preserve">教職員感謝デー</t>
         </is>
       </c>
       <c r="K44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC and Primary Parents are invited to come and see the lessons in the morning and experience the morning routines with their child.</t>
+          <t xml:space="preserve">The school community will celebrate Teacher Appreciation Day by recognizing and thanking teachers for their dedication, care, and support.</t>
         </is>
       </c>
       <c r="L44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部・小学部の保護者の皆様をお招きし、朝の授業をご参観いただき、お子様と一緒に朝の日課を体験していただきます。</t>
+          <t xml:space="preserve">学校コミュニティ全体で、教員の献身、思いやり、支えに感謝を伝える日です。</t>
         </is>
       </c>
       <c r="M44" t="inlineStr" s="2">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="O44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-27-parents-morning-1.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-27-teacher-appreciation-day.webp</t>
         </is>
       </c>
       <c r="P44" t="inlineStr" s="2">
@@ -4350,17 +4350,17 @@
     <row r="45">
       <c r="A45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-27-teacher-appreciation-day</t>
+          <t xml:space="preserve">2026-11-28-2026-enishi-futsal-tournament</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-27</t>
+          <t xml:space="preserve">2026-11-28</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-27</t>
+          <t xml:space="preserve">2026-11-28</t>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="3">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="E45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F45" t="inlineStr" s="2">
@@ -4390,22 +4390,22 @@
       </c>
       <c r="I45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Teacher Appreciation Day</t>
+          <t xml:space="preserve">2026 - Enishi Futsal Tournament</t>
         </is>
       </c>
       <c r="J45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">教職員感謝デー</t>
+          <t xml:space="preserve">2026 Enishiフットサル大会</t>
         </is>
       </c>
       <c r="K45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The school community will celebrate Teacher Appreciation Day by recognizing and thanking teachers for their dedication, care, and support.</t>
+          <t xml:space="preserve">Enishi will host a Middle School Futsal tournament at our school with multiple schools participating.</t>
         </is>
       </c>
       <c r="L45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学校コミュニティ全体で、教員の献身、思いやり、支えに感謝を伝える日です。</t>
+          <t xml:space="preserve">本校にて複数校が参加する中学生フットサル大会を開催します。</t>
         </is>
       </c>
       <c r="M45" t="inlineStr" s="2">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="O45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-27-teacher-appreciation-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-28-2026-enishi-futsal-tournament.webp</t>
         </is>
       </c>
       <c r="P45" t="inlineStr" s="2">
@@ -4447,32 +4447,32 @@
     <row r="46">
       <c r="A46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-28-2026-enishi-futsal-tournament</t>
+          <t xml:space="preserve">2026-12-03-grade-3-4-musical</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-28</t>
+          <t xml:space="preserve">2026-12-03</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-28</t>
+          <t xml:space="preserve">2026-12-03</t>
         </is>
       </c>
       <c r="D46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">17:30</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G46" t="inlineStr" s="2">
@@ -4487,22 +4487,22 @@
       </c>
       <c r="I46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026 - Enishi Futsal Tournament</t>
+          <t xml:space="preserve">Grade 3, 4 Musical</t>
         </is>
       </c>
       <c r="J46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026 Enishiフットサル大会</t>
+          <t xml:space="preserve">3・4年生ミュージカル</t>
         </is>
       </c>
       <c r="K46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Enishi will host a Middle School Futsal tournament at our school with multiple schools participating.</t>
+          <t xml:space="preserve">Students present a musical performance showcasing their talents in singing, acting, and teamwork. Families are invited to enjoy this special production.</t>
         </is>
       </c>
       <c r="L46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">本校にて複数校が参加する中学生フットサル大会を開催します。</t>
+          <t xml:space="preserve">歌、演技、チームワークを披露するミュージカルを上演します。ご家族の皆様もぜひこの特別な公演をお楽しみください。</t>
         </is>
       </c>
       <c r="M46" t="inlineStr" s="2">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="O46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-28-2026-enishi-futsal-tournament.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-03-grade-3-4-musical.webp</t>
         </is>
       </c>
       <c r="P46" t="inlineStr" s="2">
@@ -4544,32 +4544,32 @@
     <row r="47">
       <c r="A47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-03-grade-3-4-musical</t>
+          <t xml:space="preserve">2026-12-05-sat-test-5</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-03</t>
+          <t xml:space="preserve">2026-12-05</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-03</t>
+          <t xml:space="preserve">2026-12-05</t>
         </is>
       </c>
       <c r="D47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">17:30</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G47" t="inlineStr" s="2">
@@ -4584,22 +4584,22 @@
       </c>
       <c r="I47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 3, 4 Musical</t>
+          <t xml:space="preserve">SAT Test #5</t>
         </is>
       </c>
       <c r="J47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3・4年生ミュージカル</t>
+          <t xml:space="preserve">SAT試験 第5回</t>
         </is>
       </c>
       <c r="K47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students present a musical performance showcasing their talents in singing, acting, and teamwork. Families are invited to enjoy this special production.</t>
+          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
         </is>
       </c>
       <c r="L47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">歌、演技、チームワークを披露するミュージカルを上演します。ご家族の皆様もぜひこの特別な公演をお楽しみください。</t>
+          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
         </is>
       </c>
       <c r="M47" t="inlineStr" s="2">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="O47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-03-grade-3-4-musical.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-05-sat-test-5.webp</t>
         </is>
       </c>
       <c r="P47" t="inlineStr" s="2">
@@ -4641,17 +4641,17 @@
     <row r="48">
       <c r="A48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-05-sat-test-5</t>
+          <t xml:space="preserve">2026-12-10-choir-and-orchestra-concert</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-05</t>
+          <t xml:space="preserve">2026-12-10</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-05</t>
+          <t xml:space="preserve">2026-12-10</t>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="3">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="E48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G48" t="inlineStr" s="2">
@@ -4681,22 +4681,22 @@
       </c>
       <c r="I48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT Test #5</t>
+          <t xml:space="preserve">Choir and Orchestra Concert</t>
         </is>
       </c>
       <c r="J48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT試験 第5回</t>
+          <t xml:space="preserve">合唱・オーケストラコンサート</t>
         </is>
       </c>
       <c r="K48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
+          <t xml:space="preserve">Choir class and orchestra club will perform the music repertoire they have been rehearsing for an audience of family, peers and teachers.</t>
         </is>
       </c>
       <c r="L48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
+          <t xml:space="preserve">合唱クラスとオーケストラクラブが、練習を重ねてきた曲目をご家族、友人、教員の前で演奏します。</t>
         </is>
       </c>
       <c r="M48" t="inlineStr" s="2">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-05-sat-test-5.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-10-choir-and-orchestra-concert.webp</t>
         </is>
       </c>
       <c r="P48" t="inlineStr" s="2">
@@ -4738,17 +4738,17 @@
     <row r="49">
       <c r="A49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-10-choir-and-orchestra-concert</t>
+          <t xml:space="preserve">2026-12-11-silent-auction</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-10</t>
+          <t xml:space="preserve">2026-12-11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-10</t>
+          <t xml:space="preserve">2026-12-11</t>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="3">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="E49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F49" t="inlineStr" s="2">
@@ -4778,22 +4778,22 @@
       </c>
       <c r="I49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choir and Orchestra Concert</t>
+          <t xml:space="preserve">Silent Auction</t>
         </is>
       </c>
       <c r="J49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合唱・オーケストラコンサート</t>
+          <t xml:space="preserve">サイレントオークション</t>
         </is>
       </c>
       <c r="K49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choir class and orchestra club will perform the music repertoire they have been rehearsing for an audience of family, peers and teachers.</t>
+          <t xml:space="preserve">Families and community members can bid on donated items and experiences to support initiatives chosen by the primary student council.</t>
         </is>
       </c>
       <c r="L49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合唱クラスとオーケストラクラブが、練習を重ねてきた曲目をご家族、友人、教員の前で演奏します。</t>
+          <t xml:space="preserve">ご家族や地域の皆様が寄付された品物や体験に入札し、小学部生徒会が選んだ取り組みを支援します。</t>
         </is>
       </c>
       <c r="M49" t="inlineStr" s="2">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="O49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-10-choir-and-orchestra-concert.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-11-silent-auction.webp</t>
         </is>
       </c>
       <c r="P49" t="inlineStr" s="2">
@@ -4835,17 +4835,17 @@
     <row r="50">
       <c r="A50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-11-silent-auction</t>
+          <t xml:space="preserve">2026-12-16-industry-visit-tech-company</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-11</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-11</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="3">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G50" t="inlineStr" s="2">
@@ -4875,22 +4875,22 @@
       </c>
       <c r="I50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Silent Auction</t>
+          <t xml:space="preserve">Industry Visit (Tech Company)</t>
         </is>
       </c>
       <c r="J50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">サイレントオークション</t>
+          <t xml:space="preserve">企業訪問（テクノロジー企業）</t>
         </is>
       </c>
       <c r="K50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Families and community members can bid on donated items and experiences to support initiatives chosen by the primary student council.</t>
+          <t xml:space="preserve">Students will visit a local technology company to gain firsthand insight into the modern workplace and explore careers in technology and innovation.</t>
         </is>
       </c>
       <c r="L50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ご家族や地域の皆様が寄付された品物や体験に入札し、小学部生徒会が選んだ取り組みを支援します。</t>
+          <t xml:space="preserve">地元のテクノロジー企業を訪問し、現代の職場を直接知るとともに、テクノロジーやイノベーション分野のキャリアについて考えます。</t>
         </is>
       </c>
       <c r="M50" t="inlineStr" s="2">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-11-silent-auction.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-16-industry-visit-tech-company.webp</t>
         </is>
       </c>
       <c r="P50" t="inlineStr" s="2">
@@ -4932,7 +4932,7 @@
     <row r="51">
       <c r="A51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-16-industry-visit-tech-company</t>
+          <t xml:space="preserve">2026-12-16-winter-party-eagle-nest</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="3">
@@ -4952,7 +4952,7 @@
       </c>
       <c r="E51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr" s="2">
@@ -4972,22 +4972,22 @@
       </c>
       <c r="I51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Industry Visit (Tech Company)</t>
+          <t xml:space="preserve">Winter Party (Eagle Nest)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">企業訪問（テクノロジー企業）</t>
+          <t xml:space="preserve">ウィンターパーティー（イーグルネスト）</t>
         </is>
       </c>
       <c r="K51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will visit a local technology company to gain firsthand insight into the modern workplace and explore careers in technology and innovation.</t>
+          <t xml:space="preserve">Students celebrate the season with fun activities, games, and opportunities to connect with peers in their Eagle Nests. This is led by the primary student council.</t>
         </is>
       </c>
       <c r="L51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">地元のテクノロジー企業を訪問し、現代の職場を直接知るとともに、テクノロジーやイノベーション分野のキャリアについて考えます。</t>
+          <t xml:space="preserve">イーグルネストごとに、楽しい活動やゲームを通して仲間と交流し、季節を祝います。小学部生徒会が主催します。</t>
         </is>
       </c>
       <c r="M51" t="inlineStr" s="2">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="O51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-16-industry-visit-tech-company.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-16-winter-party-eagle-nest.webp</t>
         </is>
       </c>
       <c r="P51" t="inlineStr" s="2">
@@ -5029,17 +5029,17 @@
     <row r="52">
       <c r="A52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-16-winter-party-eagle-nest</t>
+          <t xml:space="preserve">2026-12-17-talent-day</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-16</t>
+          <t xml:space="preserve">2026-12-17</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-16</t>
+          <t xml:space="preserve">2026-12-17</t>
         </is>
       </c>
       <c r="D52" t="inlineStr" s="3">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G52" t="inlineStr" s="2">
@@ -5069,22 +5069,22 @@
       </c>
       <c r="I52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Winter Party (Eagle Nest)</t>
+          <t xml:space="preserve">Talent Day</t>
         </is>
       </c>
       <c r="J52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ウィンターパーティー（イーグルネスト）</t>
+          <t xml:space="preserve">タレントデー</t>
         </is>
       </c>
       <c r="K52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students celebrate the season with fun activities, games, and opportunities to connect with peers in their Eagle Nests. This is led by the primary student council.</t>
+          <t xml:space="preserve">Students have the opportunity to showcase their unique talents and interests in a supportive and encouraging environment led by the performing arts teacher.</t>
         </is>
       </c>
       <c r="L52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">イーグルネストごとに、楽しい活動やゲームを通して仲間と交流し、季節を祝います。小学部生徒会が主催します。</t>
+          <t xml:space="preserve">舞台芸術の先生のもと、温かく励まし合う雰囲気の中で、一人ひとりの特技や興味を披露します。</t>
         </is>
       </c>
       <c r="M52" t="inlineStr" s="2">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="O52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-16-winter-party-eagle-nest.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-17-talent-day.webp</t>
         </is>
       </c>
       <c r="P52" t="inlineStr" s="2">
@@ -5126,17 +5126,17 @@
     <row r="53">
       <c r="A53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-17-talent-day</t>
+          <t xml:space="preserve">2026-12-18-tea-party-pta-for-all</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-17</t>
+          <t xml:space="preserve">2026-12-18</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-17</t>
+          <t xml:space="preserve">2026-12-18</t>
         </is>
       </c>
       <c r="D53" t="inlineStr" s="3">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="E53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">PTA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr" s="2">
@@ -5166,22 +5166,22 @@
       </c>
       <c r="I53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Talent Day</t>
+          <t xml:space="preserve">Tea Party / PTA for all</t>
         </is>
       </c>
       <c r="J53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">タレントデー</t>
+          <t xml:space="preserve">PTAティーパーティー（どなたでも参加できます）</t>
         </is>
       </c>
       <c r="K53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students have the opportunity to showcase their unique talents and interests in a supportive and encouraging environment led by the performing arts teacher.</t>
+          <t xml:space="preserve">Families are invited to enjoy refreshments while connecting with the PTA, school staff, and other members of the community.</t>
         </is>
       </c>
       <c r="L53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">舞台芸術の先生のもと、温かく励まし合う雰囲気の中で、一人ひとりの特技や興味を披露します。</t>
+          <t xml:space="preserve">軽食を楽しみながら、PTA、教職員、コミュニティの皆様と交流していただける集いです。</t>
         </is>
       </c>
       <c r="M53" t="inlineStr" s="2">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="O53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-17-talent-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-18-tea-party-pta-for-all.webp</t>
         </is>
       </c>
       <c r="P53" t="inlineStr" s="2">
@@ -5223,7 +5223,7 @@
     <row r="54">
       <c r="A54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-18-tea-party-pta-for-all</t>
+          <t xml:space="preserve">2026-12-18-eagle-bucks-store</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="3">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="E54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTA</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G54" t="inlineStr" s="2">
@@ -5263,22 +5263,22 @@
       </c>
       <c r="I54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Tea Party / PTA for all</t>
+          <t xml:space="preserve">Eagle Bucks Store</t>
         </is>
       </c>
       <c r="J54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTAティーパーティー（どなたでも参加できます）</t>
+          <t xml:space="preserve">イーグルバックス・ストア</t>
         </is>
       </c>
       <c r="K54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Families are invited to enjoy refreshments while connecting with the PTA, school staff, and other members of the community.</t>
+          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
         </is>
       </c>
       <c r="L54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">軽食を楽しみながら、PTA、教職員、コミュニティの皆様と交流していただける集いです。</t>
+          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
         </is>
       </c>
       <c r="M54" t="inlineStr" s="2">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="O54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-18-tea-party-pta-for-all.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-18-eagle-bucks-store.webp</t>
         </is>
       </c>
       <c r="P54" t="inlineStr" s="2">
@@ -5320,17 +5320,17 @@
     <row r="55">
       <c r="A55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-18-eagle-bucks-store</t>
+          <t xml:space="preserve">2026-12-19-end-of-term-1-activity-sleep-over-program-g6-10</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-18</t>
+          <t xml:space="preserve">2026-12-19</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-18</t>
+          <t xml:space="preserve">2026-12-19</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="3">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="E55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F55" t="inlineStr" s="2">
@@ -5360,22 +5360,22 @@
       </c>
       <c r="I55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Eagle Bucks Store</t>
+          <t xml:space="preserve">End of Term 1 Activity-Sleep Over Program: G6-10</t>
         </is>
       </c>
       <c r="J55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">イーグルバックス・ストア</t>
+          <t xml:space="preserve">第1学期末行事：宿泊プログラム（G6–10）</t>
         </is>
       </c>
       <c r="K55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
+          <t xml:space="preserve">Grade 6 to 10 students will take part in a school sleepover program to celebrate the end of Term 1 through shared activities and community building.</t>
         </is>
       </c>
       <c r="L55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
+          <t xml:space="preserve">6～10年生が校内での宿泊プログラムに参加し、共に活動しながら仲間づくりを行い、第1学期の終わりを祝います。</t>
         </is>
       </c>
       <c r="M55" t="inlineStr" s="2">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="O55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-18-eagle-bucks-store.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-19-end-of-term-1-activity-sleep-over-program-g6-10.webp</t>
         </is>
       </c>
       <c r="P55" t="inlineStr" s="2">
@@ -5417,17 +5417,17 @@
     <row r="56">
       <c r="A56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-19-end-of-term-1-activity-sleep-over-program-g6-10</t>
+          <t xml:space="preserve">2026-12-21-winter-study-camp-g11-12</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-19</t>
+          <t xml:space="preserve">2026-12-21</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-19</t>
+          <t xml:space="preserve">2026-12-23</t>
         </is>
       </c>
       <c r="D56" t="inlineStr" s="3">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="E56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F56" t="inlineStr" s="2">
@@ -5457,22 +5457,22 @@
       </c>
       <c r="I56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">End of Term 1 Activity-Sleep Over Program: G6-10</t>
+          <t xml:space="preserve">Winter Study Camp: G11-12</t>
         </is>
       </c>
       <c r="J56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第1学期末行事：宿泊プログラム（G6–10）</t>
+          <t xml:space="preserve">冬季学習合宿：G11–12</t>
         </is>
       </c>
       <c r="K56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 6 to 10 students will take part in a school sleepover program to celebrate the end of Term 1 through shared activities and community building.</t>
+          <t xml:space="preserve">Grade 11 and 12 students will take part in an off-campus Winter Study Camp focused on concentrated study, academic review, and exam preparation.</t>
         </is>
       </c>
       <c r="L56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">6～10年生が校内での宿泊プログラムに参加し、共に活動しながら仲間づくりを行い、第1学期の終わりを祝います。</t>
+          <t xml:space="preserve">11・12年生が校外での冬季学習合宿に参加し、集中学習、復習、試験対策に取り組みます。</t>
         </is>
       </c>
       <c r="M56" t="inlineStr" s="2">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="O56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-19-end-of-term-1-activity-sleep-over-program-g6-10.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-21-winter-study-camp-g11-12.webp</t>
         </is>
       </c>
       <c r="P56" t="inlineStr" s="2">
@@ -5514,17 +5514,17 @@
     <row r="57">
       <c r="A57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-21-winter-study-camp-g11-12</t>
+          <t xml:space="preserve">2027-01-14-g10-parent-info-session-high-school-subject-choi</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-21</t>
+          <t xml:space="preserve">2027-01-14</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-23</t>
+          <t xml:space="preserve">2027-01-14</t>
         </is>
       </c>
       <c r="D57" t="inlineStr" s="3">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="E57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G57" t="inlineStr" s="2">
@@ -5554,22 +5554,22 @@
       </c>
       <c r="I57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Winter Study Camp: G11-12</t>
+          <t xml:space="preserve">G10 Parent info Session (High School Subject Choice)</t>
         </is>
       </c>
       <c r="J57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">冬季学習合宿：G11–12</t>
+          <t xml:space="preserve">G10保護者向け説明会（高等部科目選択）</t>
         </is>
       </c>
       <c r="K57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 11 and 12 students will take part in an off-campus Winter Study Camp focused on concentrated study, academic review, and exam preparation.</t>
+          <t xml:space="preserve">Grade 10 parents are invited to an information session about DP subject choices and guidance for planning the next stage of their child’s learning.</t>
         </is>
       </c>
       <c r="L57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11・12年生が校外での冬季学習合宿に参加し、集中学習、復習、試験対策に取り組みます。</t>
+          <t xml:space="preserve">10年生の保護者の皆様を対象に、DPの科目選択と、お子様の次のステージの学びを計画するためのガイダンスを行います。</t>
         </is>
       </c>
       <c r="M57" t="inlineStr" s="2">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="O57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-21-winter-study-camp-g11-12.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-01-14-g10-parent-info-session-high-school-subject-choi.webp</t>
         </is>
       </c>
       <c r="P57" t="inlineStr" s="2">
@@ -5611,17 +5611,17 @@
     <row r="58">
       <c r="A58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-14-g10-parent-info-session-high-school-subject-choi</t>
+          <t xml:space="preserve">2027-01-22-open-campus</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-14</t>
+          <t xml:space="preserve">2027-01-22</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-14</t>
+          <t xml:space="preserve">2027-01-22</t>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="3">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G58" t="inlineStr" s="2">
@@ -5651,22 +5651,22 @@
       </c>
       <c r="I58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G10 Parent info Session (High School Subject Choice)</t>
+          <t xml:space="preserve">Open Campus</t>
         </is>
       </c>
       <c r="J58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G10保護者向け説明会（高等部科目選択）</t>
+          <t xml:space="preserve">オープンキャンパス</t>
         </is>
       </c>
       <c r="K58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 10 parents are invited to an information session about DP subject choices and guidance for planning the next stage of their child’s learning.</t>
+          <t xml:space="preserve">Any person interested in seeing the daily operation of the school is invited to join a tour of the school during its regular hours.</t>
         </is>
       </c>
       <c r="L58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10年生の保護者の皆様を対象に、DPの科目選択と、お子様の次のステージの学びを計画するためのガイダンスを行います。</t>
+          <t xml:space="preserve">学校の日常の様子にご関心のある方は、通常授業時間中の校内見学にご参加いただけます。</t>
         </is>
       </c>
       <c r="M58" t="inlineStr" s="2">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="O58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-01-14-g10-parent-info-session-high-school-subject-choi.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-01-22-open-campus.webp</t>
         </is>
       </c>
       <c r="P58" t="inlineStr" s="2">
@@ -5708,17 +5708,17 @@
     <row r="59">
       <c r="A59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-22-open-campus</t>
+          <t xml:space="preserve">2027-01-23-alumni-talk</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-22</t>
+          <t xml:space="preserve">2027-01-23</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-22</t>
+          <t xml:space="preserve">2027-01-23</t>
         </is>
       </c>
       <c r="D59" t="inlineStr" s="3">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="E59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F59" t="inlineStr" s="2">
@@ -5748,22 +5748,22 @@
       </c>
       <c r="I59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Open Campus</t>
+          <t xml:space="preserve">Alumni Talk</t>
         </is>
       </c>
       <c r="J59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">オープンキャンパス</t>
+          <t xml:space="preserve">卒業生トーク</t>
         </is>
       </c>
       <c r="K59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Any person interested in seeing the daily operation of the school is invited to join a tour of the school during its regular hours.</t>
+          <t xml:space="preserve">Alumni will share their experiences and advice with students, offering insight into life after School and future pathways.</t>
         </is>
       </c>
       <c r="L59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学校の日常の様子にご関心のある方は、通常授業時間中の校内見学にご参加いただけます。</t>
+          <t xml:space="preserve">卒業生が自身の経験やアドバイスを生徒に伝え、卒業後の生活や将来の進路について話します。</t>
         </is>
       </c>
       <c r="M59" t="inlineStr" s="2">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-01-22-open-campus.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-01-23-alumni-talk.webp</t>
         </is>
       </c>
       <c r="P59" t="inlineStr" s="2">
@@ -5805,17 +5805,17 @@
     <row r="60">
       <c r="A60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-23-alumni-talk</t>
+          <t xml:space="preserve">2027-01-27-natural-disaster-field-trip</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-23</t>
+          <t xml:space="preserve">2027-01-27</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-23</t>
+          <t xml:space="preserve">2027-01-27</t>
         </is>
       </c>
       <c r="D60" t="inlineStr" s="3">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="E60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">ELC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr" s="2">
@@ -5845,22 +5845,22 @@
       </c>
       <c r="I60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Alumni Talk</t>
+          <t xml:space="preserve">Natural Disaster Field Trip</t>
         </is>
       </c>
       <c r="J60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">卒業生トーク</t>
+          <t xml:space="preserve">防災校外学習</t>
         </is>
       </c>
       <c r="K60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Alumni will share their experiences and advice with students, offering insight into life after School and future pathways.</t>
+          <t xml:space="preserve">Students explore disaster preparedness and safety through interactive learning experiences related to natural disasters and emergency response.</t>
         </is>
       </c>
       <c r="L60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">卒業生が自身の経験やアドバイスを生徒に伝え、卒業後の生活や将来の進路について話します。</t>
+          <t xml:space="preserve">自然災害や緊急時の対応に関する体験型学習を通して、防災と安全について学びます。</t>
         </is>
       </c>
       <c r="M60" t="inlineStr" s="2">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="O60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-01-23-alumni-talk.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-01-27-natural-disaster-field-trip.webp</t>
         </is>
       </c>
       <c r="P60" t="inlineStr" s="2">
@@ -5902,17 +5902,17 @@
     <row r="61">
       <c r="A61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-27-natural-disaster-field-trip</t>
+          <t xml:space="preserve">2027-01-30-model-united-nations-event-mun</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-27</t>
+          <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-27</t>
+          <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
       <c r="D61" t="inlineStr" s="3">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="E61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F61" t="inlineStr" s="2">
@@ -5942,22 +5942,22 @@
       </c>
       <c r="I61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Natural Disaster Field Trip</t>
+          <t xml:space="preserve">Model United Nations Event (MUN)</t>
         </is>
       </c>
       <c r="J61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">防災校外学習</t>
+          <t xml:space="preserve">模擬国連（MUN）</t>
         </is>
       </c>
       <c r="K61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students explore disaster preparedness and safety through interactive learning experiences related to natural disasters and emergency response.</t>
+          <t xml:space="preserve">Students will participate in Model United Nations, developing public speaking, research, collaboration, and global awareness through discussion of real-world issues.</t>
         </is>
       </c>
       <c r="L61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">自然災害や緊急時の対応に関する体験型学習を通して、防災と安全について学びます。</t>
+          <t xml:space="preserve">模擬国連に参加し、現実の課題について議論することで、スピーチ力、調査力、協働する力、国際的な意識を育みます。</t>
         </is>
       </c>
       <c r="M61" t="inlineStr" s="2">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="O61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-01-27-natural-disaster-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-01-30-model-united-nations-event-mun.webp</t>
         </is>
       </c>
       <c r="P61" t="inlineStr" s="2">
@@ -5999,17 +5999,17 @@
     <row r="62">
       <c r="A62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-30-model-united-nations-event-mun</t>
+          <t xml:space="preserve">2027-02-01-friendly-volleyball-tournament-internal</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-30</t>
+          <t xml:space="preserve">2027-02-01</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-30</t>
+          <t xml:space="preserve">2027-02-05</t>
         </is>
       </c>
       <c r="D62" t="inlineStr" s="3">
@@ -6039,22 +6039,22 @@
       </c>
       <c r="I62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Model United Nations Event (MUN)</t>
+          <t xml:space="preserve">Friendly Volleyball Tournament (Internal)</t>
         </is>
       </c>
       <c r="J62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">模擬国連（MUN）</t>
+          <t xml:space="preserve">校内バレーボール大会</t>
         </is>
       </c>
       <c r="K62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will participate in Model United Nations, developing public speaking, research, collaboration, and global awareness through discussion of real-world issues.</t>
+          <t xml:space="preserve">Students will take part in a friendly internal volleyball tournament, promoting teamwork, sportsmanship, and school spirit.</t>
         </is>
       </c>
       <c r="L62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">模擬国連に参加し、現実の課題について議論することで、スピーチ力、調査力、協働する力、国際的な意識を育みます。</t>
+          <t xml:space="preserve">校内バレーボール大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
         </is>
       </c>
       <c r="M62" t="inlineStr" s="2">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="O62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-01-30-model-united-nations-event-mun.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-01-friendly-volleyball-tournament-internal.webp</t>
         </is>
       </c>
       <c r="P62" t="inlineStr" s="2">
@@ -6096,7 +6096,7 @@
     <row r="63">
       <c r="A63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-01-friendly-volleyball-tournament-internal</t>
+          <t xml:space="preserve">2027-02-01-concept-con-language</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="3">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr" s="2">
@@ -6136,22 +6136,22 @@
       </c>
       <c r="I63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Friendly Volleyball Tournament (Internal)</t>
+          <t xml:space="preserve">Concept Con (Language)</t>
         </is>
       </c>
       <c r="J63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内バレーボール大会</t>
+          <t xml:space="preserve">コンセプト・コン（言語）</t>
         </is>
       </c>
       <c r="K63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in a friendly internal volleyball tournament, promoting teamwork, sportsmanship, and school spirit.</t>
+          <t xml:space="preserve">Students celebrate language and communication through presentations, performances, and projects that showcase their learning and creativity.</t>
         </is>
       </c>
       <c r="L63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内バレーボール大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
+          <t xml:space="preserve">学びと創造性を示す発表、パフォーマンス、プロジェクトを通して、言語とコミュニケーションを祝います。</t>
         </is>
       </c>
       <c r="M63" t="inlineStr" s="2">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-01-friendly-volleyball-tournament-internal.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-01-concept-con-language.webp</t>
         </is>
       </c>
       <c r="P63" t="inlineStr" s="2">
@@ -6193,17 +6193,17 @@
     <row r="64">
       <c r="A64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-01-concept-con-language</t>
+          <t xml:space="preserve">2027-02-18-career-support-second-career-roundtable-and-care</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-01</t>
+          <t xml:space="preserve">2027-02-18</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-05</t>
+          <t xml:space="preserve">2027-02-18</t>
         </is>
       </c>
       <c r="D64" t="inlineStr" s="3">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G64" t="inlineStr" s="2">
@@ -6233,22 +6233,22 @@
       </c>
       <c r="I64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Concept Con (Language)</t>
+          <t xml:space="preserve">Career Support: Second Career Roundtable and Career Fair</t>
         </is>
       </c>
       <c r="J64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">コンセプト・コン（言語）</t>
+          <t xml:space="preserve">進路支援：第2回キャリア座談会・キャリアフェア</t>
         </is>
       </c>
       <c r="K64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students celebrate language and communication through presentations, performances, and projects that showcase their learning and creativity.</t>
+          <t xml:space="preserve">An informative event where students and parents can learn about IB university admissions, holistic admissions strategies in Japan and abroad, and explore future academic and career opportunities through discussions with experts and representatives.</t>
         </is>
       </c>
       <c r="L64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学びと創造性を示す発表、パフォーマンス、プロジェクトを通して、言語とコミュニケーションを祝います。</t>
+          <t xml:space="preserve">専門家や関係者との対話を通して、生徒と保護者の皆様がIBでの大学入試、国内外の総合型選抜の戦略について学び、将来の進学やキャリアの可能性を探る説明会です。</t>
         </is>
       </c>
       <c r="M64" t="inlineStr" s="2">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="O64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-01-concept-con-language.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-18-career-support-second-career-roundtable-and-care.webp</t>
         </is>
       </c>
       <c r="P64" t="inlineStr" s="2">
@@ -6290,17 +6290,17 @@
     <row r="65">
       <c r="A65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-18-career-support-second-career-roundtable-and-care</t>
+          <t xml:space="preserve">2027-02-19-collective-field-trip</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-18</t>
+          <t xml:space="preserve">2027-02-19</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-18</t>
+          <t xml:space="preserve">2027-02-19</t>
         </is>
       </c>
       <c r="D65" t="inlineStr" s="3">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="E65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G65" t="inlineStr" s="2">
@@ -6330,22 +6330,22 @@
       </c>
       <c r="I65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Career Support: Second Career Roundtable and Career Fair</t>
+          <t xml:space="preserve">Collective Field Trip</t>
         </is>
       </c>
       <c r="J65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">進路支援：第2回キャリア座談会・キャリアフェア</t>
+          <t xml:space="preserve">合同校外学習</t>
         </is>
       </c>
       <c r="K65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An informative event where students and parents can learn about IB university admissions, holistic admissions strategies in Japan and abroad, and explore future academic and career opportunities through discussions with experts and representatives.</t>
+          <t xml:space="preserve">Students participate in an off-campus learning experience that connects classroom learning with real-world exploration and discovery.</t>
         </is>
       </c>
       <c r="L65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">専門家や関係者との対話を通して、生徒と保護者の皆様がIBでの大学入試、国内外の総合型選抜の戦略について学び、将来の進学やキャリアの可能性を探る説明会です。</t>
+          <t xml:space="preserve">校外での学習体験を通して、教室での学びを実社会での探究や発見と結びつけます。</t>
         </is>
       </c>
       <c r="M65" t="inlineStr" s="2">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="O65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-18-career-support-second-career-roundtable-and-care.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-19-collective-field-trip.webp</t>
         </is>
       </c>
       <c r="P65" t="inlineStr" s="2">
@@ -6387,17 +6387,17 @@
     <row r="66">
       <c r="A66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-19-collective-field-trip</t>
+          <t xml:space="preserve">2027-02-22-world-thinking-day</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-19</t>
+          <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-19</t>
+          <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
       <c r="D66" t="inlineStr" s="3">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="E66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr" s="2">
@@ -6427,22 +6427,22 @@
       </c>
       <c r="I66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Collective Field Trip</t>
+          <t xml:space="preserve">World Thinking Day</t>
         </is>
       </c>
       <c r="J66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合同校外学習</t>
+          <t xml:space="preserve">ワールド・シンキング・デー</t>
         </is>
       </c>
       <c r="K66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students participate in an off-campus learning experience that connects classroom learning with real-world exploration and discovery.</t>
+          <t xml:space="preserve">Students learn about cultures, traditions, and global citizenship while celebrating international understanding and connection.</t>
         </is>
       </c>
       <c r="L66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校外での学習体験を通して、教室での学びを実社会での探究や発見と結びつけます。</t>
+          <t xml:space="preserve">国際理解とつながりを祝いながら、さまざまな文化や伝統、地球市民としてのあり方について学びます。</t>
         </is>
       </c>
       <c r="M66" t="inlineStr" s="2">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="O66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-19-collective-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-22-world-thinking-day.webp</t>
         </is>
       </c>
       <c r="P66" t="inlineStr" s="2">
@@ -6484,7 +6484,7 @@
     <row r="67">
       <c r="A67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-22-world-thinking-day</t>
+          <t xml:space="preserve">2027-02-22-secondary-sports-day-rehearsal-1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="3">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="E67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F67" t="inlineStr" s="2">
@@ -6524,22 +6524,22 @@
       </c>
       <c r="I67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">World Thinking Day</t>
+          <t xml:space="preserve">Secondary Sports Day Rehearsal #1</t>
         </is>
       </c>
       <c r="J67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ワールド・シンキング・デー</t>
+          <t xml:space="preserve">中等部運動会リハーサル #1</t>
         </is>
       </c>
       <c r="K67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students learn about cultures, traditions, and global citizenship while celebrating international understanding and connection.</t>
+          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
         </is>
       </c>
       <c r="L67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国際理解とつながりを祝いながら、さまざまな文化や伝統、地球市民としてのあり方について学びます。</t>
+          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
         </is>
       </c>
       <c r="M67" t="inlineStr" s="2">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="O67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-22-world-thinking-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-22-secondary-sports-day-rehearsal-1.webp</t>
         </is>
       </c>
       <c r="P67" t="inlineStr" s="2">
@@ -6581,17 +6581,17 @@
     <row r="68">
       <c r="A68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-22-secondary-sports-day-rehearsal-1</t>
+          <t xml:space="preserve">2027-02-25-primary-sports-day-rehearsal-1</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-22</t>
+          <t xml:space="preserve">2027-02-25</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-22</t>
+          <t xml:space="preserve">2027-02-25</t>
         </is>
       </c>
       <c r="D68" t="inlineStr" s="3">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="E68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F68" t="inlineStr" s="2">
@@ -6621,22 +6621,22 @@
       </c>
       <c r="I68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary Sports Day Rehearsal #1</t>
+          <t xml:space="preserve">Primary Sports Day Rehearsal #1</t>
         </is>
       </c>
       <c r="J68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部運動会リハーサル #1</t>
+          <t xml:space="preserve">小学部運動会リハーサル #1</t>
         </is>
       </c>
       <c r="K68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
+          <t xml:space="preserve">Students begin preparing for Sports Day by practicing events, routines, and teamwork activities.</t>
         </is>
       </c>
       <c r="L68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
+          <t xml:space="preserve">種目、流れ、チームワークの練習を通して、運動会に向けた準備を始めます。</t>
         </is>
       </c>
       <c r="M68" t="inlineStr" s="2">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="O68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-22-secondary-sports-day-rehearsal-1.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-25-primary-sports-day-rehearsal-1.webp</t>
         </is>
       </c>
       <c r="P68" t="inlineStr" s="2">
@@ -6678,17 +6678,17 @@
     <row r="69">
       <c r="A69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-25-primary-sports-day-rehearsal-1</t>
+          <t xml:space="preserve">2027-02-26-parents-morning-2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-25</t>
+          <t xml:space="preserve">2027-02-26</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-25</t>
+          <t xml:space="preserve">2027-02-26</t>
         </is>
       </c>
       <c r="D69" t="inlineStr" s="3">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="E69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G69" t="inlineStr" s="2">
@@ -6718,22 +6718,22 @@
       </c>
       <c r="I69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary Sports Day Rehearsal #1</t>
+          <t xml:space="preserve">Parents Morning #2</t>
         </is>
       </c>
       <c r="J69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小学部運動会リハーサル #1</t>
+          <t xml:space="preserve">朝の授業参観 #2</t>
         </is>
       </c>
       <c r="K69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students begin preparing for Sports Day by practicing events, routines, and teamwork activities.</t>
+          <t xml:space="preserve">ELC and Primary Parents are invited to come and see the lessons in the morning and experience the morning routines with their child.</t>
         </is>
       </c>
       <c r="L69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">種目、流れ、チームワークの練習を通して、運動会に向けた準備を始めます。</t>
+          <t xml:space="preserve">幼稚部・小学部の保護者の皆様をお招きし、朝の授業をご参観いただき、お子様と一緒に朝の日課を体験していただきます。</t>
         </is>
       </c>
       <c r="M69" t="inlineStr" s="2">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="O69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-25-primary-sports-day-rehearsal-1.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-26-parents-morning-2.webp</t>
         </is>
       </c>
       <c r="P69" t="inlineStr" s="2">
@@ -6775,7 +6775,7 @@
     <row r="70">
       <c r="A70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-26-parents-morning-2</t>
+          <t xml:space="preserve">2027-02-26-eagle-talks</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="3">
@@ -6815,22 +6815,22 @@
       </c>
       <c r="I70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parents Morning #2</t>
+          <t xml:space="preserve">Eagle Talks</t>
         </is>
       </c>
       <c r="J70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">朝の授業参観 #2</t>
+          <t xml:space="preserve">イーグル・トーク</t>
         </is>
       </c>
       <c r="K70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC and Primary Parents are invited to come and see the lessons in the morning and experience the morning routines with their child.</t>
+          <t xml:space="preserve">Students share ideas, experiences, and learning through short presentations designed to build confidence, communication, and leadership skills.</t>
         </is>
       </c>
       <c r="L70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部・小学部の保護者の皆様をお招きし、朝の授業をご参観いただき、お子様と一緒に朝の日課を体験していただきます。</t>
+          <t xml:space="preserve">短いプレゼンテーションを通して考えや経験、学びを共有し、自信、コミュニケーション力、リーダーシップを育みます。</t>
         </is>
       </c>
       <c r="M70" t="inlineStr" s="2">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-26-parents-morning-2.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-26-eagle-talks.webp</t>
         </is>
       </c>
       <c r="P70" t="inlineStr" s="2">
@@ -6872,17 +6872,17 @@
     <row r="71">
       <c r="A71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-26-eagle-talks</t>
+          <t xml:space="preserve">2027-03-04-grade-1-2-musical</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-26</t>
+          <t xml:space="preserve">2027-03-04</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-26</t>
+          <t xml:space="preserve">2027-03-05</t>
         </is>
       </c>
       <c r="D71" t="inlineStr" s="3">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="E71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F71" t="inlineStr" s="2">
@@ -6912,22 +6912,22 @@
       </c>
       <c r="I71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Eagle Talks</t>
+          <t xml:space="preserve">Grade 1, 2 Musical</t>
         </is>
       </c>
       <c r="J71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">イーグル・トーク</t>
+          <t xml:space="preserve">1・2年生ミュージカル</t>
         </is>
       </c>
       <c r="K71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students share ideas, experiences, and learning through short presentations designed to build confidence, communication, and leadership skills.</t>
+          <t xml:space="preserve">Students showcase their creativity and confidence through a musical performance featuring songs, acting, and teamwork.</t>
         </is>
       </c>
       <c r="L71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">短いプレゼンテーションを通して考えや経験、学びを共有し、自信、コミュニケーション力、リーダーシップを育みます。</t>
+          <t xml:space="preserve">歌、演技、チームワークによるミュージカルを通して、創造性と自信あふれる姿を披露します。</t>
         </is>
       </c>
       <c r="M71" t="inlineStr" s="2">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="O71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-26-eagle-talks.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-04-grade-1-2-musical.webp</t>
         </is>
       </c>
       <c r="P71" t="inlineStr" s="2">
@@ -6969,12 +6969,12 @@
     <row r="72">
       <c r="A72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-04-grade-1-2-musical</t>
+          <t xml:space="preserve">2027-03-05-higashiyama-zoo-botanical-garden</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-04</t>
+          <t xml:space="preserve">2027-03-05</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="3">
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G72" t="inlineStr" s="2">
@@ -7009,22 +7009,22 @@
       </c>
       <c r="I72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 1, 2 Musical</t>
+          <t xml:space="preserve">Higashiyama Zoo &amp; Botanical Garden</t>
         </is>
       </c>
       <c r="J72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1・2年生ミュージカル</t>
+          <t xml:space="preserve">東山動植物園</t>
         </is>
       </c>
       <c r="K72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students showcase their creativity and confidence through a musical performance featuring songs, acting, and teamwork.</t>
+          <t xml:space="preserve">Grade 7 Science students will visit Higashiyama Zoo and Botanical Gardens to support their learning through observation and real-world examples.</t>
         </is>
       </c>
       <c r="L72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">歌、演技、チームワークによるミュージカルを通して、創造性と自信あふれる姿を披露します。</t>
+          <t xml:space="preserve">7年生が理科の学習の一環として東山動植物園を訪れ、観察や実物を通して学びを深めます。</t>
         </is>
       </c>
       <c r="M72" t="inlineStr" s="2">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="O72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-04-grade-1-2-musical.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-05-higashiyama-zoo-botanical-garden.webp</t>
         </is>
       </c>
       <c r="P72" t="inlineStr" s="2">
@@ -7066,17 +7066,17 @@
     <row r="73">
       <c r="A73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-05-higashiyama-zoo-botanical-garden</t>
+          <t xml:space="preserve">2027-03-06-sat-test-6</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-05</t>
+          <t xml:space="preserve">2027-03-06</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-05</t>
+          <t xml:space="preserve">2027-03-06</t>
         </is>
       </c>
       <c r="D73" t="inlineStr" s="3">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="E73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F73" t="inlineStr" s="2">
@@ -7106,22 +7106,22 @@
       </c>
       <c r="I73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Higashiyama Zoo &amp; Botanical Garden</t>
+          <t xml:space="preserve">SAT Test #6</t>
         </is>
       </c>
       <c r="J73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">東山動植物園</t>
+          <t xml:space="preserve">SAT試験 第6回</t>
         </is>
       </c>
       <c r="K73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 7 Science students will visit Higashiyama Zoo and Botanical Gardens to support their learning through observation and real-world examples.</t>
+          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
         </is>
       </c>
       <c r="L73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7年生が理科の学習の一環として東山動植物園を訪れ、観察や実物を通して学びを深めます。</t>
+          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
         </is>
       </c>
       <c r="M73" t="inlineStr" s="2">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="O73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-05-higashiyama-zoo-botanical-garden.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-06-sat-test-6.webp</t>
         </is>
       </c>
       <c r="P73" t="inlineStr" s="2">
@@ -7163,17 +7163,17 @@
     <row r="74">
       <c r="A74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-06-sat-test-6</t>
+          <t xml:space="preserve">2027-03-09-primary-sports-day-rehearsal-2</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-06</t>
+          <t xml:space="preserve">2027-03-09</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-06</t>
+          <t xml:space="preserve">2027-03-09</t>
         </is>
       </c>
       <c r="D74" t="inlineStr" s="3">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="E74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F74" t="inlineStr" s="2">
@@ -7203,22 +7203,22 @@
       </c>
       <c r="I74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT Test #6</t>
+          <t xml:space="preserve">Primary Sports Day Rehearsal #2</t>
         </is>
       </c>
       <c r="J74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT試験 第6回</t>
+          <t xml:space="preserve">小学部運動会リハーサル #2</t>
         </is>
       </c>
       <c r="K74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
+          <t xml:space="preserve">Students continue building skills and confidence as they prepare for Sports Day events and activities.</t>
         </is>
       </c>
       <c r="L74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
+          <t xml:space="preserve">運動会の種目や活動に向けて準備を進めながら、技能と自信をさらに高めます。</t>
         </is>
       </c>
       <c r="M74" t="inlineStr" s="2">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="O74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-06-sat-test-6.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-09-primary-sports-day-rehearsal-2.webp</t>
         </is>
       </c>
       <c r="P74" t="inlineStr" s="2">
@@ -7260,17 +7260,17 @@
     <row r="75">
       <c r="A75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-09-primary-sports-day-rehearsal-2</t>
+          <t xml:space="preserve">2027-03-12-secondary-sports-day-rehearsal-2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-09</t>
+          <t xml:space="preserve">2027-03-12</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-09</t>
+          <t xml:space="preserve">2027-03-12</t>
         </is>
       </c>
       <c r="D75" t="inlineStr" s="3">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="E75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F75" t="inlineStr" s="2">
@@ -7300,22 +7300,22 @@
       </c>
       <c r="I75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary Sports Day Rehearsal #2</t>
+          <t xml:space="preserve">Secondary Sports Day Rehearsal #2</t>
         </is>
       </c>
       <c r="J75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小学部運動会リハーサル #2</t>
+          <t xml:space="preserve">中等部運動会リハーサル #2</t>
         </is>
       </c>
       <c r="K75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students continue building skills and confidence as they prepare for Sports Day events and activities.</t>
+          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
         </is>
       </c>
       <c r="L75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会の種目や活動に向けて準備を進めながら、技能と自信をさらに高めます。</t>
+          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
         </is>
       </c>
       <c r="M75" t="inlineStr" s="2">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="O75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-09-primary-sports-day-rehearsal-2.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-12-secondary-sports-day-rehearsal-2.webp</t>
         </is>
       </c>
       <c r="P75" t="inlineStr" s="2">
@@ -7357,17 +7357,17 @@
     <row r="76">
       <c r="A76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-12-secondary-sports-day-rehearsal-2</t>
+          <t xml:space="preserve">2027-03-18-japanese-culture-day</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-12</t>
+          <t xml:space="preserve">2027-03-18</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-12</t>
+          <t xml:space="preserve">2027-03-18</t>
         </is>
       </c>
       <c r="D76" t="inlineStr" s="3">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G76" t="inlineStr" s="2">
@@ -7397,22 +7397,22 @@
       </c>
       <c r="I76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary Sports Day Rehearsal #2</t>
+          <t xml:space="preserve">Japanese Culture Day</t>
         </is>
       </c>
       <c r="J76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部運動会リハーサル #2</t>
+          <t xml:space="preserve">日本文化デー</t>
         </is>
       </c>
       <c r="K76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
+          <t xml:space="preserve">Students will deepen their understanding and appreciation of Japanese culture through a variety of interactive activities with school community.</t>
         </is>
       </c>
       <c r="L76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
+          <t xml:space="preserve">学校コミュニティとともにさまざまな体験型の活動に取り組み、日本文化への理解と関心を深めます。</t>
         </is>
       </c>
       <c r="M76" t="inlineStr" s="2">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="O76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-12-secondary-sports-day-rehearsal-2.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-18-japanese-culture-day.webp</t>
         </is>
       </c>
       <c r="P76" t="inlineStr" s="2">
@@ -7454,17 +7454,17 @@
     <row r="77">
       <c r="A77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-18-japanese-culture-day</t>
+          <t xml:space="preserve">2027-03-19-eagle-bucks-store</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-18</t>
+          <t xml:space="preserve">2027-03-19</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-18</t>
+          <t xml:space="preserve">2027-03-19</t>
         </is>
       </c>
       <c r="D77" t="inlineStr" s="3">
@@ -7474,12 +7474,12 @@
       </c>
       <c r="E77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G77" t="inlineStr" s="2">
@@ -7494,22 +7494,22 @@
       </c>
       <c r="I77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Japanese Culture Day</t>
+          <t xml:space="preserve">Eagle Bucks Store</t>
         </is>
       </c>
       <c r="J77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">日本文化デー</t>
+          <t xml:space="preserve">イーグルバックス・ストア</t>
         </is>
       </c>
       <c r="K77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will deepen their understanding and appreciation of Japanese culture through a variety of interactive activities with school community.</t>
+          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
         </is>
       </c>
       <c r="L77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学校コミュニティとともにさまざまな体験型の活動に取り組み、日本文化への理解と関心を深めます。</t>
+          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
         </is>
       </c>
       <c r="M77" t="inlineStr" s="2">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="O77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-18-japanese-culture-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-19-eagle-bucks-store.webp</t>
         </is>
       </c>
       <c r="P77" t="inlineStr" s="2">
@@ -7551,7 +7551,7 @@
     <row r="78">
       <c r="A78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-19-eagle-bucks-store</t>
+          <t xml:space="preserve">2027-03-19-tea-party-pta-for-all</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="3">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="E78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">PTA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G78" t="inlineStr" s="2">
@@ -7591,22 +7591,22 @@
       </c>
       <c r="I78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Eagle Bucks Store</t>
+          <t xml:space="preserve">Tea Party / PTA for all</t>
         </is>
       </c>
       <c r="J78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">イーグルバックス・ストア</t>
+          <t xml:space="preserve">PTAティーパーティー（どなたでも参加できます）</t>
         </is>
       </c>
       <c r="K78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
+          <t xml:space="preserve">A social gathering organized by the PTA and Community Club where staff and students are welcome to enjoy a variety of teas, snacks, and friendly conversation together.</t>
         </is>
       </c>
       <c r="L78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
+          <t xml:space="preserve">PTAとコミュニティクラブが主催する交流会です。教職員や生徒も参加でき、さまざまなお茶や軽食、和やかな会話を楽しめます。</t>
         </is>
       </c>
       <c r="M78" t="inlineStr" s="2">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="O78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-19-eagle-bucks-store.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-19-tea-party-pta-for-all.webp</t>
         </is>
       </c>
       <c r="P78" t="inlineStr" s="2">
@@ -7648,7 +7648,7 @@
     <row r="79">
       <c r="A79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-19-tea-party-pta-for-all</t>
+          <t xml:space="preserve">2027-03-19-end-of-term-2-activity-g9-12</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="3">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="C79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-19</t>
+          <t xml:space="preserve">2027-03-20</t>
         </is>
       </c>
       <c r="D79" t="inlineStr" s="3">
@@ -7668,12 +7668,12 @@
       </c>
       <c r="E79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTA</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G79" t="inlineStr" s="2">
@@ -7688,22 +7688,22 @@
       </c>
       <c r="I79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Tea Party / PTA for all</t>
+          <t xml:space="preserve">End of Term 2 Activity: G9-12</t>
         </is>
       </c>
       <c r="J79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTAティーパーティー（どなたでも参加できます）</t>
+          <t xml:space="preserve">第2学期末行事：G9–12</t>
         </is>
       </c>
       <c r="K79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A social gathering organized by the PTA and Community Club where staff and students are welcome to enjoy a variety of teas, snacks, and friendly conversation together.</t>
+          <t xml:space="preserve">Students will take part in an off-campus day trip activity to celebrate the end of Term 2.</t>
         </is>
       </c>
       <c r="L79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTAとコミュニティクラブが主催する交流会です。教職員や生徒も参加でき、さまざまなお茶や軽食、和やかな会話を楽しめます。</t>
+          <t xml:space="preserve">第2学期の終わりを祝い、校外への日帰り活動に参加します。</t>
         </is>
       </c>
       <c r="M79" t="inlineStr" s="2">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="O79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-19-tea-party-pta-for-all.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-19-end-of-term-2-activity-g9-12.webp</t>
         </is>
       </c>
       <c r="P79" t="inlineStr" s="2">
@@ -7745,17 +7745,17 @@
     <row r="80">
       <c r="A80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-19-end-of-term-2-activity-g9-12</t>
+          <t xml:space="preserve">2027-03-20-end-of-term-2-activity-g6-8</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-19</t>
+          <t xml:space="preserve">2027-03-20</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-20</t>
+          <t xml:space="preserve">2027-03-21</t>
         </is>
       </c>
       <c r="D80" t="inlineStr" s="3">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="E80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F80" t="inlineStr" s="2">
@@ -7785,22 +7785,22 @@
       </c>
       <c r="I80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">End of Term 2 Activity: G9-12</t>
+          <t xml:space="preserve">End of Term 2 Activity: G6-8</t>
         </is>
       </c>
       <c r="J80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第2学期末行事：G9–12</t>
+          <t xml:space="preserve">第2学期末行事：G6–8</t>
         </is>
       </c>
       <c r="K80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in an off-campus day trip activity to celebrate the end of Term 2.</t>
+          <t xml:space="preserve">Students will take part in an overnight camp at an off-campus camping facility to celebrate the end of Term 2.</t>
         </is>
       </c>
       <c r="L80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第2学期の終わりを祝い、校外への日帰り活動に参加します。</t>
+          <t xml:space="preserve">第2学期の終わりを祝い、校外のキャンプ施設での一泊キャンプに参加します。</t>
         </is>
       </c>
       <c r="M80" t="inlineStr" s="2">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="O80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-19-end-of-term-2-activity-g9-12.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-20-end-of-term-2-activity-g6-8.webp</t>
         </is>
       </c>
       <c r="P80" t="inlineStr" s="2">
@@ -7842,17 +7842,17 @@
     <row r="81">
       <c r="A81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-20-end-of-term-2-activity-g6-8</t>
+          <t xml:space="preserve">2027-03-30-parent-teacher-conferences</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-20</t>
+          <t xml:space="preserve">2027-03-30</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-21</t>
+          <t xml:space="preserve">2027-03-30</t>
         </is>
       </c>
       <c r="D81" t="inlineStr" s="3">
@@ -7862,17 +7862,17 @@
       </c>
       <c r="E81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="H81" t="inlineStr" s="2">
@@ -7882,22 +7882,22 @@
       </c>
       <c r="I81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">End of Term 2 Activity: G6-8</t>
+          <t xml:space="preserve">Parent Teacher Conferences</t>
         </is>
       </c>
       <c r="J81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第2学期末行事：G6–8</t>
+          <t xml:space="preserve">保護者面談</t>
         </is>
       </c>
       <c r="K81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in an overnight camp at an off-campus camping facility to celebrate the end of Term 2.</t>
+          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on this day.</t>
         </is>
       </c>
       <c r="L81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第2学期の終わりを祝い、校外のキャンプ施設での一泊キャンプに参加します。</t>
+          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。当日、生徒は登校しません。</t>
         </is>
       </c>
       <c r="M81" t="inlineStr" s="2">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-20-end-of-term-2-activity-g6-8.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-30-parent-teacher-conferences.webp</t>
         </is>
       </c>
       <c r="P81" t="inlineStr" s="2">
@@ -7939,17 +7939,17 @@
     <row r="82">
       <c r="A82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-30-parent-teacher-conferences</t>
+          <t xml:space="preserve">2027-03-31-secondary-sports-day-rehearsal-3</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-30</t>
+          <t xml:space="preserve">2027-03-31</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-30</t>
+          <t xml:space="preserve">2027-03-31</t>
         </is>
       </c>
       <c r="D82" t="inlineStr" s="3">
@@ -7959,17 +7959,17 @@
       </c>
       <c r="E82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H82" t="inlineStr" s="2">
@@ -7979,22 +7979,22 @@
       </c>
       <c r="I82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parent Teacher Conferences</t>
+          <t xml:space="preserve">Secondary Sports Day Rehearsal #3</t>
         </is>
       </c>
       <c r="J82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者面談</t>
+          <t xml:space="preserve">中等部運動会リハーサル #3</t>
         </is>
       </c>
       <c r="K82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on this day.</t>
+          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
         </is>
       </c>
       <c r="L82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。当日、生徒は登校しません。</t>
+          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
         </is>
       </c>
       <c r="M82" t="inlineStr" s="2">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="O82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-30-parent-teacher-conferences.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-31-secondary-sports-day-rehearsal-3.webp</t>
         </is>
       </c>
       <c r="P82" t="inlineStr" s="2">
@@ -8036,17 +8036,17 @@
     <row r="83">
       <c r="A83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-31-secondary-sports-day-rehearsal-3</t>
+          <t xml:space="preserve">2027-04-01-primary-sports-day-rehearsal-3</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-31</t>
+          <t xml:space="preserve">2027-04-01</t>
         </is>
       </c>
       <c r="C83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-31</t>
+          <t xml:space="preserve">2027-04-01</t>
         </is>
       </c>
       <c r="D83" t="inlineStr" s="3">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="E83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F83" t="inlineStr" s="2">
@@ -8076,22 +8076,22 @@
       </c>
       <c r="I83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary Sports Day Rehearsal #3</t>
+          <t xml:space="preserve">Primary Sports Day Rehearsal #3</t>
         </is>
       </c>
       <c r="J83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部運動会リハーサル #3</t>
+          <t xml:space="preserve">小学部運動会リハーサル #3</t>
         </is>
       </c>
       <c r="K83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
+          <t xml:space="preserve">The final rehearsal provides students with an opportunity to practice events and ensure they are ready for Sports Day.</t>
         </is>
       </c>
       <c r="L83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
+          <t xml:space="preserve">最終リハーサルで各種目を練習し、運動会当日に向けて準備を整えます。</t>
         </is>
       </c>
       <c r="M83" t="inlineStr" s="2">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="O83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-31-secondary-sports-day-rehearsal-3.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-01-primary-sports-day-rehearsal-3.webp</t>
         </is>
       </c>
       <c r="P83" t="inlineStr" s="2">
@@ -8133,17 +8133,17 @@
     <row r="84">
       <c r="A84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-01-primary-sports-day-rehearsal-3</t>
+          <t xml:space="preserve">2027-04-03-sports-day</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-01</t>
+          <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
       <c r="C84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-01</t>
+          <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
       <c r="D84" t="inlineStr" s="3">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="E84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G84" t="inlineStr" s="2">
@@ -8173,22 +8173,22 @@
       </c>
       <c r="I84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary Sports Day Rehearsal #3</t>
+          <t xml:space="preserve">Sports Day</t>
         </is>
       </c>
       <c r="J84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小学部運動会リハーサル #3</t>
+          <t xml:space="preserve">運動会</t>
         </is>
       </c>
       <c r="K84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The final rehearsal provides students with an opportunity to practice events and ensure they are ready for Sports Day.</t>
+          <t xml:space="preserve">Students will take part in Sports Day activities, participating in team games, athletic challenges, and school spirit events.</t>
         </is>
       </c>
       <c r="L84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">最終リハーサルで各種目を練習し、運動会当日に向けて準備を整えます。</t>
+          <t xml:space="preserve">運動会に参加し、チームゲーム、運動競技、応援などの行事に取り組みます。</t>
         </is>
       </c>
       <c r="M84" t="inlineStr" s="2">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="O84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-01-primary-sports-day-rehearsal-3.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-03-sports-day.webp</t>
         </is>
       </c>
       <c r="P84" t="inlineStr" s="2">
@@ -8230,7 +8230,7 @@
     <row r="85">
       <c r="A85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-03-sports-day</t>
+          <t xml:space="preserve">2027-04-03-primary-sports-day-2027</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="3">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="E85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F85" t="inlineStr" s="2">
@@ -8270,22 +8270,22 @@
       </c>
       <c r="I85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sports Day</t>
+          <t xml:space="preserve">Primary Sports Day 2027</t>
         </is>
       </c>
       <c r="J85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会</t>
+          <t xml:space="preserve">小学部運動会 2027</t>
         </is>
       </c>
       <c r="K85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in Sports Day activities, participating in team games, athletic challenges, and school spirit events.</t>
+          <t xml:space="preserve">Students participate in a day of fun, fitness, and friendly competition while demonstrating teamwork, perseverance, and sportsmanship.</t>
         </is>
       </c>
       <c r="L85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会に参加し、チームゲーム、運動競技、応援などの行事に取り組みます。</t>
+          <t xml:space="preserve">チームワーク、粘り強さ、スポーツマンシップを発揮しながら、楽しく体を動かし、仲間と競い合う一日を過ごします。</t>
         </is>
       </c>
       <c r="M85" t="inlineStr" s="2">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="O85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-03-sports-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-03-primary-sports-day-2027.webp</t>
         </is>
       </c>
       <c r="P85" t="inlineStr" s="2">
@@ -8327,17 +8327,17 @@
     <row r="86">
       <c r="A86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-03-primary-sports-day-2027</t>
+          <t xml:space="preserve">2027-04-15-world-art-day</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-03</t>
+          <t xml:space="preserve">2027-04-15</t>
         </is>
       </c>
       <c r="C86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-03</t>
+          <t xml:space="preserve">2027-04-15</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="3">
@@ -8347,7 +8347,7 @@
       </c>
       <c r="E86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr" s="2">
@@ -8367,22 +8367,22 @@
       </c>
       <c r="I86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary Sports Day 2027</t>
+          <t xml:space="preserve">World Art Day</t>
         </is>
       </c>
       <c r="J86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小学部運動会 2027</t>
+          <t xml:space="preserve">ワールド・アート・デー</t>
         </is>
       </c>
       <c r="K86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students participate in a day of fun, fitness, and friendly competition while demonstrating teamwork, perseverance, and sportsmanship.</t>
+          <t xml:space="preserve">Students celebrate creativity through art activities, exhibitions, and opportunities to explore different artistic styles and cultures.</t>
         </is>
       </c>
       <c r="L86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">チームワーク、粘り強さ、スポーツマンシップを発揮しながら、楽しく体を動かし、仲間と競い合う一日を過ごします。</t>
+          <t xml:space="preserve">アート活動や展示を通して創造性を祝い、さまざまな芸術様式や文化に触れます。</t>
         </is>
       </c>
       <c r="M86" t="inlineStr" s="2">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="O86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-03-primary-sports-day-2027.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-15-world-art-day.webp</t>
         </is>
       </c>
       <c r="P86" t="inlineStr" s="2">
@@ -8424,17 +8424,17 @@
     <row r="87">
       <c r="A87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-15-world-art-day</t>
+          <t xml:space="preserve">2027-04-16-foundation-field-trip</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-15</t>
+          <t xml:space="preserve">2027-04-16</t>
         </is>
       </c>
       <c r="C87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-15</t>
+          <t xml:space="preserve">2027-04-16</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="3">
@@ -8444,7 +8444,7 @@
       </c>
       <c r="E87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F87" t="inlineStr" s="2">
@@ -8464,22 +8464,22 @@
       </c>
       <c r="I87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">World Art Day</t>
+          <t xml:space="preserve">Foundation Field Trip</t>
         </is>
       </c>
       <c r="J87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ワールド・アート・デー</t>
+          <t xml:space="preserve">ファウンデーション校外学習</t>
         </is>
       </c>
       <c r="K87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students celebrate creativity through art activities, exhibitions, and opportunities to explore different artistic styles and cultures.</t>
+          <t xml:space="preserve">Our youngest learners will enjoy an age-appropriate educational excursion that supports classroom learning through hands-on experiences.</t>
         </is>
       </c>
       <c r="L87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">アート活動や展示を通して創造性を祝い、さまざまな芸術様式や文化に触れます。</t>
+          <t xml:space="preserve">年少の子どもたちが、年齢に合った校外学習に出かけ、体験を通して教室での学びを深めます。</t>
         </is>
       </c>
       <c r="M87" t="inlineStr" s="2">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="O87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-15-world-art-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-16-foundation-field-trip.webp</t>
         </is>
       </c>
       <c r="P87" t="inlineStr" s="2">
@@ -8521,17 +8521,17 @@
     <row r="88">
       <c r="A88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-16-foundation-field-trip</t>
+          <t xml:space="preserve">2027-04-21-hackathon-hour-of-code</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-16</t>
+          <t xml:space="preserve">2027-04-21</t>
         </is>
       </c>
       <c r="C88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-16</t>
+          <t xml:space="preserve">2027-04-21</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="3">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="E88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G88" t="inlineStr" s="2">
@@ -8561,22 +8561,22 @@
       </c>
       <c r="I88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Foundation Field Trip</t>
+          <t xml:space="preserve">Hackathon (Hour of Code)</t>
         </is>
       </c>
       <c r="J88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ファウンデーション校外学習</t>
+          <t xml:space="preserve">ハッカソン（Hour of Code）</t>
         </is>
       </c>
       <c r="K88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Our youngest learners will enjoy an age-appropriate educational excursion that supports classroom learning through hands-on experiences.</t>
+          <t xml:space="preserve">Students will take part in an engaging Hour of Code challenge, using creativity and problem-solving skills to build simple coding projects. This event encourages computational thinking, teamwork, and confidence in technology in a fun and supportive environment.</t>
         </is>
       </c>
       <c r="L88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">年少の子どもたちが、年齢に合った校外学習に出かけ、体験を通して教室での学びを深めます。</t>
+          <t xml:space="preserve">Hour of Codeチャレンジに参加し、創造性と問題解決力を生かして簡単なプログラミング作品を作ります。楽しく支え合う環境の中で、コンピュテーショナル・シンキング、チームワーク、テクノロジーへの自信を育みます。</t>
         </is>
       </c>
       <c r="M88" t="inlineStr" s="2">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="O88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-16-foundation-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-21-hackathon-hour-of-code.webp</t>
         </is>
       </c>
       <c r="P88" t="inlineStr" s="2">
@@ -8618,17 +8618,17 @@
     <row r="89">
       <c r="A89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-21-hackathon-hour-of-code</t>
+          <t xml:space="preserve">2027-04-22-biology-ia-prep-field-trip-shore-ecosystem</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-21</t>
+          <t xml:space="preserve">2027-04-22</t>
         </is>
       </c>
       <c r="C89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-21</t>
+          <t xml:space="preserve">2027-04-22</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="3">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="E89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F89" t="inlineStr" s="2">
@@ -8658,22 +8658,22 @@
       </c>
       <c r="I89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hackathon (Hour of Code)</t>
+          <t xml:space="preserve">Biology IA Prep. Field Trip: Shore Ecosystem</t>
         </is>
       </c>
       <c r="J89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ハッカソン（Hour of Code）</t>
+          <t xml:space="preserve">生物IA準備校外学習：海岸生態系調査</t>
         </is>
       </c>
       <c r="K89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in an engaging Hour of Code challenge, using creativity and problem-solving skills to build simple coding projects. This event encourages computational thinking, teamwork, and confidence in technology in a fun and supportive environment.</t>
+          <t xml:space="preserve">Grade 11 and 12 Biology students will visit a shore ecosystem to prepare for their Biology Internal Assessment by collecting fieldwork data and practicing research methods.</t>
         </is>
       </c>
       <c r="L89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hour of Codeチャレンジに参加し、創造性と問題解決力を生かして簡単なプログラミング作品を作ります。楽しく支え合う環境の中で、コンピュテーショナル・シンキング、チームワーク、テクノロジーへの自信を育みます。</t>
+          <t xml:space="preserve">11・12年生の生物履修者が海岸の生態系を訪れ、フィールドワークでのデータ収集や研究手法の練習を通して、生物の内部評価（IA）に向けた準備を行います。</t>
         </is>
       </c>
       <c r="M89" t="inlineStr" s="2">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="O89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-21-hackathon-hour-of-code.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-22-biology-ia-prep-field-trip-shore-ecosystem.webp</t>
         </is>
       </c>
       <c r="P89" t="inlineStr" s="2">
@@ -8715,17 +8715,17 @@
     <row r="90">
       <c r="A90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-22-biology-ia-prep-field-trip-shore-ecosystem</t>
+          <t xml:space="preserve">2027-04-23-g12-celebration</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-22</t>
+          <t xml:space="preserve">2027-04-23</t>
         </is>
       </c>
       <c r="C90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-22</t>
+          <t xml:space="preserve">2027-04-23</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="3">
@@ -8755,22 +8755,22 @@
       </c>
       <c r="I90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Biology IA Prep. Field Trip: Shore Ecosystem</t>
+          <t xml:space="preserve">G12 Celebration</t>
         </is>
       </c>
       <c r="J90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">生物IA準備校外学習：海岸生態系調査</t>
+          <t xml:space="preserve">G12修了記念イベント</t>
         </is>
       </c>
       <c r="K90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 11 and 12 Biology students will visit a shore ecosystem to prepare for their Biology Internal Assessment by collecting fieldwork data and practicing research methods.</t>
+          <t xml:space="preserve">Grade 12 students will take part in a Graduation Walk as the school community celebrates them ahead of graduation.</t>
         </is>
       </c>
       <c r="L90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11・12年生の生物履修者が海岸の生態系を訪れ、フィールドワークでのデータ収集や研究手法の練習を通して、生物の内部評価（IA）に向けた準備を行います。</t>
+          <t xml:space="preserve">卒業を前に、12年生がグラデュエーション・ウォークに参加し、学校コミュニティ全体でお祝いします。</t>
         </is>
       </c>
       <c r="M90" t="inlineStr" s="2">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="O90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-22-biology-ia-prep-field-trip-shore-ecosystem.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-23-g12-celebration.webp</t>
         </is>
       </c>
       <c r="P90" t="inlineStr" s="2">
@@ -8812,17 +8812,17 @@
     <row r="91">
       <c r="A91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-23-g12-celebration</t>
+          <t xml:space="preserve">2027-04-26-grade-4-5-camping-trip</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-23</t>
+          <t xml:space="preserve">2027-04-26</t>
         </is>
       </c>
       <c r="C91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-23</t>
+          <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="3">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="E91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F91" t="inlineStr" s="2">
@@ -8852,22 +8852,22 @@
       </c>
       <c r="I91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G12 Celebration</t>
+          <t xml:space="preserve">Grade 4, 5 Camping Trip</t>
         </is>
       </c>
       <c r="J91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G12修了記念イベント</t>
+          <t xml:space="preserve">4・5年生キャンプ</t>
         </is>
       </c>
       <c r="K91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 12 students will take part in a Graduation Walk as the school community celebrates them ahead of graduation.</t>
+          <t xml:space="preserve">Students enjoy an outdoor learning experience that promotes independence, teamwork, resilience, and a connection with nature.</t>
         </is>
       </c>
       <c r="L91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">卒業を前に、12年生がグラデュエーション・ウォークに参加し、学校コミュニティ全体でお祝いします。</t>
+          <t xml:space="preserve">自立心、チームワーク、たくましさ、自然とのつながりを育む野外学習を楽しみます。</t>
         </is>
       </c>
       <c r="M91" t="inlineStr" s="2">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="O91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-23-g12-celebration.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-26-grade-4-5-camping-trip.webp</t>
         </is>
       </c>
       <c r="P91" t="inlineStr" s="2">
@@ -8909,12 +8909,12 @@
     <row r="92">
       <c r="A92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-26-grade-4-5-camping-trip</t>
+          <t xml:space="preserve">2027-04-27-choir-and-orchestra-concert</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-26</t>
+          <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
       <c r="C92" t="inlineStr" s="3">
@@ -8929,12 +8929,12 @@
       </c>
       <c r="E92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G92" t="inlineStr" s="2">
@@ -8949,22 +8949,22 @@
       </c>
       <c r="I92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 4, 5 Camping Trip</t>
+          <t xml:space="preserve">Choir and Orchestra Concert</t>
         </is>
       </c>
       <c r="J92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4・5年生キャンプ</t>
+          <t xml:space="preserve">合唱・オーケストラコンサート</t>
         </is>
       </c>
       <c r="K92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students enjoy an outdoor learning experience that promotes independence, teamwork, resilience, and a connection with nature.</t>
+          <t xml:space="preserve">Choir class and orchestra club will perform the music repertoire they have been rehearsing for an audience of family, peers and teachers.</t>
         </is>
       </c>
       <c r="L92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">自立心、チームワーク、たくましさ、自然とのつながりを育む野外学習を楽しみます。</t>
+          <t xml:space="preserve">合唱クラスとオーケストラクラブが、練習を重ねてきた曲目をご家族、友人、教員の前で演奏します。</t>
         </is>
       </c>
       <c r="M92" t="inlineStr" s="2">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="O92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-26-grade-4-5-camping-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-27-choir-and-orchestra-concert.webp</t>
         </is>
       </c>
       <c r="P92" t="inlineStr" s="2">
@@ -9006,17 +9006,17 @@
     <row r="93">
       <c r="A93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-27-choir-and-orchestra-concert</t>
+          <t xml:space="preserve">2027-04-30-science-fair</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-27</t>
+          <t xml:space="preserve">2027-04-30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-27</t>
+          <t xml:space="preserve">2027-04-30</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="3">
@@ -9046,22 +9046,22 @@
       </c>
       <c r="I93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choir and Orchestra Concert</t>
+          <t xml:space="preserve">Science Fair</t>
         </is>
       </c>
       <c r="J93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合唱・オーケストラコンサート</t>
+          <t xml:space="preserve">サイエンスフェア</t>
         </is>
       </c>
       <c r="K93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choir class and orchestra club will perform the music repertoire they have been rehearsing for an audience of family, peers and teachers.</t>
+          <t xml:space="preserve">Students will share their science projects and investigations with the school community, showcasing their research, creativity, and scientific thinking.</t>
         </is>
       </c>
       <c r="L93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合唱クラスとオーケストラクラブが、練習を重ねてきた曲目をご家族、友人、教員の前で演奏します。</t>
+          <t xml:space="preserve">理科のプロジェクトや探究の成果を学校コミュニティに発表し、研究、創造性、科学的思考を披露します。</t>
         </is>
       </c>
       <c r="M93" t="inlineStr" s="2">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="O93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-27-choir-and-orchestra-concert.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-30-science-fair.webp</t>
         </is>
       </c>
       <c r="P93" t="inlineStr" s="2">
@@ -9103,17 +9103,17 @@
     <row r="94">
       <c r="A94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-30-science-fair</t>
+          <t xml:space="preserve">2027-05-17-friendly-basketball-tournament-internal</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-30</t>
+          <t xml:space="preserve">2027-05-17</t>
         </is>
       </c>
       <c r="C94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-30</t>
+          <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="3">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="F94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G94" t="inlineStr" s="2">
@@ -9143,22 +9143,22 @@
       </c>
       <c r="I94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Science Fair</t>
+          <t xml:space="preserve">Friendly Basketball Tournament (Internal)</t>
         </is>
       </c>
       <c r="J94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">サイエンスフェア</t>
+          <t xml:space="preserve">校内バスケットボール大会</t>
         </is>
       </c>
       <c r="K94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will share their science projects and investigations with the school community, showcasing their research, creativity, and scientific thinking.</t>
+          <t xml:space="preserve">Students will take part in a friendly internal basketball tournament, promoting teamwork, sportsmanship, and school spirit.</t>
         </is>
       </c>
       <c r="L94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">理科のプロジェクトや探究の成果を学校コミュニティに発表し、研究、創造性、科学的思考を披露します。</t>
+          <t xml:space="preserve">校内バスケットボール大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
         </is>
       </c>
       <c r="M94" t="inlineStr" s="2">
@@ -9173,7 +9173,7 @@
       </c>
       <c r="O94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-30-science-fair.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-17-friendly-basketball-tournament-internal.webp</t>
         </is>
       </c>
       <c r="P94" t="inlineStr" s="2">
@@ -9200,17 +9200,17 @@
     <row r="95">
       <c r="A95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-17-friendly-basketball-tournament-internal</t>
+          <t xml:space="preserve">2027-05-19-entrepreneurs-day</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-17</t>
+          <t xml:space="preserve">2027-05-19</t>
         </is>
       </c>
       <c r="C95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-21</t>
+          <t xml:space="preserve">2027-05-20</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="3">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="E95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G95" t="inlineStr" s="2">
@@ -9240,22 +9240,22 @@
       </c>
       <c r="I95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Friendly Basketball Tournament (Internal)</t>
+          <t xml:space="preserve">Entrepreneurs Day</t>
         </is>
       </c>
       <c r="J95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内バスケットボール大会</t>
+          <t xml:space="preserve">アントレプレナーシップ・デー</t>
         </is>
       </c>
       <c r="K95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in a friendly internal basketball tournament, promoting teamwork, sportsmanship, and school spirit.</t>
+          <t xml:space="preserve">Students develop and showcase business ideas while learning about creativity, financial literacy, problem-solving, and entrepreneurship.</t>
         </is>
       </c>
       <c r="L95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内バスケットボール大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
+          <t xml:space="preserve">創造性、金融リテラシー、問題解決、起業家精神について学びながら、ビジネスのアイデアを考え、発表します。</t>
         </is>
       </c>
       <c r="M95" t="inlineStr" s="2">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="O95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-17-friendly-basketball-tournament-internal.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-19-entrepreneurs-day.webp</t>
         </is>
       </c>
       <c r="P95" t="inlineStr" s="2">
@@ -9297,17 +9297,17 @@
     <row r="96">
       <c r="A96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-19-entrepreneurs-day</t>
+          <t xml:space="preserve">2027-05-21-collective-field-trip</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-19</t>
+          <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
       <c r="C96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-20</t>
+          <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="3">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="F96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G96" t="inlineStr" s="2">
@@ -9337,22 +9337,22 @@
       </c>
       <c r="I96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Entrepreneurs Day</t>
+          <t xml:space="preserve">Collective Field Trip</t>
         </is>
       </c>
       <c r="J96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">アントレプレナーシップ・デー</t>
+          <t xml:space="preserve">合同校外学習</t>
         </is>
       </c>
       <c r="K96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students develop and showcase business ideas while learning about creativity, financial literacy, problem-solving, and entrepreneurship.</t>
+          <t xml:space="preserve">Students participate in a shared educational experience that promotes collaboration, inquiry, and real-world learning.</t>
         </is>
       </c>
       <c r="L96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">創造性、金融リテラシー、問題解決、起業家精神について学びながら、ビジネスのアイデアを考え、発表します。</t>
+          <t xml:space="preserve">協働、探究、実社会での学びを促す合同の学習体験に参加します。</t>
         </is>
       </c>
       <c r="M96" t="inlineStr" s="2">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="O96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-19-entrepreneurs-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-21-collective-field-trip.webp</t>
         </is>
       </c>
       <c r="P96" t="inlineStr" s="2">
@@ -9394,17 +9394,17 @@
     <row r="97">
       <c r="A97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-21-collective-field-trip</t>
+          <t xml:space="preserve">2027-05-22-saturday-school-last-day-event</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-21</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="C97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-21</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="3">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="E97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F97" t="inlineStr" s="2">
@@ -9434,22 +9434,22 @@
       </c>
       <c r="I97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Collective Field Trip</t>
+          <t xml:space="preserve">Saturday School Last Day Event</t>
         </is>
       </c>
       <c r="J97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合同校外学習</t>
+          <t xml:space="preserve">土曜校最終日イベント</t>
         </is>
       </c>
       <c r="K97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students participate in a shared educational experience that promotes collaboration, inquiry, and real-world learning.</t>
+          <t xml:space="preserve">Students will take part in a relaxed final Saturday School session, with leisure activities at school to celebrate the last day.</t>
         </is>
       </c>
       <c r="L97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">協働、探究、実社会での学びを促す合同の学習体験に参加します。</t>
+          <t xml:space="preserve">土曜校の最終日を、校内でのレクリエーション活動とともにリラックスして過ごし、お祝いします。</t>
         </is>
       </c>
       <c r="M97" t="inlineStr" s="2">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="O97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-21-collective-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-22-saturday-school-last-day-event.webp</t>
         </is>
       </c>
       <c r="P97" t="inlineStr" s="2">
@@ -9491,17 +9491,17 @@
     <row r="98">
       <c r="A98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-22-saturday-school-last-day-event</t>
+          <t xml:space="preserve">2027-05-24-concept-con-future-focus</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-05-24</t>
         </is>
       </c>
       <c r="C98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-05-28</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="3">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="E98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F98" t="inlineStr" s="2">
@@ -9531,22 +9531,22 @@
       </c>
       <c r="I98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saturday School Last Day Event</t>
+          <t xml:space="preserve">Concept Con (Future Focus)</t>
         </is>
       </c>
       <c r="J98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">土曜校最終日イベント</t>
+          <t xml:space="preserve">コンセプト・コン（未来を考える）</t>
         </is>
       </c>
       <c r="K98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in a relaxed final Saturday School session, with leisure activities at school to celebrate the last day.</t>
+          <t xml:space="preserve">Students investigate future possibilities, innovations, and solutions to real-world challenges through inquiry-based projects and presentations.</t>
         </is>
       </c>
       <c r="L98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">土曜校の最終日を、校内でのレクリエーション活動とともにリラックスして過ごし、お祝いします。</t>
+          <t xml:space="preserve">探究型のプロジェクトや発表を通して、未来の可能性、イノベーション、現実の課題の解決策について考えます。</t>
         </is>
       </c>
       <c r="M98" t="inlineStr" s="2">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="O98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-22-saturday-school-last-day-event.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-24-concept-con-future-focus.webp</t>
         </is>
       </c>
       <c r="P98" t="inlineStr" s="2">
@@ -9588,12 +9588,12 @@
     <row r="99">
       <c r="A99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-24-concept-con-future-focus</t>
+          <t xml:space="preserve">2027-05-28-g12-graduation-with-performances</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-24</t>
+          <t xml:space="preserve">2027-05-28</t>
         </is>
       </c>
       <c r="C99" t="inlineStr" s="3">
@@ -9608,12 +9608,12 @@
       </c>
       <c r="E99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G99" t="inlineStr" s="2">
@@ -9628,22 +9628,22 @@
       </c>
       <c r="I99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Concept Con (Future Focus)</t>
+          <t xml:space="preserve">G12 Graduation with Performances</t>
         </is>
       </c>
       <c r="J99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">コンセプト・コン（未来を考える）</t>
+          <t xml:space="preserve">G12卒業式・記念パフォーマンス</t>
         </is>
       </c>
       <c r="K99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students investigate future possibilities, innovations, and solutions to real-world challenges through inquiry-based projects and presentations.</t>
+          <t xml:space="preserve">Grade 12 students will celebrate their graduation with a formal ceremony featuring student performances and the wider school community.</t>
         </is>
       </c>
       <c r="L99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">探究型のプロジェクトや発表を通して、未来の可能性、イノベーション、現実の課題の解決策について考えます。</t>
+          <t xml:space="preserve">12年生が、生徒によるパフォーマンスを交えた式典で、学校コミュニティ全体とともに卒業を祝います。</t>
         </is>
       </c>
       <c r="M99" t="inlineStr" s="2">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="O99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-24-concept-con-future-focus.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-28-g12-graduation-with-performances.webp</t>
         </is>
       </c>
       <c r="P99" t="inlineStr" s="2">
@@ -9685,17 +9685,17 @@
     <row r="100">
       <c r="A100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-28-g12-graduation-with-performances</t>
+          <t xml:space="preserve">2027-06-03-celebration-of-learning-prep</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-28</t>
+          <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
       <c r="C100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-28</t>
+          <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="3">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="E100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G100" t="inlineStr" s="2">
@@ -9725,22 +9725,22 @@
       </c>
       <c r="I100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G12 Graduation with Performances</t>
+          <t xml:space="preserve">Celebration of Learning Prep</t>
         </is>
       </c>
       <c r="J100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G12卒業式・記念パフォーマンス</t>
+          <t xml:space="preserve">学びの発表会準備</t>
         </is>
       </c>
       <c r="K100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 12 students will celebrate their graduation with a formal ceremony featuring student performances and the wider school community.</t>
+          <t xml:space="preserve">Students help prepare the school for the Celebration of Learning by organizing learning spaces, setting up displays, arranging materials, and ensuring classrooms and common areas are ready to welcome visitors. This preparation helps create an engaging and welcoming environment for families and guests.</t>
         </is>
       </c>
       <c r="L100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12年生が、生徒によるパフォーマンスを交えた式典で、学校コミュニティ全体とともに卒業を祝います。</t>
+          <t xml:space="preserve">学びの発表会に向けて、学習スペースの整理、展示の設営、資料の準備を行い、教室や共用エリアで来場者をお迎えできるよう整えます。ご家族やお客様にとって魅力的で温かな空間づくりにつながります。</t>
         </is>
       </c>
       <c r="M100" t="inlineStr" s="2">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="O100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-28-g12-graduation-with-performances.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-03-celebration-of-learning-prep.webp</t>
         </is>
       </c>
       <c r="P100" t="inlineStr" s="2">
@@ -9782,7 +9782,7 @@
     <row r="101">
       <c r="A101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-03-celebration-of-learning-prep</t>
+          <t xml:space="preserve">2027-06-03-ukulele-concert</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="3">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-03</t>
+          <t xml:space="preserve">2027-06-04</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="3">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G101" t="inlineStr" s="2">
@@ -9822,22 +9822,22 @@
       </c>
       <c r="I101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Celebration of Learning Prep</t>
+          <t xml:space="preserve">Ukulele Concert</t>
         </is>
       </c>
       <c r="J101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学びの発表会準備</t>
+          <t xml:space="preserve">ウクレレコンサート</t>
         </is>
       </c>
       <c r="K101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students help prepare the school for the Celebration of Learning by organizing learning spaces, setting up displays, arranging materials, and ensuring classrooms and common areas are ready to welcome visitors. This preparation helps create an engaging and welcoming environment for families and guests.</t>
+          <t xml:space="preserve">Students perform musical pieces they have learned throughout the year, demonstrating their growth, confidence, and musical skills.</t>
         </is>
       </c>
       <c r="L101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学びの発表会に向けて、学習スペースの整理、展示の設営、資料の準備を行い、教室や共用エリアで来場者をお迎えできるよう整えます。ご家族やお客様にとって魅力的で温かな空間づくりにつながります。</t>
+          <t xml:space="preserve">一年を通して学んだ曲を演奏し、成長、自信、音楽の技能を披露します。</t>
         </is>
       </c>
       <c r="M101" t="inlineStr" s="2">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="O101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-03-celebration-of-learning-prep.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-03-ukulele-concert.webp</t>
         </is>
       </c>
       <c r="P101" t="inlineStr" s="2">
@@ -9879,12 +9879,12 @@
     <row r="102">
       <c r="A102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-03-ukulele-concert</t>
+          <t xml:space="preserve">2027-06-04-celebration-of-learning</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-03</t>
+          <t xml:space="preserve">2027-06-04</t>
         </is>
       </c>
       <c r="C102" t="inlineStr" s="3">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="E102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F102" t="inlineStr" s="2">
@@ -9919,22 +9919,22 @@
       </c>
       <c r="I102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ukulele Concert</t>
+          <t xml:space="preserve">Celebration of Learning</t>
         </is>
       </c>
       <c r="J102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ウクレレコンサート</t>
+          <t xml:space="preserve">学びの発表会</t>
         </is>
       </c>
       <c r="K102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students perform musical pieces they have learned throughout the year, demonstrating their growth, confidence, and musical skills.</t>
+          <t xml:space="preserve">The school community will celebrate learning as students share projects and exhibitions, including PYPX, MYPX, CAS, EE, TOK and Foundation to 4 projects.</t>
         </is>
       </c>
       <c r="L102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一年を通して学んだ曲を演奏し、成長、自信、音楽の技能を披露します。</t>
+          <t xml:space="preserve">PYPX、MYPX、CAS、EE、TOK、ファウンデーション～4年生のプロジェクトなど、生徒の作品や展示を通して学校コミュニティ全体で学びを祝います。</t>
         </is>
       </c>
       <c r="M102" t="inlineStr" s="2">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="O102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-03-ukulele-concert.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-04-celebration-of-learning.webp</t>
         </is>
       </c>
       <c r="P102" t="inlineStr" s="2">
@@ -9976,17 +9976,17 @@
     <row r="103">
       <c r="A103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-04-celebration-of-learning</t>
+          <t xml:space="preserve">2027-06-05-sat-test-7</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-04</t>
+          <t xml:space="preserve">2027-06-05</t>
         </is>
       </c>
       <c r="C103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-04</t>
+          <t xml:space="preserve">2027-06-05</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="3">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="E103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G103" t="inlineStr" s="2">
@@ -10016,22 +10016,22 @@
       </c>
       <c r="I103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Celebration of Learning</t>
+          <t xml:space="preserve">SAT Test #7</t>
         </is>
       </c>
       <c r="J103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学びの発表会</t>
+          <t xml:space="preserve">SAT試験 第7回</t>
         </is>
       </c>
       <c r="K103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The school community will celebrate learning as students share projects and exhibitions, including PYPX, MYPX, CAS, EE, TOK and Foundation to 4 projects.</t>
+          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
         </is>
       </c>
       <c r="L103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PYPX、MYPX、CAS、EE、TOK、ファウンデーション～4年生のプロジェクトなど、生徒の作品や展示を通して学校コミュニティ全体で学びを祝います。</t>
+          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
         </is>
       </c>
       <c r="M103" t="inlineStr" s="2">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="O103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-04-celebration-of-learning.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-05-sat-test-7.webp</t>
         </is>
       </c>
       <c r="P103" t="inlineStr" s="2">
@@ -10073,17 +10073,17 @@
     <row r="104">
       <c r="A104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-05-sat-test-7</t>
+          <t xml:space="preserve">2027-06-17-eagle-bucks-store</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-05</t>
+          <t xml:space="preserve">2027-06-17</t>
         </is>
       </c>
       <c r="C104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-05</t>
+          <t xml:space="preserve">2027-06-17</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="3">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="E104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr" s="2">
@@ -10113,22 +10113,22 @@
       </c>
       <c r="I104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT Test #7</t>
+          <t xml:space="preserve">Eagle Bucks Store</t>
         </is>
       </c>
       <c r="J104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT試験 第7回</t>
+          <t xml:space="preserve">イーグルバックス・ストア</t>
         </is>
       </c>
       <c r="K104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
+          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
         </is>
       </c>
       <c r="L104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
+          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
         </is>
       </c>
       <c r="M104" t="inlineStr" s="2">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="O104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-05-sat-test-7.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-17-eagle-bucks-store.webp</t>
         </is>
       </c>
       <c r="P104" t="inlineStr" s="2">
@@ -10170,17 +10170,17 @@
     <row r="105">
       <c r="A105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-17-eagle-bucks-store</t>
+          <t xml:space="preserve">2027-06-18-kindergarten-and-grade-5-graduation</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-17</t>
+          <t xml:space="preserve">2027-06-18</t>
         </is>
       </c>
       <c r="C105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-17</t>
+          <t xml:space="preserve">2027-06-18</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="3">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="F105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G105" t="inlineStr" s="2">
@@ -10210,22 +10210,22 @@
       </c>
       <c r="I105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Eagle Bucks Store</t>
+          <t xml:space="preserve">Kindergarten and Grade 5 Graduation</t>
         </is>
       </c>
       <c r="J105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">イーグルバックス・ストア</t>
+          <t xml:space="preserve">幼稚部・5年生卒業式</t>
         </is>
       </c>
       <c r="K105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
+          <t xml:space="preserve">Students participate in graduation ceremonies to celebrate important milestones in their educational journey. The events recognize student growth, achievements, and readiness for the next stage of learning while bringing together families, staff, and the school community in celebration.</t>
         </is>
       </c>
       <c r="L105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
+          <t xml:space="preserve">学びの歩みにおける大切な節目を祝う卒業式に参加します。生徒の成長と成果、そして次のステージへの準備が整ったことを、ご家族、教職員、学校コミュニティが一堂に会して祝福します。</t>
         </is>
       </c>
       <c r="M105" t="inlineStr" s="2">
@@ -10240,7 +10240,7 @@
       </c>
       <c r="O105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-17-eagle-bucks-store.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-18-kindergarten-and-grade-5-graduation.webp</t>
         </is>
       </c>
       <c r="P105" t="inlineStr" s="2">
@@ -10267,7 +10267,7 @@
     <row r="106">
       <c r="A106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-18-kindergarten-and-grade-5-graduation</t>
+          <t xml:space="preserve">2027-06-18-primary-elc-year-end-performance</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="3">
@@ -10307,22 +10307,22 @@
       </c>
       <c r="I106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Kindergarten and Grade 5 Graduation</t>
+          <t xml:space="preserve">Primary &amp; ELC Year End Performance</t>
         </is>
       </c>
       <c r="J106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部・5年生卒業式</t>
+          <t xml:space="preserve">小学部・幼稚部年度末発表会</t>
         </is>
       </c>
       <c r="K106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students participate in graduation ceremonies to celebrate important milestones in their educational journey. The events recognize student growth, achievements, and readiness for the next stage of learning while bringing together families, staff, and the school community in celebration.</t>
+          <t xml:space="preserve">Students participate in music, dance, drama, and other performance activities to showcase their learning, creativity, and talents. These performances provide an opportunity to celebrate the school year and share achievements with families and the school community.</t>
         </is>
       </c>
       <c r="L106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学びの歩みにおける大切な節目を祝う卒業式に参加します。生徒の成長と成果、そして次のステージへの準備が整ったことを、ご家族、教職員、学校コミュニティが一堂に会して祝福します。</t>
+          <t xml:space="preserve">音楽、ダンス、演劇などのパフォーマンスを通して、学び、創造性、才能を披露します。一年の締めくくりを祝い、その成果をご家族や学校コミュニティと分かち合う機会です。</t>
         </is>
       </c>
       <c r="M106" t="inlineStr" s="2">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="O106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-18-kindergarten-and-grade-5-graduation.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-18-primary-elc-year-end-performance.webp</t>
         </is>
       </c>
       <c r="P106" t="inlineStr" s="2">
@@ -10364,17 +10364,17 @@
     <row r="107">
       <c r="A107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-18-primary-elc-year-end-performance</t>
+          <t xml:space="preserve">2027-06-19-end-of-term-3-activity-g6-10</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-18</t>
+          <t xml:space="preserve">2027-06-19</t>
         </is>
       </c>
       <c r="C107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-18</t>
+          <t xml:space="preserve">2027-06-19</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="3">
@@ -10384,12 +10384,12 @@
       </c>
       <c r="E107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G107" t="inlineStr" s="2">
@@ -10404,22 +10404,22 @@
       </c>
       <c r="I107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary &amp; ELC Year End Performance</t>
+          <t xml:space="preserve">End of Term 3 Activity: G6-10</t>
         </is>
       </c>
       <c r="J107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小学部・幼稚部年度末発表会</t>
+          <t xml:space="preserve">第3学期末行事：G6–10</t>
         </is>
       </c>
       <c r="K107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students participate in music, dance, drama, and other performance activities to showcase their learning, creativity, and talents. These performances provide an opportunity to celebrate the school year and share achievements with families and the school community.</t>
+          <t xml:space="preserve">Students will take part in an off-campus day trip outside Nagoya to celebrate the end of Term 3.</t>
         </is>
       </c>
       <c r="L107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">音楽、ダンス、演劇などのパフォーマンスを通して、学び、創造性、才能を披露します。一年の締めくくりを祝い、その成果をご家族や学校コミュニティと分かち合う機会です。</t>
+          <t xml:space="preserve">第3学期の終わりを祝い、名古屋近郊への日帰り校外活動に参加します。</t>
         </is>
       </c>
       <c r="M107" t="inlineStr" s="2">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="O107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-18-primary-elc-year-end-performance.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-19-end-of-term-3-activity-g6-10.webp</t>
         </is>
       </c>
       <c r="P107" t="inlineStr" s="2">
@@ -10461,17 +10461,17 @@
     <row r="108">
       <c r="A108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-19-end-of-term-3-activity-g6-10</t>
+          <t xml:space="preserve">2027-06-22-parent-teacher-conferences</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-19</t>
+          <t xml:space="preserve">2027-06-22</t>
         </is>
       </c>
       <c r="C108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-19</t>
+          <t xml:space="preserve">2027-06-23</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="3">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="E108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="H108" t="inlineStr" s="2">
@@ -10501,22 +10501,22 @@
       </c>
       <c r="I108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">End of Term 3 Activity: G6-10</t>
+          <t xml:space="preserve">Parent Teacher Conferences</t>
         </is>
       </c>
       <c r="J108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第3学期末行事：G6–10</t>
+          <t xml:space="preserve">保護者面談</t>
         </is>
       </c>
       <c r="K108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in an off-campus day trip outside Nagoya to celebrate the end of Term 3.</t>
+          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on these days.</t>
         </is>
       </c>
       <c r="L108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第3学期の終わりを祝い、名古屋近郊への日帰り校外活動に参加します。</t>
+          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。期間中、生徒は登校しません。</t>
         </is>
       </c>
       <c r="M108" t="inlineStr" s="2">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="O108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-19-end-of-term-3-activity-g6-10.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-22-parent-teacher-conferences.webp</t>
         </is>
       </c>
       <c r="P108" t="inlineStr" s="2">
@@ -10558,17 +10558,17 @@
     <row r="109">
       <c r="A109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-22-parent-teacher-conferences</t>
+          <t xml:space="preserve">2027-06-28-summer-school</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-22</t>
+          <t xml:space="preserve">2027-06-28</t>
         </is>
       </c>
       <c r="C109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-23</t>
+          <t xml:space="preserve">2027-07-24</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="3">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="F109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H109" t="inlineStr" s="2">
@@ -10598,22 +10598,22 @@
       </c>
       <c r="I109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parent Teacher Conferences</t>
+          <t xml:space="preserve">Summer School</t>
         </is>
       </c>
       <c r="J109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者面談</t>
+          <t xml:space="preserve">サマースクール</t>
         </is>
       </c>
       <c r="K109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on these days.</t>
+          <t xml:space="preserve">Participate in fun English style summer camps that challenge students and help foster friendships and connections with others.</t>
         </is>
       </c>
       <c r="L109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。期間中、生徒は登校しません。</t>
+          <t xml:space="preserve">英語で楽しく過ごすサマーキャンプに参加し、新たなことに挑戦しながら友情や人とのつながりを育みます。</t>
         </is>
       </c>
       <c r="M109" t="inlineStr" s="2">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="O109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-22-parent-teacher-conferences.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-28-summer-school.webp</t>
         </is>
       </c>
       <c r="P109" t="inlineStr" s="2">
@@ -10647,103 +10647,6 @@
         </is>
       </c>
       <c r="S109" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">2027-06-28-summer-school</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">2027-06-28</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">2027-07-24</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Whole School</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Summer School</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">サマースクール</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Participate in fun English style summer camps that challenge students and help foster friendships and connections with others.</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">英語で楽しく過ごすサマーキャンプに参加し、新たなことに挑戦しながら友情や人とのつながりを育みます。</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">compass/images/events/2027-06-28-summer-school.webp</t>
-        </is>
-      </c>
-      <c r="P110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="S110" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>

--- a/admin/EIS-Compass-events.xlsx
+++ b/admin/EIS-Compass-events.xlsx
@@ -9593,12 +9593,12 @@
       </c>
       <c r="B99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-28</t>
+          <t xml:space="preserve">2027-05-29</t>
         </is>
       </c>
       <c r="C99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-28</t>
+          <t xml:space="preserve">2027-05-29</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="3">
@@ -9623,7 +9623,7 @@
       </c>
       <c r="H99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">changed</t>
         </is>
       </c>
       <c r="I99" t="inlineStr" s="2">
@@ -10568,85 +10568,182 @@
       </c>
       <c r="C109" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">2027-07-18</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Whole School</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Summer School</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">サマースクール</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Participate in fun English style summer camps that challenge students and help foster friendships and connections with others.</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">英語で楽しく過ごすサマーキャンプに参加し、新たなことに挑戦しながら友情や人とのつながりを育みます。</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">compass/images/events/2027-06-28-summer-school.webp</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">2027-07-20-summer-school</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2027-07-20</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">2027-07-24</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr" s="2">
+      <c r="D110" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Whole School</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr" s="2">
+      <c r="F110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Summer School</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr" s="2">
+      <c r="J110" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">サマースクール</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr" s="2">
+      <c r="K110" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Participate in fun English style summer camps that challenge students and help foster friendships and connections with others.</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr" s="2">
+      <c r="L110" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">英語で楽しく過ごすサマーキャンプに参加し、新たなことに挑戦しながら友情や人とのつながりを育みます。</t>
         </is>
       </c>
-      <c r="M109" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O109" t="inlineStr" s="2">
+      <c r="M110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">compass/images/events/2027-06-28-summer-school.webp</t>
         </is>
       </c>
-      <c r="P109" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q109" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R109" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="S109" t="inlineStr" s="2">
+      <c r="P110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -10966,39 +11063,39 @@
     <row r="12">
       <c r="A12" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-11</t>
+          <t xml:space="preserve">2027-01-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-11</t>
+          <t xml:space="preserve">2027-01-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">national</t>
+          <t xml:space="preserve">noclass</t>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">National Foundation Day</t>
+          <t xml:space="preserve">No classes</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">建国記念の日</t>
+          <t xml:space="preserve">授業なし</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-23</t>
+          <t xml:space="preserve">2027-02-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-23</t>
+          <t xml:space="preserve">2027-02-11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
@@ -11008,24 +11105,24 @@
       </c>
       <c r="D13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Emperor's Birthday</t>
+          <t xml:space="preserve">National Foundation Day</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">天皇誕生日</t>
+          <t xml:space="preserve">建国記念の日</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-21</t>
+          <t xml:space="preserve">2027-02-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-21</t>
+          <t xml:space="preserve">2027-02-23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
@@ -11035,105 +11132,105 @@
       </c>
       <c r="D14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Vernal Equinox Day</t>
+          <t xml:space="preserve">Emperor's Birthday</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">春分の日</t>
+          <t xml:space="preserve">天皇誕生日</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-22</t>
+          <t xml:space="preserve">2027-03-21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-26</t>
+          <t xml:space="preserve">2027-03-21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">school</t>
+          <t xml:space="preserve">national</t>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">School Holiday</t>
+          <t xml:space="preserve">Vernal Equinox Day</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学校休日</t>
+          <t xml:space="preserve">春分の日</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-29</t>
+          <t xml:space="preserve">2027-03-22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-29</t>
+          <t xml:space="preserve">2027-03-26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">noclass</t>
+          <t xml:space="preserve">school</t>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Staff Prep Day (no classes)</t>
+          <t xml:space="preserve">School Holiday</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">教職員準備日（授業なし）</t>
+          <t xml:space="preserve">学校休日</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-03</t>
+          <t xml:space="preserve">2027-03-29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-03</t>
+          <t xml:space="preserve">2027-03-29</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">national</t>
+          <t xml:space="preserve">noclass</t>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Constitution Memorial Day</t>
+          <t xml:space="preserve">Staff Prep Day (no classes)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">憲法記念日</t>
+          <t xml:space="preserve">教職員準備日（授業なし）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-04</t>
+          <t xml:space="preserve">2027-05-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-04</t>
+          <t xml:space="preserve">2027-05-03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
@@ -11143,24 +11240,24 @@
       </c>
       <c r="D18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Greenery Day</t>
+          <t xml:space="preserve">Constitution Memorial Day</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">みどりの日</t>
+          <t xml:space="preserve">憲法記念日</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-05</t>
+          <t xml:space="preserve">2027-05-04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-05</t>
+          <t xml:space="preserve">2027-05-04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
@@ -11170,51 +11267,51 @@
       </c>
       <c r="D19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Children's Day</t>
+          <t xml:space="preserve">Greenery Day</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">こどもの日</t>
+          <t xml:space="preserve">みどりの日</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-06</t>
+          <t xml:space="preserve">2027-05-05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-07</t>
+          <t xml:space="preserve">2027-05-05</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">school</t>
+          <t xml:space="preserve">national</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">School Holiday</t>
+          <t xml:space="preserve">Children's Day</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学校休日</t>
+          <t xml:space="preserve">こどもの日</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-06</t>
+          <t xml:space="preserve">2027-05-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-07</t>
+          <t xml:space="preserve">2027-05-07</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">

--- a/admin/EIS-Compass-events.xlsx
+++ b/admin/EIS-Compass-events.xlsx
@@ -5514,17 +5514,17 @@
     <row r="57">
       <c r="A57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-14-g10-parent-info-session-high-school-subject-choi</t>
+          <t xml:space="preserve">2027-01-08-parent-teacher-conferences</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-14</t>
+          <t xml:space="preserve">2027-01-08</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-14</t>
+          <t xml:space="preserve">2027-01-08</t>
         </is>
       </c>
       <c r="D57" t="inlineStr" s="3">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="E57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F57" t="inlineStr" s="2">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="G57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="H57" t="inlineStr" s="2">
@@ -5554,22 +5554,22 @@
       </c>
       <c r="I57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G10 Parent info Session (High School Subject Choice)</t>
+          <t xml:space="preserve">Parent Teacher Conferences</t>
         </is>
       </c>
       <c r="J57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G10保護者向け説明会（高等部科目選択）</t>
+          <t xml:space="preserve">保護者面談</t>
         </is>
       </c>
       <c r="K57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 10 parents are invited to an information session about DP subject choices and guidance for planning the next stage of their child’s learning.</t>
+          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on this day.</t>
         </is>
       </c>
       <c r="L57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10年生の保護者の皆様を対象に、DPの科目選択と、お子様の次のステージの学びを計画するためのガイダンスを行います。</t>
+          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。当日、生徒は登校しません。</t>
         </is>
       </c>
       <c r="M57" t="inlineStr" s="2">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="O57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-01-14-g10-parent-info-session-high-school-subject-choi.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-19-parent-teacher-conferences.webp</t>
         </is>
       </c>
       <c r="P57" t="inlineStr" s="2">
@@ -5611,17 +5611,17 @@
     <row r="58">
       <c r="A58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-22-open-campus</t>
+          <t xml:space="preserve">2027-01-14-g10-parent-info-session-high-school-subject-choi</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-22</t>
+          <t xml:space="preserve">2027-01-14</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-22</t>
+          <t xml:space="preserve">2027-01-14</t>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="3">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G58" t="inlineStr" s="2">
@@ -5651,22 +5651,22 @@
       </c>
       <c r="I58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Open Campus</t>
+          <t xml:space="preserve">G10 Parent info Session (High School Subject Choice)</t>
         </is>
       </c>
       <c r="J58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">オープンキャンパス</t>
+          <t xml:space="preserve">G10保護者向け説明会（高等部科目選択）</t>
         </is>
       </c>
       <c r="K58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Any person interested in seeing the daily operation of the school is invited to join a tour of the school during its regular hours.</t>
+          <t xml:space="preserve">Grade 10 parents are invited to an information session about DP subject choices and guidance for planning the next stage of their child’s learning.</t>
         </is>
       </c>
       <c r="L58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学校の日常の様子にご関心のある方は、通常授業時間中の校内見学にご参加いただけます。</t>
+          <t xml:space="preserve">10年生の保護者の皆様を対象に、DPの科目選択と、お子様の次のステージの学びを計画するためのガイダンスを行います。</t>
         </is>
       </c>
       <c r="M58" t="inlineStr" s="2">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="O58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-01-22-open-campus.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-01-14-g10-parent-info-session-high-school-subject-choi.webp</t>
         </is>
       </c>
       <c r="P58" t="inlineStr" s="2">
@@ -5708,17 +5708,17 @@
     <row r="59">
       <c r="A59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-23-alumni-talk</t>
+          <t xml:space="preserve">2027-01-22-open-campus</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-23</t>
+          <t xml:space="preserve">2027-01-22</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-23</t>
+          <t xml:space="preserve">2027-01-22</t>
         </is>
       </c>
       <c r="D59" t="inlineStr" s="3">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="E59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F59" t="inlineStr" s="2">
@@ -5748,22 +5748,22 @@
       </c>
       <c r="I59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Alumni Talk</t>
+          <t xml:space="preserve">Open Campus</t>
         </is>
       </c>
       <c r="J59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">卒業生トーク</t>
+          <t xml:space="preserve">オープンキャンパス</t>
         </is>
       </c>
       <c r="K59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Alumni will share their experiences and advice with students, offering insight into life after School and future pathways.</t>
+          <t xml:space="preserve">Any person interested in seeing the daily operation of the school is invited to join a tour of the school during its regular hours.</t>
         </is>
       </c>
       <c r="L59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">卒業生が自身の経験やアドバイスを生徒に伝え、卒業後の生活や将来の進路について話します。</t>
+          <t xml:space="preserve">学校の日常の様子にご関心のある方は、通常授業時間中の校内見学にご参加いただけます。</t>
         </is>
       </c>
       <c r="M59" t="inlineStr" s="2">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-01-23-alumni-talk.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-01-22-open-campus.webp</t>
         </is>
       </c>
       <c r="P59" t="inlineStr" s="2">
@@ -5805,17 +5805,17 @@
     <row r="60">
       <c r="A60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-27-natural-disaster-field-trip</t>
+          <t xml:space="preserve">2027-01-23-alumni-talk</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-27</t>
+          <t xml:space="preserve">2027-01-23</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-27</t>
+          <t xml:space="preserve">2027-01-23</t>
         </is>
       </c>
       <c r="D60" t="inlineStr" s="3">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="E60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F60" t="inlineStr" s="2">
@@ -5845,22 +5845,22 @@
       </c>
       <c r="I60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Natural Disaster Field Trip</t>
+          <t xml:space="preserve">Alumni Talk</t>
         </is>
       </c>
       <c r="J60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">防災校外学習</t>
+          <t xml:space="preserve">卒業生トーク</t>
         </is>
       </c>
       <c r="K60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students explore disaster preparedness and safety through interactive learning experiences related to natural disasters and emergency response.</t>
+          <t xml:space="preserve">Alumni will share their experiences and advice with students, offering insight into life after School and future pathways.</t>
         </is>
       </c>
       <c r="L60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">自然災害や緊急時の対応に関する体験型学習を通して、防災と安全について学びます。</t>
+          <t xml:space="preserve">卒業生が自身の経験やアドバイスを生徒に伝え、卒業後の生活や将来の進路について話します。</t>
         </is>
       </c>
       <c r="M60" t="inlineStr" s="2">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="O60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-01-27-natural-disaster-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-01-23-alumni-talk.webp</t>
         </is>
       </c>
       <c r="P60" t="inlineStr" s="2">
@@ -5902,17 +5902,17 @@
     <row r="61">
       <c r="A61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-30-model-united-nations-event-mun</t>
+          <t xml:space="preserve">2027-01-27-natural-disaster-field-trip</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-30</t>
+          <t xml:space="preserve">2027-01-27</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-30</t>
+          <t xml:space="preserve">2027-01-27</t>
         </is>
       </c>
       <c r="D61" t="inlineStr" s="3">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="E61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">ELC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr" s="2">
@@ -5942,22 +5942,22 @@
       </c>
       <c r="I61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Model United Nations Event (MUN)</t>
+          <t xml:space="preserve">Natural Disaster Field Trip</t>
         </is>
       </c>
       <c r="J61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">模擬国連（MUN）</t>
+          <t xml:space="preserve">防災校外学習</t>
         </is>
       </c>
       <c r="K61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will participate in Model United Nations, developing public speaking, research, collaboration, and global awareness through discussion of real-world issues.</t>
+          <t xml:space="preserve">Students explore disaster preparedness and safety through interactive learning experiences related to natural disasters and emergency response.</t>
         </is>
       </c>
       <c r="L61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">模擬国連に参加し、現実の課題について議論することで、スピーチ力、調査力、協働する力、国際的な意識を育みます。</t>
+          <t xml:space="preserve">自然災害や緊急時の対応に関する体験型学習を通して、防災と安全について学びます。</t>
         </is>
       </c>
       <c r="M61" t="inlineStr" s="2">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="O61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-01-30-model-united-nations-event-mun.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-01-27-natural-disaster-field-trip.webp</t>
         </is>
       </c>
       <c r="P61" t="inlineStr" s="2">
@@ -5999,17 +5999,17 @@
     <row r="62">
       <c r="A62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-01-friendly-volleyball-tournament-internal</t>
+          <t xml:space="preserve">2027-01-30-model-united-nations-event-mun</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-01</t>
+          <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-05</t>
+          <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
       <c r="D62" t="inlineStr" s="3">
@@ -6039,22 +6039,22 @@
       </c>
       <c r="I62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Friendly Volleyball Tournament (Internal)</t>
+          <t xml:space="preserve">Model United Nations Event (MUN)</t>
         </is>
       </c>
       <c r="J62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内バレーボール大会</t>
+          <t xml:space="preserve">模擬国連（MUN）</t>
         </is>
       </c>
       <c r="K62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in a friendly internal volleyball tournament, promoting teamwork, sportsmanship, and school spirit.</t>
+          <t xml:space="preserve">Students will participate in Model United Nations, developing public speaking, research, collaboration, and global awareness through discussion of real-world issues.</t>
         </is>
       </c>
       <c r="L62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内バレーボール大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
+          <t xml:space="preserve">模擬国連に参加し、現実の課題について議論することで、スピーチ力、調査力、協働する力、国際的な意識を育みます。</t>
         </is>
       </c>
       <c r="M62" t="inlineStr" s="2">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="O62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-01-friendly-volleyball-tournament-internal.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-01-30-model-united-nations-event-mun.webp</t>
         </is>
       </c>
       <c r="P62" t="inlineStr" s="2">
@@ -6096,7 +6096,7 @@
     <row r="63">
       <c r="A63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-01-concept-con-language</t>
+          <t xml:space="preserve">2027-02-01-friendly-volleyball-tournament-internal</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="3">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F63" t="inlineStr" s="2">
@@ -6136,22 +6136,22 @@
       </c>
       <c r="I63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Concept Con (Language)</t>
+          <t xml:space="preserve">Friendly Volleyball Tournament (Internal)</t>
         </is>
       </c>
       <c r="J63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">コンセプト・コン（言語）</t>
+          <t xml:space="preserve">校内バレーボール大会</t>
         </is>
       </c>
       <c r="K63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students celebrate language and communication through presentations, performances, and projects that showcase their learning and creativity.</t>
+          <t xml:space="preserve">Students will take part in a friendly internal volleyball tournament, promoting teamwork, sportsmanship, and school spirit.</t>
         </is>
       </c>
       <c r="L63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学びと創造性を示す発表、パフォーマンス、プロジェクトを通して、言語とコミュニケーションを祝います。</t>
+          <t xml:space="preserve">校内バレーボール大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
         </is>
       </c>
       <c r="M63" t="inlineStr" s="2">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-01-concept-con-language.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-01-friendly-volleyball-tournament-internal.webp</t>
         </is>
       </c>
       <c r="P63" t="inlineStr" s="2">
@@ -6193,17 +6193,17 @@
     <row r="64">
       <c r="A64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-18-career-support-second-career-roundtable-and-care</t>
+          <t xml:space="preserve">2027-02-01-concept-con-language</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-18</t>
+          <t xml:space="preserve">2027-02-01</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-18</t>
+          <t xml:space="preserve">2027-02-05</t>
         </is>
       </c>
       <c r="D64" t="inlineStr" s="3">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G64" t="inlineStr" s="2">
@@ -6233,22 +6233,22 @@
       </c>
       <c r="I64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Career Support: Second Career Roundtable and Career Fair</t>
+          <t xml:space="preserve">Concept Con (Language)</t>
         </is>
       </c>
       <c r="J64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">進路支援：第2回キャリア座談会・キャリアフェア</t>
+          <t xml:space="preserve">コンセプト・コン（言語）</t>
         </is>
       </c>
       <c r="K64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An informative event where students and parents can learn about IB university admissions, holistic admissions strategies in Japan and abroad, and explore future academic and career opportunities through discussions with experts and representatives.</t>
+          <t xml:space="preserve">Students celebrate language and communication through presentations, performances, and projects that showcase their learning and creativity.</t>
         </is>
       </c>
       <c r="L64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">専門家や関係者との対話を通して、生徒と保護者の皆様がIBでの大学入試、国内外の総合型選抜の戦略について学び、将来の進学やキャリアの可能性を探る説明会です。</t>
+          <t xml:space="preserve">学びと創造性を示す発表、パフォーマンス、プロジェクトを通して、言語とコミュニケーションを祝います。</t>
         </is>
       </c>
       <c r="M64" t="inlineStr" s="2">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="O64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-18-career-support-second-career-roundtable-and-care.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-01-concept-con-language.webp</t>
         </is>
       </c>
       <c r="P64" t="inlineStr" s="2">
@@ -6290,17 +6290,17 @@
     <row r="65">
       <c r="A65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-19-collective-field-trip</t>
+          <t xml:space="preserve">2027-02-18-career-support-second-career-roundtable-and-care</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-19</t>
+          <t xml:space="preserve">2027-02-18</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-19</t>
+          <t xml:space="preserve">2027-02-18</t>
         </is>
       </c>
       <c r="D65" t="inlineStr" s="3">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="E65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G65" t="inlineStr" s="2">
@@ -6330,22 +6330,22 @@
       </c>
       <c r="I65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Collective Field Trip</t>
+          <t xml:space="preserve">Career Support: Second Career Roundtable and Career Fair</t>
         </is>
       </c>
       <c r="J65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合同校外学習</t>
+          <t xml:space="preserve">進路支援：第2回キャリア座談会・キャリアフェア</t>
         </is>
       </c>
       <c r="K65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students participate in an off-campus learning experience that connects classroom learning with real-world exploration and discovery.</t>
+          <t xml:space="preserve">An informative event where students and parents can learn about IB university admissions, holistic admissions strategies in Japan and abroad, and explore future academic and career opportunities through discussions with experts and representatives.</t>
         </is>
       </c>
       <c r="L65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校外での学習体験を通して、教室での学びを実社会での探究や発見と結びつけます。</t>
+          <t xml:space="preserve">専門家や関係者との対話を通して、生徒と保護者の皆様がIBでの大学入試、国内外の総合型選抜の戦略について学び、将来の進学やキャリアの可能性を探る説明会です。</t>
         </is>
       </c>
       <c r="M65" t="inlineStr" s="2">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="O65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-19-collective-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-18-career-support-second-career-roundtable-and-care.webp</t>
         </is>
       </c>
       <c r="P65" t="inlineStr" s="2">
@@ -6387,17 +6387,17 @@
     <row r="66">
       <c r="A66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-22-world-thinking-day</t>
+          <t xml:space="preserve">2027-02-19-collective-field-trip</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-22</t>
+          <t xml:space="preserve">2027-02-19</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-22</t>
+          <t xml:space="preserve">2027-02-19</t>
         </is>
       </c>
       <c r="D66" t="inlineStr" s="3">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="E66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F66" t="inlineStr" s="2">
@@ -6427,22 +6427,22 @@
       </c>
       <c r="I66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">World Thinking Day</t>
+          <t xml:space="preserve">Collective Field Trip</t>
         </is>
       </c>
       <c r="J66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ワールド・シンキング・デー</t>
+          <t xml:space="preserve">合同校外学習</t>
         </is>
       </c>
       <c r="K66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students learn about cultures, traditions, and global citizenship while celebrating international understanding and connection.</t>
+          <t xml:space="preserve">Students participate in an off-campus learning experience that connects classroom learning with real-world exploration and discovery.</t>
         </is>
       </c>
       <c r="L66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国際理解とつながりを祝いながら、さまざまな文化や伝統、地球市民としてのあり方について学びます。</t>
+          <t xml:space="preserve">校外での学習体験を通して、教室での学びを実社会での探究や発見と結びつけます。</t>
         </is>
       </c>
       <c r="M66" t="inlineStr" s="2">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="O66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-22-world-thinking-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-19-collective-field-trip.webp</t>
         </is>
       </c>
       <c r="P66" t="inlineStr" s="2">
@@ -6484,7 +6484,7 @@
     <row r="67">
       <c r="A67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-22-secondary-sports-day-rehearsal-1</t>
+          <t xml:space="preserve">2027-02-22-world-thinking-day</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="3">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="E67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr" s="2">
@@ -6524,22 +6524,22 @@
       </c>
       <c r="I67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary Sports Day Rehearsal #1</t>
+          <t xml:space="preserve">World Thinking Day</t>
         </is>
       </c>
       <c r="J67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部運動会リハーサル #1</t>
+          <t xml:space="preserve">ワールド・シンキング・デー</t>
         </is>
       </c>
       <c r="K67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
+          <t xml:space="preserve">Students learn about cultures, traditions, and global citizenship while celebrating international understanding and connection.</t>
         </is>
       </c>
       <c r="L67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
+          <t xml:space="preserve">国際理解とつながりを祝いながら、さまざまな文化や伝統、地球市民としてのあり方について学びます。</t>
         </is>
       </c>
       <c r="M67" t="inlineStr" s="2">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="O67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-22-secondary-sports-day-rehearsal-1.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-22-world-thinking-day.webp</t>
         </is>
       </c>
       <c r="P67" t="inlineStr" s="2">
@@ -6581,17 +6581,17 @@
     <row r="68">
       <c r="A68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-25-primary-sports-day-rehearsal-1</t>
+          <t xml:space="preserve">2027-02-22-secondary-sports-day-rehearsal-1</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-25</t>
+          <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-25</t>
+          <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
       <c r="D68" t="inlineStr" s="3">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="E68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F68" t="inlineStr" s="2">
@@ -6621,22 +6621,22 @@
       </c>
       <c r="I68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary Sports Day Rehearsal #1</t>
+          <t xml:space="preserve">Secondary Sports Day Rehearsal #1</t>
         </is>
       </c>
       <c r="J68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小学部運動会リハーサル #1</t>
+          <t xml:space="preserve">中等部運動会リハーサル #1</t>
         </is>
       </c>
       <c r="K68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students begin preparing for Sports Day by practicing events, routines, and teamwork activities.</t>
+          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
         </is>
       </c>
       <c r="L68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">種目、流れ、チームワークの練習を通して、運動会に向けた準備を始めます。</t>
+          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
         </is>
       </c>
       <c r="M68" t="inlineStr" s="2">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="O68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-25-primary-sports-day-rehearsal-1.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-22-secondary-sports-day-rehearsal-1.webp</t>
         </is>
       </c>
       <c r="P68" t="inlineStr" s="2">
@@ -6678,17 +6678,17 @@
     <row r="69">
       <c r="A69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-26-parents-morning-2</t>
+          <t xml:space="preserve">2027-02-25-primary-sports-day-rehearsal-1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-26</t>
+          <t xml:space="preserve">2027-02-25</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-26</t>
+          <t xml:space="preserve">2027-02-25</t>
         </is>
       </c>
       <c r="D69" t="inlineStr" s="3">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="E69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G69" t="inlineStr" s="2">
@@ -6718,22 +6718,22 @@
       </c>
       <c r="I69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parents Morning #2</t>
+          <t xml:space="preserve">Primary Sports Day Rehearsal #1</t>
         </is>
       </c>
       <c r="J69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">朝の授業参観 #2</t>
+          <t xml:space="preserve">小学部運動会リハーサル #1</t>
         </is>
       </c>
       <c r="K69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC and Primary Parents are invited to come and see the lessons in the morning and experience the morning routines with their child.</t>
+          <t xml:space="preserve">Students begin preparing for Sports Day by practicing events, routines, and teamwork activities.</t>
         </is>
       </c>
       <c r="L69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部・小学部の保護者の皆様をお招きし、朝の授業をご参観いただき、お子様と一緒に朝の日課を体験していただきます。</t>
+          <t xml:space="preserve">種目、流れ、チームワークの練習を通して、運動会に向けた準備を始めます。</t>
         </is>
       </c>
       <c r="M69" t="inlineStr" s="2">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="O69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-26-parents-morning-2.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-25-primary-sports-day-rehearsal-1.webp</t>
         </is>
       </c>
       <c r="P69" t="inlineStr" s="2">
@@ -6775,7 +6775,7 @@
     <row r="70">
       <c r="A70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-26-eagle-talks</t>
+          <t xml:space="preserve">2027-02-26-parents-morning-2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="3">
@@ -6815,22 +6815,22 @@
       </c>
       <c r="I70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Eagle Talks</t>
+          <t xml:space="preserve">Parents Morning #2</t>
         </is>
       </c>
       <c r="J70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">イーグル・トーク</t>
+          <t xml:space="preserve">朝の授業参観 #2</t>
         </is>
       </c>
       <c r="K70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students share ideas, experiences, and learning through short presentations designed to build confidence, communication, and leadership skills.</t>
+          <t xml:space="preserve">ELC and Primary Parents are invited to come and see the lessons in the morning and experience the morning routines with their child.</t>
         </is>
       </c>
       <c r="L70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">短いプレゼンテーションを通して考えや経験、学びを共有し、自信、コミュニケーション力、リーダーシップを育みます。</t>
+          <t xml:space="preserve">幼稚部・小学部の保護者の皆様をお招きし、朝の授業をご参観いただき、お子様と一緒に朝の日課を体験していただきます。</t>
         </is>
       </c>
       <c r="M70" t="inlineStr" s="2">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-26-eagle-talks.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-26-parents-morning-2.webp</t>
         </is>
       </c>
       <c r="P70" t="inlineStr" s="2">
@@ -6872,17 +6872,17 @@
     <row r="71">
       <c r="A71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-04-grade-1-2-musical</t>
+          <t xml:space="preserve">2027-02-26-eagle-talks</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-04</t>
+          <t xml:space="preserve">2027-02-26</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-05</t>
+          <t xml:space="preserve">2027-02-26</t>
         </is>
       </c>
       <c r="D71" t="inlineStr" s="3">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="E71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr" s="2">
@@ -6912,22 +6912,22 @@
       </c>
       <c r="I71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 1, 2 Musical</t>
+          <t xml:space="preserve">Eagle Talks</t>
         </is>
       </c>
       <c r="J71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1・2年生ミュージカル</t>
+          <t xml:space="preserve">イーグル・トーク</t>
         </is>
       </c>
       <c r="K71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students showcase their creativity and confidence through a musical performance featuring songs, acting, and teamwork.</t>
+          <t xml:space="preserve">Students share ideas, experiences, and learning through short presentations designed to build confidence, communication, and leadership skills.</t>
         </is>
       </c>
       <c r="L71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">歌、演技、チームワークによるミュージカルを通して、創造性と自信あふれる姿を披露します。</t>
+          <t xml:space="preserve">短いプレゼンテーションを通して考えや経験、学びを共有し、自信、コミュニケーション力、リーダーシップを育みます。</t>
         </is>
       </c>
       <c r="M71" t="inlineStr" s="2">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="O71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-04-grade-1-2-musical.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-26-eagle-talks.webp</t>
         </is>
       </c>
       <c r="P71" t="inlineStr" s="2">
@@ -6969,19 +6969,19 @@
     <row r="72">
       <c r="A72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-05-higashiyama-zoo-botanical-garden</t>
+          <t xml:space="preserve">2027-03-04-grade-1-2-musical</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">2027-03-04</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">2027-03-05</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">2027-03-05</t>
-        </is>
-      </c>
       <c r="D72" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G72" t="inlineStr" s="2">
@@ -7009,22 +7009,22 @@
       </c>
       <c r="I72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Higashiyama Zoo &amp; Botanical Garden</t>
+          <t xml:space="preserve">Grade 1, 2 Musical</t>
         </is>
       </c>
       <c r="J72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">東山動植物園</t>
+          <t xml:space="preserve">1・2年生ミュージカル</t>
         </is>
       </c>
       <c r="K72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 7 Science students will visit Higashiyama Zoo and Botanical Gardens to support their learning through observation and real-world examples.</t>
+          <t xml:space="preserve">Students showcase their creativity and confidence through a musical performance featuring songs, acting, and teamwork.</t>
         </is>
       </c>
       <c r="L72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7年生が理科の学習の一環として東山動植物園を訪れ、観察や実物を通して学びを深めます。</t>
+          <t xml:space="preserve">歌、演技、チームワークによるミュージカルを通して、創造性と自信あふれる姿を披露します。</t>
         </is>
       </c>
       <c r="M72" t="inlineStr" s="2">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="O72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-05-higashiyama-zoo-botanical-garden.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-04-grade-1-2-musical.webp</t>
         </is>
       </c>
       <c r="P72" t="inlineStr" s="2">
@@ -7066,17 +7066,17 @@
     <row r="73">
       <c r="A73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-06-sat-test-6</t>
+          <t xml:space="preserve">2027-03-05-higashiyama-zoo-botanical-garden</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-06</t>
+          <t xml:space="preserve">2027-03-05</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-06</t>
+          <t xml:space="preserve">2027-03-05</t>
         </is>
       </c>
       <c r="D73" t="inlineStr" s="3">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="E73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F73" t="inlineStr" s="2">
@@ -7106,22 +7106,22 @@
       </c>
       <c r="I73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT Test #6</t>
+          <t xml:space="preserve">Higashiyama Zoo &amp; Botanical Garden</t>
         </is>
       </c>
       <c r="J73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT試験 第6回</t>
+          <t xml:space="preserve">東山動植物園</t>
         </is>
       </c>
       <c r="K73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
+          <t xml:space="preserve">Grade 7 Science students will visit Higashiyama Zoo and Botanical Gardens to support their learning through observation and real-world examples.</t>
         </is>
       </c>
       <c r="L73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
+          <t xml:space="preserve">7年生が理科の学習の一環として東山動植物園を訪れ、観察や実物を通して学びを深めます。</t>
         </is>
       </c>
       <c r="M73" t="inlineStr" s="2">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="O73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-06-sat-test-6.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-05-higashiyama-zoo-botanical-garden.webp</t>
         </is>
       </c>
       <c r="P73" t="inlineStr" s="2">
@@ -7163,17 +7163,17 @@
     <row r="74">
       <c r="A74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-09-primary-sports-day-rehearsal-2</t>
+          <t xml:space="preserve">2027-03-06-sat-test-6</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-09</t>
+          <t xml:space="preserve">2027-03-06</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-09</t>
+          <t xml:space="preserve">2027-03-06</t>
         </is>
       </c>
       <c r="D74" t="inlineStr" s="3">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="E74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F74" t="inlineStr" s="2">
@@ -7203,22 +7203,22 @@
       </c>
       <c r="I74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary Sports Day Rehearsal #2</t>
+          <t xml:space="preserve">SAT Test #6</t>
         </is>
       </c>
       <c r="J74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小学部運動会リハーサル #2</t>
+          <t xml:space="preserve">SAT試験 第6回</t>
         </is>
       </c>
       <c r="K74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students continue building skills and confidence as they prepare for Sports Day events and activities.</t>
+          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
         </is>
       </c>
       <c r="L74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会の種目や活動に向けて準備を進めながら、技能と自信をさらに高めます。</t>
+          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
         </is>
       </c>
       <c r="M74" t="inlineStr" s="2">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="O74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-09-primary-sports-day-rehearsal-2.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-06-sat-test-6.webp</t>
         </is>
       </c>
       <c r="P74" t="inlineStr" s="2">
@@ -7260,17 +7260,17 @@
     <row r="75">
       <c r="A75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-12-secondary-sports-day-rehearsal-2</t>
+          <t xml:space="preserve">2027-03-09-primary-sports-day-rehearsal-2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-12</t>
+          <t xml:space="preserve">2027-03-09</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-12</t>
+          <t xml:space="preserve">2027-03-09</t>
         </is>
       </c>
       <c r="D75" t="inlineStr" s="3">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="E75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F75" t="inlineStr" s="2">
@@ -7300,22 +7300,22 @@
       </c>
       <c r="I75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary Sports Day Rehearsal #2</t>
+          <t xml:space="preserve">Primary Sports Day Rehearsal #2</t>
         </is>
       </c>
       <c r="J75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部運動会リハーサル #2</t>
+          <t xml:space="preserve">小学部運動会リハーサル #2</t>
         </is>
       </c>
       <c r="K75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
+          <t xml:space="preserve">Students continue building skills and confidence as they prepare for Sports Day events and activities.</t>
         </is>
       </c>
       <c r="L75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
+          <t xml:space="preserve">運動会の種目や活動に向けて準備を進めながら、技能と自信をさらに高めます。</t>
         </is>
       </c>
       <c r="M75" t="inlineStr" s="2">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="O75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-12-secondary-sports-day-rehearsal-2.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-09-primary-sports-day-rehearsal-2.webp</t>
         </is>
       </c>
       <c r="P75" t="inlineStr" s="2">
@@ -7357,17 +7357,17 @@
     <row r="76">
       <c r="A76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-18-japanese-culture-day</t>
+          <t xml:space="preserve">2027-03-12-secondary-sports-day-rehearsal-2</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-18</t>
+          <t xml:space="preserve">2027-03-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-18</t>
+          <t xml:space="preserve">2027-03-12</t>
         </is>
       </c>
       <c r="D76" t="inlineStr" s="3">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G76" t="inlineStr" s="2">
@@ -7397,22 +7397,22 @@
       </c>
       <c r="I76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Japanese Culture Day</t>
+          <t xml:space="preserve">Secondary Sports Day Rehearsal #2</t>
         </is>
       </c>
       <c r="J76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">日本文化デー</t>
+          <t xml:space="preserve">中等部運動会リハーサル #2</t>
         </is>
       </c>
       <c r="K76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will deepen their understanding and appreciation of Japanese culture through a variety of interactive activities with school community.</t>
+          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
         </is>
       </c>
       <c r="L76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学校コミュニティとともにさまざまな体験型の活動に取り組み、日本文化への理解と関心を深めます。</t>
+          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
         </is>
       </c>
       <c r="M76" t="inlineStr" s="2">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="O76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-18-japanese-culture-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-12-secondary-sports-day-rehearsal-2.webp</t>
         </is>
       </c>
       <c r="P76" t="inlineStr" s="2">
@@ -7454,17 +7454,17 @@
     <row r="77">
       <c r="A77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-19-eagle-bucks-store</t>
+          <t xml:space="preserve">2027-03-18-japanese-culture-day</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-19</t>
+          <t xml:space="preserve">2027-03-18</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-19</t>
+          <t xml:space="preserve">2027-03-18</t>
         </is>
       </c>
       <c r="D77" t="inlineStr" s="3">
@@ -7474,12 +7474,12 @@
       </c>
       <c r="E77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G77" t="inlineStr" s="2">
@@ -7494,22 +7494,22 @@
       </c>
       <c r="I77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Eagle Bucks Store</t>
+          <t xml:space="preserve">Japanese Culture Day</t>
         </is>
       </c>
       <c r="J77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">イーグルバックス・ストア</t>
+          <t xml:space="preserve">日本文化デー</t>
         </is>
       </c>
       <c r="K77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
+          <t xml:space="preserve">Students will deepen their understanding and appreciation of Japanese culture through a variety of interactive activities with school community.</t>
         </is>
       </c>
       <c r="L77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
+          <t xml:space="preserve">学校コミュニティとともにさまざまな体験型の活動に取り組み、日本文化への理解と関心を深めます。</t>
         </is>
       </c>
       <c r="M77" t="inlineStr" s="2">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="O77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-19-eagle-bucks-store.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-18-japanese-culture-day.webp</t>
         </is>
       </c>
       <c r="P77" t="inlineStr" s="2">
@@ -7551,7 +7551,7 @@
     <row r="78">
       <c r="A78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-19-tea-party-pta-for-all</t>
+          <t xml:space="preserve">2027-03-19-eagle-bucks-store</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="3">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="E78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTA</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G78" t="inlineStr" s="2">
@@ -7591,22 +7591,22 @@
       </c>
       <c r="I78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Tea Party / PTA for all</t>
+          <t xml:space="preserve">Eagle Bucks Store</t>
         </is>
       </c>
       <c r="J78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTAティーパーティー（どなたでも参加できます）</t>
+          <t xml:space="preserve">イーグルバックス・ストア</t>
         </is>
       </c>
       <c r="K78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A social gathering organized by the PTA and Community Club where staff and students are welcome to enjoy a variety of teas, snacks, and friendly conversation together.</t>
+          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
         </is>
       </c>
       <c r="L78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTAとコミュニティクラブが主催する交流会です。教職員や生徒も参加でき、さまざまなお茶や軽食、和やかな会話を楽しめます。</t>
+          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
         </is>
       </c>
       <c r="M78" t="inlineStr" s="2">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="O78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-19-tea-party-pta-for-all.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-19-eagle-bucks-store.webp</t>
         </is>
       </c>
       <c r="P78" t="inlineStr" s="2">
@@ -7648,7 +7648,7 @@
     <row r="79">
       <c r="A79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-19-end-of-term-2-activity-g9-12</t>
+          <t xml:space="preserve">2027-03-19-tea-party-pta-for-all</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="3">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="C79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-20</t>
+          <t xml:space="preserve">2027-03-19</t>
         </is>
       </c>
       <c r="D79" t="inlineStr" s="3">
@@ -7668,12 +7668,12 @@
       </c>
       <c r="E79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">PTA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G79" t="inlineStr" s="2">
@@ -7688,22 +7688,22 @@
       </c>
       <c r="I79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">End of Term 2 Activity: G9-12</t>
+          <t xml:space="preserve">Tea Party / PTA for all</t>
         </is>
       </c>
       <c r="J79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第2学期末行事：G9–12</t>
+          <t xml:space="preserve">PTAティーパーティー（どなたでも参加できます）</t>
         </is>
       </c>
       <c r="K79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in an off-campus day trip activity to celebrate the end of Term 2.</t>
+          <t xml:space="preserve">A social gathering organized by the PTA and Community Club where staff and students are welcome to enjoy a variety of teas, snacks, and friendly conversation together.</t>
         </is>
       </c>
       <c r="L79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第2学期の終わりを祝い、校外への日帰り活動に参加します。</t>
+          <t xml:space="preserve">PTAとコミュニティクラブが主催する交流会です。教職員や生徒も参加でき、さまざまなお茶や軽食、和やかな会話を楽しめます。</t>
         </is>
       </c>
       <c r="M79" t="inlineStr" s="2">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="O79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-19-end-of-term-2-activity-g9-12.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-19-tea-party-pta-for-all.webp</t>
         </is>
       </c>
       <c r="P79" t="inlineStr" s="2">
@@ -7745,19 +7745,19 @@
     <row r="80">
       <c r="A80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-20-end-of-term-2-activity-g6-8</t>
+          <t xml:space="preserve">2027-03-19-end-of-term-2-activity-g9-12</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">2027-03-19</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">2027-03-20</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">2027-03-21</t>
-        </is>
-      </c>
       <c r="D80" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="E80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F80" t="inlineStr" s="2">
@@ -7785,22 +7785,22 @@
       </c>
       <c r="I80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">End of Term 2 Activity: G6-8</t>
+          <t xml:space="preserve">End of Term 2 Activity: G9-12</t>
         </is>
       </c>
       <c r="J80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第2学期末行事：G6–8</t>
+          <t xml:space="preserve">第2学期末行事：G9–12</t>
         </is>
       </c>
       <c r="K80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in an overnight camp at an off-campus camping facility to celebrate the end of Term 2.</t>
+          <t xml:space="preserve">Students will take part in an off-campus day trip activity to celebrate the end of Term 2.</t>
         </is>
       </c>
       <c r="L80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第2学期の終わりを祝い、校外のキャンプ施設での一泊キャンプに参加します。</t>
+          <t xml:space="preserve">第2学期の終わりを祝い、校外への日帰り活動に参加します。</t>
         </is>
       </c>
       <c r="M80" t="inlineStr" s="2">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="O80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-20-end-of-term-2-activity-g6-8.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-19-end-of-term-2-activity-g9-12.webp</t>
         </is>
       </c>
       <c r="P80" t="inlineStr" s="2">
@@ -7842,17 +7842,17 @@
     <row r="81">
       <c r="A81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-30-parent-teacher-conferences</t>
+          <t xml:space="preserve">2027-03-20-end-of-term-2-activity-g6-8</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-30</t>
+          <t xml:space="preserve">2027-03-20</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-30</t>
+          <t xml:space="preserve">2027-03-21</t>
         </is>
       </c>
       <c r="D81" t="inlineStr" s="3">
@@ -7862,17 +7862,17 @@
       </c>
       <c r="E81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H81" t="inlineStr" s="2">
@@ -7882,22 +7882,22 @@
       </c>
       <c r="I81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parent Teacher Conferences</t>
+          <t xml:space="preserve">End of Term 2 Activity: G6-8</t>
         </is>
       </c>
       <c r="J81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者面談</t>
+          <t xml:space="preserve">第2学期末行事：G6–8</t>
         </is>
       </c>
       <c r="K81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on this day.</t>
+          <t xml:space="preserve">Students will take part in an overnight camp at an off-campus camping facility to celebrate the end of Term 2.</t>
         </is>
       </c>
       <c r="L81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。当日、生徒は登校しません。</t>
+          <t xml:space="preserve">第2学期の終わりを祝い、校外のキャンプ施設での一泊キャンプに参加します。</t>
         </is>
       </c>
       <c r="M81" t="inlineStr" s="2">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-30-parent-teacher-conferences.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-20-end-of-term-2-activity-g6-8.webp</t>
         </is>
       </c>
       <c r="P81" t="inlineStr" s="2">
@@ -7939,17 +7939,17 @@
     <row r="82">
       <c r="A82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-31-secondary-sports-day-rehearsal-3</t>
+          <t xml:space="preserve">2027-03-30-parent-teacher-conferences</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-31</t>
+          <t xml:space="preserve">2027-03-30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-31</t>
+          <t xml:space="preserve">2027-03-30</t>
         </is>
       </c>
       <c r="D82" t="inlineStr" s="3">
@@ -7959,17 +7959,17 @@
       </c>
       <c r="E82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="H82" t="inlineStr" s="2">
@@ -7979,22 +7979,22 @@
       </c>
       <c r="I82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary Sports Day Rehearsal #3</t>
+          <t xml:space="preserve">Parent Teacher Conferences</t>
         </is>
       </c>
       <c r="J82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部運動会リハーサル #3</t>
+          <t xml:space="preserve">保護者面談</t>
         </is>
       </c>
       <c r="K82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
+          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on this day.</t>
         </is>
       </c>
       <c r="L82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
+          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。当日、生徒は登校しません。</t>
         </is>
       </c>
       <c r="M82" t="inlineStr" s="2">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="O82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-31-secondary-sports-day-rehearsal-3.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-30-parent-teacher-conferences.webp</t>
         </is>
       </c>
       <c r="P82" t="inlineStr" s="2">
@@ -8036,17 +8036,17 @@
     <row r="83">
       <c r="A83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-01-primary-sports-day-rehearsal-3</t>
+          <t xml:space="preserve">2027-03-31-secondary-sports-day-rehearsal-3</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-01</t>
+          <t xml:space="preserve">2027-03-31</t>
         </is>
       </c>
       <c r="C83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-01</t>
+          <t xml:space="preserve">2027-03-31</t>
         </is>
       </c>
       <c r="D83" t="inlineStr" s="3">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="E83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F83" t="inlineStr" s="2">
@@ -8076,22 +8076,22 @@
       </c>
       <c r="I83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary Sports Day Rehearsal #3</t>
+          <t xml:space="preserve">Secondary Sports Day Rehearsal #3</t>
         </is>
       </c>
       <c r="J83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小学部運動会リハーサル #3</t>
+          <t xml:space="preserve">中等部運動会リハーサル #3</t>
         </is>
       </c>
       <c r="K83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The final rehearsal provides students with an opportunity to practice events and ensure they are ready for Sports Day.</t>
+          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
         </is>
       </c>
       <c r="L83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">最終リハーサルで各種目を練習し、運動会当日に向けて準備を整えます。</t>
+          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
         </is>
       </c>
       <c r="M83" t="inlineStr" s="2">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="O83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-01-primary-sports-day-rehearsal-3.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-31-secondary-sports-day-rehearsal-3.webp</t>
         </is>
       </c>
       <c r="P83" t="inlineStr" s="2">
@@ -8133,17 +8133,17 @@
     <row r="84">
       <c r="A84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-03-sports-day</t>
+          <t xml:space="preserve">2027-04-01-primary-sports-day-rehearsal-3</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-03</t>
+          <t xml:space="preserve">2027-04-01</t>
         </is>
       </c>
       <c r="C84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-03</t>
+          <t xml:space="preserve">2027-04-01</t>
         </is>
       </c>
       <c r="D84" t="inlineStr" s="3">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="E84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G84" t="inlineStr" s="2">
@@ -8173,22 +8173,22 @@
       </c>
       <c r="I84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sports Day</t>
+          <t xml:space="preserve">Primary Sports Day Rehearsal #3</t>
         </is>
       </c>
       <c r="J84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会</t>
+          <t xml:space="preserve">小学部運動会リハーサル #3</t>
         </is>
       </c>
       <c r="K84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in Sports Day activities, participating in team games, athletic challenges, and school spirit events.</t>
+          <t xml:space="preserve">The final rehearsal provides students with an opportunity to practice events and ensure they are ready for Sports Day.</t>
         </is>
       </c>
       <c r="L84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会に参加し、チームゲーム、運動競技、応援などの行事に取り組みます。</t>
+          <t xml:space="preserve">最終リハーサルで各種目を練習し、運動会当日に向けて準備を整えます。</t>
         </is>
       </c>
       <c r="M84" t="inlineStr" s="2">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="O84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-03-sports-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-01-primary-sports-day-rehearsal-3.webp</t>
         </is>
       </c>
       <c r="P84" t="inlineStr" s="2">
@@ -8230,7 +8230,7 @@
     <row r="85">
       <c r="A85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-03-primary-sports-day-2027</t>
+          <t xml:space="preserve">2027-04-03-sports-day</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="3">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="E85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F85" t="inlineStr" s="2">
@@ -8270,22 +8270,22 @@
       </c>
       <c r="I85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary Sports Day 2027</t>
+          <t xml:space="preserve">Sports Day</t>
         </is>
       </c>
       <c r="J85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小学部運動会 2027</t>
+          <t xml:space="preserve">運動会</t>
         </is>
       </c>
       <c r="K85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students participate in a day of fun, fitness, and friendly competition while demonstrating teamwork, perseverance, and sportsmanship.</t>
+          <t xml:space="preserve">Students will take part in Sports Day activities, participating in team games, athletic challenges, and school spirit events.</t>
         </is>
       </c>
       <c r="L85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">チームワーク、粘り強さ、スポーツマンシップを発揮しながら、楽しく体を動かし、仲間と競い合う一日を過ごします。</t>
+          <t xml:space="preserve">運動会に参加し、チームゲーム、運動競技、応援などの行事に取り組みます。</t>
         </is>
       </c>
       <c r="M85" t="inlineStr" s="2">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="O85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-03-primary-sports-day-2027.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-03-sports-day.webp</t>
         </is>
       </c>
       <c r="P85" t="inlineStr" s="2">
@@ -8327,17 +8327,17 @@
     <row r="86">
       <c r="A86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-15-world-art-day</t>
+          <t xml:space="preserve">2027-04-03-primary-sports-day-2027</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-15</t>
+          <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
       <c r="C86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-15</t>
+          <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="3">
@@ -8347,7 +8347,7 @@
       </c>
       <c r="E86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F86" t="inlineStr" s="2">
@@ -8367,22 +8367,22 @@
       </c>
       <c r="I86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">World Art Day</t>
+          <t xml:space="preserve">Primary Sports Day 2027</t>
         </is>
       </c>
       <c r="J86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ワールド・アート・デー</t>
+          <t xml:space="preserve">小学部運動会 2027</t>
         </is>
       </c>
       <c r="K86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students celebrate creativity through art activities, exhibitions, and opportunities to explore different artistic styles and cultures.</t>
+          <t xml:space="preserve">Students participate in a day of fun, fitness, and friendly competition while demonstrating teamwork, perseverance, and sportsmanship.</t>
         </is>
       </c>
       <c r="L86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">アート活動や展示を通して創造性を祝い、さまざまな芸術様式や文化に触れます。</t>
+          <t xml:space="preserve">チームワーク、粘り強さ、スポーツマンシップを発揮しながら、楽しく体を動かし、仲間と競い合う一日を過ごします。</t>
         </is>
       </c>
       <c r="M86" t="inlineStr" s="2">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="O86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-15-world-art-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-03-primary-sports-day-2027.webp</t>
         </is>
       </c>
       <c r="P86" t="inlineStr" s="2">
@@ -8424,17 +8424,17 @@
     <row r="87">
       <c r="A87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-16-foundation-field-trip</t>
+          <t xml:space="preserve">2027-04-15-world-art-day</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-16</t>
+          <t xml:space="preserve">2027-04-15</t>
         </is>
       </c>
       <c r="C87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-16</t>
+          <t xml:space="preserve">2027-04-15</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="3">
@@ -8444,7 +8444,7 @@
       </c>
       <c r="E87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr" s="2">
@@ -8464,22 +8464,22 @@
       </c>
       <c r="I87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Foundation Field Trip</t>
+          <t xml:space="preserve">World Art Day</t>
         </is>
       </c>
       <c r="J87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ファウンデーション校外学習</t>
+          <t xml:space="preserve">ワールド・アート・デー</t>
         </is>
       </c>
       <c r="K87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Our youngest learners will enjoy an age-appropriate educational excursion that supports classroom learning through hands-on experiences.</t>
+          <t xml:space="preserve">Students celebrate creativity through art activities, exhibitions, and opportunities to explore different artistic styles and cultures.</t>
         </is>
       </c>
       <c r="L87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">年少の子どもたちが、年齢に合った校外学習に出かけ、体験を通して教室での学びを深めます。</t>
+          <t xml:space="preserve">アート活動や展示を通して創造性を祝い、さまざまな芸術様式や文化に触れます。</t>
         </is>
       </c>
       <c r="M87" t="inlineStr" s="2">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="O87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-16-foundation-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-15-world-art-day.webp</t>
         </is>
       </c>
       <c r="P87" t="inlineStr" s="2">
@@ -8521,17 +8521,17 @@
     <row r="88">
       <c r="A88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-21-hackathon-hour-of-code</t>
+          <t xml:space="preserve">2027-04-16-foundation-field-trip</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-21</t>
+          <t xml:space="preserve">2027-04-16</t>
         </is>
       </c>
       <c r="C88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-21</t>
+          <t xml:space="preserve">2027-04-16</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="3">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="E88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G88" t="inlineStr" s="2">
@@ -8561,22 +8561,22 @@
       </c>
       <c r="I88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hackathon (Hour of Code)</t>
+          <t xml:space="preserve">Foundation Field Trip</t>
         </is>
       </c>
       <c r="J88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ハッカソン（Hour of Code）</t>
+          <t xml:space="preserve">ファウンデーション校外学習</t>
         </is>
       </c>
       <c r="K88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in an engaging Hour of Code challenge, using creativity and problem-solving skills to build simple coding projects. This event encourages computational thinking, teamwork, and confidence in technology in a fun and supportive environment.</t>
+          <t xml:space="preserve">Our youngest learners will enjoy an age-appropriate educational excursion that supports classroom learning through hands-on experiences.</t>
         </is>
       </c>
       <c r="L88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hour of Codeチャレンジに参加し、創造性と問題解決力を生かして簡単なプログラミング作品を作ります。楽しく支え合う環境の中で、コンピュテーショナル・シンキング、チームワーク、テクノロジーへの自信を育みます。</t>
+          <t xml:space="preserve">年少の子どもたちが、年齢に合った校外学習に出かけ、体験を通して教室での学びを深めます。</t>
         </is>
       </c>
       <c r="M88" t="inlineStr" s="2">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="O88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-21-hackathon-hour-of-code.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-16-foundation-field-trip.webp</t>
         </is>
       </c>
       <c r="P88" t="inlineStr" s="2">
@@ -8618,17 +8618,17 @@
     <row r="89">
       <c r="A89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-22-biology-ia-prep-field-trip-shore-ecosystem</t>
+          <t xml:space="preserve">2027-04-21-hackathon-hour-of-code</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-22</t>
+          <t xml:space="preserve">2027-04-21</t>
         </is>
       </c>
       <c r="C89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-22</t>
+          <t xml:space="preserve">2027-04-21</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="3">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="E89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F89" t="inlineStr" s="2">
@@ -8658,22 +8658,22 @@
       </c>
       <c r="I89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Biology IA Prep. Field Trip: Shore Ecosystem</t>
+          <t xml:space="preserve">Hackathon (Hour of Code)</t>
         </is>
       </c>
       <c r="J89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">生物IA準備校外学習：海岸生態系調査</t>
+          <t xml:space="preserve">ハッカソン（Hour of Code）</t>
         </is>
       </c>
       <c r="K89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 11 and 12 Biology students will visit a shore ecosystem to prepare for their Biology Internal Assessment by collecting fieldwork data and practicing research methods.</t>
+          <t xml:space="preserve">Students will take part in an engaging Hour of Code challenge, using creativity and problem-solving skills to build simple coding projects. This event encourages computational thinking, teamwork, and confidence in technology in a fun and supportive environment.</t>
         </is>
       </c>
       <c r="L89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11・12年生の生物履修者が海岸の生態系を訪れ、フィールドワークでのデータ収集や研究手法の練習を通して、生物の内部評価（IA）に向けた準備を行います。</t>
+          <t xml:space="preserve">Hour of Codeチャレンジに参加し、創造性と問題解決力を生かして簡単なプログラミング作品を作ります。楽しく支え合う環境の中で、コンピュテーショナル・シンキング、チームワーク、テクノロジーへの自信を育みます。</t>
         </is>
       </c>
       <c r="M89" t="inlineStr" s="2">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="O89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-22-biology-ia-prep-field-trip-shore-ecosystem.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-21-hackathon-hour-of-code.webp</t>
         </is>
       </c>
       <c r="P89" t="inlineStr" s="2">
@@ -8715,17 +8715,17 @@
     <row r="90">
       <c r="A90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-23-g12-celebration</t>
+          <t xml:space="preserve">2027-04-22-biology-ia-prep-field-trip-shore-ecosystem</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-23</t>
+          <t xml:space="preserve">2027-04-22</t>
         </is>
       </c>
       <c r="C90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-23</t>
+          <t xml:space="preserve">2027-04-22</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="3">
@@ -8755,22 +8755,22 @@
       </c>
       <c r="I90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G12 Celebration</t>
+          <t xml:space="preserve">Biology IA Prep. Field Trip: Shore Ecosystem</t>
         </is>
       </c>
       <c r="J90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G12修了記念イベント</t>
+          <t xml:space="preserve">生物IA準備校外学習：海岸生態系調査</t>
         </is>
       </c>
       <c r="K90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 12 students will take part in a Graduation Walk as the school community celebrates them ahead of graduation.</t>
+          <t xml:space="preserve">Grade 11 and 12 Biology students will visit a shore ecosystem to prepare for their Biology Internal Assessment by collecting fieldwork data and practicing research methods.</t>
         </is>
       </c>
       <c r="L90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">卒業を前に、12年生がグラデュエーション・ウォークに参加し、学校コミュニティ全体でお祝いします。</t>
+          <t xml:space="preserve">11・12年生の生物履修者が海岸の生態系を訪れ、フィールドワークでのデータ収集や研究手法の練習を通して、生物の内部評価（IA）に向けた準備を行います。</t>
         </is>
       </c>
       <c r="M90" t="inlineStr" s="2">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="O90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-23-g12-celebration.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-22-biology-ia-prep-field-trip-shore-ecosystem.webp</t>
         </is>
       </c>
       <c r="P90" t="inlineStr" s="2">
@@ -8812,17 +8812,17 @@
     <row r="91">
       <c r="A91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-26-grade-4-5-camping-trip</t>
+          <t xml:space="preserve">2027-04-23-g12-celebration</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-26</t>
+          <t xml:space="preserve">2027-04-23</t>
         </is>
       </c>
       <c r="C91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-27</t>
+          <t xml:space="preserve">2027-04-23</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="3">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="E91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F91" t="inlineStr" s="2">
@@ -8852,22 +8852,22 @@
       </c>
       <c r="I91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 4, 5 Camping Trip</t>
+          <t xml:space="preserve">G12 Celebration</t>
         </is>
       </c>
       <c r="J91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4・5年生キャンプ</t>
+          <t xml:space="preserve">G12修了記念イベント</t>
         </is>
       </c>
       <c r="K91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students enjoy an outdoor learning experience that promotes independence, teamwork, resilience, and a connection with nature.</t>
+          <t xml:space="preserve">Grade 12 students will take part in a Graduation Walk as the school community celebrates them ahead of graduation.</t>
         </is>
       </c>
       <c r="L91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">自立心、チームワーク、たくましさ、自然とのつながりを育む野外学習を楽しみます。</t>
+          <t xml:space="preserve">卒業を前に、12年生がグラデュエーション・ウォークに参加し、学校コミュニティ全体でお祝いします。</t>
         </is>
       </c>
       <c r="M91" t="inlineStr" s="2">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="O91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-26-grade-4-5-camping-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-23-g12-celebration.webp</t>
         </is>
       </c>
       <c r="P91" t="inlineStr" s="2">
@@ -8909,19 +8909,19 @@
     <row r="92">
       <c r="A92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-27-choir-and-orchestra-concert</t>
+          <t xml:space="preserve">2027-04-26-grade-4-5-camping-trip</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">2027-04-26</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">2027-04-27</t>
-        </is>
-      </c>
       <c r="D92" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
@@ -8929,12 +8929,12 @@
       </c>
       <c r="E92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G92" t="inlineStr" s="2">
@@ -8949,22 +8949,22 @@
       </c>
       <c r="I92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choir and Orchestra Concert</t>
+          <t xml:space="preserve">Grade 4, 5 Camping Trip</t>
         </is>
       </c>
       <c r="J92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合唱・オーケストラコンサート</t>
+          <t xml:space="preserve">4・5年生キャンプ</t>
         </is>
       </c>
       <c r="K92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choir class and orchestra club will perform the music repertoire they have been rehearsing for an audience of family, peers and teachers.</t>
+          <t xml:space="preserve">Students enjoy an outdoor learning experience that promotes independence, teamwork, resilience, and a connection with nature.</t>
         </is>
       </c>
       <c r="L92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合唱クラスとオーケストラクラブが、練習を重ねてきた曲目をご家族、友人、教員の前で演奏します。</t>
+          <t xml:space="preserve">自立心、チームワーク、たくましさ、自然とのつながりを育む野外学習を楽しみます。</t>
         </is>
       </c>
       <c r="M92" t="inlineStr" s="2">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="O92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-27-choir-and-orchestra-concert.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-26-grade-4-5-camping-trip.webp</t>
         </is>
       </c>
       <c r="P92" t="inlineStr" s="2">
@@ -9006,17 +9006,17 @@
     <row r="93">
       <c r="A93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-30-science-fair</t>
+          <t xml:space="preserve">2027-04-27-choir-and-orchestra-concert</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-30</t>
+          <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
       <c r="C93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-30</t>
+          <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="3">
@@ -9046,22 +9046,22 @@
       </c>
       <c r="I93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Science Fair</t>
+          <t xml:space="preserve">Choir and Orchestra Concert</t>
         </is>
       </c>
       <c r="J93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">サイエンスフェア</t>
+          <t xml:space="preserve">合唱・オーケストラコンサート</t>
         </is>
       </c>
       <c r="K93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will share their science projects and investigations with the school community, showcasing their research, creativity, and scientific thinking.</t>
+          <t xml:space="preserve">Choir class and orchestra club will perform the music repertoire they have been rehearsing for an audience of family, peers and teachers.</t>
         </is>
       </c>
       <c r="L93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">理科のプロジェクトや探究の成果を学校コミュニティに発表し、研究、創造性、科学的思考を披露します。</t>
+          <t xml:space="preserve">合唱クラスとオーケストラクラブが、練習を重ねてきた曲目をご家族、友人、教員の前で演奏します。</t>
         </is>
       </c>
       <c r="M93" t="inlineStr" s="2">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="O93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-30-science-fair.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-27-choir-and-orchestra-concert.webp</t>
         </is>
       </c>
       <c r="P93" t="inlineStr" s="2">
@@ -9103,17 +9103,17 @@
     <row r="94">
       <c r="A94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-17-friendly-basketball-tournament-internal</t>
+          <t xml:space="preserve">2027-04-30-science-fair</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-17</t>
+          <t xml:space="preserve">2027-04-30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-21</t>
+          <t xml:space="preserve">2027-04-30</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="3">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="F94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G94" t="inlineStr" s="2">
@@ -9143,22 +9143,22 @@
       </c>
       <c r="I94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Friendly Basketball Tournament (Internal)</t>
+          <t xml:space="preserve">Science Fair</t>
         </is>
       </c>
       <c r="J94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内バスケットボール大会</t>
+          <t xml:space="preserve">サイエンスフェア</t>
         </is>
       </c>
       <c r="K94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in a friendly internal basketball tournament, promoting teamwork, sportsmanship, and school spirit.</t>
+          <t xml:space="preserve">Students will share their science projects and investigations with the school community, showcasing their research, creativity, and scientific thinking.</t>
         </is>
       </c>
       <c r="L94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内バスケットボール大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
+          <t xml:space="preserve">理科のプロジェクトや探究の成果を学校コミュニティに発表し、研究、創造性、科学的思考を披露します。</t>
         </is>
       </c>
       <c r="M94" t="inlineStr" s="2">
@@ -9173,7 +9173,7 @@
       </c>
       <c r="O94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-17-friendly-basketball-tournament-internal.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-30-science-fair.webp</t>
         </is>
       </c>
       <c r="P94" t="inlineStr" s="2">
@@ -9200,17 +9200,17 @@
     <row r="95">
       <c r="A95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-19-entrepreneurs-day</t>
+          <t xml:space="preserve">2027-05-17-friendly-basketball-tournament-internal</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-19</t>
+          <t xml:space="preserve">2027-05-17</t>
         </is>
       </c>
       <c r="C95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-20</t>
+          <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="3">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="E95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G95" t="inlineStr" s="2">
@@ -9240,22 +9240,22 @@
       </c>
       <c r="I95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Entrepreneurs Day</t>
+          <t xml:space="preserve">Friendly Basketball Tournament (Internal)</t>
         </is>
       </c>
       <c r="J95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">アントレプレナーシップ・デー</t>
+          <t xml:space="preserve">校内バスケットボール大会</t>
         </is>
       </c>
       <c r="K95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students develop and showcase business ideas while learning about creativity, financial literacy, problem-solving, and entrepreneurship.</t>
+          <t xml:space="preserve">Students will take part in a friendly internal basketball tournament, promoting teamwork, sportsmanship, and school spirit.</t>
         </is>
       </c>
       <c r="L95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">創造性、金融リテラシー、問題解決、起業家精神について学びながら、ビジネスのアイデアを考え、発表します。</t>
+          <t xml:space="preserve">校内バスケットボール大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
         </is>
       </c>
       <c r="M95" t="inlineStr" s="2">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="O95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-19-entrepreneurs-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-17-friendly-basketball-tournament-internal.webp</t>
         </is>
       </c>
       <c r="P95" t="inlineStr" s="2">
@@ -9297,17 +9297,17 @@
     <row r="96">
       <c r="A96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-21-collective-field-trip</t>
+          <t xml:space="preserve">2027-05-19-entrepreneurs-day</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-21</t>
+          <t xml:space="preserve">2027-05-19</t>
         </is>
       </c>
       <c r="C96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-21</t>
+          <t xml:space="preserve">2027-05-20</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="3">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="F96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G96" t="inlineStr" s="2">
@@ -9337,22 +9337,22 @@
       </c>
       <c r="I96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Collective Field Trip</t>
+          <t xml:space="preserve">Entrepreneurs Day</t>
         </is>
       </c>
       <c r="J96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合同校外学習</t>
+          <t xml:space="preserve">アントレプレナーシップ・デー</t>
         </is>
       </c>
       <c r="K96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students participate in a shared educational experience that promotes collaboration, inquiry, and real-world learning.</t>
+          <t xml:space="preserve">Students develop and showcase business ideas while learning about creativity, financial literacy, problem-solving, and entrepreneurship.</t>
         </is>
       </c>
       <c r="L96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">協働、探究、実社会での学びを促す合同の学習体験に参加します。</t>
+          <t xml:space="preserve">創造性、金融リテラシー、問題解決、起業家精神について学びながら、ビジネスのアイデアを考え、発表します。</t>
         </is>
       </c>
       <c r="M96" t="inlineStr" s="2">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="O96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-21-collective-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-19-entrepreneurs-day.webp</t>
         </is>
       </c>
       <c r="P96" t="inlineStr" s="2">
@@ -9394,17 +9394,17 @@
     <row r="97">
       <c r="A97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-22-saturday-school-last-day-event</t>
+          <t xml:space="preserve">2027-05-21-collective-field-trip</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
       <c r="C97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="3">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="E97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F97" t="inlineStr" s="2">
@@ -9434,22 +9434,22 @@
       </c>
       <c r="I97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saturday School Last Day Event</t>
+          <t xml:space="preserve">Collective Field Trip</t>
         </is>
       </c>
       <c r="J97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">土曜校最終日イベント</t>
+          <t xml:space="preserve">合同校外学習</t>
         </is>
       </c>
       <c r="K97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in a relaxed final Saturday School session, with leisure activities at school to celebrate the last day.</t>
+          <t xml:space="preserve">Students participate in a shared educational experience that promotes collaboration, inquiry, and real-world learning.</t>
         </is>
       </c>
       <c r="L97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">土曜校の最終日を、校内でのレクリエーション活動とともにリラックスして過ごし、お祝いします。</t>
+          <t xml:space="preserve">協働、探究、実社会での学びを促す合同の学習体験に参加します。</t>
         </is>
       </c>
       <c r="M97" t="inlineStr" s="2">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="O97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-22-saturday-school-last-day-event.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-21-collective-field-trip.webp</t>
         </is>
       </c>
       <c r="P97" t="inlineStr" s="2">
@@ -9491,17 +9491,17 @@
     <row r="98">
       <c r="A98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-24-concept-con-future-focus</t>
+          <t xml:space="preserve">2027-05-22-saturday-school-last-day-event</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-24</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="C98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-28</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="3">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="E98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F98" t="inlineStr" s="2">
@@ -9531,22 +9531,22 @@
       </c>
       <c r="I98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Concept Con (Future Focus)</t>
+          <t xml:space="preserve">Saturday School Last Day Event</t>
         </is>
       </c>
       <c r="J98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">コンセプト・コン（未来を考える）</t>
+          <t xml:space="preserve">土曜校最終日イベント</t>
         </is>
       </c>
       <c r="K98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students investigate future possibilities, innovations, and solutions to real-world challenges through inquiry-based projects and presentations.</t>
+          <t xml:space="preserve">Students will take part in a relaxed final Saturday School session, with leisure activities at school to celebrate the last day.</t>
         </is>
       </c>
       <c r="L98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">探究型のプロジェクトや発表を通して、未来の可能性、イノベーション、現実の課題の解決策について考えます。</t>
+          <t xml:space="preserve">土曜校の最終日を、校内でのレクリエーション活動とともにリラックスして過ごし、お祝いします。</t>
         </is>
       </c>
       <c r="M98" t="inlineStr" s="2">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="O98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-24-concept-con-future-focus.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-22-saturday-school-last-day-event.webp</t>
         </is>
       </c>
       <c r="P98" t="inlineStr" s="2">
@@ -9588,17 +9588,17 @@
     <row r="99">
       <c r="A99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-28-g12-graduation-with-performances</t>
+          <t xml:space="preserve">2027-05-24-concept-con-future-focus</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-29</t>
+          <t xml:space="preserve">2027-05-24</t>
         </is>
       </c>
       <c r="C99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-29</t>
+          <t xml:space="preserve">2027-05-28</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="3">
@@ -9608,12 +9608,12 @@
       </c>
       <c r="E99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G99" t="inlineStr" s="2">
@@ -9623,27 +9623,27 @@
       </c>
       <c r="H99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">changed</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G12 Graduation with Performances</t>
+          <t xml:space="preserve">Concept Con (Future Focus)</t>
         </is>
       </c>
       <c r="J99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G12卒業式・記念パフォーマンス</t>
+          <t xml:space="preserve">コンセプト・コン（未来を考える）</t>
         </is>
       </c>
       <c r="K99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 12 students will celebrate their graduation with a formal ceremony featuring student performances and the wider school community.</t>
+          <t xml:space="preserve">Students investigate future possibilities, innovations, and solutions to real-world challenges through inquiry-based projects and presentations.</t>
         </is>
       </c>
       <c r="L99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12年生が、生徒によるパフォーマンスを交えた式典で、学校コミュニティ全体とともに卒業を祝います。</t>
+          <t xml:space="preserve">探究型のプロジェクトや発表を通して、未来の可能性、イノベーション、現実の課題の解決策について考えます。</t>
         </is>
       </c>
       <c r="M99" t="inlineStr" s="2">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="O99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-28-g12-graduation-with-performances.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-24-concept-con-future-focus.webp</t>
         </is>
       </c>
       <c r="P99" t="inlineStr" s="2">
@@ -9685,17 +9685,17 @@
     <row r="100">
       <c r="A100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-03-celebration-of-learning-prep</t>
+          <t xml:space="preserve">2027-05-28-g12-graduation-with-performances</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-03</t>
+          <t xml:space="preserve">2027-05-29</t>
         </is>
       </c>
       <c r="C100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-03</t>
+          <t xml:space="preserve">2027-05-29</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="3">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="E100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G100" t="inlineStr" s="2">
@@ -9720,27 +9720,27 @@
       </c>
       <c r="H100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">changed</t>
         </is>
       </c>
       <c r="I100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Celebration of Learning Prep</t>
+          <t xml:space="preserve">G12 Graduation with Performances</t>
         </is>
       </c>
       <c r="J100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学びの発表会準備</t>
+          <t xml:space="preserve">G12卒業式・記念パフォーマンス</t>
         </is>
       </c>
       <c r="K100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students help prepare the school for the Celebration of Learning by organizing learning spaces, setting up displays, arranging materials, and ensuring classrooms and common areas are ready to welcome visitors. This preparation helps create an engaging and welcoming environment for families and guests.</t>
+          <t xml:space="preserve">Grade 12 students will celebrate their graduation with a formal ceremony featuring student performances and the wider school community.</t>
         </is>
       </c>
       <c r="L100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学びの発表会に向けて、学習スペースの整理、展示の設営、資料の準備を行い、教室や共用エリアで来場者をお迎えできるよう整えます。ご家族やお客様にとって魅力的で温かな空間づくりにつながります。</t>
+          <t xml:space="preserve">12年生が、生徒によるパフォーマンスを交えた式典で、学校コミュニティ全体とともに卒業を祝います。</t>
         </is>
       </c>
       <c r="M100" t="inlineStr" s="2">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="O100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-03-celebration-of-learning-prep.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-28-g12-graduation-with-performances.webp</t>
         </is>
       </c>
       <c r="P100" t="inlineStr" s="2">
@@ -9782,7 +9782,7 @@
     <row r="101">
       <c r="A101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-03-ukulele-concert</t>
+          <t xml:space="preserve">2027-06-03-celebration-of-learning-prep</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="3">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-04</t>
+          <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="3">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G101" t="inlineStr" s="2">
@@ -9822,22 +9822,22 @@
       </c>
       <c r="I101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ukulele Concert</t>
+          <t xml:space="preserve">Celebration of Learning Prep</t>
         </is>
       </c>
       <c r="J101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ウクレレコンサート</t>
+          <t xml:space="preserve">学びの発表会準備</t>
         </is>
       </c>
       <c r="K101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students perform musical pieces they have learned throughout the year, demonstrating their growth, confidence, and musical skills.</t>
+          <t xml:space="preserve">Students help prepare the school for the Celebration of Learning by organizing learning spaces, setting up displays, arranging materials, and ensuring classrooms and common areas are ready to welcome visitors. This preparation helps create an engaging and welcoming environment for families and guests.</t>
         </is>
       </c>
       <c r="L101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一年を通して学んだ曲を演奏し、成長、自信、音楽の技能を披露します。</t>
+          <t xml:space="preserve">学びの発表会に向けて、学習スペースの整理、展示の設営、資料の準備を行い、教室や共用エリアで来場者をお迎えできるよう整えます。ご家族やお客様にとって魅力的で温かな空間づくりにつながります。</t>
         </is>
       </c>
       <c r="M101" t="inlineStr" s="2">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="O101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-03-ukulele-concert.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-03-celebration-of-learning-prep.webp</t>
         </is>
       </c>
       <c r="P101" t="inlineStr" s="2">
@@ -9879,19 +9879,19 @@
     <row r="102">
       <c r="A102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-04-celebration-of-learning</t>
+          <t xml:space="preserve">2027-06-03-ukulele-concert</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">2027-06-03</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">2027-06-04</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">2027-06-04</t>
-        </is>
-      </c>
       <c r="D102" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="E102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F102" t="inlineStr" s="2">
@@ -9919,22 +9919,22 @@
       </c>
       <c r="I102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Celebration of Learning</t>
+          <t xml:space="preserve">Ukulele Concert</t>
         </is>
       </c>
       <c r="J102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学びの発表会</t>
+          <t xml:space="preserve">ウクレレコンサート</t>
         </is>
       </c>
       <c r="K102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The school community will celebrate learning as students share projects and exhibitions, including PYPX, MYPX, CAS, EE, TOK and Foundation to 4 projects.</t>
+          <t xml:space="preserve">Students perform musical pieces they have learned throughout the year, demonstrating their growth, confidence, and musical skills.</t>
         </is>
       </c>
       <c r="L102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PYPX、MYPX、CAS、EE、TOK、ファウンデーション～4年生のプロジェクトなど、生徒の作品や展示を通して学校コミュニティ全体で学びを祝います。</t>
+          <t xml:space="preserve">一年を通して学んだ曲を演奏し、成長、自信、音楽の技能を披露します。</t>
         </is>
       </c>
       <c r="M102" t="inlineStr" s="2">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="O102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-04-celebration-of-learning.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-03-ukulele-concert.webp</t>
         </is>
       </c>
       <c r="P102" t="inlineStr" s="2">
@@ -9976,17 +9976,17 @@
     <row r="103">
       <c r="A103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-05-sat-test-7</t>
+          <t xml:space="preserve">2027-06-04-celebration-of-learning</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-05</t>
+          <t xml:space="preserve">2027-06-04</t>
         </is>
       </c>
       <c r="C103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-05</t>
+          <t xml:space="preserve">2027-06-04</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="3">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="E103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G103" t="inlineStr" s="2">
@@ -10016,22 +10016,22 @@
       </c>
       <c r="I103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT Test #7</t>
+          <t xml:space="preserve">Celebration of Learning</t>
         </is>
       </c>
       <c r="J103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT試験 第7回</t>
+          <t xml:space="preserve">学びの発表会</t>
         </is>
       </c>
       <c r="K103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
+          <t xml:space="preserve">The school community will celebrate learning as students share projects and exhibitions, including PYPX, MYPX, CAS, EE, TOK and Foundation to 4 projects.</t>
         </is>
       </c>
       <c r="L103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
+          <t xml:space="preserve">PYPX、MYPX、CAS、EE、TOK、ファウンデーション～4年生のプロジェクトなど、生徒の作品や展示を通して学校コミュニティ全体で学びを祝います。</t>
         </is>
       </c>
       <c r="M103" t="inlineStr" s="2">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="O103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-05-sat-test-7.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-04-celebration-of-learning.webp</t>
         </is>
       </c>
       <c r="P103" t="inlineStr" s="2">
@@ -10073,17 +10073,17 @@
     <row r="104">
       <c r="A104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-17-eagle-bucks-store</t>
+          <t xml:space="preserve">2027-06-05-sat-test-7</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-17</t>
+          <t xml:space="preserve">2027-06-05</t>
         </is>
       </c>
       <c r="C104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-17</t>
+          <t xml:space="preserve">2027-06-05</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="3">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="E104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F104" t="inlineStr" s="2">
@@ -10113,22 +10113,22 @@
       </c>
       <c r="I104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Eagle Bucks Store</t>
+          <t xml:space="preserve">SAT Test #7</t>
         </is>
       </c>
       <c r="J104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">イーグルバックス・ストア</t>
+          <t xml:space="preserve">SAT試験 第7回</t>
         </is>
       </c>
       <c r="K104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
+          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
         </is>
       </c>
       <c r="L104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
+          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
         </is>
       </c>
       <c r="M104" t="inlineStr" s="2">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="O104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-17-eagle-bucks-store.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-05-sat-test-7.webp</t>
         </is>
       </c>
       <c r="P104" t="inlineStr" s="2">
@@ -10170,17 +10170,17 @@
     <row r="105">
       <c r="A105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-18-kindergarten-and-grade-5-graduation</t>
+          <t xml:space="preserve">2027-06-17-eagle-bucks-store</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-18</t>
+          <t xml:space="preserve">2027-06-17</t>
         </is>
       </c>
       <c r="C105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-18</t>
+          <t xml:space="preserve">2027-06-17</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="3">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="F105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G105" t="inlineStr" s="2">
@@ -10210,22 +10210,22 @@
       </c>
       <c r="I105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Kindergarten and Grade 5 Graduation</t>
+          <t xml:space="preserve">Eagle Bucks Store</t>
         </is>
       </c>
       <c r="J105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部・5年生卒業式</t>
+          <t xml:space="preserve">イーグルバックス・ストア</t>
         </is>
       </c>
       <c r="K105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students participate in graduation ceremonies to celebrate important milestones in their educational journey. The events recognize student growth, achievements, and readiness for the next stage of learning while bringing together families, staff, and the school community in celebration.</t>
+          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
         </is>
       </c>
       <c r="L105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学びの歩みにおける大切な節目を祝う卒業式に参加します。生徒の成長と成果、そして次のステージへの準備が整ったことを、ご家族、教職員、学校コミュニティが一堂に会して祝福します。</t>
+          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
         </is>
       </c>
       <c r="M105" t="inlineStr" s="2">
@@ -10240,7 +10240,7 @@
       </c>
       <c r="O105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-18-kindergarten-and-grade-5-graduation.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-17-eagle-bucks-store.webp</t>
         </is>
       </c>
       <c r="P105" t="inlineStr" s="2">
@@ -10267,7 +10267,7 @@
     <row r="106">
       <c r="A106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-18-primary-elc-year-end-performance</t>
+          <t xml:space="preserve">2027-06-18-kindergarten-and-grade-5-graduation</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="3">
@@ -10307,22 +10307,22 @@
       </c>
       <c r="I106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary &amp; ELC Year End Performance</t>
+          <t xml:space="preserve">Kindergarten and Grade 5 Graduation</t>
         </is>
       </c>
       <c r="J106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小学部・幼稚部年度末発表会</t>
+          <t xml:space="preserve">幼稚部・5年生卒業式</t>
         </is>
       </c>
       <c r="K106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students participate in music, dance, drama, and other performance activities to showcase their learning, creativity, and talents. These performances provide an opportunity to celebrate the school year and share achievements with families and the school community.</t>
+          <t xml:space="preserve">Students participate in graduation ceremonies to celebrate important milestones in their educational journey. The events recognize student growth, achievements, and readiness for the next stage of learning while bringing together families, staff, and the school community in celebration.</t>
         </is>
       </c>
       <c r="L106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">音楽、ダンス、演劇などのパフォーマンスを通して、学び、創造性、才能を披露します。一年の締めくくりを祝い、その成果をご家族や学校コミュニティと分かち合う機会です。</t>
+          <t xml:space="preserve">学びの歩みにおける大切な節目を祝う卒業式に参加します。生徒の成長と成果、そして次のステージへの準備が整ったことを、ご家族、教職員、学校コミュニティが一堂に会して祝福します。</t>
         </is>
       </c>
       <c r="M106" t="inlineStr" s="2">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="O106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-18-primary-elc-year-end-performance.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-18-kindergarten-and-grade-5-graduation.webp</t>
         </is>
       </c>
       <c r="P106" t="inlineStr" s="2">
@@ -10364,17 +10364,17 @@
     <row r="107">
       <c r="A107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-19-end-of-term-3-activity-g6-10</t>
+          <t xml:space="preserve">2027-06-18-primary-elc-year-end-performance</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-19</t>
+          <t xml:space="preserve">2027-06-18</t>
         </is>
       </c>
       <c r="C107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-19</t>
+          <t xml:space="preserve">2027-06-18</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="3">
@@ -10384,12 +10384,12 @@
       </c>
       <c r="E107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G107" t="inlineStr" s="2">
@@ -10404,22 +10404,22 @@
       </c>
       <c r="I107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">End of Term 3 Activity: G6-10</t>
+          <t xml:space="preserve">Primary &amp; ELC Year End Performance</t>
         </is>
       </c>
       <c r="J107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第3学期末行事：G6–10</t>
+          <t xml:space="preserve">小学部・幼稚部年度末発表会</t>
         </is>
       </c>
       <c r="K107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in an off-campus day trip outside Nagoya to celebrate the end of Term 3.</t>
+          <t xml:space="preserve">Students participate in music, dance, drama, and other performance activities to showcase their learning, creativity, and talents. These performances provide an opportunity to celebrate the school year and share achievements with families and the school community.</t>
         </is>
       </c>
       <c r="L107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第3学期の終わりを祝い、名古屋近郊への日帰り校外活動に参加します。</t>
+          <t xml:space="preserve">音楽、ダンス、演劇などのパフォーマンスを通して、学び、創造性、才能を披露します。一年の締めくくりを祝い、その成果をご家族や学校コミュニティと分かち合う機会です。</t>
         </is>
       </c>
       <c r="M107" t="inlineStr" s="2">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="O107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-19-end-of-term-3-activity-g6-10.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-18-primary-elc-year-end-performance.webp</t>
         </is>
       </c>
       <c r="P107" t="inlineStr" s="2">
@@ -10461,17 +10461,17 @@
     <row r="108">
       <c r="A108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-22-parent-teacher-conferences</t>
+          <t xml:space="preserve">2027-06-19-end-of-term-3-activity-g6-10</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-22</t>
+          <t xml:space="preserve">2027-06-19</t>
         </is>
       </c>
       <c r="C108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-23</t>
+          <t xml:space="preserve">2027-06-19</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="3">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="E108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H108" t="inlineStr" s="2">
@@ -10501,22 +10501,22 @@
       </c>
       <c r="I108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parent Teacher Conferences</t>
+          <t xml:space="preserve">End of Term 3 Activity: G6-10</t>
         </is>
       </c>
       <c r="J108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者面談</t>
+          <t xml:space="preserve">第3学期末行事：G6–10</t>
         </is>
       </c>
       <c r="K108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on these days.</t>
+          <t xml:space="preserve">Students will take part in an off-campus day trip outside Nagoya to celebrate the end of Term 3.</t>
         </is>
       </c>
       <c r="L108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。期間中、生徒は登校しません。</t>
+          <t xml:space="preserve">第3学期の終わりを祝い、名古屋近郊への日帰り校外活動に参加します。</t>
         </is>
       </c>
       <c r="M108" t="inlineStr" s="2">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="O108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-22-parent-teacher-conferences.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-19-end-of-term-3-activity-g6-10.webp</t>
         </is>
       </c>
       <c r="P108" t="inlineStr" s="2">
@@ -10558,17 +10558,17 @@
     <row r="109">
       <c r="A109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-28-summer-school</t>
+          <t xml:space="preserve">2027-06-22-parent-teacher-conferences</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-28</t>
+          <t xml:space="preserve">2027-06-22</t>
         </is>
       </c>
       <c r="C109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-07-18</t>
+          <t xml:space="preserve">2027-06-23</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="3">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="F109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="H109" t="inlineStr" s="2">
@@ -10598,22 +10598,22 @@
       </c>
       <c r="I109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Summer School</t>
+          <t xml:space="preserve">Parent Teacher Conferences</t>
         </is>
       </c>
       <c r="J109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">サマースクール</t>
+          <t xml:space="preserve">保護者面談</t>
         </is>
       </c>
       <c r="K109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Participate in fun English style summer camps that challenge students and help foster friendships and connections with others.</t>
+          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on these days.</t>
         </is>
       </c>
       <c r="L109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">英語で楽しく過ごすサマーキャンプに参加し、新たなことに挑戦しながら友情や人とのつながりを育みます。</t>
+          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。期間中、生徒は登校しません。</t>
         </is>
       </c>
       <c r="M109" t="inlineStr" s="2">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="O109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-28-summer-school.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-22-parent-teacher-conferences.webp</t>
         </is>
       </c>
       <c r="P109" t="inlineStr" s="2">
@@ -10655,95 +10655,192 @@
     <row r="110">
       <c r="A110" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2027-06-28-summer-school</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2027-06-28</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2027-07-18</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Whole School</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Summer School</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">サマースクール</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Participate in fun English style summer camps that challenge students and help foster friendships and connections with others.</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">英語で楽しく過ごすサマーキャンプに参加し、新たなことに挑戦しながら友情や人とのつながりを育みます。</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">compass/images/events/2027-06-28-summer-school.webp</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2027-07-20-summer-school</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr" s="3">
+      <c r="B111" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-07-20</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr" s="3">
+      <c r="C111" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-07-24</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr" s="2">
+      <c r="D111" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Whole School</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr" s="2">
+      <c r="F111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Summer School</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr" s="2">
+      <c r="J111" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">サマースクール</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr" s="2">
+      <c r="K111" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Participate in fun English style summer camps that challenge students and help foster friendships and connections with others.</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr" s="2">
+      <c r="L111" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">英語で楽しく過ごすサマーキャンプに参加し、新たなことに挑戦しながら友情や人とのつながりを育みます。</t>
         </is>
       </c>
-      <c r="M110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O110" t="inlineStr" s="2">
+      <c r="M111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">compass/images/events/2027-06-28-summer-school.webp</t>
         </is>
       </c>
-      <c r="P110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R110" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="S110" t="inlineStr" s="2">
+      <c r="P111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -11068,7 +11165,7 @@
       </c>
       <c r="B12" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-08</t>
+          <t xml:space="preserve">2027-01-07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">

--- a/admin/EIS-Compass-events.xlsx
+++ b/admin/EIS-Compass-events.xlsx
@@ -2022,17 +2022,17 @@
     <row r="21">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-09-eagle-bucks-store</t>
+          <t xml:space="preserve">2026-10-05-clubs-pause</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-09</t>
+          <t xml:space="preserve">2026-10-05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-09</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="3">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="E21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F21" t="inlineStr" s="2">
@@ -2062,22 +2062,22 @@
       </c>
       <c r="I21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Eagle Bucks Store</t>
+          <t xml:space="preserve">Clubs Pause</t>
         </is>
       </c>
       <c r="J21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">イーグルバックス・ストア</t>
+          <t xml:space="preserve">クラブ活動休止</t>
         </is>
       </c>
       <c r="K21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
+          <t xml:space="preserve">After-school clubs are paused during this period. Bus reminder: the afternoon Red bus runs only on club days, so it does not run while clubs are paused. Please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
         </is>
       </c>
       <c r="L21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
+          <t xml:space="preserve">この期間、放課後のクラブ活動はお休みです。【バスについて】午後の赤バスはクラブ活動がある日のみ運行するため、休止期間中は運行しません。午後の下校時は青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
         </is>
       </c>
       <c r="M21" t="inlineStr" s="2">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="O21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-09-eagle-bucks-store.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P21" t="inlineStr" s="2">
@@ -2119,32 +2119,32 @@
     <row r="22">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-19-elc-primary-curriculum-night</t>
+          <t xml:space="preserve">2026-10-09-eagle-bucks-store</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-19</t>
+          <t xml:space="preserve">2026-10-09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-19</t>
+          <t xml:space="preserve">2026-10-09</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">17:30-20:30</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G22" t="inlineStr" s="2">
@@ -2159,37 +2159,37 @@
       </c>
       <c r="I22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC &amp; Primary Curriculum Night</t>
+          <t xml:space="preserve">Eagle Bucks Store</t>
         </is>
       </c>
       <c r="J22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部・小学部カリキュラム説明会</t>
+          <t xml:space="preserve">イーグルバックス・ストア</t>
         </is>
       </c>
       <c r="K22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An evening to help families understand what children learn, how they learn, how progress is assessed, and how learning can be supported at home. Families will experience classroom activities, explore topics of interest, and ask questions. The evening begins with a welcome in the Community Room, followed by two breakout sessions and a panel Q&amp;A. Please complete the attendance and session selection form; sessions with limited interest may be cancelled.</t>
+          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
         </is>
       </c>
       <c r="L22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">お子さまが何を、どのように学んでいるのか、学習の進歩をどのように評価しているのか、ご家庭でどのように学びを支えられるのかについて理解を深めていただく会です。教室での活動を体験し、関心のあるテーマについて学び、質問していただけます。コミュニティルームでの開会の後、2つの分科会とパネル質疑応答を行います。参加確認・セッション選択フォームへのご回答をお願いいたします（参加希望者が少ないセッションは中止となる場合があります）。</t>
+          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
         </is>
       </c>
       <c r="M22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Community Room</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="N22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">コミュニティルーム</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="O22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-19-elc-primary-curriculum-night.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-09-eagle-bucks-store.webp</t>
         </is>
       </c>
       <c r="P22" t="inlineStr" s="2">
@@ -2216,7 +2216,7 @@
     <row r="23">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-19-parent-teacher-conferences</t>
+          <t xml:space="preserve">2026-10-19-elc-primary-curriculum-night</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="3">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="D23" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">17:30-20:30</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="2">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H23" t="inlineStr" s="2">
@@ -2256,37 +2256,37 @@
       </c>
       <c r="I23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parent Teacher Conferences</t>
+          <t xml:space="preserve">ELC &amp; Primary Curriculum Night</t>
         </is>
       </c>
       <c r="J23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者面談</t>
+          <t xml:space="preserve">幼稚部・小学部カリキュラム説明会</t>
         </is>
       </c>
       <c r="K23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on this day.</t>
+          <t xml:space="preserve">An evening to help families understand what children learn, how they learn, how progress is assessed, and how learning can be supported at home. Families will experience classroom activities, explore topics of interest, and ask questions. The evening begins with a welcome in the Community Room, followed by two breakout sessions and a panel Q&amp;A. Please complete the attendance and session selection form; sessions with limited interest may be cancelled.</t>
         </is>
       </c>
       <c r="L23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。当日、生徒は登校しません。</t>
+          <t xml:space="preserve">お子さまが何を、どのように学んでいるのか、学習の進歩をどのように評価しているのか、ご家庭でどのように学びを支えられるのかについて理解を深めていただく会です。教室での活動を体験し、関心のあるテーマについて学び、質問していただけます。コミュニティルームでの開会の後、2つの分科会とパネル質疑応答を行います。参加確認・セッション選択フォームへのご回答をお願いいたします（参加希望者が少ないセッションは中止となる場合があります）。</t>
         </is>
       </c>
       <c r="M23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Community Room</t>
         </is>
       </c>
       <c r="N23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">コミュニティルーム</t>
         </is>
       </c>
       <c r="O23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-19-parent-teacher-conferences.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-19-elc-primary-curriculum-night.webp</t>
         </is>
       </c>
       <c r="P23" t="inlineStr" s="2">
@@ -2313,17 +2313,17 @@
     <row r="24">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-20-secondary-curriculum-night</t>
+          <t xml:space="preserve">2026-10-19-parent-teacher-conferences</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-10-19</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-10-19</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="3">
@@ -2333,17 +2333,17 @@
       </c>
       <c r="E24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="H24" t="inlineStr" s="2">
@@ -2353,22 +2353,22 @@
       </c>
       <c r="I24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary Curriculum Night</t>
+          <t xml:space="preserve">Parent Teacher Conferences</t>
         </is>
       </c>
       <c r="J24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部カリキュラム説明会</t>
+          <t xml:space="preserve">保護者面談</t>
         </is>
       </c>
       <c r="K24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary parents are invited to Curriculum Night to learn more about subject expectations, learning goals, assessment, and support for students in Grades 6 to 10.</t>
+          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on this day.</t>
         </is>
       </c>
       <c r="L24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部の保護者の皆様を対象に、6～10年生の各教科で求められること、学習目標、評価、生徒への支援についてご説明します。</t>
+          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。当日、生徒は登校しません。</t>
         </is>
       </c>
       <c r="M24" t="inlineStr" s="2">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="O24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-20-secondary-curriculum-night.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-19-parent-teacher-conferences.webp</t>
         </is>
       </c>
       <c r="P24" t="inlineStr" s="2">
@@ -2410,17 +2410,17 @@
     <row r="25">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-21-college-fair</t>
+          <t xml:space="preserve">2026-10-20-secondary-curriculum-night</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="3">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="E25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G25" t="inlineStr" s="2">
@@ -2450,22 +2450,22 @@
       </c>
       <c r="I25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">College Fair</t>
+          <t xml:space="preserve">Secondary Curriculum Night</t>
         </is>
       </c>
       <c r="J25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">大学進学フェア</t>
+          <t xml:space="preserve">中等部カリキュラム説明会</t>
         </is>
       </c>
       <c r="K25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A special event where representatives from several international and Japanese universities visit our school to introduce their programs and admission opportunities. The fair is open to all students and parents, and students from other international schools in the area are also invited to attend.</t>
+          <t xml:space="preserve">Secondary parents are invited to Curriculum Night to learn more about subject expectations, learning goals, assessment, and support for students in Grades 6 to 10.</t>
         </is>
       </c>
       <c r="L25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国内外の複数の大学の担当者が来校し、各大学のプログラムや入学機会を紹介する特別イベントです。全生徒・保護者が参加でき、近隣のインターナショナルスクールの生徒もご招待しています。</t>
+          <t xml:space="preserve">中等部の保護者の皆様を対象に、6～10年生の各教科で求められること、学習目標、評価、生徒への支援についてご説明します。</t>
         </is>
       </c>
       <c r="M25" t="inlineStr" s="2">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="O25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-21-college-fair.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-20-secondary-curriculum-night.webp</t>
         </is>
       </c>
       <c r="P25" t="inlineStr" s="2">
@@ -2507,17 +2507,17 @@
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-23-nagoya-university-biology-laboratory-visit</t>
+          <t xml:space="preserve">2026-10-21-college-fair</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-23</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-23</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="3">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="F26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G26" t="inlineStr" s="2">
@@ -2547,22 +2547,22 @@
       </c>
       <c r="I26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Nagoya University Biology Laboratory Visit</t>
+          <t xml:space="preserve">College Fair</t>
         </is>
       </c>
       <c r="J26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">名古屋大学 生物学研究室訪問</t>
+          <t xml:space="preserve">大学進学フェア</t>
         </is>
       </c>
       <c r="K26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 11 and 12 Biology students will visit Nagoya University for a guided laboratory experience, connecting classroom learning with real-world scientific research.</t>
+          <t xml:space="preserve">A special event where representatives from several international and Japanese universities visit our school to introduce their programs and admission opportunities. The fair is open to all students and parents, and students from other international schools in the area are also invited to attend.</t>
         </is>
       </c>
       <c r="L26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11・12年生の生物履修者が名古屋大学を訪問し、研究室での体験を通して授業での学びと実際の科学研究を結びつけます。</t>
+          <t xml:space="preserve">国内外の複数の大学の担当者が来校し、各大学のプログラムや入学機会を紹介する特別イベントです。全生徒・保護者が参加でき、近隣のインターナショナルスクールの生徒もご招待しています。</t>
         </is>
       </c>
       <c r="M26" t="inlineStr" s="2">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="O26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-23-nagoya-university-biology-laboratory-visit.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-21-college-fair.webp</t>
         </is>
       </c>
       <c r="P26" t="inlineStr" s="2">
@@ -2604,17 +2604,17 @@
     <row r="27">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-25-pta-picnic</t>
+          <t xml:space="preserve">2026-10-23-nagoya-university-biology-laboratory-visit</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-25</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-25</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="3">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="E27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTA</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F27" t="inlineStr" s="2">
@@ -2644,22 +2644,22 @@
       </c>
       <c r="I27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTA Picnic</t>
+          <t xml:space="preserve">Nagoya University Biology Laboratory Visit</t>
         </is>
       </c>
       <c r="J27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTAピクニック</t>
+          <t xml:space="preserve">名古屋大学 生物学研究室訪問</t>
         </is>
       </c>
       <c r="K27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Families, students, and staff come together for a fun outdoor gathering that strengthens relationships and builds school community.</t>
+          <t xml:space="preserve">Grade 11 and 12 Biology students will visit Nagoya University for a guided laboratory experience, connecting classroom learning with real-world scientific research.</t>
         </is>
       </c>
       <c r="L27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ご家族、生徒、教職員が集まり、屋外で楽しく交流しながら絆を深め、学校コミュニティを育みます。</t>
+          <t xml:space="preserve">11・12年生の生物履修者が名古屋大学を訪問し、研究室での体験を通して授業での学びと実際の科学研究を結びつけます。</t>
         </is>
       </c>
       <c r="M27" t="inlineStr" s="2">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="O27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-25-pta-picnic.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-23-nagoya-university-biology-laboratory-visit.webp</t>
         </is>
       </c>
       <c r="P27" t="inlineStr" s="2">
@@ -2701,17 +2701,17 @@
     <row r="28">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-26-toyota-college-trip</t>
+          <t xml:space="preserve">2026-10-25-pta-picnic</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-26</t>
+          <t xml:space="preserve">2026-10-25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-26</t>
+          <t xml:space="preserve">2026-10-25</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="3">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="E28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">PTA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="2">
@@ -2741,22 +2741,22 @@
       </c>
       <c r="I28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Toyota College Trip</t>
+          <t xml:space="preserve">PTA Picnic</t>
         </is>
       </c>
       <c r="J28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">豊田高専見学</t>
+          <t xml:space="preserve">PTAピクニック</t>
         </is>
       </c>
       <c r="K28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 8 Science students will visit Toyota College for a curriculum-based learning experience connected to their science studies.</t>
+          <t xml:space="preserve">Families, students, and staff come together for a fun outdoor gathering that strengthens relationships and builds school community.</t>
         </is>
       </c>
       <c r="L28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8年生が理科の授業と関連したカリキュラムに基づく学習として、豊田高専を訪問します。</t>
+          <t xml:space="preserve">ご家族、生徒、教職員が集まり、屋外で楽しく交流しながら絆を深め、学校コミュニティを育みます。</t>
         </is>
       </c>
       <c r="M28" t="inlineStr" s="2">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="O28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-26-toyota-college-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-25-pta-picnic.webp</t>
         </is>
       </c>
       <c r="P28" t="inlineStr" s="2">
@@ -2798,17 +2798,17 @@
     <row r="29">
       <c r="A29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-30-sensory-wonderland</t>
+          <t xml:space="preserve">2026-10-26-toyota-college-trip</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-30</t>
+          <t xml:space="preserve">2026-10-26</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-30</t>
+          <t xml:space="preserve">2026-10-26</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="3">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="E29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="2">
@@ -2838,22 +2838,22 @@
       </c>
       <c r="I29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sensory Wonderland</t>
+          <t xml:space="preserve">Toyota College Trip</t>
         </is>
       </c>
       <c r="J29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">センサリー・ワンダーランド</t>
+          <t xml:space="preserve">豊田高専見学</t>
         </is>
       </c>
       <c r="K29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students explore a variety of interactive sensory experiences designed to engage curiosity, creativity, and learning through play.</t>
+          <t xml:space="preserve">Grade 8 Science students will visit Toyota College for a curriculum-based learning experience connected to their science studies.</t>
         </is>
       </c>
       <c r="L29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">好奇心と創造性を刺激し、遊びを通して学ぶ、さまざまな体験型の感覚活動を楽しみます。</t>
+          <t xml:space="preserve">8年生が理科の授業と関連したカリキュラムに基づく学習として、豊田高専を訪問します。</t>
         </is>
       </c>
       <c r="M29" t="inlineStr" s="2">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="O29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">compass/images/events/2026-10-26-toyota-college-trip.webp</t>
         </is>
       </c>
       <c r="P29" t="inlineStr" s="2">
@@ -2895,22 +2895,22 @@
     <row r="30">
       <c r="A30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-31-international-mindedness-festival</t>
+          <t xml:space="preserve">2026-10-26-clubs-resume</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-31</t>
+          <t xml:space="preserve">2026-10-26</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-31</t>
+          <t xml:space="preserve">2026-10-26</t>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">10:00-14:00</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="F30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G30" t="inlineStr" s="2">
@@ -2935,22 +2935,22 @@
       </c>
       <c r="I30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">International Mindedness Festival</t>
+          <t xml:space="preserve">Clubs Resume</t>
         </is>
       </c>
       <c r="J30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">インターナショナル・マインデッドネス・フェスティバル</t>
+          <t xml:space="preserve">クラブ活動再開</t>
         </is>
       </c>
       <c r="K30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This year’s theme is “Festivals and Holidays Around the World”. A Saturday family event celebrating traditions, cultures, stories, arts, music and celebrations from around the world, with student activities, cultural displays, performances, arts and crafts, and interactive booths. Clean-up runs from 14:00 to 15:00, and community members are welcome to help. ELC and Primary students must attend with a parent or guardian and may not be dropped off. School buses will not operate. More details will be shared soon.</t>
+          <t xml:space="preserve">After-school clubs start again today. Bus reminder: the afternoon Red bus runs only on club days. On other days, please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
         </is>
       </c>
       <c r="L30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">今年のテーマは「世界の祭りと祝日」です。世界各地の伝統、文化、物語、芸術、音楽、お祝いを紹介する、土曜日のご家族参加型イベントです。児童・生徒の活動、文化展示、パフォーマンス、工作、体験型ブースをお楽しみいただけます。午後2時～3時に片付けを行います（学校コミュニティの皆さまのご協力も歓迎します）。幼稚部・小学部の児童は必ず保護者同伴でご参加ください（お子さまだけを送り届けることはできません）。当日はスクールバスの運行はありません。詳細は近日中にお知らせします。</t>
+          <t xml:space="preserve">本日から放課後のクラブ活動が再開します。【バスについて】午後の赤バスはクラブ活動がある日のみ運行します。それ以外の日は、午後の下校時に青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
         </is>
       </c>
       <c r="M30" t="inlineStr" s="2">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="O30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-31-international-mindedness-festival.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P30" t="inlineStr" s="2">
@@ -2992,17 +2992,17 @@
     <row r="31">
       <c r="A31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-04-elc-sports-day-rehearsal-1</t>
+          <t xml:space="preserve">2026-10-30-sensory-wonderland</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-04</t>
+          <t xml:space="preserve">2026-10-30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-04</t>
+          <t xml:space="preserve">2026-10-30</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="3">
@@ -3032,22 +3032,22 @@
       </c>
       <c r="I31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC Sports Day Rehearsal #1</t>
+          <t xml:space="preserve">Sensory Wonderland</t>
         </is>
       </c>
       <c r="J31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部運動会リハーサル #1</t>
+          <t xml:space="preserve">センサリー・ワンダーランド</t>
         </is>
       </c>
       <c r="K31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">During Sports Day practice, students participate in a variety of physical activities, team games, relays, and event rehearsals in preparation for Sports Day. They develop teamwork, cooperation, sportsmanship, and physical fitness while learning event procedures, safety expectations, and cheering routines. Practice sessions help students build confidence and ensure they are prepared to participate successfully in the Sports Day celebration.</t>
+          <t xml:space="preserve">Students explore a variety of interactive sensory experiences designed to engage curiosity, creativity, and learning through play.</t>
         </is>
       </c>
       <c r="L31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会に向けた練習では、さまざまな運動、チームゲーム、リレー、種目のリハーサルに取り組みます。進行の流れ、安全面のルール、応援の仕方を学びながら、チームワーク、協調性、スポーツマンシップ、体力を養います。練習を通して自信をつけ、運動会当日に力を発揮できるよう準備します。</t>
+          <t xml:space="preserve">好奇心と創造性を刺激し、遊びを通して学ぶ、さまざまな体験型の感覚活動を楽しみます。</t>
         </is>
       </c>
       <c r="M31" t="inlineStr" s="2">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="O31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-04-elc-sports-day-rehearsal-1.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P31" t="inlineStr" s="2">
@@ -3089,32 +3089,32 @@
     <row r="32">
       <c r="A32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-05-toyota-museum-field-trip</t>
+          <t xml:space="preserve">2026-10-31-international-mindedness-festival</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-05</t>
+          <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-05</t>
+          <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">10:00-14:00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G32" t="inlineStr" s="2">
@@ -3129,22 +3129,22 @@
       </c>
       <c r="I32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Toyota Museum Field Trip</t>
+          <t xml:space="preserve">International Mindedness Festival</t>
         </is>
       </c>
       <c r="J32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">トヨタ博物館校外学習</t>
+          <t xml:space="preserve">インターナショナル・マインデッドネス・フェスティバル</t>
         </is>
       </c>
       <c r="K32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 9 students go to the Toyota museum down the road and view the exhibits taking some notes on machines they learned about.</t>
+          <t xml:space="preserve">This year’s theme is “Festivals and Holidays Around the World”. A Saturday family event celebrating traditions, cultures, stories, arts, music and celebrations from around the world, with student activities, cultural displays, performances, arts and crafts, and interactive booths. Clean-up runs from 14:00 to 15:00, and community members are welcome to help. ELC and Primary students must attend with a parent or guardian and may not be dropped off. School buses will not operate. More details will be shared soon.</t>
         </is>
       </c>
       <c r="L32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9年生が近くのトヨタの博物館を訪れ、授業で学んだ機械について展示を見学しながらメモを取ります。</t>
+          <t xml:space="preserve">今年のテーマは「世界の祭りと祝日」です。世界各地の伝統、文化、物語、芸術、音楽、お祝いを紹介する、土曜日のご家族参加型イベントです。児童・生徒の活動、文化展示、パフォーマンス、工作、体験型ブースをお楽しみいただけます。午後2時～3時に片付けを行います（学校コミュニティの皆さまのご協力も歓迎します）。幼稚部・小学部の児童は必ず保護者同伴でご参加ください（お子さまだけを送り届けることはできません）。当日はスクールバスの運行はありません。詳細は近日中にお知らせします。</t>
         </is>
       </c>
       <c r="M32" t="inlineStr" s="2">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="O32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-05-toyota-museum-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-31-international-mindedness-festival.webp</t>
         </is>
       </c>
       <c r="P32" t="inlineStr" s="2">
@@ -3186,17 +3186,17 @@
     <row r="33">
       <c r="A33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-06-extracurricular-activities-autumn-cas-project-su</t>
+          <t xml:space="preserve">2026-11-04-elc-sports-day-rehearsal-1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-06</t>
+          <t xml:space="preserve">2026-11-04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-06</t>
+          <t xml:space="preserve">2026-11-04</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="3">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="E33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">ELC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G33" t="inlineStr" s="2">
@@ -3226,22 +3226,22 @@
       </c>
       <c r="I33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Extracurricular Activities: Autumn CAS &amp; Project Support Fair</t>
+          <t xml:space="preserve">ELC Sports Day Rehearsal #1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">課外活動：秋のCAS・プロジェクトサポートフェア</t>
+          <t xml:space="preserve">幼稚部運動会リハーサル #1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary PTA Supported Event to help students understand various volunteering and CAS project opportunities in the community. Open to MYP and DP Students.</t>
+          <t xml:space="preserve">During Sports Day practice, students participate in a variety of physical activities, team games, relays, and event rehearsals in preparation for Sports Day. They develop teamwork, cooperation, sportsmanship, and physical fitness while learning event procedures, safety expectations, and cheering routines. Practice sessions help students build confidence and ensure they are prepared to participate successfully in the Sports Day celebration.</t>
         </is>
       </c>
       <c r="L33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部PTAの支援による行事で、地域でのさまざまなボランティアやCASプロジェクトの機会について知ることができます。MYP・DP生徒が対象です。</t>
+          <t xml:space="preserve">運動会に向けた練習では、さまざまな運動、チームゲーム、リレー、種目のリハーサルに取り組みます。進行の流れ、安全面のルール、応援の仕方を学びながら、チームワーク、協調性、スポーツマンシップ、体力を養います。練習を通して自信をつけ、運動会当日に力を発揮できるよう準備します。</t>
         </is>
       </c>
       <c r="M33" t="inlineStr" s="2">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="O33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-06-extracurricular-activities-autumn-cas-project-su.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-04-elc-sports-day-rehearsal-1.webp</t>
         </is>
       </c>
       <c r="P33" t="inlineStr" s="2">
@@ -3283,17 +3283,17 @@
     <row r="34">
       <c r="A34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-07-sat-test-4</t>
+          <t xml:space="preserve">2026-11-05-toyota-museum-field-trip</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-07</t>
+          <t xml:space="preserve">2026-11-05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-07</t>
+          <t xml:space="preserve">2026-11-05</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="3">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="E34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F34" t="inlineStr" s="2">
@@ -3323,22 +3323,22 @@
       </c>
       <c r="I34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT Test #4</t>
+          <t xml:space="preserve">Toyota Museum Field Trip</t>
         </is>
       </c>
       <c r="J34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT試験 第4回</t>
+          <t xml:space="preserve">トヨタ博物館校外学習</t>
         </is>
       </c>
       <c r="K34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
+          <t xml:space="preserve">Grade 9 students go to the Toyota museum down the road and view the exhibits taking some notes on machines they learned about.</t>
         </is>
       </c>
       <c r="L34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
+          <t xml:space="preserve">9年生が近くのトヨタの博物館を訪れ、授業で学んだ機械について展示を見学しながらメモを取ります。</t>
         </is>
       </c>
       <c r="M34" t="inlineStr" s="2">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="O34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-07-sat-test-4.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-05-toyota-museum-field-trip.webp</t>
         </is>
       </c>
       <c r="P34" t="inlineStr" s="2">
@@ -3380,17 +3380,17 @@
     <row r="35">
       <c r="A35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-09-wellbeing-week</t>
+          <t xml:space="preserve">2026-11-06-extracurricular-activities-autumn-cas-project-su</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-09</t>
+          <t xml:space="preserve">2026-11-06</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-13</t>
+          <t xml:space="preserve">2026-11-06</t>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="3">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="E35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G35" t="inlineStr" s="2">
@@ -3420,22 +3420,22 @@
       </c>
       <c r="I35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wellbeing Week</t>
+          <t xml:space="preserve">Extracurricular Activities: Autumn CAS &amp; Project Support Fair</t>
         </is>
       </c>
       <c r="J35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ウェルビーイング週間</t>
+          <t xml:space="preserve">課外活動：秋のCAS・プロジェクトサポートフェア</t>
         </is>
       </c>
       <c r="K35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A school wide event focused on raising awareness for wellbeing.</t>
+          <t xml:space="preserve">Secondary PTA Supported Event to help students understand various volunteering and CAS project opportunities in the community. Open to MYP and DP Students.</t>
         </is>
       </c>
       <c r="L35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ウェルビーイング（心身の健康）への意識を高めることを目的とした全校行事です。</t>
+          <t xml:space="preserve">中等部PTAの支援による行事で、地域でのさまざまなボランティアやCASプロジェクトの機会について知ることができます。MYP・DP生徒が対象です。</t>
         </is>
       </c>
       <c r="M35" t="inlineStr" s="2">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="O35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-09-wellbeing-week.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-06-extracurricular-activities-autumn-cas-project-su.webp</t>
         </is>
       </c>
       <c r="P35" t="inlineStr" s="2">
@@ -3477,17 +3477,17 @@
     <row r="36">
       <c r="A36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-09-concept-con-wellbeing</t>
+          <t xml:space="preserve">2026-11-07-sat-test-4</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-09</t>
+          <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-13</t>
+          <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="3">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="E36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F36" t="inlineStr" s="2">
@@ -3517,22 +3517,22 @@
       </c>
       <c r="I36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Concept Con (Wellbeing)</t>
+          <t xml:space="preserve">SAT Test #4</t>
         </is>
       </c>
       <c r="J36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">コンセプト・コン（ウェルビーイング）</t>
+          <t xml:space="preserve">SAT試験 第4回</t>
         </is>
       </c>
       <c r="K36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Primary Concept Conference on the theme of wellbeing, held during Wellbeing Week.</t>
+          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
         </is>
       </c>
       <c r="L36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ウェルビーイング週間に合わせて行う、小学部のコンセプト・カンファレンス（テーマ：ウェルビーイング）です。</t>
+          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
         </is>
       </c>
       <c r="M36" t="inlineStr" s="2">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="O36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">compass/images/events/2026-11-07-sat-test-4.webp</t>
         </is>
       </c>
       <c r="P36" t="inlineStr" s="2">
@@ -3574,17 +3574,17 @@
     <row r="37">
       <c r="A37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-11-elc-sports-day-rehearsal-2</t>
+          <t xml:space="preserve">2026-11-09-wellbeing-week</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-11</t>
+          <t xml:space="preserve">2026-11-09</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-11</t>
+          <t xml:space="preserve">2026-11-13</t>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="3">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="E37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F37" t="inlineStr" s="2">
@@ -3614,22 +3614,22 @@
       </c>
       <c r="I37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC Sports Day Rehearsal #2</t>
+          <t xml:space="preserve">Wellbeing Week</t>
         </is>
       </c>
       <c r="J37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部運動会リハーサル #2</t>
+          <t xml:space="preserve">ウェルビーイング週間</t>
         </is>
       </c>
       <c r="K37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">During Sports Day practice, students participate in a variety of physical activities, team games, relays, and event rehearsals in preparation for Sports Day. They develop teamwork, cooperation, sportsmanship, and physical fitness while learning event procedures, safety expectations, and cheering routines. Practice sessions help students build confidence and ensure they are prepared to participate successfully in the Sports Day celebration.</t>
+          <t xml:space="preserve">A school wide event focused on raising awareness for wellbeing.</t>
         </is>
       </c>
       <c r="L37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会に向けた練習では、さまざまな運動、チームゲーム、リレー、種目のリハーサルに取り組みます。進行の流れ、安全面のルール、応援の仕方を学びながら、チームワーク、協調性、スポーツマンシップ、体力を養います。練習を通して自信をつけ、運動会当日に力を発揮できるよう準備します。</t>
+          <t xml:space="preserve">ウェルビーイング（心身の健康）への意識を高めることを目的とした全校行事です。</t>
         </is>
       </c>
       <c r="M37" t="inlineStr" s="2">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-11-elc-sports-day-rehearsal-2.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-09-wellbeing-week.webp</t>
         </is>
       </c>
       <c r="P37" t="inlineStr" s="2">
@@ -3671,17 +3671,17 @@
     <row r="38">
       <c r="A38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-14-elc-sports-day</t>
+          <t xml:space="preserve">2026-11-09-concept-con-wellbeing</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-14</t>
+          <t xml:space="preserve">2026-11-09</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-14</t>
+          <t xml:space="preserve">2026-11-13</t>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="3">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="E38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F38" t="inlineStr" s="2">
@@ -3711,22 +3711,22 @@
       </c>
       <c r="I38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC Sports Day</t>
+          <t xml:space="preserve">Concept Con (Wellbeing)</t>
         </is>
       </c>
       <c r="J38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部運動会</t>
+          <t xml:space="preserve">コンセプト・コン（ウェルビーイング）</t>
         </is>
       </c>
       <c r="K38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">During Sports Day, students participate in a variety of athletic events, relay races, team challenges, and cooperative games. They demonstrate teamwork, perseverance, sportsmanship, and school spirit while celebrating physical activity and healthy competition. Sports Day provides an opportunity for students to challenge themselves, support their peers, and enjoy a fun day of community participation and achievement.</t>
+          <t xml:space="preserve">The Primary Concept Conference on the theme of wellbeing, held during Wellbeing Week.</t>
         </is>
       </c>
       <c r="L38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会では、さまざまな競技、リレー、チーム対抗戦、協力ゲームに参加します。体を動かすことと健全な競争を楽しみながら、チームワーク、粘り強さ、スポーツマンシップ、愛校心を発揮します。自分に挑戦し、仲間を応援し、コミュニティ全体で達成感を味わう楽しい一日です。</t>
+          <t xml:space="preserve">ウェルビーイング週間に合わせて行う、小学部のコンセプト・カンファレンス（テーマ：ウェルビーイング）です。</t>
         </is>
       </c>
       <c r="M38" t="inlineStr" s="2">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="O38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-14-elc-sports-day.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P38" t="inlineStr" s="2">
@@ -3768,17 +3768,17 @@
     <row r="39">
       <c r="A39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-16-friendly-soccer-tournament-internal</t>
+          <t xml:space="preserve">2026-11-11-elc-sports-day-rehearsal-2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-16</t>
+          <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-20</t>
+          <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="3">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="E39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">ELC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr" s="2">
@@ -3808,22 +3808,22 @@
       </c>
       <c r="I39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Friendly Soccer Tournament (Internal)</t>
+          <t xml:space="preserve">ELC Sports Day Rehearsal #2</t>
         </is>
       </c>
       <c r="J39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内サッカー大会</t>
+          <t xml:space="preserve">幼稚部運動会リハーサル #2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in a friendly internal soccer tournament, promoting teamwork, sportsmanship, and school spirit.</t>
+          <t xml:space="preserve">During Sports Day practice, students participate in a variety of physical activities, team games, relays, and event rehearsals in preparation for Sports Day. They develop teamwork, cooperation, sportsmanship, and physical fitness while learning event procedures, safety expectations, and cheering routines. Practice sessions help students build confidence and ensure they are prepared to participate successfully in the Sports Day celebration.</t>
         </is>
       </c>
       <c r="L39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内サッカー大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
+          <t xml:space="preserve">運動会に向けた練習では、さまざまな運動、チームゲーム、リレー、種目のリハーサルに取り組みます。進行の流れ、安全面のルール、応援の仕方を学びながら、チームワーク、協調性、スポーツマンシップ、体力を養います。練習を通して自信をつけ、運動会当日に力を発揮できるよう準備します。</t>
         </is>
       </c>
       <c r="M39" t="inlineStr" s="2">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="O39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-16-friendly-soccer-tournament-internal.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-11-elc-sports-day-rehearsal-2.webp</t>
         </is>
       </c>
       <c r="P39" t="inlineStr" s="2">
@@ -3865,17 +3865,17 @@
     <row r="40">
       <c r="A40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-17-foundation-field-trip</t>
+          <t xml:space="preserve">2026-11-14-elc-sports-day</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-17</t>
+          <t xml:space="preserve">2026-11-14</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-17</t>
+          <t xml:space="preserve">2026-11-14</t>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="3">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="F40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G40" t="inlineStr" s="2">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="I40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Foundation Field Trip</t>
+          <t xml:space="preserve">ELC Sports Day</t>
         </is>
       </c>
       <c r="J40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ファウンデーション校外学習</t>
+          <t xml:space="preserve">幼稚部運動会</t>
         </is>
       </c>
       <c r="K40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Our youngest learners will enjoy an age-appropriate educational excursion that supports classroom learning through hands-on experiences.</t>
+          <t xml:space="preserve">During Sports Day, students participate in a variety of athletic events, relay races, team challenges, and cooperative games. They demonstrate teamwork, perseverance, sportsmanship, and school spirit while celebrating physical activity and healthy competition. Sports Day provides an opportunity for students to challenge themselves, support their peers, and enjoy a fun day of community participation and achievement.</t>
         </is>
       </c>
       <c r="L40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">年少の子どもたちが、年齢に合った校外学習に出かけ、体験を通して教室での学びを深めます。</t>
+          <t xml:space="preserve">運動会では、さまざまな競技、リレー、チーム対抗戦、協力ゲームに参加します。体を動かすことと健全な競争を楽しみながら、チームワーク、粘り強さ、スポーツマンシップ、愛校心を発揮します。自分に挑戦し、仲間を応援し、コミュニティ全体で達成感を味わう楽しい一日です。</t>
         </is>
       </c>
       <c r="M40" t="inlineStr" s="2">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="O40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-17-foundation-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-14-elc-sports-day.webp</t>
         </is>
       </c>
       <c r="P40" t="inlineStr" s="2">
@@ -3962,19 +3962,19 @@
     <row r="41">
       <c r="A41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-20-gifu-kakamigahara-air-and-space-museum</t>
+          <t xml:space="preserve">2026-11-16-friendly-soccer-tournament-internal</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">2026-11-16</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">2026-11-20</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">2026-11-20</t>
-        </is>
-      </c>
       <c r="D41" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
@@ -4002,22 +4002,22 @@
       </c>
       <c r="I41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Gifu Kakamigahara Air and Space Museum</t>
+          <t xml:space="preserve">Friendly Soccer Tournament (Internal)</t>
         </is>
       </c>
       <c r="J41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">岐阜かかみがはら航空宇宙博物館</t>
+          <t xml:space="preserve">校内サッカー大会</t>
         </is>
       </c>
       <c r="K41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will be going to the air and space museum to complete a practical where they will be analyzing plane design throughout history.</t>
+          <t xml:space="preserve">Students will take part in a friendly internal soccer tournament, promoting teamwork, sportsmanship, and school spirit.</t>
         </is>
       </c>
       <c r="L41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">航空宇宙博物館を訪れ、歴史を通じた飛行機のデザインを分析する実習に取り組みます。</t>
+          <t xml:space="preserve">校内サッカー大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
         </is>
       </c>
       <c r="M41" t="inlineStr" s="2">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="O41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-20-gifu-kakamigahara-air-and-space-museum.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-16-friendly-soccer-tournament-internal.webp</t>
         </is>
       </c>
       <c r="P41" t="inlineStr" s="2">
@@ -4059,27 +4059,27 @@
     <row r="42">
       <c r="A42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-24-winter-art-contest</t>
+          <t xml:space="preserve">2026-11-17-foundation-field-trip</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-24</t>
+          <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-24</t>
+          <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">13:10-14:55</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">ELC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr" s="2">
@@ -4099,37 +4099,37 @@
       </c>
       <c r="I42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Gallery Day: ELC &amp; Primary Art Showcase</t>
+          <t xml:space="preserve">Foundation Field Trip</t>
         </is>
       </c>
       <c r="J42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ギャラリーデー：幼稚部・小学部アート展</t>
+          <t xml:space="preserve">ファウンデーション校外学習</t>
         </is>
       </c>
       <c r="K42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC and Primary students display the artwork they have created with the visual arts teacher. Parents are welcome to view the gallery from 13:10 to 14:55. Students vote for their favourite artworks, and the winners for each grade are announced.</t>
+          <t xml:space="preserve">Our youngest learners will enjoy an age-appropriate educational excursion that supports classroom learning through hands-on experiences.</t>
         </is>
       </c>
       <c r="L42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部・小学部の児童が美術の授業で制作した作品を展示します。保護者の皆さまは13:10～14:55にご鑑賞いただけます。児童による投票を行い、学年ごとの受賞作品を発表します。</t>
+          <t xml:space="preserve">年少の子どもたちが、年齢に合った校外学習に出かけ、体験を通して教室での学びを深めます。</t>
         </is>
       </c>
       <c r="M42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Gym</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="N42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">体育館</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="O42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-24-winter-art-contest.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-17-foundation-field-trip.webp</t>
         </is>
       </c>
       <c r="P42" t="inlineStr" s="2">
@@ -4156,17 +4156,17 @@
     <row r="43">
       <c r="A43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-27-parents-morning-1</t>
+          <t xml:space="preserve">2026-11-20-gifu-kakamigahara-air-and-space-museum</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-27</t>
+          <t xml:space="preserve">2026-11-20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-27</t>
+          <t xml:space="preserve">2026-11-20</t>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="3">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="E43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G43" t="inlineStr" s="2">
@@ -4196,22 +4196,22 @@
       </c>
       <c r="I43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parents Morning #1</t>
+          <t xml:space="preserve">Gifu Kakamigahara Air and Space Museum</t>
         </is>
       </c>
       <c r="J43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">朝の授業参観 #1</t>
+          <t xml:space="preserve">岐阜かかみがはら航空宇宙博物館</t>
         </is>
       </c>
       <c r="K43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC and Primary Parents are invited to come and see the lessons in the morning and experience the morning routines with their child.</t>
+          <t xml:space="preserve">Students will be going to the air and space museum to complete a practical where they will be analyzing plane design throughout history.</t>
         </is>
       </c>
       <c r="L43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部・小学部の保護者の皆様をお招きし、朝の授業をご参観いただき、お子様と一緒に朝の日課を体験していただきます。</t>
+          <t xml:space="preserve">航空宇宙博物館を訪れ、歴史を通じた飛行機のデザインを分析する実習に取り組みます。</t>
         </is>
       </c>
       <c r="M43" t="inlineStr" s="2">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="O43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-27-parents-morning-1.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-20-gifu-kakamigahara-air-and-space-museum.webp</t>
         </is>
       </c>
       <c r="P43" t="inlineStr" s="2">
@@ -4253,32 +4253,32 @@
     <row r="44">
       <c r="A44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-27-teacher-appreciation-day</t>
+          <t xml:space="preserve">2026-11-24-winter-art-contest</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-27</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-27</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="D44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">13:10-14:55</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G44" t="inlineStr" s="2">
@@ -4293,37 +4293,37 @@
       </c>
       <c r="I44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Teacher Appreciation Day</t>
+          <t xml:space="preserve">Gallery Day: ELC &amp; Primary Art Showcase</t>
         </is>
       </c>
       <c r="J44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">教職員感謝デー</t>
+          <t xml:space="preserve">ギャラリーデー：幼稚部・小学部アート展</t>
         </is>
       </c>
       <c r="K44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The school community will celebrate Teacher Appreciation Day by recognizing and thanking teachers for their dedication, care, and support.</t>
+          <t xml:space="preserve">ELC and Primary students display the artwork they have created with the visual arts teacher. Parents are welcome to view the gallery from 13:10 to 14:55. Students vote for their favourite artworks, and the winners for each grade are announced.</t>
         </is>
       </c>
       <c r="L44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学校コミュニティ全体で、教員の献身、思いやり、支えに感謝を伝える日です。</t>
+          <t xml:space="preserve">幼稚部・小学部の児童が美術の授業で制作した作品を展示します。保護者の皆さまは13:10～14:55にご鑑賞いただけます。児童による投票を行い、学年ごとの受賞作品を発表します。</t>
         </is>
       </c>
       <c r="M44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Gym</t>
         </is>
       </c>
       <c r="N44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">体育館</t>
         </is>
       </c>
       <c r="O44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-27-teacher-appreciation-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-24-winter-art-contest.webp</t>
         </is>
       </c>
       <c r="P44" t="inlineStr" s="2">
@@ -4350,17 +4350,17 @@
     <row r="45">
       <c r="A45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-28-2026-enishi-futsal-tournament</t>
+          <t xml:space="preserve">2026-11-27-parents-morning-1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-28</t>
+          <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-28</t>
+          <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="3">
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G45" t="inlineStr" s="2">
@@ -4390,22 +4390,22 @@
       </c>
       <c r="I45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026 - Enishi Futsal Tournament</t>
+          <t xml:space="preserve">Parents Morning #1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026 Enishiフットサル大会</t>
+          <t xml:space="preserve">朝の授業参観 #1</t>
         </is>
       </c>
       <c r="K45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Enishi will host a Middle School Futsal tournament at our school with multiple schools participating.</t>
+          <t xml:space="preserve">ELC and Primary Parents are invited to come and see the lessons in the morning and experience the morning routines with their child.</t>
         </is>
       </c>
       <c r="L45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">本校にて複数校が参加する中学生フットサル大会を開催します。</t>
+          <t xml:space="preserve">幼稚部・小学部の保護者の皆様をお招きし、朝の授業をご参観いただき、お子様と一緒に朝の日課を体験していただきます。</t>
         </is>
       </c>
       <c r="M45" t="inlineStr" s="2">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="O45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-28-2026-enishi-futsal-tournament.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-27-parents-morning-1.webp</t>
         </is>
       </c>
       <c r="P45" t="inlineStr" s="2">
@@ -4447,32 +4447,32 @@
     <row r="46">
       <c r="A46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-03-grade-3-4-musical</t>
+          <t xml:space="preserve">2026-11-27-teacher-appreciation-day</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-03</t>
+          <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-03</t>
+          <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
       <c r="D46" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">17:30</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G46" t="inlineStr" s="2">
@@ -4487,22 +4487,22 @@
       </c>
       <c r="I46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 3, 4 Musical</t>
+          <t xml:space="preserve">Teacher Appreciation Day</t>
         </is>
       </c>
       <c r="J46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3・4年生ミュージカル</t>
+          <t xml:space="preserve">教職員感謝デー</t>
         </is>
       </c>
       <c r="K46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students present a musical performance showcasing their talents in singing, acting, and teamwork. Families are invited to enjoy this special production.</t>
+          <t xml:space="preserve">The school community will celebrate Teacher Appreciation Day by recognizing and thanking teachers for their dedication, care, and support.</t>
         </is>
       </c>
       <c r="L46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">歌、演技、チームワークを披露するミュージカルを上演します。ご家族の皆様もぜひこの特別な公演をお楽しみください。</t>
+          <t xml:space="preserve">学校コミュニティ全体で、教員の献身、思いやり、支えに感謝を伝える日です。</t>
         </is>
       </c>
       <c r="M46" t="inlineStr" s="2">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="O46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-03-grade-3-4-musical.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-27-teacher-appreciation-day.webp</t>
         </is>
       </c>
       <c r="P46" t="inlineStr" s="2">
@@ -4544,17 +4544,17 @@
     <row r="47">
       <c r="A47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-05-sat-test-5</t>
+          <t xml:space="preserve">2026-11-28-2026-enishi-futsal-tournament</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-05</t>
+          <t xml:space="preserve">2026-11-28</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-05</t>
+          <t xml:space="preserve">2026-11-28</t>
         </is>
       </c>
       <c r="D47" t="inlineStr" s="3">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="E47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F47" t="inlineStr" s="2">
@@ -4584,22 +4584,22 @@
       </c>
       <c r="I47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT Test #5</t>
+          <t xml:space="preserve">2026 - Enishi Futsal Tournament</t>
         </is>
       </c>
       <c r="J47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT試験 第5回</t>
+          <t xml:space="preserve">2026 Enishiフットサル大会</t>
         </is>
       </c>
       <c r="K47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
+          <t xml:space="preserve">Enishi will host a Middle School Futsal tournament at our school with multiple schools participating.</t>
         </is>
       </c>
       <c r="L47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
+          <t xml:space="preserve">本校にて複数校が参加する中学生フットサル大会を開催します。</t>
         </is>
       </c>
       <c r="M47" t="inlineStr" s="2">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="O47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-05-sat-test-5.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-28-2026-enishi-futsal-tournament.webp</t>
         </is>
       </c>
       <c r="P47" t="inlineStr" s="2">
@@ -4641,27 +4641,27 @@
     <row r="48">
       <c r="A48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-10-choir-and-orchestra-concert</t>
+          <t xml:space="preserve">2026-12-03-grade-3-4-musical</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-10</t>
+          <t xml:space="preserve">2026-12-03</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-10</t>
+          <t xml:space="preserve">2026-12-03</t>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">17:30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F48" t="inlineStr" s="2">
@@ -4681,22 +4681,22 @@
       </c>
       <c r="I48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choir and Orchestra Concert</t>
+          <t xml:space="preserve">Grade 3, 4 Musical</t>
         </is>
       </c>
       <c r="J48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合唱・オーケストラコンサート</t>
+          <t xml:space="preserve">3・4年生ミュージカル</t>
         </is>
       </c>
       <c r="K48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choir class and orchestra club will perform the music repertoire they have been rehearsing for an audience of family, peers and teachers.</t>
+          <t xml:space="preserve">Students present a musical performance showcasing their talents in singing, acting, and teamwork. Families are invited to enjoy this special production.</t>
         </is>
       </c>
       <c r="L48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合唱クラスとオーケストラクラブが、練習を重ねてきた曲目をご家族、友人、教員の前で演奏します。</t>
+          <t xml:space="preserve">歌、演技、チームワークを披露するミュージカルを上演します。ご家族の皆様もぜひこの特別な公演をお楽しみください。</t>
         </is>
       </c>
       <c r="M48" t="inlineStr" s="2">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-10-choir-and-orchestra-concert.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-03-grade-3-4-musical.webp</t>
         </is>
       </c>
       <c r="P48" t="inlineStr" s="2">
@@ -4738,17 +4738,17 @@
     <row r="49">
       <c r="A49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-11-silent-auction</t>
+          <t xml:space="preserve">2026-12-05-sat-test-5</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-11</t>
+          <t xml:space="preserve">2026-12-05</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-11</t>
+          <t xml:space="preserve">2026-12-05</t>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="3">
@@ -4758,12 +4758,12 @@
       </c>
       <c r="E49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G49" t="inlineStr" s="2">
@@ -4778,22 +4778,22 @@
       </c>
       <c r="I49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Silent Auction</t>
+          <t xml:space="preserve">SAT Test #5</t>
         </is>
       </c>
       <c r="J49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">サイレントオークション</t>
+          <t xml:space="preserve">SAT試験 第5回</t>
         </is>
       </c>
       <c r="K49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Families and community members can bid on donated items and experiences to support initiatives chosen by the primary student council.</t>
+          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
         </is>
       </c>
       <c r="L49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ご家族や地域の皆様が寄付された品物や体験に入札し、小学部生徒会が選んだ取り組みを支援します。</t>
+          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
         </is>
       </c>
       <c r="M49" t="inlineStr" s="2">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="O49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-11-silent-auction.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-05-sat-test-5.webp</t>
         </is>
       </c>
       <c r="P49" t="inlineStr" s="2">
@@ -4835,17 +4835,17 @@
     <row r="50">
       <c r="A50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-16-industry-visit-tech-company</t>
+          <t xml:space="preserve">2026-12-10-choir-and-orchestra-concert</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-16</t>
+          <t xml:space="preserve">2026-12-10</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-16</t>
+          <t xml:space="preserve">2026-12-10</t>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="3">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="F50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G50" t="inlineStr" s="2">
@@ -4875,22 +4875,22 @@
       </c>
       <c r="I50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Industry Visit (Tech Company)</t>
+          <t xml:space="preserve">Choir and Orchestra Concert</t>
         </is>
       </c>
       <c r="J50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">企業訪問（テクノロジー企業）</t>
+          <t xml:space="preserve">合唱・オーケストラコンサート</t>
         </is>
       </c>
       <c r="K50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will visit a local technology company to gain firsthand insight into the modern workplace and explore careers in technology and innovation.</t>
+          <t xml:space="preserve">Choir class and orchestra club will perform the music repertoire they have been rehearsing for an audience of family, peers and teachers.</t>
         </is>
       </c>
       <c r="L50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">地元のテクノロジー企業を訪問し、現代の職場を直接知るとともに、テクノロジーやイノベーション分野のキャリアについて考えます。</t>
+          <t xml:space="preserve">合唱クラスとオーケストラクラブが、練習を重ねてきた曲目をご家族、友人、教員の前で演奏します。</t>
         </is>
       </c>
       <c r="M50" t="inlineStr" s="2">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-16-industry-visit-tech-company.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-10-choir-and-orchestra-concert.webp</t>
         </is>
       </c>
       <c r="P50" t="inlineStr" s="2">
@@ -4932,17 +4932,17 @@
     <row r="51">
       <c r="A51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-16-winter-party-eagle-nest</t>
+          <t xml:space="preserve">2026-12-11-silent-auction</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-16</t>
+          <t xml:space="preserve">2026-12-11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-16</t>
+          <t xml:space="preserve">2026-12-11</t>
         </is>
       </c>
       <c r="D51" t="inlineStr" s="3">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="E51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G51" t="inlineStr" s="2">
@@ -4972,22 +4972,22 @@
       </c>
       <c r="I51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Winter Party (Eagle Nest)</t>
+          <t xml:space="preserve">Silent Auction</t>
         </is>
       </c>
       <c r="J51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ウィンターパーティー（イーグルネスト）</t>
+          <t xml:space="preserve">サイレントオークション</t>
         </is>
       </c>
       <c r="K51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students celebrate the season with fun activities, games, and opportunities to connect with peers in their Eagle Nests. This is led by the primary student council.</t>
+          <t xml:space="preserve">Families and community members can bid on donated items and experiences to support initiatives chosen by the primary student council.</t>
         </is>
       </c>
       <c r="L51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">イーグルネストごとに、楽しい活動やゲームを通して仲間と交流し、季節を祝います。小学部生徒会が主催します。</t>
+          <t xml:space="preserve">ご家族や地域の皆様が寄付された品物や体験に入札し、小学部生徒会が選んだ取り組みを支援します。</t>
         </is>
       </c>
       <c r="M51" t="inlineStr" s="2">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="O51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-16-winter-party-eagle-nest.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-11-silent-auction.webp</t>
         </is>
       </c>
       <c r="P51" t="inlineStr" s="2">
@@ -5029,17 +5029,17 @@
     <row r="52">
       <c r="A52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-17-talent-day</t>
+          <t xml:space="preserve">2026-12-14-clubs-pause</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-17</t>
+          <t xml:space="preserve">2026-12-14</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-17</t>
+          <t xml:space="preserve">2027-01-15</t>
         </is>
       </c>
       <c r="D52" t="inlineStr" s="3">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G52" t="inlineStr" s="2">
@@ -5069,22 +5069,22 @@
       </c>
       <c r="I52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Talent Day</t>
+          <t xml:space="preserve">Clubs Pause</t>
         </is>
       </c>
       <c r="J52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">タレントデー</t>
+          <t xml:space="preserve">クラブ活動休止</t>
         </is>
       </c>
       <c r="K52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students have the opportunity to showcase their unique talents and interests in a supportive and encouraging environment led by the performing arts teacher.</t>
+          <t xml:space="preserve">After-school clubs are paused during this period. Bus reminder: the afternoon Red bus runs only on club days, so it does not run while clubs are paused. Please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
         </is>
       </c>
       <c r="L52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">舞台芸術の先生のもと、温かく励まし合う雰囲気の中で、一人ひとりの特技や興味を披露します。</t>
+          <t xml:space="preserve">この期間、放課後のクラブ活動はお休みです。【バスについて】午後の赤バスはクラブ活動がある日のみ運行するため、休止期間中は運行しません。午後の下校時は青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
         </is>
       </c>
       <c r="M52" t="inlineStr" s="2">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="O52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-17-talent-day.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P52" t="inlineStr" s="2">
@@ -5126,17 +5126,17 @@
     <row r="53">
       <c r="A53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-18-tea-party-pta-for-all</t>
+          <t xml:space="preserve">2026-12-16-industry-visit-tech-company</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-18</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-18</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="D53" t="inlineStr" s="3">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="E53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTA</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G53" t="inlineStr" s="2">
@@ -5166,22 +5166,22 @@
       </c>
       <c r="I53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Tea Party / PTA for all</t>
+          <t xml:space="preserve">Industry Visit (Tech Company)</t>
         </is>
       </c>
       <c r="J53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTAティーパーティー（どなたでも参加できます）</t>
+          <t xml:space="preserve">企業訪問（テクノロジー企業）</t>
         </is>
       </c>
       <c r="K53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Families are invited to enjoy refreshments while connecting with the PTA, school staff, and other members of the community.</t>
+          <t xml:space="preserve">Students will visit a local technology company to gain firsthand insight into the modern workplace and explore careers in technology and innovation.</t>
         </is>
       </c>
       <c r="L53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">軽食を楽しみながら、PTA、教職員、コミュニティの皆様と交流していただける集いです。</t>
+          <t xml:space="preserve">地元のテクノロジー企業を訪問し、現代の職場を直接知るとともに、テクノロジーやイノベーション分野のキャリアについて考えます。</t>
         </is>
       </c>
       <c r="M53" t="inlineStr" s="2">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="O53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-18-tea-party-pta-for-all.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-16-industry-visit-tech-company.webp</t>
         </is>
       </c>
       <c r="P53" t="inlineStr" s="2">
@@ -5223,17 +5223,17 @@
     <row r="54">
       <c r="A54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-18-eagle-bucks-store</t>
+          <t xml:space="preserve">2026-12-16-winter-party-eagle-nest</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-18</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-18</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="D54" t="inlineStr" s="3">
@@ -5263,22 +5263,22 @@
       </c>
       <c r="I54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Eagle Bucks Store</t>
+          <t xml:space="preserve">Winter Party (Eagle Nest)</t>
         </is>
       </c>
       <c r="J54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">イーグルバックス・ストア</t>
+          <t xml:space="preserve">ウィンターパーティー（イーグルネスト）</t>
         </is>
       </c>
       <c r="K54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
+          <t xml:space="preserve">Students celebrate the season with fun activities, games, and opportunities to connect with peers in their Eagle Nests. This is led by the primary student council.</t>
         </is>
       </c>
       <c r="L54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
+          <t xml:space="preserve">イーグルネストごとに、楽しい活動やゲームを通して仲間と交流し、季節を祝います。小学部生徒会が主催します。</t>
         </is>
       </c>
       <c r="M54" t="inlineStr" s="2">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="O54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-18-eagle-bucks-store.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-16-winter-party-eagle-nest.webp</t>
         </is>
       </c>
       <c r="P54" t="inlineStr" s="2">
@@ -5320,17 +5320,17 @@
     <row r="55">
       <c r="A55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-19-end-of-term-1-activity-sleep-over-program-g6-10</t>
+          <t xml:space="preserve">2026-12-17-talent-day</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-19</t>
+          <t xml:space="preserve">2026-12-17</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-19</t>
+          <t xml:space="preserve">2026-12-17</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="3">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="E55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G55" t="inlineStr" s="2">
@@ -5360,22 +5360,22 @@
       </c>
       <c r="I55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">End of Term 1 Activity-Sleep Over Program: G6-10</t>
+          <t xml:space="preserve">Talent Day</t>
         </is>
       </c>
       <c r="J55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第1学期末行事：宿泊プログラム（G6–10）</t>
+          <t xml:space="preserve">タレントデー</t>
         </is>
       </c>
       <c r="K55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 6 to 10 students will take part in a school sleepover program to celebrate the end of Term 1 through shared activities and community building.</t>
+          <t xml:space="preserve">Students have the opportunity to showcase their unique talents and interests in a supportive and encouraging environment led by the performing arts teacher.</t>
         </is>
       </c>
       <c r="L55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">6～10年生が校内での宿泊プログラムに参加し、共に活動しながら仲間づくりを行い、第1学期の終わりを祝います。</t>
+          <t xml:space="preserve">舞台芸術の先生のもと、温かく励まし合う雰囲気の中で、一人ひとりの特技や興味を披露します。</t>
         </is>
       </c>
       <c r="M55" t="inlineStr" s="2">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="O55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-19-end-of-term-1-activity-sleep-over-program-g6-10.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-17-talent-day.webp</t>
         </is>
       </c>
       <c r="P55" t="inlineStr" s="2">
@@ -5417,17 +5417,17 @@
     <row r="56">
       <c r="A56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-21-winter-study-camp-g11-12</t>
+          <t xml:space="preserve">2026-12-18-tea-party-pta-for-all</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-21</t>
+          <t xml:space="preserve">2026-12-18</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-23</t>
+          <t xml:space="preserve">2026-12-18</t>
         </is>
       </c>
       <c r="D56" t="inlineStr" s="3">
@@ -5437,12 +5437,12 @@
       </c>
       <c r="E56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">PTA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G56" t="inlineStr" s="2">
@@ -5457,22 +5457,22 @@
       </c>
       <c r="I56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Winter Study Camp: G11-12</t>
+          <t xml:space="preserve">Tea Party / PTA for all</t>
         </is>
       </c>
       <c r="J56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">冬季学習合宿：G11–12</t>
+          <t xml:space="preserve">PTAティーパーティー（どなたでも参加できます）</t>
         </is>
       </c>
       <c r="K56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 11 and 12 students will take part in an off-campus Winter Study Camp focused on concentrated study, academic review, and exam preparation.</t>
+          <t xml:space="preserve">Families are invited to enjoy refreshments while connecting with the PTA, school staff, and other members of the community.</t>
         </is>
       </c>
       <c r="L56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11・12年生が校外での冬季学習合宿に参加し、集中学習、復習、試験対策に取り組みます。</t>
+          <t xml:space="preserve">軽食を楽しみながら、PTA、教職員、コミュニティの皆様と交流していただける集いです。</t>
         </is>
       </c>
       <c r="M56" t="inlineStr" s="2">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="O56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-21-winter-study-camp-g11-12.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-18-tea-party-pta-for-all.webp</t>
         </is>
       </c>
       <c r="P56" t="inlineStr" s="2">
@@ -5514,17 +5514,17 @@
     <row r="57">
       <c r="A57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-08-parent-teacher-conferences</t>
+          <t xml:space="preserve">2026-12-18-eagle-bucks-store</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-08</t>
+          <t xml:space="preserve">2026-12-18</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-08</t>
+          <t xml:space="preserve">2026-12-18</t>
         </is>
       </c>
       <c r="D57" t="inlineStr" s="3">
@@ -5534,17 +5534,17 @@
       </c>
       <c r="E57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H57" t="inlineStr" s="2">
@@ -5554,22 +5554,22 @@
       </c>
       <c r="I57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parent Teacher Conferences</t>
+          <t xml:space="preserve">Eagle Bucks Store</t>
         </is>
       </c>
       <c r="J57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者面談</t>
+          <t xml:space="preserve">イーグルバックス・ストア</t>
         </is>
       </c>
       <c r="K57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on this day.</t>
+          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
         </is>
       </c>
       <c r="L57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。当日、生徒は登校しません。</t>
+          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
         </is>
       </c>
       <c r="M57" t="inlineStr" s="2">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="O57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-19-parent-teacher-conferences.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-18-eagle-bucks-store.webp</t>
         </is>
       </c>
       <c r="P57" t="inlineStr" s="2">
@@ -5611,17 +5611,17 @@
     <row r="58">
       <c r="A58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-14-g10-parent-info-session-high-school-subject-choi</t>
+          <t xml:space="preserve">2026-12-19-end-of-term-1-activity-sleep-over-program-g6-10</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-14</t>
+          <t xml:space="preserve">2026-12-19</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-14</t>
+          <t xml:space="preserve">2026-12-19</t>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="3">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="F58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G58" t="inlineStr" s="2">
@@ -5651,22 +5651,22 @@
       </c>
       <c r="I58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G10 Parent info Session (High School Subject Choice)</t>
+          <t xml:space="preserve">End of Term 1 Activity-Sleep Over Program: G6-10</t>
         </is>
       </c>
       <c r="J58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G10保護者向け説明会（高等部科目選択）</t>
+          <t xml:space="preserve">第1学期末行事：宿泊プログラム（G6–10）</t>
         </is>
       </c>
       <c r="K58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 10 parents are invited to an information session about DP subject choices and guidance for planning the next stage of their child’s learning.</t>
+          <t xml:space="preserve">Grade 6 to 10 students will take part in a school sleepover program to celebrate the end of Term 1 through shared activities and community building.</t>
         </is>
       </c>
       <c r="L58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10年生の保護者の皆様を対象に、DPの科目選択と、お子様の次のステージの学びを計画するためのガイダンスを行います。</t>
+          <t xml:space="preserve">6～10年生が校内での宿泊プログラムに参加し、共に活動しながら仲間づくりを行い、第1学期の終わりを祝います。</t>
         </is>
       </c>
       <c r="M58" t="inlineStr" s="2">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="O58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-01-14-g10-parent-info-session-high-school-subject-choi.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-19-end-of-term-1-activity-sleep-over-program-g6-10.webp</t>
         </is>
       </c>
       <c r="P58" t="inlineStr" s="2">
@@ -5708,17 +5708,17 @@
     <row r="59">
       <c r="A59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-22-open-campus</t>
+          <t xml:space="preserve">2026-12-21-winter-study-camp-g11-12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-22</t>
+          <t xml:space="preserve">2026-12-21</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-22</t>
+          <t xml:space="preserve">2026-12-23</t>
         </is>
       </c>
       <c r="D59" t="inlineStr" s="3">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="E59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F59" t="inlineStr" s="2">
@@ -5748,22 +5748,22 @@
       </c>
       <c r="I59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Open Campus</t>
+          <t xml:space="preserve">Winter Study Camp: G11-12</t>
         </is>
       </c>
       <c r="J59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">オープンキャンパス</t>
+          <t xml:space="preserve">冬季学習合宿：G11–12</t>
         </is>
       </c>
       <c r="K59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Any person interested in seeing the daily operation of the school is invited to join a tour of the school during its regular hours.</t>
+          <t xml:space="preserve">Grade 11 and 12 students will take part in an off-campus Winter Study Camp focused on concentrated study, academic review, and exam preparation.</t>
         </is>
       </c>
       <c r="L59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学校の日常の様子にご関心のある方は、通常授業時間中の校内見学にご参加いただけます。</t>
+          <t xml:space="preserve">11・12年生が校外での冬季学習合宿に参加し、集中学習、復習、試験対策に取り組みます。</t>
         </is>
       </c>
       <c r="M59" t="inlineStr" s="2">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-01-22-open-campus.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-21-winter-study-camp-g11-12.webp</t>
         </is>
       </c>
       <c r="P59" t="inlineStr" s="2">
@@ -5805,17 +5805,17 @@
     <row r="60">
       <c r="A60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-23-alumni-talk</t>
+          <t xml:space="preserve">2027-01-08-parent-teacher-conferences</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-23</t>
+          <t xml:space="preserve">2027-01-08</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-23</t>
+          <t xml:space="preserve">2027-01-08</t>
         </is>
       </c>
       <c r="D60" t="inlineStr" s="3">
@@ -5825,17 +5825,17 @@
       </c>
       <c r="E60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="H60" t="inlineStr" s="2">
@@ -5845,22 +5845,22 @@
       </c>
       <c r="I60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Alumni Talk</t>
+          <t xml:space="preserve">Parent Teacher Conferences</t>
         </is>
       </c>
       <c r="J60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">卒業生トーク</t>
+          <t xml:space="preserve">保護者面談</t>
         </is>
       </c>
       <c r="K60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Alumni will share their experiences and advice with students, offering insight into life after School and future pathways.</t>
+          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on this day.</t>
         </is>
       </c>
       <c r="L60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">卒業生が自身の経験やアドバイスを生徒に伝え、卒業後の生活や将来の進路について話します。</t>
+          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。当日、生徒は登校しません。</t>
         </is>
       </c>
       <c r="M60" t="inlineStr" s="2">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="O60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-01-23-alumni-talk.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-19-parent-teacher-conferences.webp</t>
         </is>
       </c>
       <c r="P60" t="inlineStr" s="2">
@@ -5902,17 +5902,17 @@
     <row r="61">
       <c r="A61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-27-natural-disaster-field-trip</t>
+          <t xml:space="preserve">2027-01-14-g10-parent-info-session-high-school-subject-choi</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-27</t>
+          <t xml:space="preserve">2027-01-14</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-27</t>
+          <t xml:space="preserve">2027-01-14</t>
         </is>
       </c>
       <c r="D61" t="inlineStr" s="3">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="E61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G61" t="inlineStr" s="2">
@@ -5942,22 +5942,22 @@
       </c>
       <c r="I61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Natural Disaster Field Trip</t>
+          <t xml:space="preserve">G10 Parent info Session (High School Subject Choice)</t>
         </is>
       </c>
       <c r="J61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">防災校外学習</t>
+          <t xml:space="preserve">G10保護者向け説明会（高等部科目選択）</t>
         </is>
       </c>
       <c r="K61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students explore disaster preparedness and safety through interactive learning experiences related to natural disasters and emergency response.</t>
+          <t xml:space="preserve">Grade 10 parents are invited to an information session about DP subject choices and guidance for planning the next stage of their child’s learning.</t>
         </is>
       </c>
       <c r="L61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">自然災害や緊急時の対応に関する体験型学習を通して、防災と安全について学びます。</t>
+          <t xml:space="preserve">10年生の保護者の皆様を対象に、DPの科目選択と、お子様の次のステージの学びを計画するためのガイダンスを行います。</t>
         </is>
       </c>
       <c r="M61" t="inlineStr" s="2">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="O61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-01-27-natural-disaster-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-01-14-g10-parent-info-session-high-school-subject-choi.webp</t>
         </is>
       </c>
       <c r="P61" t="inlineStr" s="2">
@@ -5999,17 +5999,17 @@
     <row r="62">
       <c r="A62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-30-model-united-nations-event-mun</t>
+          <t xml:space="preserve">2027-01-18-clubs-resume</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-30</t>
+          <t xml:space="preserve">2027-01-18</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-30</t>
+          <t xml:space="preserve">2027-01-18</t>
         </is>
       </c>
       <c r="D62" t="inlineStr" s="3">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="E62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F62" t="inlineStr" s="2">
@@ -6039,22 +6039,22 @@
       </c>
       <c r="I62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Model United Nations Event (MUN)</t>
+          <t xml:space="preserve">Clubs Resume</t>
         </is>
       </c>
       <c r="J62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">模擬国連（MUN）</t>
+          <t xml:space="preserve">クラブ活動再開</t>
         </is>
       </c>
       <c r="K62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will participate in Model United Nations, developing public speaking, research, collaboration, and global awareness through discussion of real-world issues.</t>
+          <t xml:space="preserve">After-school clubs start again today. Bus reminder: the afternoon Red bus runs only on club days. On other days, please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
         </is>
       </c>
       <c r="L62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">模擬国連に参加し、現実の課題について議論することで、スピーチ力、調査力、協働する力、国際的な意識を育みます。</t>
+          <t xml:space="preserve">本日から放課後のクラブ活動が再開します。【バスについて】午後の赤バスはクラブ活動がある日のみ運行します。それ以外の日は、午後の下校時に青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
         </is>
       </c>
       <c r="M62" t="inlineStr" s="2">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="O62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-01-30-model-united-nations-event-mun.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P62" t="inlineStr" s="2">
@@ -6096,17 +6096,17 @@
     <row r="63">
       <c r="A63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-01-friendly-volleyball-tournament-internal</t>
+          <t xml:space="preserve">2027-01-22-open-campus</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-01</t>
+          <t xml:space="preserve">2027-01-22</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-05</t>
+          <t xml:space="preserve">2027-01-22</t>
         </is>
       </c>
       <c r="D63" t="inlineStr" s="3">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F63" t="inlineStr" s="2">
@@ -6136,22 +6136,22 @@
       </c>
       <c r="I63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Friendly Volleyball Tournament (Internal)</t>
+          <t xml:space="preserve">Open Campus</t>
         </is>
       </c>
       <c r="J63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内バレーボール大会</t>
+          <t xml:space="preserve">オープンキャンパス</t>
         </is>
       </c>
       <c r="K63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in a friendly internal volleyball tournament, promoting teamwork, sportsmanship, and school spirit.</t>
+          <t xml:space="preserve">Any person interested in seeing the daily operation of the school is invited to join a tour of the school during its regular hours.</t>
         </is>
       </c>
       <c r="L63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内バレーボール大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
+          <t xml:space="preserve">学校の日常の様子にご関心のある方は、通常授業時間中の校内見学にご参加いただけます。</t>
         </is>
       </c>
       <c r="M63" t="inlineStr" s="2">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-01-friendly-volleyball-tournament-internal.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-01-22-open-campus.webp</t>
         </is>
       </c>
       <c r="P63" t="inlineStr" s="2">
@@ -6193,17 +6193,17 @@
     <row r="64">
       <c r="A64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-01-concept-con-language</t>
+          <t xml:space="preserve">2027-01-23-alumni-talk</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-01</t>
+          <t xml:space="preserve">2027-01-23</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-05</t>
+          <t xml:space="preserve">2027-01-23</t>
         </is>
       </c>
       <c r="D64" t="inlineStr" s="3">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="E64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F64" t="inlineStr" s="2">
@@ -6233,22 +6233,22 @@
       </c>
       <c r="I64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Concept Con (Language)</t>
+          <t xml:space="preserve">Alumni Talk</t>
         </is>
       </c>
       <c r="J64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">コンセプト・コン（言語）</t>
+          <t xml:space="preserve">卒業生トーク</t>
         </is>
       </c>
       <c r="K64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students celebrate language and communication through presentations, performances, and projects that showcase their learning and creativity.</t>
+          <t xml:space="preserve">Alumni will share their experiences and advice with students, offering insight into life after School and future pathways.</t>
         </is>
       </c>
       <c r="L64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学びと創造性を示す発表、パフォーマンス、プロジェクトを通して、言語とコミュニケーションを祝います。</t>
+          <t xml:space="preserve">卒業生が自身の経験やアドバイスを生徒に伝え、卒業後の生活や将来の進路について話します。</t>
         </is>
       </c>
       <c r="M64" t="inlineStr" s="2">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="O64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-01-concept-con-language.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-01-23-alumni-talk.webp</t>
         </is>
       </c>
       <c r="P64" t="inlineStr" s="2">
@@ -6290,17 +6290,17 @@
     <row r="65">
       <c r="A65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-18-career-support-second-career-roundtable-and-care</t>
+          <t xml:space="preserve">2027-01-27-natural-disaster-field-trip</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-18</t>
+          <t xml:space="preserve">2027-01-27</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-18</t>
+          <t xml:space="preserve">2027-01-27</t>
         </is>
       </c>
       <c r="D65" t="inlineStr" s="3">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="E65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">ELC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G65" t="inlineStr" s="2">
@@ -6330,22 +6330,22 @@
       </c>
       <c r="I65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Career Support: Second Career Roundtable and Career Fair</t>
+          <t xml:space="preserve">Natural Disaster Field Trip</t>
         </is>
       </c>
       <c r="J65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">進路支援：第2回キャリア座談会・キャリアフェア</t>
+          <t xml:space="preserve">防災校外学習</t>
         </is>
       </c>
       <c r="K65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An informative event where students and parents can learn about IB university admissions, holistic admissions strategies in Japan and abroad, and explore future academic and career opportunities through discussions with experts and representatives.</t>
+          <t xml:space="preserve">Students explore disaster preparedness and safety through interactive learning experiences related to natural disasters and emergency response.</t>
         </is>
       </c>
       <c r="L65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">専門家や関係者との対話を通して、生徒と保護者の皆様がIBでの大学入試、国内外の総合型選抜の戦略について学び、将来の進学やキャリアの可能性を探る説明会です。</t>
+          <t xml:space="preserve">自然災害や緊急時の対応に関する体験型学習を通して、防災と安全について学びます。</t>
         </is>
       </c>
       <c r="M65" t="inlineStr" s="2">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="O65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-18-career-support-second-career-roundtable-and-care.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-01-27-natural-disaster-field-trip.webp</t>
         </is>
       </c>
       <c r="P65" t="inlineStr" s="2">
@@ -6387,17 +6387,17 @@
     <row r="66">
       <c r="A66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-19-collective-field-trip</t>
+          <t xml:space="preserve">2027-01-30-model-united-nations-event-mun</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-19</t>
+          <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-19</t>
+          <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
       <c r="D66" t="inlineStr" s="3">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="E66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F66" t="inlineStr" s="2">
@@ -6427,22 +6427,22 @@
       </c>
       <c r="I66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Collective Field Trip</t>
+          <t xml:space="preserve">Model United Nations Event (MUN)</t>
         </is>
       </c>
       <c r="J66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合同校外学習</t>
+          <t xml:space="preserve">模擬国連（MUN）</t>
         </is>
       </c>
       <c r="K66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students participate in an off-campus learning experience that connects classroom learning with real-world exploration and discovery.</t>
+          <t xml:space="preserve">Students will participate in Model United Nations, developing public speaking, research, collaboration, and global awareness through discussion of real-world issues.</t>
         </is>
       </c>
       <c r="L66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校外での学習体験を通して、教室での学びを実社会での探究や発見と結びつけます。</t>
+          <t xml:space="preserve">模擬国連に参加し、現実の課題について議論することで、スピーチ力、調査力、協働する力、国際的な意識を育みます。</t>
         </is>
       </c>
       <c r="M66" t="inlineStr" s="2">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="O66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-19-collective-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-01-30-model-united-nations-event-mun.webp</t>
         </is>
       </c>
       <c r="P66" t="inlineStr" s="2">
@@ -6484,17 +6484,17 @@
     <row r="67">
       <c r="A67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-22-world-thinking-day</t>
+          <t xml:space="preserve">2027-02-01-friendly-volleyball-tournament-internal</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-22</t>
+          <t xml:space="preserve">2027-02-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-22</t>
+          <t xml:space="preserve">2027-02-05</t>
         </is>
       </c>
       <c r="D67" t="inlineStr" s="3">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="E67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F67" t="inlineStr" s="2">
@@ -6524,22 +6524,22 @@
       </c>
       <c r="I67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">World Thinking Day</t>
+          <t xml:space="preserve">Friendly Volleyball Tournament (Internal)</t>
         </is>
       </c>
       <c r="J67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ワールド・シンキング・デー</t>
+          <t xml:space="preserve">校内バレーボール大会</t>
         </is>
       </c>
       <c r="K67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students learn about cultures, traditions, and global citizenship while celebrating international understanding and connection.</t>
+          <t xml:space="preserve">Students will take part in a friendly internal volleyball tournament, promoting teamwork, sportsmanship, and school spirit.</t>
         </is>
       </c>
       <c r="L67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国際理解とつながりを祝いながら、さまざまな文化や伝統、地球市民としてのあり方について学びます。</t>
+          <t xml:space="preserve">校内バレーボール大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
         </is>
       </c>
       <c r="M67" t="inlineStr" s="2">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="O67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-22-world-thinking-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-01-friendly-volleyball-tournament-internal.webp</t>
         </is>
       </c>
       <c r="P67" t="inlineStr" s="2">
@@ -6581,17 +6581,17 @@
     <row r="68">
       <c r="A68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-22-secondary-sports-day-rehearsal-1</t>
+          <t xml:space="preserve">2027-02-01-concept-con-language</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-22</t>
+          <t xml:space="preserve">2027-02-01</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-22</t>
+          <t xml:space="preserve">2027-02-05</t>
         </is>
       </c>
       <c r="D68" t="inlineStr" s="3">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="E68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr" s="2">
@@ -6621,22 +6621,22 @@
       </c>
       <c r="I68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary Sports Day Rehearsal #1</t>
+          <t xml:space="preserve">Concept Con (Language)</t>
         </is>
       </c>
       <c r="J68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部運動会リハーサル #1</t>
+          <t xml:space="preserve">コンセプト・コン（言語）</t>
         </is>
       </c>
       <c r="K68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
+          <t xml:space="preserve">Students celebrate language and communication through presentations, performances, and projects that showcase their learning and creativity.</t>
         </is>
       </c>
       <c r="L68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
+          <t xml:space="preserve">学びと創造性を示す発表、パフォーマンス、プロジェクトを通して、言語とコミュニケーションを祝います。</t>
         </is>
       </c>
       <c r="M68" t="inlineStr" s="2">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="O68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-22-secondary-sports-day-rehearsal-1.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-01-concept-con-language.webp</t>
         </is>
       </c>
       <c r="P68" t="inlineStr" s="2">
@@ -6678,17 +6678,17 @@
     <row r="69">
       <c r="A69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-25-primary-sports-day-rehearsal-1</t>
+          <t xml:space="preserve">2027-02-18-career-support-second-career-roundtable-and-care</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-25</t>
+          <t xml:space="preserve">2027-02-18</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-25</t>
+          <t xml:space="preserve">2027-02-18</t>
         </is>
       </c>
       <c r="D69" t="inlineStr" s="3">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="E69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G69" t="inlineStr" s="2">
@@ -6718,22 +6718,22 @@
       </c>
       <c r="I69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary Sports Day Rehearsal #1</t>
+          <t xml:space="preserve">Career Support: Second Career Roundtable and Career Fair</t>
         </is>
       </c>
       <c r="J69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小学部運動会リハーサル #1</t>
+          <t xml:space="preserve">進路支援：第2回キャリア座談会・キャリアフェア</t>
         </is>
       </c>
       <c r="K69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students begin preparing for Sports Day by practicing events, routines, and teamwork activities.</t>
+          <t xml:space="preserve">An informative event where students and parents can learn about IB university admissions, holistic admissions strategies in Japan and abroad, and explore future academic and career opportunities through discussions with experts and representatives.</t>
         </is>
       </c>
       <c r="L69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">種目、流れ、チームワークの練習を通して、運動会に向けた準備を始めます。</t>
+          <t xml:space="preserve">専門家や関係者との対話を通して、生徒と保護者の皆様がIBでの大学入試、国内外の総合型選抜の戦略について学び、将来の進学やキャリアの可能性を探る説明会です。</t>
         </is>
       </c>
       <c r="M69" t="inlineStr" s="2">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="O69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-25-primary-sports-day-rehearsal-1.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-18-career-support-second-career-roundtable-and-care.webp</t>
         </is>
       </c>
       <c r="P69" t="inlineStr" s="2">
@@ -6775,17 +6775,17 @@
     <row r="70">
       <c r="A70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-26-parents-morning-2</t>
+          <t xml:space="preserve">2027-02-19-collective-field-trip</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-26</t>
+          <t xml:space="preserve">2027-02-19</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-26</t>
+          <t xml:space="preserve">2027-02-19</t>
         </is>
       </c>
       <c r="D70" t="inlineStr" s="3">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="E70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G70" t="inlineStr" s="2">
@@ -6815,22 +6815,22 @@
       </c>
       <c r="I70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parents Morning #2</t>
+          <t xml:space="preserve">Collective Field Trip</t>
         </is>
       </c>
       <c r="J70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">朝の授業参観 #2</t>
+          <t xml:space="preserve">合同校外学習</t>
         </is>
       </c>
       <c r="K70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC and Primary Parents are invited to come and see the lessons in the morning and experience the morning routines with their child.</t>
+          <t xml:space="preserve">Students participate in an off-campus learning experience that connects classroom learning with real-world exploration and discovery.</t>
         </is>
       </c>
       <c r="L70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部・小学部の保護者の皆様をお招きし、朝の授業をご参観いただき、お子様と一緒に朝の日課を体験していただきます。</t>
+          <t xml:space="preserve">校外での学習体験を通して、教室での学びを実社会での探究や発見と結びつけます。</t>
         </is>
       </c>
       <c r="M70" t="inlineStr" s="2">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-26-parents-morning-2.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-19-collective-field-trip.webp</t>
         </is>
       </c>
       <c r="P70" t="inlineStr" s="2">
@@ -6872,17 +6872,17 @@
     <row r="71">
       <c r="A71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-26-eagle-talks</t>
+          <t xml:space="preserve">2027-02-22-world-thinking-day</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-26</t>
+          <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-26</t>
+          <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
       <c r="D71" t="inlineStr" s="3">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="F71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G71" t="inlineStr" s="2">
@@ -6912,22 +6912,22 @@
       </c>
       <c r="I71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Eagle Talks</t>
+          <t xml:space="preserve">World Thinking Day</t>
         </is>
       </c>
       <c r="J71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">イーグル・トーク</t>
+          <t xml:space="preserve">ワールド・シンキング・デー</t>
         </is>
       </c>
       <c r="K71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students share ideas, experiences, and learning through short presentations designed to build confidence, communication, and leadership skills.</t>
+          <t xml:space="preserve">Students learn about cultures, traditions, and global citizenship while celebrating international understanding and connection.</t>
         </is>
       </c>
       <c r="L71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">短いプレゼンテーションを通して考えや経験、学びを共有し、自信、コミュニケーション力、リーダーシップを育みます。</t>
+          <t xml:space="preserve">国際理解とつながりを祝いながら、さまざまな文化や伝統、地球市民としてのあり方について学びます。</t>
         </is>
       </c>
       <c r="M71" t="inlineStr" s="2">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="O71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-26-eagle-talks.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-22-world-thinking-day.webp</t>
         </is>
       </c>
       <c r="P71" t="inlineStr" s="2">
@@ -6969,17 +6969,17 @@
     <row r="72">
       <c r="A72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-04-grade-1-2-musical</t>
+          <t xml:space="preserve">2027-02-22-secondary-sports-day-rehearsal-1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-04</t>
+          <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-05</t>
+          <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
       <c r="D72" t="inlineStr" s="3">
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G72" t="inlineStr" s="2">
@@ -7009,22 +7009,22 @@
       </c>
       <c r="I72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 1, 2 Musical</t>
+          <t xml:space="preserve">Secondary Sports Day Rehearsal #1</t>
         </is>
       </c>
       <c r="J72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1・2年生ミュージカル</t>
+          <t xml:space="preserve">中等部運動会リハーサル #1</t>
         </is>
       </c>
       <c r="K72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students showcase their creativity and confidence through a musical performance featuring songs, acting, and teamwork.</t>
+          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
         </is>
       </c>
       <c r="L72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">歌、演技、チームワークによるミュージカルを通して、創造性と自信あふれる姿を披露します。</t>
+          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
         </is>
       </c>
       <c r="M72" t="inlineStr" s="2">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="O72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-04-grade-1-2-musical.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-22-secondary-sports-day-rehearsal-1.webp</t>
         </is>
       </c>
       <c r="P72" t="inlineStr" s="2">
@@ -7066,17 +7066,17 @@
     <row r="73">
       <c r="A73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-05-higashiyama-zoo-botanical-garden</t>
+          <t xml:space="preserve">2027-02-25-primary-sports-day-rehearsal-1</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-05</t>
+          <t xml:space="preserve">2027-02-25</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-05</t>
+          <t xml:space="preserve">2027-02-25</t>
         </is>
       </c>
       <c r="D73" t="inlineStr" s="3">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="E73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F73" t="inlineStr" s="2">
@@ -7106,22 +7106,22 @@
       </c>
       <c r="I73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Higashiyama Zoo &amp; Botanical Garden</t>
+          <t xml:space="preserve">Primary Sports Day Rehearsal #1</t>
         </is>
       </c>
       <c r="J73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">東山動植物園</t>
+          <t xml:space="preserve">小学部運動会リハーサル #1</t>
         </is>
       </c>
       <c r="K73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 7 Science students will visit Higashiyama Zoo and Botanical Gardens to support their learning through observation and real-world examples.</t>
+          <t xml:space="preserve">Students begin preparing for Sports Day by practicing events, routines, and teamwork activities.</t>
         </is>
       </c>
       <c r="L73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7年生が理科の学習の一環として東山動植物園を訪れ、観察や実物を通して学びを深めます。</t>
+          <t xml:space="preserve">種目、流れ、チームワークの練習を通して、運動会に向けた準備を始めます。</t>
         </is>
       </c>
       <c r="M73" t="inlineStr" s="2">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="O73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-05-higashiyama-zoo-botanical-garden.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-25-primary-sports-day-rehearsal-1.webp</t>
         </is>
       </c>
       <c r="P73" t="inlineStr" s="2">
@@ -7163,17 +7163,17 @@
     <row r="74">
       <c r="A74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-06-sat-test-6</t>
+          <t xml:space="preserve">2027-02-26-parents-morning-2</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-06</t>
+          <t xml:space="preserve">2027-02-26</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-06</t>
+          <t xml:space="preserve">2027-02-26</t>
         </is>
       </c>
       <c r="D74" t="inlineStr" s="3">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="E74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G74" t="inlineStr" s="2">
@@ -7203,22 +7203,22 @@
       </c>
       <c r="I74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT Test #6</t>
+          <t xml:space="preserve">Parents Morning #2</t>
         </is>
       </c>
       <c r="J74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT試験 第6回</t>
+          <t xml:space="preserve">朝の授業参観 #2</t>
         </is>
       </c>
       <c r="K74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
+          <t xml:space="preserve">ELC and Primary Parents are invited to come and see the lessons in the morning and experience the morning routines with their child.</t>
         </is>
       </c>
       <c r="L74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
+          <t xml:space="preserve">幼稚部・小学部の保護者の皆様をお招きし、朝の授業をご参観いただき、お子様と一緒に朝の日課を体験していただきます。</t>
         </is>
       </c>
       <c r="M74" t="inlineStr" s="2">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="O74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-06-sat-test-6.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-26-parents-morning-2.webp</t>
         </is>
       </c>
       <c r="P74" t="inlineStr" s="2">
@@ -7260,17 +7260,17 @@
     <row r="75">
       <c r="A75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-09-primary-sports-day-rehearsal-2</t>
+          <t xml:space="preserve">2027-02-26-eagle-talks</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-09</t>
+          <t xml:space="preserve">2027-02-26</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-09</t>
+          <t xml:space="preserve">2027-02-26</t>
         </is>
       </c>
       <c r="D75" t="inlineStr" s="3">
@@ -7280,12 +7280,12 @@
       </c>
       <c r="E75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G75" t="inlineStr" s="2">
@@ -7300,22 +7300,22 @@
       </c>
       <c r="I75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary Sports Day Rehearsal #2</t>
+          <t xml:space="preserve">Eagle Talks</t>
         </is>
       </c>
       <c r="J75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小学部運動会リハーサル #2</t>
+          <t xml:space="preserve">イーグル・トーク</t>
         </is>
       </c>
       <c r="K75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students continue building skills and confidence as they prepare for Sports Day events and activities.</t>
+          <t xml:space="preserve">Students share ideas, experiences, and learning through short presentations designed to build confidence, communication, and leadership skills.</t>
         </is>
       </c>
       <c r="L75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会の種目や活動に向けて準備を進めながら、技能と自信をさらに高めます。</t>
+          <t xml:space="preserve">短いプレゼンテーションを通して考えや経験、学びを共有し、自信、コミュニケーション力、リーダーシップを育みます。</t>
         </is>
       </c>
       <c r="M75" t="inlineStr" s="2">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="O75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-09-primary-sports-day-rehearsal-2.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-26-eagle-talks.webp</t>
         </is>
       </c>
       <c r="P75" t="inlineStr" s="2">
@@ -7357,17 +7357,17 @@
     <row r="76">
       <c r="A76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-12-secondary-sports-day-rehearsal-2</t>
+          <t xml:space="preserve">2027-03-04-grade-1-2-musical</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-12</t>
+          <t xml:space="preserve">2027-03-04</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-12</t>
+          <t xml:space="preserve">2027-03-05</t>
         </is>
       </c>
       <c r="D76" t="inlineStr" s="3">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G76" t="inlineStr" s="2">
@@ -7397,22 +7397,22 @@
       </c>
       <c r="I76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary Sports Day Rehearsal #2</t>
+          <t xml:space="preserve">Grade 1, 2 Musical</t>
         </is>
       </c>
       <c r="J76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部運動会リハーサル #2</t>
+          <t xml:space="preserve">1・2年生ミュージカル</t>
         </is>
       </c>
       <c r="K76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
+          <t xml:space="preserve">Students showcase their creativity and confidence through a musical performance featuring songs, acting, and teamwork.</t>
         </is>
       </c>
       <c r="L76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
+          <t xml:space="preserve">歌、演技、チームワークによるミュージカルを通して、創造性と自信あふれる姿を披露します。</t>
         </is>
       </c>
       <c r="M76" t="inlineStr" s="2">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="O76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-12-secondary-sports-day-rehearsal-2.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-04-grade-1-2-musical.webp</t>
         </is>
       </c>
       <c r="P76" t="inlineStr" s="2">
@@ -7454,17 +7454,17 @@
     <row r="77">
       <c r="A77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-18-japanese-culture-day</t>
+          <t xml:space="preserve">2027-03-05-higashiyama-zoo-botanical-garden</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-18</t>
+          <t xml:space="preserve">2027-03-05</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-18</t>
+          <t xml:space="preserve">2027-03-05</t>
         </is>
       </c>
       <c r="D77" t="inlineStr" s="3">
@@ -7474,12 +7474,12 @@
       </c>
       <c r="E77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G77" t="inlineStr" s="2">
@@ -7494,22 +7494,22 @@
       </c>
       <c r="I77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Japanese Culture Day</t>
+          <t xml:space="preserve">Higashiyama Zoo &amp; Botanical Garden</t>
         </is>
       </c>
       <c r="J77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">日本文化デー</t>
+          <t xml:space="preserve">東山動植物園</t>
         </is>
       </c>
       <c r="K77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will deepen their understanding and appreciation of Japanese culture through a variety of interactive activities with school community.</t>
+          <t xml:space="preserve">Grade 7 Science students will visit Higashiyama Zoo and Botanical Gardens to support their learning through observation and real-world examples.</t>
         </is>
       </c>
       <c r="L77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学校コミュニティとともにさまざまな体験型の活動に取り組み、日本文化への理解と関心を深めます。</t>
+          <t xml:space="preserve">7年生が理科の学習の一環として東山動植物園を訪れ、観察や実物を通して学びを深めます。</t>
         </is>
       </c>
       <c r="M77" t="inlineStr" s="2">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="O77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-18-japanese-culture-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-05-higashiyama-zoo-botanical-garden.webp</t>
         </is>
       </c>
       <c r="P77" t="inlineStr" s="2">
@@ -7551,17 +7551,17 @@
     <row r="78">
       <c r="A78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-19-eagle-bucks-store</t>
+          <t xml:space="preserve">2027-03-06-sat-test-6</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-19</t>
+          <t xml:space="preserve">2027-03-06</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-19</t>
+          <t xml:space="preserve">2027-03-06</t>
         </is>
       </c>
       <c r="D78" t="inlineStr" s="3">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="E78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F78" t="inlineStr" s="2">
@@ -7591,22 +7591,22 @@
       </c>
       <c r="I78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Eagle Bucks Store</t>
+          <t xml:space="preserve">SAT Test #6</t>
         </is>
       </c>
       <c r="J78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">イーグルバックス・ストア</t>
+          <t xml:space="preserve">SAT試験 第6回</t>
         </is>
       </c>
       <c r="K78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
+          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
         </is>
       </c>
       <c r="L78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
+          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
         </is>
       </c>
       <c r="M78" t="inlineStr" s="2">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="O78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-19-eagle-bucks-store.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-06-sat-test-6.webp</t>
         </is>
       </c>
       <c r="P78" t="inlineStr" s="2">
@@ -7648,17 +7648,17 @@
     <row r="79">
       <c r="A79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-19-tea-party-pta-for-all</t>
+          <t xml:space="preserve">2027-03-09-primary-sports-day-rehearsal-2</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-19</t>
+          <t xml:space="preserve">2027-03-09</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-19</t>
+          <t xml:space="preserve">2027-03-09</t>
         </is>
       </c>
       <c r="D79" t="inlineStr" s="3">
@@ -7668,12 +7668,12 @@
       </c>
       <c r="E79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTA</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G79" t="inlineStr" s="2">
@@ -7688,22 +7688,22 @@
       </c>
       <c r="I79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Tea Party / PTA for all</t>
+          <t xml:space="preserve">Primary Sports Day Rehearsal #2</t>
         </is>
       </c>
       <c r="J79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTAティーパーティー（どなたでも参加できます）</t>
+          <t xml:space="preserve">小学部運動会リハーサル #2</t>
         </is>
       </c>
       <c r="K79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A social gathering organized by the PTA and Community Club where staff and students are welcome to enjoy a variety of teas, snacks, and friendly conversation together.</t>
+          <t xml:space="preserve">Students continue building skills and confidence as they prepare for Sports Day events and activities.</t>
         </is>
       </c>
       <c r="L79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTAとコミュニティクラブが主催する交流会です。教職員や生徒も参加でき、さまざまなお茶や軽食、和やかな会話を楽しめます。</t>
+          <t xml:space="preserve">運動会の種目や活動に向けて準備を進めながら、技能と自信をさらに高めます。</t>
         </is>
       </c>
       <c r="M79" t="inlineStr" s="2">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="O79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-19-tea-party-pta-for-all.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-09-primary-sports-day-rehearsal-2.webp</t>
         </is>
       </c>
       <c r="P79" t="inlineStr" s="2">
@@ -7745,17 +7745,17 @@
     <row r="80">
       <c r="A80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-19-end-of-term-2-activity-g9-12</t>
+          <t xml:space="preserve">2027-03-12-secondary-sports-day-rehearsal-2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-19</t>
+          <t xml:space="preserve">2027-03-12</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-20</t>
+          <t xml:space="preserve">2027-03-12</t>
         </is>
       </c>
       <c r="D80" t="inlineStr" s="3">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="E80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F80" t="inlineStr" s="2">
@@ -7785,22 +7785,22 @@
       </c>
       <c r="I80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">End of Term 2 Activity: G9-12</t>
+          <t xml:space="preserve">Secondary Sports Day Rehearsal #2</t>
         </is>
       </c>
       <c r="J80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第2学期末行事：G9–12</t>
+          <t xml:space="preserve">中等部運動会リハーサル #2</t>
         </is>
       </c>
       <c r="K80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in an off-campus day trip activity to celebrate the end of Term 2.</t>
+          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
         </is>
       </c>
       <c r="L80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第2学期の終わりを祝い、校外への日帰り活動に参加します。</t>
+          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
         </is>
       </c>
       <c r="M80" t="inlineStr" s="2">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="O80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-19-end-of-term-2-activity-g9-12.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-12-secondary-sports-day-rehearsal-2.webp</t>
         </is>
       </c>
       <c r="P80" t="inlineStr" s="2">
@@ -7842,17 +7842,17 @@
     <row r="81">
       <c r="A81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-20-end-of-term-2-activity-g6-8</t>
+          <t xml:space="preserve">2027-03-15-clubs-pause</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-20</t>
+          <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-21</t>
+          <t xml:space="preserve">2027-04-02</t>
         </is>
       </c>
       <c r="D81" t="inlineStr" s="3">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="E81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F81" t="inlineStr" s="2">
@@ -7882,22 +7882,22 @@
       </c>
       <c r="I81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">End of Term 2 Activity: G6-8</t>
+          <t xml:space="preserve">Clubs Pause</t>
         </is>
       </c>
       <c r="J81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第2学期末行事：G6–8</t>
+          <t xml:space="preserve">クラブ活動休止</t>
         </is>
       </c>
       <c r="K81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in an overnight camp at an off-campus camping facility to celebrate the end of Term 2.</t>
+          <t xml:space="preserve">After-school clubs are paused during this period. Bus reminder: the afternoon Red bus runs only on club days, so it does not run while clubs are paused. Please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
         </is>
       </c>
       <c r="L81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第2学期の終わりを祝い、校外のキャンプ施設での一泊キャンプに参加します。</t>
+          <t xml:space="preserve">この期間、放課後のクラブ活動はお休みです。【バスについて】午後の赤バスはクラブ活動がある日のみ運行するため、休止期間中は運行しません。午後の下校時は青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
         </is>
       </c>
       <c r="M81" t="inlineStr" s="2">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-20-end-of-term-2-activity-g6-8.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P81" t="inlineStr" s="2">
@@ -7939,17 +7939,17 @@
     <row r="82">
       <c r="A82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-30-parent-teacher-conferences</t>
+          <t xml:space="preserve">2027-03-18-japanese-culture-day</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-30</t>
+          <t xml:space="preserve">2027-03-18</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-30</t>
+          <t xml:space="preserve">2027-03-18</t>
         </is>
       </c>
       <c r="D82" t="inlineStr" s="3">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="G82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H82" t="inlineStr" s="2">
@@ -7979,22 +7979,22 @@
       </c>
       <c r="I82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parent Teacher Conferences</t>
+          <t xml:space="preserve">Japanese Culture Day</t>
         </is>
       </c>
       <c r="J82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者面談</t>
+          <t xml:space="preserve">日本文化デー</t>
         </is>
       </c>
       <c r="K82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on this day.</t>
+          <t xml:space="preserve">Students will deepen their understanding and appreciation of Japanese culture through a variety of interactive activities with school community.</t>
         </is>
       </c>
       <c r="L82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。当日、生徒は登校しません。</t>
+          <t xml:space="preserve">学校コミュニティとともにさまざまな体験型の活動に取り組み、日本文化への理解と関心を深めます。</t>
         </is>
       </c>
       <c r="M82" t="inlineStr" s="2">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="O82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-30-parent-teacher-conferences.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-18-japanese-culture-day.webp</t>
         </is>
       </c>
       <c r="P82" t="inlineStr" s="2">
@@ -8036,17 +8036,17 @@
     <row r="83">
       <c r="A83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-31-secondary-sports-day-rehearsal-3</t>
+          <t xml:space="preserve">2027-03-19-eagle-bucks-store</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-31</t>
+          <t xml:space="preserve">2027-03-19</t>
         </is>
       </c>
       <c r="C83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-31</t>
+          <t xml:space="preserve">2027-03-19</t>
         </is>
       </c>
       <c r="D83" t="inlineStr" s="3">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="E83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr" s="2">
@@ -8076,22 +8076,22 @@
       </c>
       <c r="I83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary Sports Day Rehearsal #3</t>
+          <t xml:space="preserve">Eagle Bucks Store</t>
         </is>
       </c>
       <c r="J83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部運動会リハーサル #3</t>
+          <t xml:space="preserve">イーグルバックス・ストア</t>
         </is>
       </c>
       <c r="K83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
+          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
         </is>
       </c>
       <c r="L83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
+          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
         </is>
       </c>
       <c r="M83" t="inlineStr" s="2">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="O83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-31-secondary-sports-day-rehearsal-3.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-19-eagle-bucks-store.webp</t>
         </is>
       </c>
       <c r="P83" t="inlineStr" s="2">
@@ -8133,17 +8133,17 @@
     <row r="84">
       <c r="A84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-01-primary-sports-day-rehearsal-3</t>
+          <t xml:space="preserve">2027-03-19-tea-party-pta-for-all</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-01</t>
+          <t xml:space="preserve">2027-03-19</t>
         </is>
       </c>
       <c r="C84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-01</t>
+          <t xml:space="preserve">2027-03-19</t>
         </is>
       </c>
       <c r="D84" t="inlineStr" s="3">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="E84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">PTA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G84" t="inlineStr" s="2">
@@ -8173,22 +8173,22 @@
       </c>
       <c r="I84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary Sports Day Rehearsal #3</t>
+          <t xml:space="preserve">Tea Party / PTA for all</t>
         </is>
       </c>
       <c r="J84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小学部運動会リハーサル #3</t>
+          <t xml:space="preserve">PTAティーパーティー（どなたでも参加できます）</t>
         </is>
       </c>
       <c r="K84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The final rehearsal provides students with an opportunity to practice events and ensure they are ready for Sports Day.</t>
+          <t xml:space="preserve">A social gathering organized by the PTA and Community Club where staff and students are welcome to enjoy a variety of teas, snacks, and friendly conversation together.</t>
         </is>
       </c>
       <c r="L84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">最終リハーサルで各種目を練習し、運動会当日に向けて準備を整えます。</t>
+          <t xml:space="preserve">PTAとコミュニティクラブが主催する交流会です。教職員や生徒も参加でき、さまざまなお茶や軽食、和やかな会話を楽しめます。</t>
         </is>
       </c>
       <c r="M84" t="inlineStr" s="2">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="O84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-01-primary-sports-day-rehearsal-3.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-19-tea-party-pta-for-all.webp</t>
         </is>
       </c>
       <c r="P84" t="inlineStr" s="2">
@@ -8230,17 +8230,17 @@
     <row r="85">
       <c r="A85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-03-sports-day</t>
+          <t xml:space="preserve">2027-03-19-end-of-term-2-activity-g9-12</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-03</t>
+          <t xml:space="preserve">2027-03-19</t>
         </is>
       </c>
       <c r="C85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-03</t>
+          <t xml:space="preserve">2027-03-20</t>
         </is>
       </c>
       <c r="D85" t="inlineStr" s="3">
@@ -8250,12 +8250,12 @@
       </c>
       <c r="E85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G85" t="inlineStr" s="2">
@@ -8270,22 +8270,22 @@
       </c>
       <c r="I85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sports Day</t>
+          <t xml:space="preserve">End of Term 2 Activity: G9-12</t>
         </is>
       </c>
       <c r="J85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会</t>
+          <t xml:space="preserve">第2学期末行事：G9–12</t>
         </is>
       </c>
       <c r="K85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in Sports Day activities, participating in team games, athletic challenges, and school spirit events.</t>
+          <t xml:space="preserve">Students will take part in an off-campus day trip activity to celebrate the end of Term 2.</t>
         </is>
       </c>
       <c r="L85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会に参加し、チームゲーム、運動競技、応援などの行事に取り組みます。</t>
+          <t xml:space="preserve">第2学期の終わりを祝い、校外への日帰り活動に参加します。</t>
         </is>
       </c>
       <c r="M85" t="inlineStr" s="2">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="O85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-03-sports-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-19-end-of-term-2-activity-g9-12.webp</t>
         </is>
       </c>
       <c r="P85" t="inlineStr" s="2">
@@ -8327,17 +8327,17 @@
     <row r="86">
       <c r="A86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-03-primary-sports-day-2027</t>
+          <t xml:space="preserve">2027-03-20-end-of-term-2-activity-g6-8</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-03</t>
+          <t xml:space="preserve">2027-03-20</t>
         </is>
       </c>
       <c r="C86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-03</t>
+          <t xml:space="preserve">2027-03-21</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="3">
@@ -8347,12 +8347,12 @@
       </c>
       <c r="E86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G86" t="inlineStr" s="2">
@@ -8367,22 +8367,22 @@
       </c>
       <c r="I86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary Sports Day 2027</t>
+          <t xml:space="preserve">End of Term 2 Activity: G6-8</t>
         </is>
       </c>
       <c r="J86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小学部運動会 2027</t>
+          <t xml:space="preserve">第2学期末行事：G6–8</t>
         </is>
       </c>
       <c r="K86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students participate in a day of fun, fitness, and friendly competition while demonstrating teamwork, perseverance, and sportsmanship.</t>
+          <t xml:space="preserve">Students will take part in an overnight camp at an off-campus camping facility to celebrate the end of Term 2.</t>
         </is>
       </c>
       <c r="L86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">チームワーク、粘り強さ、スポーツマンシップを発揮しながら、楽しく体を動かし、仲間と競い合う一日を過ごします。</t>
+          <t xml:space="preserve">第2学期の終わりを祝い、校外のキャンプ施設での一泊キャンプに参加します。</t>
         </is>
       </c>
       <c r="M86" t="inlineStr" s="2">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="O86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-03-primary-sports-day-2027.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-20-end-of-term-2-activity-g6-8.webp</t>
         </is>
       </c>
       <c r="P86" t="inlineStr" s="2">
@@ -8424,17 +8424,17 @@
     <row r="87">
       <c r="A87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-15-world-art-day</t>
+          <t xml:space="preserve">2027-03-30-parent-teacher-conferences</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-15</t>
+          <t xml:space="preserve">2027-03-30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-15</t>
+          <t xml:space="preserve">2027-03-30</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="3">
@@ -8444,7 +8444,7 @@
       </c>
       <c r="E87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F87" t="inlineStr" s="2">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="G87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="H87" t="inlineStr" s="2">
@@ -8464,22 +8464,22 @@
       </c>
       <c r="I87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">World Art Day</t>
+          <t xml:space="preserve">Parent Teacher Conferences</t>
         </is>
       </c>
       <c r="J87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ワールド・アート・デー</t>
+          <t xml:space="preserve">保護者面談</t>
         </is>
       </c>
       <c r="K87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students celebrate creativity through art activities, exhibitions, and opportunities to explore different artistic styles and cultures.</t>
+          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on this day.</t>
         </is>
       </c>
       <c r="L87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">アート活動や展示を通して創造性を祝い、さまざまな芸術様式や文化に触れます。</t>
+          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。当日、生徒は登校しません。</t>
         </is>
       </c>
       <c r="M87" t="inlineStr" s="2">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="O87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-15-world-art-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-30-parent-teacher-conferences.webp</t>
         </is>
       </c>
       <c r="P87" t="inlineStr" s="2">
@@ -8521,17 +8521,17 @@
     <row r="88">
       <c r="A88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-16-foundation-field-trip</t>
+          <t xml:space="preserve">2027-03-31-secondary-sports-day-rehearsal-3</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-16</t>
+          <t xml:space="preserve">2027-03-31</t>
         </is>
       </c>
       <c r="C88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-16</t>
+          <t xml:space="preserve">2027-03-31</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="3">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="E88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G88" t="inlineStr" s="2">
@@ -8561,22 +8561,22 @@
       </c>
       <c r="I88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Foundation Field Trip</t>
+          <t xml:space="preserve">Secondary Sports Day Rehearsal #3</t>
         </is>
       </c>
       <c r="J88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ファウンデーション校外学習</t>
+          <t xml:space="preserve">中等部運動会リハーサル #3</t>
         </is>
       </c>
       <c r="K88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Our youngest learners will enjoy an age-appropriate educational excursion that supports classroom learning through hands-on experiences.</t>
+          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
         </is>
       </c>
       <c r="L88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">年少の子どもたちが、年齢に合った校外学習に出かけ、体験を通して教室での学びを深めます。</t>
+          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
         </is>
       </c>
       <c r="M88" t="inlineStr" s="2">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="O88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-16-foundation-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-31-secondary-sports-day-rehearsal-3.webp</t>
         </is>
       </c>
       <c r="P88" t="inlineStr" s="2">
@@ -8618,17 +8618,17 @@
     <row r="89">
       <c r="A89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-21-hackathon-hour-of-code</t>
+          <t xml:space="preserve">2027-04-01-primary-sports-day-rehearsal-3</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-21</t>
+          <t xml:space="preserve">2027-04-01</t>
         </is>
       </c>
       <c r="C89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-21</t>
+          <t xml:space="preserve">2027-04-01</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="3">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="E89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F89" t="inlineStr" s="2">
@@ -8658,22 +8658,22 @@
       </c>
       <c r="I89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hackathon (Hour of Code)</t>
+          <t xml:space="preserve">Primary Sports Day Rehearsal #3</t>
         </is>
       </c>
       <c r="J89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ハッカソン（Hour of Code）</t>
+          <t xml:space="preserve">小学部運動会リハーサル #3</t>
         </is>
       </c>
       <c r="K89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in an engaging Hour of Code challenge, using creativity and problem-solving skills to build simple coding projects. This event encourages computational thinking, teamwork, and confidence in technology in a fun and supportive environment.</t>
+          <t xml:space="preserve">The final rehearsal provides students with an opportunity to practice events and ensure they are ready for Sports Day.</t>
         </is>
       </c>
       <c r="L89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hour of Codeチャレンジに参加し、創造性と問題解決力を生かして簡単なプログラミング作品を作ります。楽しく支え合う環境の中で、コンピュテーショナル・シンキング、チームワーク、テクノロジーへの自信を育みます。</t>
+          <t xml:space="preserve">最終リハーサルで各種目を練習し、運動会当日に向けて準備を整えます。</t>
         </is>
       </c>
       <c r="M89" t="inlineStr" s="2">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="O89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-21-hackathon-hour-of-code.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-01-primary-sports-day-rehearsal-3.webp</t>
         </is>
       </c>
       <c r="P89" t="inlineStr" s="2">
@@ -8715,17 +8715,17 @@
     <row r="90">
       <c r="A90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-22-biology-ia-prep-field-trip-shore-ecosystem</t>
+          <t xml:space="preserve">2027-04-03-sports-day</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-22</t>
+          <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
       <c r="C90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-22</t>
+          <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="3">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="E90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G90" t="inlineStr" s="2">
@@ -8755,22 +8755,22 @@
       </c>
       <c r="I90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Biology IA Prep. Field Trip: Shore Ecosystem</t>
+          <t xml:space="preserve">Sports Day</t>
         </is>
       </c>
       <c r="J90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">生物IA準備校外学習：海岸生態系調査</t>
+          <t xml:space="preserve">運動会</t>
         </is>
       </c>
       <c r="K90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 11 and 12 Biology students will visit a shore ecosystem to prepare for their Biology Internal Assessment by collecting fieldwork data and practicing research methods.</t>
+          <t xml:space="preserve">Students will take part in Sports Day activities, participating in team games, athletic challenges, and school spirit events.</t>
         </is>
       </c>
       <c r="L90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11・12年生の生物履修者が海岸の生態系を訪れ、フィールドワークでのデータ収集や研究手法の練習を通して、生物の内部評価（IA）に向けた準備を行います。</t>
+          <t xml:space="preserve">運動会に参加し、チームゲーム、運動競技、応援などの行事に取り組みます。</t>
         </is>
       </c>
       <c r="M90" t="inlineStr" s="2">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="O90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-22-biology-ia-prep-field-trip-shore-ecosystem.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-03-sports-day.webp</t>
         </is>
       </c>
       <c r="P90" t="inlineStr" s="2">
@@ -8812,17 +8812,17 @@
     <row r="91">
       <c r="A91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-23-g12-celebration</t>
+          <t xml:space="preserve">2027-04-03-primary-sports-day-2027</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-23</t>
+          <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
       <c r="C91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-23</t>
+          <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="3">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G91" t="inlineStr" s="2">
@@ -8852,22 +8852,22 @@
       </c>
       <c r="I91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G12 Celebration</t>
+          <t xml:space="preserve">Primary Sports Day 2027</t>
         </is>
       </c>
       <c r="J91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G12修了記念イベント</t>
+          <t xml:space="preserve">小学部運動会 2027</t>
         </is>
       </c>
       <c r="K91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 12 students will take part in a Graduation Walk as the school community celebrates them ahead of graduation.</t>
+          <t xml:space="preserve">Students participate in a day of fun, fitness, and friendly competition while demonstrating teamwork, perseverance, and sportsmanship.</t>
         </is>
       </c>
       <c r="L91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">卒業を前に、12年生がグラデュエーション・ウォークに参加し、学校コミュニティ全体でお祝いします。</t>
+          <t xml:space="preserve">チームワーク、粘り強さ、スポーツマンシップを発揮しながら、楽しく体を動かし、仲間と競い合う一日を過ごします。</t>
         </is>
       </c>
       <c r="M91" t="inlineStr" s="2">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="O91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-23-g12-celebration.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-03-primary-sports-day-2027.webp</t>
         </is>
       </c>
       <c r="P91" t="inlineStr" s="2">
@@ -8909,17 +8909,17 @@
     <row r="92">
       <c r="A92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-26-grade-4-5-camping-trip</t>
+          <t xml:space="preserve">2027-04-05-clubs-resume</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-26</t>
+          <t xml:space="preserve">2027-04-05</t>
         </is>
       </c>
       <c r="C92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-27</t>
+          <t xml:space="preserve">2027-04-05</t>
         </is>
       </c>
       <c r="D92" t="inlineStr" s="3">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="E92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F92" t="inlineStr" s="2">
@@ -8949,22 +8949,22 @@
       </c>
       <c r="I92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 4, 5 Camping Trip</t>
+          <t xml:space="preserve">Clubs Resume</t>
         </is>
       </c>
       <c r="J92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4・5年生キャンプ</t>
+          <t xml:space="preserve">クラブ活動再開</t>
         </is>
       </c>
       <c r="K92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students enjoy an outdoor learning experience that promotes independence, teamwork, resilience, and a connection with nature.</t>
+          <t xml:space="preserve">After-school clubs start again today. Bus reminder: the afternoon Red bus runs only on club days. On other days, please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
         </is>
       </c>
       <c r="L92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">自立心、チームワーク、たくましさ、自然とのつながりを育む野外学習を楽しみます。</t>
+          <t xml:space="preserve">本日から放課後のクラブ活動が再開します。【バスについて】午後の赤バスはクラブ活動がある日のみ運行します。それ以外の日は、午後の下校時に青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
         </is>
       </c>
       <c r="M92" t="inlineStr" s="2">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="O92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-26-grade-4-5-camping-trip.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P92" t="inlineStr" s="2">
@@ -9006,17 +9006,17 @@
     <row r="93">
       <c r="A93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-27-choir-and-orchestra-concert</t>
+          <t xml:space="preserve">2027-04-15-world-art-day</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-27</t>
+          <t xml:space="preserve">2027-04-15</t>
         </is>
       </c>
       <c r="C93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-27</t>
+          <t xml:space="preserve">2027-04-15</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="3">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="E93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr" s="2">
@@ -9046,22 +9046,22 @@
       </c>
       <c r="I93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choir and Orchestra Concert</t>
+          <t xml:space="preserve">World Art Day</t>
         </is>
       </c>
       <c r="J93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合唱・オーケストラコンサート</t>
+          <t xml:space="preserve">ワールド・アート・デー</t>
         </is>
       </c>
       <c r="K93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choir class and orchestra club will perform the music repertoire they have been rehearsing for an audience of family, peers and teachers.</t>
+          <t xml:space="preserve">Students celebrate creativity through art activities, exhibitions, and opportunities to explore different artistic styles and cultures.</t>
         </is>
       </c>
       <c r="L93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合唱クラスとオーケストラクラブが、練習を重ねてきた曲目をご家族、友人、教員の前で演奏します。</t>
+          <t xml:space="preserve">アート活動や展示を通して創造性を祝い、さまざまな芸術様式や文化に触れます。</t>
         </is>
       </c>
       <c r="M93" t="inlineStr" s="2">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="O93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-27-choir-and-orchestra-concert.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-15-world-art-day.webp</t>
         </is>
       </c>
       <c r="P93" t="inlineStr" s="2">
@@ -9103,17 +9103,17 @@
     <row r="94">
       <c r="A94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-30-science-fair</t>
+          <t xml:space="preserve">2027-04-16-foundation-field-trip</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-30</t>
+          <t xml:space="preserve">2027-04-16</t>
         </is>
       </c>
       <c r="C94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-30</t>
+          <t xml:space="preserve">2027-04-16</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="3">
@@ -9123,7 +9123,7 @@
       </c>
       <c r="E94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F94" t="inlineStr" s="2">
@@ -9143,22 +9143,22 @@
       </c>
       <c r="I94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Science Fair</t>
+          <t xml:space="preserve">Foundation Field Trip</t>
         </is>
       </c>
       <c r="J94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">サイエンスフェア</t>
+          <t xml:space="preserve">ファウンデーション校外学習</t>
         </is>
       </c>
       <c r="K94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will share their science projects and investigations with the school community, showcasing their research, creativity, and scientific thinking.</t>
+          <t xml:space="preserve">Our youngest learners will enjoy an age-appropriate educational excursion that supports classroom learning through hands-on experiences.</t>
         </is>
       </c>
       <c r="L94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">理科のプロジェクトや探究の成果を学校コミュニティに発表し、研究、創造性、科学的思考を披露します。</t>
+          <t xml:space="preserve">年少の子どもたちが、年齢に合った校外学習に出かけ、体験を通して教室での学びを深めます。</t>
         </is>
       </c>
       <c r="M94" t="inlineStr" s="2">
@@ -9173,7 +9173,7 @@
       </c>
       <c r="O94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-30-science-fair.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-16-foundation-field-trip.webp</t>
         </is>
       </c>
       <c r="P94" t="inlineStr" s="2">
@@ -9200,17 +9200,17 @@
     <row r="95">
       <c r="A95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-17-friendly-basketball-tournament-internal</t>
+          <t xml:space="preserve">2027-04-21-hackathon-hour-of-code</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-17</t>
+          <t xml:space="preserve">2027-04-21</t>
         </is>
       </c>
       <c r="C95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-21</t>
+          <t xml:space="preserve">2027-04-21</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="3">
@@ -9240,22 +9240,22 @@
       </c>
       <c r="I95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Friendly Basketball Tournament (Internal)</t>
+          <t xml:space="preserve">Hackathon (Hour of Code)</t>
         </is>
       </c>
       <c r="J95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内バスケットボール大会</t>
+          <t xml:space="preserve">ハッカソン（Hour of Code）</t>
         </is>
       </c>
       <c r="K95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in a friendly internal basketball tournament, promoting teamwork, sportsmanship, and school spirit.</t>
+          <t xml:space="preserve">Students will take part in an engaging Hour of Code challenge, using creativity and problem-solving skills to build simple coding projects. This event encourages computational thinking, teamwork, and confidence in technology in a fun and supportive environment.</t>
         </is>
       </c>
       <c r="L95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内バスケットボール大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
+          <t xml:space="preserve">Hour of Codeチャレンジに参加し、創造性と問題解決力を生かして簡単なプログラミング作品を作ります。楽しく支え合う環境の中で、コンピュテーショナル・シンキング、チームワーク、テクノロジーへの自信を育みます。</t>
         </is>
       </c>
       <c r="M95" t="inlineStr" s="2">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="O95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-17-friendly-basketball-tournament-internal.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-21-hackathon-hour-of-code.webp</t>
         </is>
       </c>
       <c r="P95" t="inlineStr" s="2">
@@ -9297,17 +9297,17 @@
     <row r="96">
       <c r="A96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-19-entrepreneurs-day</t>
+          <t xml:space="preserve">2027-04-22-biology-ia-prep-field-trip-shore-ecosystem</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-19</t>
+          <t xml:space="preserve">2027-04-22</t>
         </is>
       </c>
       <c r="C96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-20</t>
+          <t xml:space="preserve">2027-04-22</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="3">
@@ -9317,12 +9317,12 @@
       </c>
       <c r="E96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G96" t="inlineStr" s="2">
@@ -9337,22 +9337,22 @@
       </c>
       <c r="I96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Entrepreneurs Day</t>
+          <t xml:space="preserve">Biology IA Prep. Field Trip: Shore Ecosystem</t>
         </is>
       </c>
       <c r="J96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">アントレプレナーシップ・デー</t>
+          <t xml:space="preserve">生物IA準備校外学習：海岸生態系調査</t>
         </is>
       </c>
       <c r="K96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students develop and showcase business ideas while learning about creativity, financial literacy, problem-solving, and entrepreneurship.</t>
+          <t xml:space="preserve">Grade 11 and 12 Biology students will visit a shore ecosystem to prepare for their Biology Internal Assessment by collecting fieldwork data and practicing research methods.</t>
         </is>
       </c>
       <c r="L96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">創造性、金融リテラシー、問題解決、起業家精神について学びながら、ビジネスのアイデアを考え、発表します。</t>
+          <t xml:space="preserve">11・12年生の生物履修者が海岸の生態系を訪れ、フィールドワークでのデータ収集や研究手法の練習を通して、生物の内部評価（IA）に向けた準備を行います。</t>
         </is>
       </c>
       <c r="M96" t="inlineStr" s="2">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="O96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-19-entrepreneurs-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-22-biology-ia-prep-field-trip-shore-ecosystem.webp</t>
         </is>
       </c>
       <c r="P96" t="inlineStr" s="2">
@@ -9394,17 +9394,17 @@
     <row r="97">
       <c r="A97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-21-collective-field-trip</t>
+          <t xml:space="preserve">2027-04-23-g12-celebration</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-21</t>
+          <t xml:space="preserve">2027-04-23</t>
         </is>
       </c>
       <c r="C97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-21</t>
+          <t xml:space="preserve">2027-04-23</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="3">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="E97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F97" t="inlineStr" s="2">
@@ -9434,22 +9434,22 @@
       </c>
       <c r="I97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Collective Field Trip</t>
+          <t xml:space="preserve">G12 Celebration</t>
         </is>
       </c>
       <c r="J97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合同校外学習</t>
+          <t xml:space="preserve">G12修了記念イベント</t>
         </is>
       </c>
       <c r="K97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students participate in a shared educational experience that promotes collaboration, inquiry, and real-world learning.</t>
+          <t xml:space="preserve">Grade 12 students will take part in a Graduation Walk as the school community celebrates them ahead of graduation.</t>
         </is>
       </c>
       <c r="L97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">協働、探究、実社会での学びを促す合同の学習体験に参加します。</t>
+          <t xml:space="preserve">卒業を前に、12年生がグラデュエーション・ウォークに参加し、学校コミュニティ全体でお祝いします。</t>
         </is>
       </c>
       <c r="M97" t="inlineStr" s="2">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="O97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-21-collective-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-23-g12-celebration.webp</t>
         </is>
       </c>
       <c r="P97" t="inlineStr" s="2">
@@ -9491,17 +9491,17 @@
     <row r="98">
       <c r="A98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-22-saturday-school-last-day-event</t>
+          <t xml:space="preserve">2027-04-26-grade-4-5-camping-trip</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-04-26</t>
         </is>
       </c>
       <c r="C98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="3">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="E98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F98" t="inlineStr" s="2">
@@ -9531,22 +9531,22 @@
       </c>
       <c r="I98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saturday School Last Day Event</t>
+          <t xml:space="preserve">Grade 4, 5 Camping Trip</t>
         </is>
       </c>
       <c r="J98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">土曜校最終日イベント</t>
+          <t xml:space="preserve">4・5年生キャンプ</t>
         </is>
       </c>
       <c r="K98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in a relaxed final Saturday School session, with leisure activities at school to celebrate the last day.</t>
+          <t xml:space="preserve">Students enjoy an outdoor learning experience that promotes independence, teamwork, resilience, and a connection with nature.</t>
         </is>
       </c>
       <c r="L98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">土曜校の最終日を、校内でのレクリエーション活動とともにリラックスして過ごし、お祝いします。</t>
+          <t xml:space="preserve">自立心、チームワーク、たくましさ、自然とのつながりを育む野外学習を楽しみます。</t>
         </is>
       </c>
       <c r="M98" t="inlineStr" s="2">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="O98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-22-saturday-school-last-day-event.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-26-grade-4-5-camping-trip.webp</t>
         </is>
       </c>
       <c r="P98" t="inlineStr" s="2">
@@ -9588,17 +9588,17 @@
     <row r="99">
       <c r="A99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-24-concept-con-future-focus</t>
+          <t xml:space="preserve">2027-04-27-choir-and-orchestra-concert</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-24</t>
+          <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
       <c r="C99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-28</t>
+          <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="3">
@@ -9608,12 +9608,12 @@
       </c>
       <c r="E99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G99" t="inlineStr" s="2">
@@ -9628,22 +9628,22 @@
       </c>
       <c r="I99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Concept Con (Future Focus)</t>
+          <t xml:space="preserve">Choir and Orchestra Concert</t>
         </is>
       </c>
       <c r="J99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">コンセプト・コン（未来を考える）</t>
+          <t xml:space="preserve">合唱・オーケストラコンサート</t>
         </is>
       </c>
       <c r="K99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students investigate future possibilities, innovations, and solutions to real-world challenges through inquiry-based projects and presentations.</t>
+          <t xml:space="preserve">Choir class and orchestra club will perform the music repertoire they have been rehearsing for an audience of family, peers and teachers.</t>
         </is>
       </c>
       <c r="L99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">探究型のプロジェクトや発表を通して、未来の可能性、イノベーション、現実の課題の解決策について考えます。</t>
+          <t xml:space="preserve">合唱クラスとオーケストラクラブが、練習を重ねてきた曲目をご家族、友人、教員の前で演奏します。</t>
         </is>
       </c>
       <c r="M99" t="inlineStr" s="2">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="O99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-24-concept-con-future-focus.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-27-choir-and-orchestra-concert.webp</t>
         </is>
       </c>
       <c r="P99" t="inlineStr" s="2">
@@ -9685,17 +9685,17 @@
     <row r="100">
       <c r="A100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-28-g12-graduation-with-performances</t>
+          <t xml:space="preserve">2027-04-30-science-fair</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-29</t>
+          <t xml:space="preserve">2027-04-30</t>
         </is>
       </c>
       <c r="C100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-29</t>
+          <t xml:space="preserve">2027-04-30</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="3">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="E100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F100" t="inlineStr" s="2">
@@ -9720,27 +9720,27 @@
       </c>
       <c r="H100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">changed</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G12 Graduation with Performances</t>
+          <t xml:space="preserve">Science Fair</t>
         </is>
       </c>
       <c r="J100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G12卒業式・記念パフォーマンス</t>
+          <t xml:space="preserve">サイエンスフェア</t>
         </is>
       </c>
       <c r="K100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 12 students will celebrate their graduation with a formal ceremony featuring student performances and the wider school community.</t>
+          <t xml:space="preserve">Students will share their science projects and investigations with the school community, showcasing their research, creativity, and scientific thinking.</t>
         </is>
       </c>
       <c r="L100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12年生が、生徒によるパフォーマンスを交えた式典で、学校コミュニティ全体とともに卒業を祝います。</t>
+          <t xml:space="preserve">理科のプロジェクトや探究の成果を学校コミュニティに発表し、研究、創造性、科学的思考を披露します。</t>
         </is>
       </c>
       <c r="M100" t="inlineStr" s="2">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="O100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-28-g12-graduation-with-performances.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-30-science-fair.webp</t>
         </is>
       </c>
       <c r="P100" t="inlineStr" s="2">
@@ -9782,17 +9782,17 @@
     <row r="101">
       <c r="A101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-03-celebration-of-learning-prep</t>
+          <t xml:space="preserve">2027-05-17-friendly-basketball-tournament-internal</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-03</t>
+          <t xml:space="preserve">2027-05-17</t>
         </is>
       </c>
       <c r="C101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-03</t>
+          <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="3">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="E101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F101" t="inlineStr" s="2">
@@ -9822,22 +9822,22 @@
       </c>
       <c r="I101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Celebration of Learning Prep</t>
+          <t xml:space="preserve">Friendly Basketball Tournament (Internal)</t>
         </is>
       </c>
       <c r="J101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学びの発表会準備</t>
+          <t xml:space="preserve">校内バスケットボール大会</t>
         </is>
       </c>
       <c r="K101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students help prepare the school for the Celebration of Learning by organizing learning spaces, setting up displays, arranging materials, and ensuring classrooms and common areas are ready to welcome visitors. This preparation helps create an engaging and welcoming environment for families and guests.</t>
+          <t xml:space="preserve">Students will take part in a friendly internal basketball tournament, promoting teamwork, sportsmanship, and school spirit.</t>
         </is>
       </c>
       <c r="L101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学びの発表会に向けて、学習スペースの整理、展示の設営、資料の準備を行い、教室や共用エリアで来場者をお迎えできるよう整えます。ご家族やお客様にとって魅力的で温かな空間づくりにつながります。</t>
+          <t xml:space="preserve">校内バスケットボール大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
         </is>
       </c>
       <c r="M101" t="inlineStr" s="2">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="O101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-03-celebration-of-learning-prep.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-17-friendly-basketball-tournament-internal.webp</t>
         </is>
       </c>
       <c r="P101" t="inlineStr" s="2">
@@ -9879,17 +9879,17 @@
     <row r="102">
       <c r="A102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-03-ukulele-concert</t>
+          <t xml:space="preserve">2027-05-19-entrepreneurs-day</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-03</t>
+          <t xml:space="preserve">2027-05-19</t>
         </is>
       </c>
       <c r="C102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-04</t>
+          <t xml:space="preserve">2027-05-20</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="3">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="E102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr" s="2">
@@ -9919,22 +9919,22 @@
       </c>
       <c r="I102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ukulele Concert</t>
+          <t xml:space="preserve">Entrepreneurs Day</t>
         </is>
       </c>
       <c r="J102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ウクレレコンサート</t>
+          <t xml:space="preserve">アントレプレナーシップ・デー</t>
         </is>
       </c>
       <c r="K102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students perform musical pieces they have learned throughout the year, demonstrating their growth, confidence, and musical skills.</t>
+          <t xml:space="preserve">Students develop and showcase business ideas while learning about creativity, financial literacy, problem-solving, and entrepreneurship.</t>
         </is>
       </c>
       <c r="L102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一年を通して学んだ曲を演奏し、成長、自信、音楽の技能を披露します。</t>
+          <t xml:space="preserve">創造性、金融リテラシー、問題解決、起業家精神について学びながら、ビジネスのアイデアを考え、発表します。</t>
         </is>
       </c>
       <c r="M102" t="inlineStr" s="2">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="O102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-03-ukulele-concert.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-19-entrepreneurs-day.webp</t>
         </is>
       </c>
       <c r="P102" t="inlineStr" s="2">
@@ -9976,17 +9976,17 @@
     <row r="103">
       <c r="A103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-04-celebration-of-learning</t>
+          <t xml:space="preserve">2027-05-21-collective-field-trip</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-04</t>
+          <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
       <c r="C103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-04</t>
+          <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="3">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="E103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G103" t="inlineStr" s="2">
@@ -10016,22 +10016,22 @@
       </c>
       <c r="I103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Celebration of Learning</t>
+          <t xml:space="preserve">Collective Field Trip</t>
         </is>
       </c>
       <c r="J103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学びの発表会</t>
+          <t xml:space="preserve">合同校外学習</t>
         </is>
       </c>
       <c r="K103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The school community will celebrate learning as students share projects and exhibitions, including PYPX, MYPX, CAS, EE, TOK and Foundation to 4 projects.</t>
+          <t xml:space="preserve">Students participate in a shared educational experience that promotes collaboration, inquiry, and real-world learning.</t>
         </is>
       </c>
       <c r="L103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PYPX、MYPX、CAS、EE、TOK、ファウンデーション～4年生のプロジェクトなど、生徒の作品や展示を通して学校コミュニティ全体で学びを祝います。</t>
+          <t xml:space="preserve">協働、探究、実社会での学びを促す合同の学習体験に参加します。</t>
         </is>
       </c>
       <c r="M103" t="inlineStr" s="2">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="O103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-04-celebration-of-learning.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-21-collective-field-trip.webp</t>
         </is>
       </c>
       <c r="P103" t="inlineStr" s="2">
@@ -10073,17 +10073,17 @@
     <row r="104">
       <c r="A104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-05-sat-test-7</t>
+          <t xml:space="preserve">2027-05-22-saturday-school-last-day-event</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-05</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="C104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-05</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="3">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="E104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F104" t="inlineStr" s="2">
@@ -10113,22 +10113,22 @@
       </c>
       <c r="I104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT Test #7</t>
+          <t xml:space="preserve">Saturday School Last Day Event</t>
         </is>
       </c>
       <c r="J104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT試験 第7回</t>
+          <t xml:space="preserve">土曜校最終日イベント</t>
         </is>
       </c>
       <c r="K104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
+          <t xml:space="preserve">Students will take part in a relaxed final Saturday School session, with leisure activities at school to celebrate the last day.</t>
         </is>
       </c>
       <c r="L104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
+          <t xml:space="preserve">土曜校の最終日を、校内でのレクリエーション活動とともにリラックスして過ごし、お祝いします。</t>
         </is>
       </c>
       <c r="M104" t="inlineStr" s="2">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="O104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-05-sat-test-7.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-22-saturday-school-last-day-event.webp</t>
         </is>
       </c>
       <c r="P104" t="inlineStr" s="2">
@@ -10170,17 +10170,17 @@
     <row r="105">
       <c r="A105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-17-eagle-bucks-store</t>
+          <t xml:space="preserve">2027-05-24-concept-con-future-focus</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-17</t>
+          <t xml:space="preserve">2027-05-24</t>
         </is>
       </c>
       <c r="C105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-17</t>
+          <t xml:space="preserve">2027-05-28</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="3">
@@ -10210,22 +10210,22 @@
       </c>
       <c r="I105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Eagle Bucks Store</t>
+          <t xml:space="preserve">Concept Con (Future Focus)</t>
         </is>
       </c>
       <c r="J105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">イーグルバックス・ストア</t>
+          <t xml:space="preserve">コンセプト・コン（未来を考える）</t>
         </is>
       </c>
       <c r="K105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
+          <t xml:space="preserve">Students investigate future possibilities, innovations, and solutions to real-world challenges through inquiry-based projects and presentations.</t>
         </is>
       </c>
       <c r="L105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
+          <t xml:space="preserve">探究型のプロジェクトや発表を通して、未来の可能性、イノベーション、現実の課題の解決策について考えます。</t>
         </is>
       </c>
       <c r="M105" t="inlineStr" s="2">
@@ -10240,7 +10240,7 @@
       </c>
       <c r="O105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-17-eagle-bucks-store.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-24-concept-con-future-focus.webp</t>
         </is>
       </c>
       <c r="P105" t="inlineStr" s="2">
@@ -10267,17 +10267,17 @@
     <row r="106">
       <c r="A106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-18-kindergarten-and-grade-5-graduation</t>
+          <t xml:space="preserve">2027-05-28-g12-graduation-with-performances</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-18</t>
+          <t xml:space="preserve">2027-05-29</t>
         </is>
       </c>
       <c r="C106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-18</t>
+          <t xml:space="preserve">2027-05-29</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="3">
@@ -10287,7 +10287,7 @@
       </c>
       <c r="E106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F106" t="inlineStr" s="2">
@@ -10302,27 +10302,27 @@
       </c>
       <c r="H106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">changed</t>
         </is>
       </c>
       <c r="I106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Kindergarten and Grade 5 Graduation</t>
+          <t xml:space="preserve">G12 Graduation with Performances</t>
         </is>
       </c>
       <c r="J106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部・5年生卒業式</t>
+          <t xml:space="preserve">G12卒業式・記念パフォーマンス</t>
         </is>
       </c>
       <c r="K106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students participate in graduation ceremonies to celebrate important milestones in their educational journey. The events recognize student growth, achievements, and readiness for the next stage of learning while bringing together families, staff, and the school community in celebration.</t>
+          <t xml:space="preserve">Grade 12 students will celebrate their graduation with a formal ceremony featuring student performances and the wider school community.</t>
         </is>
       </c>
       <c r="L106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学びの歩みにおける大切な節目を祝う卒業式に参加します。生徒の成長と成果、そして次のステージへの準備が整ったことを、ご家族、教職員、学校コミュニティが一堂に会して祝福します。</t>
+          <t xml:space="preserve">12年生が、生徒によるパフォーマンスを交えた式典で、学校コミュニティ全体とともに卒業を祝います。</t>
         </is>
       </c>
       <c r="M106" t="inlineStr" s="2">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="O106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-18-kindergarten-and-grade-5-graduation.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-28-g12-graduation-with-performances.webp</t>
         </is>
       </c>
       <c r="P106" t="inlineStr" s="2">
@@ -10364,17 +10364,17 @@
     <row r="107">
       <c r="A107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-18-primary-elc-year-end-performance</t>
+          <t xml:space="preserve">2027-06-03-celebration-of-learning-prep</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-18</t>
+          <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
       <c r="C107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-18</t>
+          <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="3">
@@ -10384,12 +10384,12 @@
       </c>
       <c r="E107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G107" t="inlineStr" s="2">
@@ -10404,22 +10404,22 @@
       </c>
       <c r="I107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary &amp; ELC Year End Performance</t>
+          <t xml:space="preserve">Celebration of Learning Prep</t>
         </is>
       </c>
       <c r="J107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小学部・幼稚部年度末発表会</t>
+          <t xml:space="preserve">学びの発表会準備</t>
         </is>
       </c>
       <c r="K107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students participate in music, dance, drama, and other performance activities to showcase their learning, creativity, and talents. These performances provide an opportunity to celebrate the school year and share achievements with families and the school community.</t>
+          <t xml:space="preserve">Students help prepare the school for the Celebration of Learning by organizing learning spaces, setting up displays, arranging materials, and ensuring classrooms and common areas are ready to welcome visitors. This preparation helps create an engaging and welcoming environment for families and guests.</t>
         </is>
       </c>
       <c r="L107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">音楽、ダンス、演劇などのパフォーマンスを通して、学び、創造性、才能を披露します。一年の締めくくりを祝い、その成果をご家族や学校コミュニティと分かち合う機会です。</t>
+          <t xml:space="preserve">学びの発表会に向けて、学習スペースの整理、展示の設営、資料の準備を行い、教室や共用エリアで来場者をお迎えできるよう整えます。ご家族やお客様にとって魅力的で温かな空間づくりにつながります。</t>
         </is>
       </c>
       <c r="M107" t="inlineStr" s="2">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="O107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-18-primary-elc-year-end-performance.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-03-celebration-of-learning-prep.webp</t>
         </is>
       </c>
       <c r="P107" t="inlineStr" s="2">
@@ -10461,17 +10461,17 @@
     <row r="108">
       <c r="A108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-19-end-of-term-3-activity-g6-10</t>
+          <t xml:space="preserve">2027-06-03-ukulele-concert</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-19</t>
+          <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
       <c r="C108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-19</t>
+          <t xml:space="preserve">2027-06-04</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="3">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="E108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G108" t="inlineStr" s="2">
@@ -10501,22 +10501,22 @@
       </c>
       <c r="I108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">End of Term 3 Activity: G6-10</t>
+          <t xml:space="preserve">Ukulele Concert</t>
         </is>
       </c>
       <c r="J108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第3学期末行事：G6–10</t>
+          <t xml:space="preserve">ウクレレコンサート</t>
         </is>
       </c>
       <c r="K108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in an off-campus day trip outside Nagoya to celebrate the end of Term 3.</t>
+          <t xml:space="preserve">Students perform musical pieces they have learned throughout the year, demonstrating their growth, confidence, and musical skills.</t>
         </is>
       </c>
       <c r="L108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第3学期の終わりを祝い、名古屋近郊への日帰り校外活動に参加します。</t>
+          <t xml:space="preserve">一年を通して学んだ曲を演奏し、成長、自信、音楽の技能を披露します。</t>
         </is>
       </c>
       <c r="M108" t="inlineStr" s="2">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="O108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-19-end-of-term-3-activity-g6-10.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-03-ukulele-concert.webp</t>
         </is>
       </c>
       <c r="P108" t="inlineStr" s="2">
@@ -10558,17 +10558,17 @@
     <row r="109">
       <c r="A109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-22-parent-teacher-conferences</t>
+          <t xml:space="preserve">2027-06-04-celebration-of-learning</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-22</t>
+          <t xml:space="preserve">2027-06-04</t>
         </is>
       </c>
       <c r="C109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-23</t>
+          <t xml:space="preserve">2027-06-04</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="3">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="G109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H109" t="inlineStr" s="2">
@@ -10598,22 +10598,22 @@
       </c>
       <c r="I109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parent Teacher Conferences</t>
+          <t xml:space="preserve">Celebration of Learning</t>
         </is>
       </c>
       <c r="J109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者面談</t>
+          <t xml:space="preserve">学びの発表会</t>
         </is>
       </c>
       <c r="K109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on these days.</t>
+          <t xml:space="preserve">The school community will celebrate learning as students share projects and exhibitions, including PYPX, MYPX, CAS, EE, TOK and Foundation to 4 projects.</t>
         </is>
       </c>
       <c r="L109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。期間中、生徒は登校しません。</t>
+          <t xml:space="preserve">PYPX、MYPX、CAS、EE、TOK、ファウンデーション～4年生のプロジェクトなど、生徒の作品や展示を通して学校コミュニティ全体で学びを祝います。</t>
         </is>
       </c>
       <c r="M109" t="inlineStr" s="2">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="O109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-22-parent-teacher-conferences.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-04-celebration-of-learning.webp</t>
         </is>
       </c>
       <c r="P109" t="inlineStr" s="2">
@@ -10655,17 +10655,17 @@
     <row r="110">
       <c r="A110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-28-summer-school</t>
+          <t xml:space="preserve">2027-06-05-sat-test-7</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-28</t>
+          <t xml:space="preserve">2027-06-05</t>
         </is>
       </c>
       <c r="C110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-07-18</t>
+          <t xml:space="preserve">2027-06-05</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="3">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="E110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F110" t="inlineStr" s="2">
@@ -10695,22 +10695,22 @@
       </c>
       <c r="I110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Summer School</t>
+          <t xml:space="preserve">SAT Test #7</t>
         </is>
       </c>
       <c r="J110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">サマースクール</t>
+          <t xml:space="preserve">SAT試験 第7回</t>
         </is>
       </c>
       <c r="K110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Participate in fun English style summer camps that challenge students and help foster friendships and connections with others.</t>
+          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
         </is>
       </c>
       <c r="L110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">英語で楽しく過ごすサマーキャンプに参加し、新たなことに挑戦しながら友情や人とのつながりを育みます。</t>
+          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
         </is>
       </c>
       <c r="M110" t="inlineStr" s="2">
@@ -10725,7 +10725,7 @@
       </c>
       <c r="O110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-28-summer-school.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-05-sat-test-7.webp</t>
         </is>
       </c>
       <c r="P110" t="inlineStr" s="2">
@@ -10752,95 +10752,774 @@
     <row r="111">
       <c r="A111" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2027-06-11-last-day-of-clubs</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2027-06-11</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2027-06-11</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Whole School</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Last Day of Clubs</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">クラブ活動最終日</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">The last day of after-school clubs for this school year. Bus reminder: the afternoon Red bus runs only on club days, so after today it no longer runs. Please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">今年度の放課後クラブ活動の最終日です。【バスについて】午後の赤バスはクラブ活動がある日のみ運行するため、本日で運行を終了します。明日以降、午後の下校時は青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">2027-06-17-eagle-bucks-store</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2027-06-17</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2027-06-17</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Primary, ELC</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Eagle Bucks Store</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">イーグルバックス・ストア</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">compass/images/events/2027-06-17-eagle-bucks-store.webp</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">2027-06-18-kindergarten-and-grade-5-graduation</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2027-06-18</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2027-06-18</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Primary, ELC</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Kindergarten and Grade 5 Graduation</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">幼稚部・5年生卒業式</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Students participate in graduation ceremonies to celebrate important milestones in their educational journey. The events recognize student growth, achievements, and readiness for the next stage of learning while bringing together families, staff, and the school community in celebration.</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">学びの歩みにおける大切な節目を祝う卒業式に参加します。生徒の成長と成果、そして次のステージへの準備が整ったことを、ご家族、教職員、学校コミュニティが一堂に会して祝福します。</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">compass/images/events/2027-06-18-kindergarten-and-grade-5-graduation.webp</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">2027-06-18-primary-elc-year-end-performance</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2027-06-18</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2027-06-18</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Primary, ELC</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Primary &amp; ELC Year End Performance</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">小学部・幼稚部年度末発表会</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Students participate in music, dance, drama, and other performance activities to showcase their learning, creativity, and talents. These performances provide an opportunity to celebrate the school year and share achievements with families and the school community.</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">音楽、ダンス、演劇などのパフォーマンスを通して、学び、創造性、才能を披露します。一年の締めくくりを祝い、その成果をご家族や学校コミュニティと分かち合う機会です。</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">compass/images/events/2027-06-18-primary-elc-year-end-performance.webp</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">2027-06-19-end-of-term-3-activity-g6-10</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2027-06-19</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2027-06-19</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Secondary</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">End of Term 3 Activity: G6-10</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">第3学期末行事：G6–10</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Students will take part in an off-campus day trip outside Nagoya to celebrate the end of Term 3.</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">第3学期の終わりを祝い、名古屋近郊への日帰り校外活動に参加します。</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">compass/images/events/2027-06-19-end-of-term-3-activity-g6-10.webp</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">2027-06-22-parent-teacher-conferences</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2027-06-22</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2027-06-23</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Whole School</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parent Teacher Conferences</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">保護者面談</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on these days.</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。期間中、生徒は登校しません。</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">compass/images/events/2027-06-22-parent-teacher-conferences.webp</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">2027-06-28-summer-school</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2027-06-28</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2027-07-18</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Whole School</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Summer School</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">サマースクール</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Participate in fun English style summer camps that challenge students and help foster friendships and connections with others.</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">英語で楽しく過ごすサマーキャンプに参加し、新たなことに挑戦しながら友情や人とのつながりを育みます。</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">compass/images/events/2027-06-28-summer-school.webp</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2027-07-20-summer-school</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr" s="3">
+      <c r="B118" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-07-20</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr" s="3">
+      <c r="C118" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-07-24</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr" s="2">
+      <c r="D118" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Whole School</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr" s="2">
+      <c r="F118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Summer School</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr" s="2">
+      <c r="J118" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">サマースクール</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr" s="2">
+      <c r="K118" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Participate in fun English style summer camps that challenge students and help foster friendships and connections with others.</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr" s="2">
+      <c r="L118" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">英語で楽しく過ごすサマーキャンプに参加し、新たなことに挑戦しながら友情や人とのつながりを育みます。</t>
         </is>
       </c>
-      <c r="M111" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O111" t="inlineStr" s="2">
+      <c r="M118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">compass/images/events/2027-06-28-summer-school.webp</t>
         </is>
       </c>
-      <c r="P111" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q111" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R111" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="S111" t="inlineStr" s="2">
+      <c r="P118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>

--- a/admin/EIS-Compass-events.xlsx
+++ b/admin/EIS-Compass-events.xlsx
@@ -2032,7 +2032,7 @@
       </c>
       <c r="C21" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-23</t>
+          <t xml:space="preserve">2026-10-09</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="3">
@@ -2507,17 +2507,17 @@
     <row r="26">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-21-college-fair</t>
+          <t xml:space="preserve">2026-10-20-clubs-pause</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="3">
@@ -2527,12 +2527,12 @@
       </c>
       <c r="E26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G26" t="inlineStr" s="2">
@@ -2547,22 +2547,22 @@
       </c>
       <c r="I26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">College Fair</t>
+          <t xml:space="preserve">Clubs Pause</t>
         </is>
       </c>
       <c r="J26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">大学進学フェア</t>
+          <t xml:space="preserve">クラブ活動休止</t>
         </is>
       </c>
       <c r="K26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A special event where representatives from several international and Japanese universities visit our school to introduce their programs and admission opportunities. The fair is open to all students and parents, and students from other international schools in the area are also invited to attend.</t>
+          <t xml:space="preserve">After-school clubs are paused during this period. Bus reminder: the afternoon Red bus runs only on club days, so it does not run while clubs are paused. Please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
         </is>
       </c>
       <c r="L26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国内外の複数の大学の担当者が来校し、各大学のプログラムや入学機会を紹介する特別イベントです。全生徒・保護者が参加でき、近隣のインターナショナルスクールの生徒もご招待しています。</t>
+          <t xml:space="preserve">この期間、放課後のクラブ活動はお休みです。【バスについて】午後の赤バスはクラブ活動がある日のみ運行するため、休止期間中は運行しません。午後の下校時は青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
         </is>
       </c>
       <c r="M26" t="inlineStr" s="2">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="O26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-21-college-fair.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P26" t="inlineStr" s="2">
@@ -2604,17 +2604,17 @@
     <row r="27">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-23-nagoya-university-biology-laboratory-visit</t>
+          <t xml:space="preserve">2026-10-21-college-fair</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-23</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-23</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="3">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="F27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G27" t="inlineStr" s="2">
@@ -2644,22 +2644,22 @@
       </c>
       <c r="I27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Nagoya University Biology Laboratory Visit</t>
+          <t xml:space="preserve">College Fair</t>
         </is>
       </c>
       <c r="J27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">名古屋大学 生物学研究室訪問</t>
+          <t xml:space="preserve">大学進学フェア</t>
         </is>
       </c>
       <c r="K27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 11 and 12 Biology students will visit Nagoya University for a guided laboratory experience, connecting classroom learning with real-world scientific research.</t>
+          <t xml:space="preserve">A special event where representatives from several international and Japanese universities visit our school to introduce their programs and admission opportunities. The fair is open to all students and parents, and students from other international schools in the area are also invited to attend.</t>
         </is>
       </c>
       <c r="L27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11・12年生の生物履修者が名古屋大学を訪問し、研究室での体験を通して授業での学びと実際の科学研究を結びつけます。</t>
+          <t xml:space="preserve">国内外の複数の大学の担当者が来校し、各大学のプログラムや入学機会を紹介する特別イベントです。全生徒・保護者が参加でき、近隣のインターナショナルスクールの生徒もご招待しています。</t>
         </is>
       </c>
       <c r="M27" t="inlineStr" s="2">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="O27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-23-nagoya-university-biology-laboratory-visit.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-21-college-fair.webp</t>
         </is>
       </c>
       <c r="P27" t="inlineStr" s="2">
@@ -2701,17 +2701,17 @@
     <row r="28">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-25-pta-picnic</t>
+          <t xml:space="preserve">2026-10-23-nagoya-university-biology-laboratory-visit</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-25</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-25</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="3">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="E28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTA</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="2">
@@ -2741,22 +2741,22 @@
       </c>
       <c r="I28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTA Picnic</t>
+          <t xml:space="preserve">Nagoya University Biology Laboratory Visit</t>
         </is>
       </c>
       <c r="J28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTAピクニック</t>
+          <t xml:space="preserve">名古屋大学 生物学研究室訪問</t>
         </is>
       </c>
       <c r="K28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Families, students, and staff come together for a fun outdoor gathering that strengthens relationships and builds school community.</t>
+          <t xml:space="preserve">Grade 11 and 12 Biology students will visit Nagoya University for a guided laboratory experience, connecting classroom learning with real-world scientific research.</t>
         </is>
       </c>
       <c r="L28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ご家族、生徒、教職員が集まり、屋外で楽しく交流しながら絆を深め、学校コミュニティを育みます。</t>
+          <t xml:space="preserve">11・12年生の生物履修者が名古屋大学を訪問し、研究室での体験を通して授業での学びと実際の科学研究を結びつけます。</t>
         </is>
       </c>
       <c r="M28" t="inlineStr" s="2">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="O28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-25-pta-picnic.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-23-nagoya-university-biology-laboratory-visit.webp</t>
         </is>
       </c>
       <c r="P28" t="inlineStr" s="2">
@@ -2798,17 +2798,17 @@
     <row r="29">
       <c r="A29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-26-toyota-college-trip</t>
+          <t xml:space="preserve">2026-10-25-pta-picnic</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-26</t>
+          <t xml:space="preserve">2026-10-25</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-26</t>
+          <t xml:space="preserve">2026-10-25</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="3">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="E29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">PTA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="2">
@@ -2838,22 +2838,22 @@
       </c>
       <c r="I29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Toyota College Trip</t>
+          <t xml:space="preserve">PTA Picnic</t>
         </is>
       </c>
       <c r="J29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">豊田高専見学</t>
+          <t xml:space="preserve">PTAピクニック</t>
         </is>
       </c>
       <c r="K29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 8 Science students will visit Toyota College for a curriculum-based learning experience connected to their science studies.</t>
+          <t xml:space="preserve">Families, students, and staff come together for a fun outdoor gathering that strengthens relationships and builds school community.</t>
         </is>
       </c>
       <c r="L29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8年生が理科の授業と関連したカリキュラムに基づく学習として、豊田高専を訪問します。</t>
+          <t xml:space="preserve">ご家族、生徒、教職員が集まり、屋外で楽しく交流しながら絆を深め、学校コミュニティを育みます。</t>
         </is>
       </c>
       <c r="M29" t="inlineStr" s="2">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="O29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-26-toyota-college-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-25-pta-picnic.webp</t>
         </is>
       </c>
       <c r="P29" t="inlineStr" s="2">
@@ -2895,7 +2895,7 @@
     <row r="30">
       <c r="A30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-26-clubs-resume</t>
+          <t xml:space="preserve">2026-10-26-toyota-college-trip</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="3">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="E30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F30" t="inlineStr" s="2">
@@ -2935,22 +2935,22 @@
       </c>
       <c r="I30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Clubs Resume</t>
+          <t xml:space="preserve">Toyota College Trip</t>
         </is>
       </c>
       <c r="J30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クラブ活動再開</t>
+          <t xml:space="preserve">豊田高専見学</t>
         </is>
       </c>
       <c r="K30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">After-school clubs start again today. Bus reminder: the afternoon Red bus runs only on club days. On other days, please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
+          <t xml:space="preserve">Grade 8 Science students will visit Toyota College for a curriculum-based learning experience connected to their science studies.</t>
         </is>
       </c>
       <c r="L30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">本日から放課後のクラブ活動が再開します。【バスについて】午後の赤バスはクラブ活動がある日のみ運行します。それ以外の日は、午後の下校時に青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
+          <t xml:space="preserve">8年生が理科の授業と関連したカリキュラムに基づく学習として、豊田高専を訪問します。</t>
         </is>
       </c>
       <c r="M30" t="inlineStr" s="2">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="O30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">compass/images/events/2026-10-26-toyota-college-trip.webp</t>
         </is>
       </c>
       <c r="P30" t="inlineStr" s="2">
@@ -2992,17 +2992,17 @@
     <row r="31">
       <c r="A31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-30-sensory-wonderland</t>
+          <t xml:space="preserve">2026-10-26-clubs-resume</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-30</t>
+          <t xml:space="preserve">2026-10-26</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-30</t>
+          <t xml:space="preserve">2026-10-26</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="3">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="E31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F31" t="inlineStr" s="2">
@@ -3032,22 +3032,22 @@
       </c>
       <c r="I31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sensory Wonderland</t>
+          <t xml:space="preserve">Clubs Resume</t>
         </is>
       </c>
       <c r="J31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">センサリー・ワンダーランド</t>
+          <t xml:space="preserve">クラブ活動再開</t>
         </is>
       </c>
       <c r="K31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students explore a variety of interactive sensory experiences designed to engage curiosity, creativity, and learning through play.</t>
+          <t xml:space="preserve">After-school clubs start again today. Bus reminder: the afternoon Red bus runs only on club days. On other days, please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
         </is>
       </c>
       <c r="L31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">好奇心と創造性を刺激し、遊びを通して学ぶ、さまざまな体験型の感覚活動を楽しみます。</t>
+          <t xml:space="preserve">本日から放課後のクラブ活動が再開します。【バスについて】午後の赤バスはクラブ活動がある日のみ運行します。それ以外の日は、午後の下校時に青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
         </is>
       </c>
       <c r="M31" t="inlineStr" s="2">
@@ -3089,32 +3089,32 @@
     <row r="32">
       <c r="A32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-31-international-mindedness-festival</t>
+          <t xml:space="preserve">2026-10-30-sensory-wonderland</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-31</t>
+          <t xml:space="preserve">2026-10-30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-31</t>
+          <t xml:space="preserve">2026-10-30</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">10:00-14:00</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">ELC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G32" t="inlineStr" s="2">
@@ -3129,22 +3129,22 @@
       </c>
       <c r="I32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">International Mindedness Festival</t>
+          <t xml:space="preserve">Sensory Wonderland</t>
         </is>
       </c>
       <c r="J32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">インターナショナル・マインデッドネス・フェスティバル</t>
+          <t xml:space="preserve">センサリー・ワンダーランド</t>
         </is>
       </c>
       <c r="K32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This year’s theme is “Festivals and Holidays Around the World”. A Saturday family event celebrating traditions, cultures, stories, arts, music and celebrations from around the world, with student activities, cultural displays, performances, arts and crafts, and interactive booths. Clean-up runs from 14:00 to 15:00, and community members are welcome to help. ELC and Primary students must attend with a parent or guardian and may not be dropped off. School buses will not operate. More details will be shared soon.</t>
+          <t xml:space="preserve">Students explore a variety of interactive sensory experiences designed to engage curiosity, creativity, and learning through play.</t>
         </is>
       </c>
       <c r="L32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">今年のテーマは「世界の祭りと祝日」です。世界各地の伝統、文化、物語、芸術、音楽、お祝いを紹介する、土曜日のご家族参加型イベントです。児童・生徒の活動、文化展示、パフォーマンス、工作、体験型ブースをお楽しみいただけます。午後2時～3時に片付けを行います（学校コミュニティの皆さまのご協力も歓迎します）。幼稚部・小学部の児童は必ず保護者同伴でご参加ください（お子さまだけを送り届けることはできません）。当日はスクールバスの運行はありません。詳細は近日中にお知らせします。</t>
+          <t xml:space="preserve">好奇心と創造性を刺激し、遊びを通して学ぶ、さまざまな体験型の感覚活動を楽しみます。</t>
         </is>
       </c>
       <c r="M32" t="inlineStr" s="2">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="O32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-31-international-mindedness-festival.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P32" t="inlineStr" s="2">
@@ -3186,32 +3186,32 @@
     <row r="33">
       <c r="A33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-04-elc-sports-day-rehearsal-1</t>
+          <t xml:space="preserve">2026-10-31-international-mindedness-festival</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-04</t>
+          <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-04</t>
+          <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">10:00-14:00</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G33" t="inlineStr" s="2">
@@ -3226,22 +3226,22 @@
       </c>
       <c r="I33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC Sports Day Rehearsal #1</t>
+          <t xml:space="preserve">International Mindedness Festival</t>
         </is>
       </c>
       <c r="J33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部運動会リハーサル #1</t>
+          <t xml:space="preserve">インターナショナル・マインデッドネス・フェスティバル</t>
         </is>
       </c>
       <c r="K33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">During Sports Day practice, students participate in a variety of physical activities, team games, relays, and event rehearsals in preparation for Sports Day. They develop teamwork, cooperation, sportsmanship, and physical fitness while learning event procedures, safety expectations, and cheering routines. Practice sessions help students build confidence and ensure they are prepared to participate successfully in the Sports Day celebration.</t>
+          <t xml:space="preserve">This year’s theme is “Festivals and Holidays Around the World”. A Saturday family event celebrating traditions, cultures, stories, arts, music and celebrations from around the world, with student activities, cultural displays, performances, arts and crafts, and interactive booths. Clean-up runs from 14:00 to 15:00, and community members are welcome to help. ELC and Primary students must attend with a parent or guardian and may not be dropped off. School buses will not operate. More details will be shared soon.</t>
         </is>
       </c>
       <c r="L33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会に向けた練習では、さまざまな運動、チームゲーム、リレー、種目のリハーサルに取り組みます。進行の流れ、安全面のルール、応援の仕方を学びながら、チームワーク、協調性、スポーツマンシップ、体力を養います。練習を通して自信をつけ、運動会当日に力を発揮できるよう準備します。</t>
+          <t xml:space="preserve">今年のテーマは「世界の祭りと祝日」です。世界各地の伝統、文化、物語、芸術、音楽、お祝いを紹介する、土曜日のご家族参加型イベントです。児童・生徒の活動、文化展示、パフォーマンス、工作、体験型ブースをお楽しみいただけます。午後2時～3時に片付けを行います（学校コミュニティの皆さまのご協力も歓迎します）。幼稚部・小学部の児童は必ず保護者同伴でご参加ください（お子さまだけを送り届けることはできません）。当日はスクールバスの運行はありません。詳細は近日中にお知らせします。</t>
         </is>
       </c>
       <c r="M33" t="inlineStr" s="2">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="O33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-04-elc-sports-day-rehearsal-1.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-31-international-mindedness-festival.webp</t>
         </is>
       </c>
       <c r="P33" t="inlineStr" s="2">
@@ -3283,17 +3283,17 @@
     <row r="34">
       <c r="A34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-05-toyota-museum-field-trip</t>
+          <t xml:space="preserve">2026-11-04-elc-sports-day-rehearsal-1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-05</t>
+          <t xml:space="preserve">2026-11-04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-05</t>
+          <t xml:space="preserve">2026-11-04</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="3">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="E34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">ELC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr" s="2">
@@ -3323,22 +3323,22 @@
       </c>
       <c r="I34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Toyota Museum Field Trip</t>
+          <t xml:space="preserve">ELC Sports Day Rehearsal #1</t>
         </is>
       </c>
       <c r="J34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">トヨタ博物館校外学習</t>
+          <t xml:space="preserve">幼稚部運動会リハーサル #1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 9 students go to the Toyota museum down the road and view the exhibits taking some notes on machines they learned about.</t>
+          <t xml:space="preserve">During Sports Day practice, students participate in a variety of physical activities, team games, relays, and event rehearsals in preparation for Sports Day. They develop teamwork, cooperation, sportsmanship, and physical fitness while learning event procedures, safety expectations, and cheering routines. Practice sessions help students build confidence and ensure they are prepared to participate successfully in the Sports Day celebration.</t>
         </is>
       </c>
       <c r="L34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9年生が近くのトヨタの博物館を訪れ、授業で学んだ機械について展示を見学しながらメモを取ります。</t>
+          <t xml:space="preserve">運動会に向けた練習では、さまざまな運動、チームゲーム、リレー、種目のリハーサルに取り組みます。進行の流れ、安全面のルール、応援の仕方を学びながら、チームワーク、協調性、スポーツマンシップ、体力を養います。練習を通して自信をつけ、運動会当日に力を発揮できるよう準備します。</t>
         </is>
       </c>
       <c r="M34" t="inlineStr" s="2">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="O34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-05-toyota-museum-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-04-elc-sports-day-rehearsal-1.webp</t>
         </is>
       </c>
       <c r="P34" t="inlineStr" s="2">
@@ -3380,17 +3380,17 @@
     <row r="35">
       <c r="A35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-06-extracurricular-activities-autumn-cas-project-su</t>
+          <t xml:space="preserve">2026-11-05-toyota-museum-field-trip</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-06</t>
+          <t xml:space="preserve">2026-11-05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-06</t>
+          <t xml:space="preserve">2026-11-05</t>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="3">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="F35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G35" t="inlineStr" s="2">
@@ -3420,22 +3420,22 @@
       </c>
       <c r="I35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Extracurricular Activities: Autumn CAS &amp; Project Support Fair</t>
+          <t xml:space="preserve">Toyota Museum Field Trip</t>
         </is>
       </c>
       <c r="J35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">課外活動：秋のCAS・プロジェクトサポートフェア</t>
+          <t xml:space="preserve">トヨタ博物館校外学習</t>
         </is>
       </c>
       <c r="K35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary PTA Supported Event to help students understand various volunteering and CAS project opportunities in the community. Open to MYP and DP Students.</t>
+          <t xml:space="preserve">Grade 9 students go to the Toyota museum down the road and view the exhibits taking some notes on machines they learned about.</t>
         </is>
       </c>
       <c r="L35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部PTAの支援による行事で、地域でのさまざまなボランティアやCASプロジェクトの機会について知ることができます。MYP・DP生徒が対象です。</t>
+          <t xml:space="preserve">9年生が近くのトヨタの博物館を訪れ、授業で学んだ機械について展示を見学しながらメモを取ります。</t>
         </is>
       </c>
       <c r="M35" t="inlineStr" s="2">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="O35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-06-extracurricular-activities-autumn-cas-project-su.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-05-toyota-museum-field-trip.webp</t>
         </is>
       </c>
       <c r="P35" t="inlineStr" s="2">
@@ -3477,17 +3477,17 @@
     <row r="36">
       <c r="A36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-07-sat-test-4</t>
+          <t xml:space="preserve">2026-11-06-extracurricular-activities-autumn-cas-project-su</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-07</t>
+          <t xml:space="preserve">2026-11-06</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-07</t>
+          <t xml:space="preserve">2026-11-06</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="3">
@@ -3497,12 +3497,12 @@
       </c>
       <c r="E36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G36" t="inlineStr" s="2">
@@ -3517,22 +3517,22 @@
       </c>
       <c r="I36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT Test #4</t>
+          <t xml:space="preserve">Extracurricular Activities: Autumn CAS &amp; Project Support Fair</t>
         </is>
       </c>
       <c r="J36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT試験 第4回</t>
+          <t xml:space="preserve">課外活動：秋のCAS・プロジェクトサポートフェア</t>
         </is>
       </c>
       <c r="K36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
+          <t xml:space="preserve">Secondary PTA Supported Event to help students understand various volunteering and CAS project opportunities in the community. Open to MYP and DP Students.</t>
         </is>
       </c>
       <c r="L36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
+          <t xml:space="preserve">中等部PTAの支援による行事で、地域でのさまざまなボランティアやCASプロジェクトの機会について知ることができます。MYP・DP生徒が対象です。</t>
         </is>
       </c>
       <c r="M36" t="inlineStr" s="2">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="O36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-07-sat-test-4.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-06-extracurricular-activities-autumn-cas-project-su.webp</t>
         </is>
       </c>
       <c r="P36" t="inlineStr" s="2">
@@ -3574,17 +3574,17 @@
     <row r="37">
       <c r="A37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-09-wellbeing-week</t>
+          <t xml:space="preserve">2026-11-07-sat-test-4</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-09</t>
+          <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-13</t>
+          <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="3">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="E37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F37" t="inlineStr" s="2">
@@ -3614,22 +3614,22 @@
       </c>
       <c r="I37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wellbeing Week</t>
+          <t xml:space="preserve">SAT Test #4</t>
         </is>
       </c>
       <c r="J37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ウェルビーイング週間</t>
+          <t xml:space="preserve">SAT試験 第4回</t>
         </is>
       </c>
       <c r="K37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A school wide event focused on raising awareness for wellbeing.</t>
+          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
         </is>
       </c>
       <c r="L37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ウェルビーイング（心身の健康）への意識を高めることを目的とした全校行事です。</t>
+          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
         </is>
       </c>
       <c r="M37" t="inlineStr" s="2">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-09-wellbeing-week.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-07-sat-test-4.webp</t>
         </is>
       </c>
       <c r="P37" t="inlineStr" s="2">
@@ -3671,7 +3671,7 @@
     <row r="38">
       <c r="A38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-09-concept-con-wellbeing</t>
+          <t xml:space="preserve">2026-11-09-wellbeing-week</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="3">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="E38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F38" t="inlineStr" s="2">
@@ -3711,22 +3711,22 @@
       </c>
       <c r="I38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Concept Con (Wellbeing)</t>
+          <t xml:space="preserve">Wellbeing Week</t>
         </is>
       </c>
       <c r="J38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">コンセプト・コン（ウェルビーイング）</t>
+          <t xml:space="preserve">ウェルビーイング週間</t>
         </is>
       </c>
       <c r="K38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Primary Concept Conference on the theme of wellbeing, held during Wellbeing Week.</t>
+          <t xml:space="preserve">A school wide event focused on raising awareness for wellbeing.</t>
         </is>
       </c>
       <c r="L38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ウェルビーイング週間に合わせて行う、小学部のコンセプト・カンファレンス（テーマ：ウェルビーイング）です。</t>
+          <t xml:space="preserve">ウェルビーイング（心身の健康）への意識を高めることを目的とした全校行事です。</t>
         </is>
       </c>
       <c r="M38" t="inlineStr" s="2">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="O38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">compass/images/events/2026-11-09-wellbeing-week.webp</t>
         </is>
       </c>
       <c r="P38" t="inlineStr" s="2">
@@ -3768,17 +3768,17 @@
     <row r="39">
       <c r="A39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-11-elc-sports-day-rehearsal-2</t>
+          <t xml:space="preserve">2026-11-09-concept-con-wellbeing</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-11</t>
+          <t xml:space="preserve">2026-11-09</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-11</t>
+          <t xml:space="preserve">2026-11-13</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="3">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="E39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F39" t="inlineStr" s="2">
@@ -3808,22 +3808,22 @@
       </c>
       <c r="I39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC Sports Day Rehearsal #2</t>
+          <t xml:space="preserve">Concept Con (Wellbeing)</t>
         </is>
       </c>
       <c r="J39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部運動会リハーサル #2</t>
+          <t xml:space="preserve">コンセプト・コン（ウェルビーイング）</t>
         </is>
       </c>
       <c r="K39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">During Sports Day practice, students participate in a variety of physical activities, team games, relays, and event rehearsals in preparation for Sports Day. They develop teamwork, cooperation, sportsmanship, and physical fitness while learning event procedures, safety expectations, and cheering routines. Practice sessions help students build confidence and ensure they are prepared to participate successfully in the Sports Day celebration.</t>
+          <t xml:space="preserve">The Primary Concept Conference on the theme of wellbeing, held during Wellbeing Week.</t>
         </is>
       </c>
       <c r="L39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会に向けた練習では、さまざまな運動、チームゲーム、リレー、種目のリハーサルに取り組みます。進行の流れ、安全面のルール、応援の仕方を学びながら、チームワーク、協調性、スポーツマンシップ、体力を養います。練習を通して自信をつけ、運動会当日に力を発揮できるよう準備します。</t>
+          <t xml:space="preserve">ウェルビーイング週間に合わせて行う、小学部のコンセプト・カンファレンス（テーマ：ウェルビーイング）です。</t>
         </is>
       </c>
       <c r="M39" t="inlineStr" s="2">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="O39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-11-elc-sports-day-rehearsal-2.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P39" t="inlineStr" s="2">
@@ -3865,17 +3865,17 @@
     <row r="40">
       <c r="A40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-14-elc-sports-day</t>
+          <t xml:space="preserve">2026-11-11-elc-sports-day-rehearsal-2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-14</t>
+          <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-14</t>
+          <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="3">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="I40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC Sports Day</t>
+          <t xml:space="preserve">ELC Sports Day Rehearsal #2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部運動会</t>
+          <t xml:space="preserve">幼稚部運動会リハーサル #2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">During Sports Day, students participate in a variety of athletic events, relay races, team challenges, and cooperative games. They demonstrate teamwork, perseverance, sportsmanship, and school spirit while celebrating physical activity and healthy competition. Sports Day provides an opportunity for students to challenge themselves, support their peers, and enjoy a fun day of community participation and achievement.</t>
+          <t xml:space="preserve">During Sports Day practice, students participate in a variety of physical activities, team games, relays, and event rehearsals in preparation for Sports Day. They develop teamwork, cooperation, sportsmanship, and physical fitness while learning event procedures, safety expectations, and cheering routines. Practice sessions help students build confidence and ensure they are prepared to participate successfully in the Sports Day celebration.</t>
         </is>
       </c>
       <c r="L40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会では、さまざまな競技、リレー、チーム対抗戦、協力ゲームに参加します。体を動かすことと健全な競争を楽しみながら、チームワーク、粘り強さ、スポーツマンシップ、愛校心を発揮します。自分に挑戦し、仲間を応援し、コミュニティ全体で達成感を味わう楽しい一日です。</t>
+          <t xml:space="preserve">運動会に向けた練習では、さまざまな運動、チームゲーム、リレー、種目のリハーサルに取り組みます。進行の流れ、安全面のルール、応援の仕方を学びながら、チームワーク、協調性、スポーツマンシップ、体力を養います。練習を通して自信をつけ、運動会当日に力を発揮できるよう準備します。</t>
         </is>
       </c>
       <c r="M40" t="inlineStr" s="2">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="O40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-14-elc-sports-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-11-elc-sports-day-rehearsal-2.webp</t>
         </is>
       </c>
       <c r="P40" t="inlineStr" s="2">
@@ -3962,17 +3962,17 @@
     <row r="41">
       <c r="A41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-16-friendly-soccer-tournament-internal</t>
+          <t xml:space="preserve">2026-11-14-elc-sports-day</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-16</t>
+          <t xml:space="preserve">2026-11-14</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-20</t>
+          <t xml:space="preserve">2026-11-14</t>
         </is>
       </c>
       <c r="D41" t="inlineStr" s="3">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="E41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">ELC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr" s="2">
@@ -4002,22 +4002,22 @@
       </c>
       <c r="I41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Friendly Soccer Tournament (Internal)</t>
+          <t xml:space="preserve">ELC Sports Day</t>
         </is>
       </c>
       <c r="J41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内サッカー大会</t>
+          <t xml:space="preserve">幼稚部運動会</t>
         </is>
       </c>
       <c r="K41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in a friendly internal soccer tournament, promoting teamwork, sportsmanship, and school spirit.</t>
+          <t xml:space="preserve">During Sports Day, students participate in a variety of athletic events, relay races, team challenges, and cooperative games. They demonstrate teamwork, perseverance, sportsmanship, and school spirit while celebrating physical activity and healthy competition. Sports Day provides an opportunity for students to challenge themselves, support their peers, and enjoy a fun day of community participation and achievement.</t>
         </is>
       </c>
       <c r="L41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内サッカー大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
+          <t xml:space="preserve">運動会では、さまざまな競技、リレー、チーム対抗戦、協力ゲームに参加します。体を動かすことと健全な競争を楽しみながら、チームワーク、粘り強さ、スポーツマンシップ、愛校心を発揮します。自分に挑戦し、仲間を応援し、コミュニティ全体で達成感を味わう楽しい一日です。</t>
         </is>
       </c>
       <c r="M41" t="inlineStr" s="2">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="O41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-16-friendly-soccer-tournament-internal.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-14-elc-sports-day.webp</t>
         </is>
       </c>
       <c r="P41" t="inlineStr" s="2">
@@ -4059,17 +4059,17 @@
     <row r="42">
       <c r="A42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-17-foundation-field-trip</t>
+          <t xml:space="preserve">2026-11-16-friendly-soccer-tournament-internal</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-17</t>
+          <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-17</t>
+          <t xml:space="preserve">2026-11-20</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="3">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="E42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G42" t="inlineStr" s="2">
@@ -4099,22 +4099,22 @@
       </c>
       <c r="I42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Foundation Field Trip</t>
+          <t xml:space="preserve">Friendly Soccer Tournament (Internal)</t>
         </is>
       </c>
       <c r="J42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ファウンデーション校外学習</t>
+          <t xml:space="preserve">校内サッカー大会</t>
         </is>
       </c>
       <c r="K42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Our youngest learners will enjoy an age-appropriate educational excursion that supports classroom learning through hands-on experiences.</t>
+          <t xml:space="preserve">Students will take part in a friendly internal soccer tournament, promoting teamwork, sportsmanship, and school spirit.</t>
         </is>
       </c>
       <c r="L42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">年少の子どもたちが、年齢に合った校外学習に出かけ、体験を通して教室での学びを深めます。</t>
+          <t xml:space="preserve">校内サッカー大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
         </is>
       </c>
       <c r="M42" t="inlineStr" s="2">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="O42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-17-foundation-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-16-friendly-soccer-tournament-internal.webp</t>
         </is>
       </c>
       <c r="P42" t="inlineStr" s="2">
@@ -4156,17 +4156,17 @@
     <row r="43">
       <c r="A43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-20-gifu-kakamigahara-air-and-space-museum</t>
+          <t xml:space="preserve">2026-11-17-foundation-field-trip</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-20</t>
+          <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-20</t>
+          <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="3">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="E43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">ELC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G43" t="inlineStr" s="2">
@@ -4196,22 +4196,22 @@
       </c>
       <c r="I43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Gifu Kakamigahara Air and Space Museum</t>
+          <t xml:space="preserve">Foundation Field Trip</t>
         </is>
       </c>
       <c r="J43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">岐阜かかみがはら航空宇宙博物館</t>
+          <t xml:space="preserve">ファウンデーション校外学習</t>
         </is>
       </c>
       <c r="K43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will be going to the air and space museum to complete a practical where they will be analyzing plane design throughout history.</t>
+          <t xml:space="preserve">Our youngest learners will enjoy an age-appropriate educational excursion that supports classroom learning through hands-on experiences.</t>
         </is>
       </c>
       <c r="L43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">航空宇宙博物館を訪れ、歴史を通じた飛行機のデザインを分析する実習に取り組みます。</t>
+          <t xml:space="preserve">年少の子どもたちが、年齢に合った校外学習に出かけ、体験を通して教室での学びを深めます。</t>
         </is>
       </c>
       <c r="M43" t="inlineStr" s="2">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="O43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-20-gifu-kakamigahara-air-and-space-museum.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-17-foundation-field-trip.webp</t>
         </is>
       </c>
       <c r="P43" t="inlineStr" s="2">
@@ -4253,32 +4253,32 @@
     <row r="44">
       <c r="A44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-24-winter-art-contest</t>
+          <t xml:space="preserve">2026-11-20-gifu-kakamigahara-air-and-space-museum</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-24</t>
+          <t xml:space="preserve">2026-11-20</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-24</t>
+          <t xml:space="preserve">2026-11-20</t>
         </is>
       </c>
       <c r="D44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">13:10-14:55</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G44" t="inlineStr" s="2">
@@ -4293,37 +4293,37 @@
       </c>
       <c r="I44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Gallery Day: ELC &amp; Primary Art Showcase</t>
+          <t xml:space="preserve">Gifu Kakamigahara Air and Space Museum</t>
         </is>
       </c>
       <c r="J44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ギャラリーデー：幼稚部・小学部アート展</t>
+          <t xml:space="preserve">岐阜かかみがはら航空宇宙博物館</t>
         </is>
       </c>
       <c r="K44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC and Primary students display the artwork they have created with the visual arts teacher. Parents are welcome to view the gallery from 13:10 to 14:55. Students vote for their favourite artworks, and the winners for each grade are announced.</t>
+          <t xml:space="preserve">Students will be going to the air and space museum to complete a practical where they will be analyzing plane design throughout history.</t>
         </is>
       </c>
       <c r="L44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部・小学部の児童が美術の授業で制作した作品を展示します。保護者の皆さまは13:10～14:55にご鑑賞いただけます。児童による投票を行い、学年ごとの受賞作品を発表します。</t>
+          <t xml:space="preserve">航空宇宙博物館を訪れ、歴史を通じた飛行機のデザインを分析する実習に取り組みます。</t>
         </is>
       </c>
       <c r="M44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Gym</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="N44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">体育館</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="O44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-24-winter-art-contest.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-20-gifu-kakamigahara-air-and-space-museum.webp</t>
         </is>
       </c>
       <c r="P44" t="inlineStr" s="2">
@@ -4350,22 +4350,22 @@
     <row r="45">
       <c r="A45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-27-parents-morning-1</t>
+          <t xml:space="preserve">2026-11-24-winter-art-contest</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-27</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-27</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">13:10-14:55</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -4390,37 +4390,37 @@
       </c>
       <c r="I45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parents Morning #1</t>
+          <t xml:space="preserve">Gallery Day: ELC &amp; Primary Art Showcase</t>
         </is>
       </c>
       <c r="J45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">朝の授業参観 #1</t>
+          <t xml:space="preserve">ギャラリーデー：幼稚部・小学部アート展</t>
         </is>
       </c>
       <c r="K45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC and Primary Parents are invited to come and see the lessons in the morning and experience the morning routines with their child.</t>
+          <t xml:space="preserve">ELC and Primary students display the artwork they have created with the visual arts teacher. Parents are welcome to view the gallery from 13:10 to 14:55. Students vote for their favourite artworks, and the winners for each grade are announced.</t>
         </is>
       </c>
       <c r="L45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部・小学部の保護者の皆様をお招きし、朝の授業をご参観いただき、お子様と一緒に朝の日課を体験していただきます。</t>
+          <t xml:space="preserve">幼稚部・小学部の児童が美術の授業で制作した作品を展示します。保護者の皆さまは13:10～14:55にご鑑賞いただけます。児童による投票を行い、学年ごとの受賞作品を発表します。</t>
         </is>
       </c>
       <c r="M45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Gym</t>
         </is>
       </c>
       <c r="N45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">体育館</t>
         </is>
       </c>
       <c r="O45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-27-parents-morning-1.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-24-winter-art-contest.webp</t>
         </is>
       </c>
       <c r="P45" t="inlineStr" s="2">
@@ -4447,7 +4447,7 @@
     <row r="46">
       <c r="A46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-27-teacher-appreciation-day</t>
+          <t xml:space="preserve">2026-11-27-parents-morning-1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="3">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="E46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G46" t="inlineStr" s="2">
@@ -4487,22 +4487,22 @@
       </c>
       <c r="I46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Teacher Appreciation Day</t>
+          <t xml:space="preserve">Parents Morning #1</t>
         </is>
       </c>
       <c r="J46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">教職員感謝デー</t>
+          <t xml:space="preserve">朝の授業参観 #1</t>
         </is>
       </c>
       <c r="K46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The school community will celebrate Teacher Appreciation Day by recognizing and thanking teachers for their dedication, care, and support.</t>
+          <t xml:space="preserve">ELC and Primary Parents are invited to come and see the lessons in the morning and experience the morning routines with their child.</t>
         </is>
       </c>
       <c r="L46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学校コミュニティ全体で、教員の献身、思いやり、支えに感謝を伝える日です。</t>
+          <t xml:space="preserve">幼稚部・小学部の保護者の皆様をお招きし、朝の授業をご参観いただき、お子様と一緒に朝の日課を体験していただきます。</t>
         </is>
       </c>
       <c r="M46" t="inlineStr" s="2">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="O46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-27-teacher-appreciation-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-27-parents-morning-1.webp</t>
         </is>
       </c>
       <c r="P46" t="inlineStr" s="2">
@@ -4544,17 +4544,17 @@
     <row r="47">
       <c r="A47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-28-2026-enishi-futsal-tournament</t>
+          <t xml:space="preserve">2026-11-27-teacher-appreciation-day</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-28</t>
+          <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-28</t>
+          <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
       <c r="D47" t="inlineStr" s="3">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="E47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F47" t="inlineStr" s="2">
@@ -4584,22 +4584,22 @@
       </c>
       <c r="I47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026 - Enishi Futsal Tournament</t>
+          <t xml:space="preserve">Teacher Appreciation Day</t>
         </is>
       </c>
       <c r="J47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026 Enishiフットサル大会</t>
+          <t xml:space="preserve">教職員感謝デー</t>
         </is>
       </c>
       <c r="K47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Enishi will host a Middle School Futsal tournament at our school with multiple schools participating.</t>
+          <t xml:space="preserve">The school community will celebrate Teacher Appreciation Day by recognizing and thanking teachers for their dedication, care, and support.</t>
         </is>
       </c>
       <c r="L47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">本校にて複数校が参加する中学生フットサル大会を開催します。</t>
+          <t xml:space="preserve">学校コミュニティ全体で、教員の献身、思いやり、支えに感謝を伝える日です。</t>
         </is>
       </c>
       <c r="M47" t="inlineStr" s="2">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="O47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-28-2026-enishi-futsal-tournament.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-27-teacher-appreciation-day.webp</t>
         </is>
       </c>
       <c r="P47" t="inlineStr" s="2">
@@ -4641,32 +4641,32 @@
     <row r="48">
       <c r="A48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-03-grade-3-4-musical</t>
+          <t xml:space="preserve">2026-11-28-2026-enishi-futsal-tournament</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-03</t>
+          <t xml:space="preserve">2026-11-28</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-03</t>
+          <t xml:space="preserve">2026-11-28</t>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">17:30</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G48" t="inlineStr" s="2">
@@ -4681,22 +4681,22 @@
       </c>
       <c r="I48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 3, 4 Musical</t>
+          <t xml:space="preserve">2026 - Enishi Futsal Tournament</t>
         </is>
       </c>
       <c r="J48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3・4年生ミュージカル</t>
+          <t xml:space="preserve">2026 Enishiフットサル大会</t>
         </is>
       </c>
       <c r="K48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students present a musical performance showcasing their talents in singing, acting, and teamwork. Families are invited to enjoy this special production.</t>
+          <t xml:space="preserve">Enishi will host a Middle School Futsal tournament at our school with multiple schools participating.</t>
         </is>
       </c>
       <c r="L48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">歌、演技、チームワークを披露するミュージカルを上演します。ご家族の皆様もぜひこの特別な公演をお楽しみください。</t>
+          <t xml:space="preserve">本校にて複数校が参加する中学生フットサル大会を開催します。</t>
         </is>
       </c>
       <c r="M48" t="inlineStr" s="2">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-03-grade-3-4-musical.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-28-2026-enishi-futsal-tournament.webp</t>
         </is>
       </c>
       <c r="P48" t="inlineStr" s="2">
@@ -4738,32 +4738,32 @@
     <row r="49">
       <c r="A49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-05-sat-test-5</t>
+          <t xml:space="preserve">2026-12-03-grade-3-4-musical</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-05</t>
+          <t xml:space="preserve">2026-12-03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-05</t>
+          <t xml:space="preserve">2026-12-03</t>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">17:30</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G49" t="inlineStr" s="2">
@@ -4778,22 +4778,22 @@
       </c>
       <c r="I49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT Test #5</t>
+          <t xml:space="preserve">Grade 3, 4 Musical</t>
         </is>
       </c>
       <c r="J49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT試験 第5回</t>
+          <t xml:space="preserve">3・4年生ミュージカル</t>
         </is>
       </c>
       <c r="K49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
+          <t xml:space="preserve">Students present a musical performance showcasing their talents in singing, acting, and teamwork. Families are invited to enjoy this special production.</t>
         </is>
       </c>
       <c r="L49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
+          <t xml:space="preserve">歌、演技、チームワークを披露するミュージカルを上演します。ご家族の皆様もぜひこの特別な公演をお楽しみください。</t>
         </is>
       </c>
       <c r="M49" t="inlineStr" s="2">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="O49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-05-sat-test-5.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-03-grade-3-4-musical.webp</t>
         </is>
       </c>
       <c r="P49" t="inlineStr" s="2">
@@ -4835,17 +4835,17 @@
     <row r="50">
       <c r="A50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-10-choir-and-orchestra-concert</t>
+          <t xml:space="preserve">2026-12-05-sat-test-5</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-10</t>
+          <t xml:space="preserve">2026-12-05</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-10</t>
+          <t xml:space="preserve">2026-12-05</t>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="3">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G50" t="inlineStr" s="2">
@@ -4875,22 +4875,22 @@
       </c>
       <c r="I50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choir and Orchestra Concert</t>
+          <t xml:space="preserve">SAT Test #5</t>
         </is>
       </c>
       <c r="J50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合唱・オーケストラコンサート</t>
+          <t xml:space="preserve">SAT試験 第5回</t>
         </is>
       </c>
       <c r="K50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choir class and orchestra club will perform the music repertoire they have been rehearsing for an audience of family, peers and teachers.</t>
+          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
         </is>
       </c>
       <c r="L50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合唱クラスとオーケストラクラブが、練習を重ねてきた曲目をご家族、友人、教員の前で演奏します。</t>
+          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
         </is>
       </c>
       <c r="M50" t="inlineStr" s="2">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-10-choir-and-orchestra-concert.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-05-sat-test-5.webp</t>
         </is>
       </c>
       <c r="P50" t="inlineStr" s="2">
@@ -4932,17 +4932,17 @@
     <row r="51">
       <c r="A51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-11-silent-auction</t>
+          <t xml:space="preserve">2026-12-10-choir-and-orchestra-concert</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-11</t>
+          <t xml:space="preserve">2026-12-10</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-11</t>
+          <t xml:space="preserve">2026-12-10</t>
         </is>
       </c>
       <c r="D51" t="inlineStr" s="3">
@@ -4952,7 +4952,7 @@
       </c>
       <c r="E51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F51" t="inlineStr" s="2">
@@ -4972,22 +4972,22 @@
       </c>
       <c r="I51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Silent Auction</t>
+          <t xml:space="preserve">Choir and Orchestra Concert</t>
         </is>
       </c>
       <c r="J51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">サイレントオークション</t>
+          <t xml:space="preserve">合唱・オーケストラコンサート</t>
         </is>
       </c>
       <c r="K51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Families and community members can bid on donated items and experiences to support initiatives chosen by the primary student council.</t>
+          <t xml:space="preserve">Choir class and orchestra club will perform the music repertoire they have been rehearsing for an audience of family, peers and teachers.</t>
         </is>
       </c>
       <c r="L51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ご家族や地域の皆様が寄付された品物や体験に入札し、小学部生徒会が選んだ取り組みを支援します。</t>
+          <t xml:space="preserve">合唱クラスとオーケストラクラブが、練習を重ねてきた曲目をご家族、友人、教員の前で演奏します。</t>
         </is>
       </c>
       <c r="M51" t="inlineStr" s="2">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="O51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-11-silent-auction.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-10-choir-and-orchestra-concert.webp</t>
         </is>
       </c>
       <c r="P51" t="inlineStr" s="2">
@@ -5029,17 +5029,17 @@
     <row r="52">
       <c r="A52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-14-clubs-pause</t>
+          <t xml:space="preserve">2026-12-11-silent-auction</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-14</t>
+          <t xml:space="preserve">2026-12-11</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-15</t>
+          <t xml:space="preserve">2026-12-11</t>
         </is>
       </c>
       <c r="D52" t="inlineStr" s="3">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G52" t="inlineStr" s="2">
@@ -5069,22 +5069,22 @@
       </c>
       <c r="I52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Clubs Pause</t>
+          <t xml:space="preserve">Silent Auction</t>
         </is>
       </c>
       <c r="J52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クラブ活動休止</t>
+          <t xml:space="preserve">サイレントオークション</t>
         </is>
       </c>
       <c r="K52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">After-school clubs are paused during this period. Bus reminder: the afternoon Red bus runs only on club days, so it does not run while clubs are paused. Please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
+          <t xml:space="preserve">Families and community members can bid on donated items and experiences to support initiatives chosen by the primary student council.</t>
         </is>
       </c>
       <c r="L52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">この期間、放課後のクラブ活動はお休みです。【バスについて】午後の赤バスはクラブ活動がある日のみ運行するため、休止期間中は運行しません。午後の下校時は青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
+          <t xml:space="preserve">ご家族や地域の皆様が寄付された品物や体験に入札し、小学部生徒会が選んだ取り組みを支援します。</t>
         </is>
       </c>
       <c r="M52" t="inlineStr" s="2">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="O52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">compass/images/events/2026-12-11-silent-auction.webp</t>
         </is>
       </c>
       <c r="P52" t="inlineStr" s="2">
@@ -5126,17 +5126,17 @@
     <row r="53">
       <c r="A53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-16-industry-visit-tech-company</t>
+          <t xml:space="preserve">2026-12-14-clubs-pause</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-16</t>
+          <t xml:space="preserve">2026-12-14</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-16</t>
+          <t xml:space="preserve">2026-12-18</t>
         </is>
       </c>
       <c r="D53" t="inlineStr" s="3">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="E53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F53" t="inlineStr" s="2">
@@ -5166,22 +5166,22 @@
       </c>
       <c r="I53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Industry Visit (Tech Company)</t>
+          <t xml:space="preserve">Clubs Pause</t>
         </is>
       </c>
       <c r="J53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">企業訪問（テクノロジー企業）</t>
+          <t xml:space="preserve">クラブ活動休止</t>
         </is>
       </c>
       <c r="K53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will visit a local technology company to gain firsthand insight into the modern workplace and explore careers in technology and innovation.</t>
+          <t xml:space="preserve">After-school clubs are paused during this period. Bus reminder: the afternoon Red bus runs only on club days, so it does not run while clubs are paused. Please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
         </is>
       </c>
       <c r="L53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">地元のテクノロジー企業を訪問し、現代の職場を直接知るとともに、テクノロジーやイノベーション分野のキャリアについて考えます。</t>
+          <t xml:space="preserve">この期間、放課後のクラブ活動はお休みです。【バスについて】午後の赤バスはクラブ活動がある日のみ運行するため、休止期間中は運行しません。午後の下校時は青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
         </is>
       </c>
       <c r="M53" t="inlineStr" s="2">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="O53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-16-industry-visit-tech-company.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P53" t="inlineStr" s="2">
@@ -5223,7 +5223,7 @@
     <row r="54">
       <c r="A54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-16-winter-party-eagle-nest</t>
+          <t xml:space="preserve">2026-12-16-industry-visit-tech-company</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="3">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="E54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F54" t="inlineStr" s="2">
@@ -5263,22 +5263,22 @@
       </c>
       <c r="I54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Winter Party (Eagle Nest)</t>
+          <t xml:space="preserve">Industry Visit (Tech Company)</t>
         </is>
       </c>
       <c r="J54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ウィンターパーティー（イーグルネスト）</t>
+          <t xml:space="preserve">企業訪問（テクノロジー企業）</t>
         </is>
       </c>
       <c r="K54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students celebrate the season with fun activities, games, and opportunities to connect with peers in their Eagle Nests. This is led by the primary student council.</t>
+          <t xml:space="preserve">Students will visit a local technology company to gain firsthand insight into the modern workplace and explore careers in technology and innovation.</t>
         </is>
       </c>
       <c r="L54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">イーグルネストごとに、楽しい活動やゲームを通して仲間と交流し、季節を祝います。小学部生徒会が主催します。</t>
+          <t xml:space="preserve">地元のテクノロジー企業を訪問し、現代の職場を直接知るとともに、テクノロジーやイノベーション分野のキャリアについて考えます。</t>
         </is>
       </c>
       <c r="M54" t="inlineStr" s="2">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="O54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-16-winter-party-eagle-nest.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-16-industry-visit-tech-company.webp</t>
         </is>
       </c>
       <c r="P54" t="inlineStr" s="2">
@@ -5320,17 +5320,17 @@
     <row r="55">
       <c r="A55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-17-talent-day</t>
+          <t xml:space="preserve">2026-12-16-winter-party-eagle-nest</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-17</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-17</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="3">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="E55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G55" t="inlineStr" s="2">
@@ -5360,22 +5360,22 @@
       </c>
       <c r="I55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Talent Day</t>
+          <t xml:space="preserve">Winter Party (Eagle Nest)</t>
         </is>
       </c>
       <c r="J55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">タレントデー</t>
+          <t xml:space="preserve">ウィンターパーティー（イーグルネスト）</t>
         </is>
       </c>
       <c r="K55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students have the opportunity to showcase their unique talents and interests in a supportive and encouraging environment led by the performing arts teacher.</t>
+          <t xml:space="preserve">Students celebrate the season with fun activities, games, and opportunities to connect with peers in their Eagle Nests. This is led by the primary student council.</t>
         </is>
       </c>
       <c r="L55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">舞台芸術の先生のもと、温かく励まし合う雰囲気の中で、一人ひとりの特技や興味を披露します。</t>
+          <t xml:space="preserve">イーグルネストごとに、楽しい活動やゲームを通して仲間と交流し、季節を祝います。小学部生徒会が主催します。</t>
         </is>
       </c>
       <c r="M55" t="inlineStr" s="2">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="O55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-17-talent-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-16-winter-party-eagle-nest.webp</t>
         </is>
       </c>
       <c r="P55" t="inlineStr" s="2">
@@ -5417,17 +5417,17 @@
     <row r="56">
       <c r="A56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-18-tea-party-pta-for-all</t>
+          <t xml:space="preserve">2026-12-17-talent-day</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-18</t>
+          <t xml:space="preserve">2026-12-17</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-18</t>
+          <t xml:space="preserve">2026-12-17</t>
         </is>
       </c>
       <c r="D56" t="inlineStr" s="3">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="E56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTA</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F56" t="inlineStr" s="2">
@@ -5457,22 +5457,22 @@
       </c>
       <c r="I56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Tea Party / PTA for all</t>
+          <t xml:space="preserve">Talent Day</t>
         </is>
       </c>
       <c r="J56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTAティーパーティー（どなたでも参加できます）</t>
+          <t xml:space="preserve">タレントデー</t>
         </is>
       </c>
       <c r="K56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Families are invited to enjoy refreshments while connecting with the PTA, school staff, and other members of the community.</t>
+          <t xml:space="preserve">Students have the opportunity to showcase their unique talents and interests in a supportive and encouraging environment led by the performing arts teacher.</t>
         </is>
       </c>
       <c r="L56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">軽食を楽しみながら、PTA、教職員、コミュニティの皆様と交流していただける集いです。</t>
+          <t xml:space="preserve">舞台芸術の先生のもと、温かく励まし合う雰囲気の中で、一人ひとりの特技や興味を披露します。</t>
         </is>
       </c>
       <c r="M56" t="inlineStr" s="2">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="O56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-18-tea-party-pta-for-all.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-17-talent-day.webp</t>
         </is>
       </c>
       <c r="P56" t="inlineStr" s="2">
@@ -5514,7 +5514,7 @@
     <row r="57">
       <c r="A57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-18-eagle-bucks-store</t>
+          <t xml:space="preserve">2026-12-18-tea-party-pta-for-all</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="3">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="E57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">PTA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G57" t="inlineStr" s="2">
@@ -5554,22 +5554,22 @@
       </c>
       <c r="I57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Eagle Bucks Store</t>
+          <t xml:space="preserve">Tea Party / PTA for all</t>
         </is>
       </c>
       <c r="J57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">イーグルバックス・ストア</t>
+          <t xml:space="preserve">PTAティーパーティー（どなたでも参加できます）</t>
         </is>
       </c>
       <c r="K57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
+          <t xml:space="preserve">Families are invited to enjoy refreshments while connecting with the PTA, school staff, and other members of the community.</t>
         </is>
       </c>
       <c r="L57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
+          <t xml:space="preserve">軽食を楽しみながら、PTA、教職員、コミュニティの皆様と交流していただける集いです。</t>
         </is>
       </c>
       <c r="M57" t="inlineStr" s="2">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="O57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-18-eagle-bucks-store.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-18-tea-party-pta-for-all.webp</t>
         </is>
       </c>
       <c r="P57" t="inlineStr" s="2">
@@ -5611,17 +5611,17 @@
     <row r="58">
       <c r="A58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-19-end-of-term-1-activity-sleep-over-program-g6-10</t>
+          <t xml:space="preserve">2026-12-18-eagle-bucks-store</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-19</t>
+          <t xml:space="preserve">2026-12-18</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-19</t>
+          <t xml:space="preserve">2026-12-18</t>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="3">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F58" t="inlineStr" s="2">
@@ -5651,22 +5651,22 @@
       </c>
       <c r="I58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">End of Term 1 Activity-Sleep Over Program: G6-10</t>
+          <t xml:space="preserve">Eagle Bucks Store</t>
         </is>
       </c>
       <c r="J58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第1学期末行事：宿泊プログラム（G6–10）</t>
+          <t xml:space="preserve">イーグルバックス・ストア</t>
         </is>
       </c>
       <c r="K58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 6 to 10 students will take part in a school sleepover program to celebrate the end of Term 1 through shared activities and community building.</t>
+          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
         </is>
       </c>
       <c r="L58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">6～10年生が校内での宿泊プログラムに参加し、共に活動しながら仲間づくりを行い、第1学期の終わりを祝います。</t>
+          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
         </is>
       </c>
       <c r="M58" t="inlineStr" s="2">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="O58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-19-end-of-term-1-activity-sleep-over-program-g6-10.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-18-eagle-bucks-store.webp</t>
         </is>
       </c>
       <c r="P58" t="inlineStr" s="2">
@@ -5708,17 +5708,17 @@
     <row r="59">
       <c r="A59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-21-winter-study-camp-g11-12</t>
+          <t xml:space="preserve">2026-12-19-end-of-term-1-activity-sleep-over-program-g6-10</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-21</t>
+          <t xml:space="preserve">2026-12-19</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-23</t>
+          <t xml:space="preserve">2026-12-19</t>
         </is>
       </c>
       <c r="D59" t="inlineStr" s="3">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="E59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F59" t="inlineStr" s="2">
@@ -5748,22 +5748,22 @@
       </c>
       <c r="I59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Winter Study Camp: G11-12</t>
+          <t xml:space="preserve">End of Term 1 Activity-Sleep Over Program: G6-10</t>
         </is>
       </c>
       <c r="J59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">冬季学習合宿：G11–12</t>
+          <t xml:space="preserve">第1学期末行事：宿泊プログラム（G6–10）</t>
         </is>
       </c>
       <c r="K59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 11 and 12 students will take part in an off-campus Winter Study Camp focused on concentrated study, academic review, and exam preparation.</t>
+          <t xml:space="preserve">Grade 6 to 10 students will take part in a school sleepover program to celebrate the end of Term 1 through shared activities and community building.</t>
         </is>
       </c>
       <c r="L59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11・12年生が校外での冬季学習合宿に参加し、集中学習、復習、試験対策に取り組みます。</t>
+          <t xml:space="preserve">6～10年生が校内での宿泊プログラムに参加し、共に活動しながら仲間づくりを行い、第1学期の終わりを祝います。</t>
         </is>
       </c>
       <c r="M59" t="inlineStr" s="2">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-21-winter-study-camp-g11-12.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-19-end-of-term-1-activity-sleep-over-program-g6-10.webp</t>
         </is>
       </c>
       <c r="P59" t="inlineStr" s="2">
@@ -5805,17 +5805,17 @@
     <row r="60">
       <c r="A60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-08-parent-teacher-conferences</t>
+          <t xml:space="preserve">2026-12-21-winter-study-camp-g11-12</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-08</t>
+          <t xml:space="preserve">2026-12-21</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-08</t>
+          <t xml:space="preserve">2026-12-23</t>
         </is>
       </c>
       <c r="D60" t="inlineStr" s="3">
@@ -5825,17 +5825,17 @@
       </c>
       <c r="E60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H60" t="inlineStr" s="2">
@@ -5845,22 +5845,22 @@
       </c>
       <c r="I60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parent Teacher Conferences</t>
+          <t xml:space="preserve">Winter Study Camp: G11-12</t>
         </is>
       </c>
       <c r="J60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者面談</t>
+          <t xml:space="preserve">冬季学習合宿：G11–12</t>
         </is>
       </c>
       <c r="K60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on this day.</t>
+          <t xml:space="preserve">Grade 11 and 12 students will take part in an off-campus Winter Study Camp focused on concentrated study, academic review, and exam preparation.</t>
         </is>
       </c>
       <c r="L60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。当日、生徒は登校しません。</t>
+          <t xml:space="preserve">11・12年生が校外での冬季学習合宿に参加し、集中学習、復習、試験対策に取り組みます。</t>
         </is>
       </c>
       <c r="M60" t="inlineStr" s="2">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="O60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-19-parent-teacher-conferences.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-21-winter-study-camp-g11-12.webp</t>
         </is>
       </c>
       <c r="P60" t="inlineStr" s="2">
@@ -5902,17 +5902,17 @@
     <row r="61">
       <c r="A61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-14-g10-parent-info-session-high-school-subject-choi</t>
+          <t xml:space="preserve">2027-01-08-parent-teacher-conferences</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-14</t>
+          <t xml:space="preserve">2027-01-08</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-14</t>
+          <t xml:space="preserve">2027-01-08</t>
         </is>
       </c>
       <c r="D61" t="inlineStr" s="3">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="E61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F61" t="inlineStr" s="2">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="G61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="H61" t="inlineStr" s="2">
@@ -5942,22 +5942,22 @@
       </c>
       <c r="I61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G10 Parent info Session (High School Subject Choice)</t>
+          <t xml:space="preserve">Parent Teacher Conferences</t>
         </is>
       </c>
       <c r="J61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G10保護者向け説明会（高等部科目選択）</t>
+          <t xml:space="preserve">保護者面談</t>
         </is>
       </c>
       <c r="K61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 10 parents are invited to an information session about DP subject choices and guidance for planning the next stage of their child’s learning.</t>
+          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on this day.</t>
         </is>
       </c>
       <c r="L61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10年生の保護者の皆様を対象に、DPの科目選択と、お子様の次のステージの学びを計画するためのガイダンスを行います。</t>
+          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。当日、生徒は登校しません。</t>
         </is>
       </c>
       <c r="M61" t="inlineStr" s="2">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="O61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-01-14-g10-parent-info-session-high-school-subject-choi.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-19-parent-teacher-conferences.webp</t>
         </is>
       </c>
       <c r="P61" t="inlineStr" s="2">
@@ -5999,17 +5999,17 @@
     <row r="62">
       <c r="A62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-18-clubs-resume</t>
+          <t xml:space="preserve">2027-01-11-clubs-pause</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-18</t>
+          <t xml:space="preserve">2027-01-11</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-18</t>
+          <t xml:space="preserve">2027-01-15</t>
         </is>
       </c>
       <c r="D62" t="inlineStr" s="3">
@@ -6039,22 +6039,22 @@
       </c>
       <c r="I62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Clubs Resume</t>
+          <t xml:space="preserve">Clubs Pause</t>
         </is>
       </c>
       <c r="J62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クラブ活動再開</t>
+          <t xml:space="preserve">クラブ活動休止</t>
         </is>
       </c>
       <c r="K62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">After-school clubs start again today. Bus reminder: the afternoon Red bus runs only on club days. On other days, please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
+          <t xml:space="preserve">After-school clubs are paused during this period. Bus reminder: the afternoon Red bus runs only on club days, so it does not run while clubs are paused. Please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
         </is>
       </c>
       <c r="L62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">本日から放課後のクラブ活動が再開します。【バスについて】午後の赤バスはクラブ活動がある日のみ運行します。それ以外の日は、午後の下校時に青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
+          <t xml:space="preserve">この期間、放課後のクラブ活動はお休みです。【バスについて】午後の赤バスはクラブ活動がある日のみ運行するため、休止期間中は運行しません。午後の下校時は青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
         </is>
       </c>
       <c r="M62" t="inlineStr" s="2">
@@ -6096,17 +6096,17 @@
     <row r="63">
       <c r="A63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-22-open-campus</t>
+          <t xml:space="preserve">2027-01-14-g10-parent-info-session-high-school-subject-choi</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-22</t>
+          <t xml:space="preserve">2027-01-14</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-22</t>
+          <t xml:space="preserve">2027-01-14</t>
         </is>
       </c>
       <c r="D63" t="inlineStr" s="3">
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G63" t="inlineStr" s="2">
@@ -6136,22 +6136,22 @@
       </c>
       <c r="I63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Open Campus</t>
+          <t xml:space="preserve">G10 Parent info Session (High School Subject Choice)</t>
         </is>
       </c>
       <c r="J63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">オープンキャンパス</t>
+          <t xml:space="preserve">G10保護者向け説明会（高等部科目選択）</t>
         </is>
       </c>
       <c r="K63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Any person interested in seeing the daily operation of the school is invited to join a tour of the school during its regular hours.</t>
+          <t xml:space="preserve">Grade 10 parents are invited to an information session about DP subject choices and guidance for planning the next stage of their child’s learning.</t>
         </is>
       </c>
       <c r="L63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学校の日常の様子にご関心のある方は、通常授業時間中の校内見学にご参加いただけます。</t>
+          <t xml:space="preserve">10年生の保護者の皆様を対象に、DPの科目選択と、お子様の次のステージの学びを計画するためのガイダンスを行います。</t>
         </is>
       </c>
       <c r="M63" t="inlineStr" s="2">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-01-22-open-campus.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-01-14-g10-parent-info-session-high-school-subject-choi.webp</t>
         </is>
       </c>
       <c r="P63" t="inlineStr" s="2">
@@ -6193,17 +6193,17 @@
     <row r="64">
       <c r="A64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-23-alumni-talk</t>
+          <t xml:space="preserve">2027-01-18-clubs-resume</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-23</t>
+          <t xml:space="preserve">2027-01-18</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-23</t>
+          <t xml:space="preserve">2027-01-18</t>
         </is>
       </c>
       <c r="D64" t="inlineStr" s="3">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="E64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F64" t="inlineStr" s="2">
@@ -6233,22 +6233,22 @@
       </c>
       <c r="I64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Alumni Talk</t>
+          <t xml:space="preserve">Clubs Resume</t>
         </is>
       </c>
       <c r="J64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">卒業生トーク</t>
+          <t xml:space="preserve">クラブ活動再開</t>
         </is>
       </c>
       <c r="K64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Alumni will share their experiences and advice with students, offering insight into life after School and future pathways.</t>
+          <t xml:space="preserve">After-school clubs start again today. Bus reminder: the afternoon Red bus runs only on club days. On other days, please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
         </is>
       </c>
       <c r="L64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">卒業生が自身の経験やアドバイスを生徒に伝え、卒業後の生活や将来の進路について話します。</t>
+          <t xml:space="preserve">本日から放課後のクラブ活動が再開します。【バスについて】午後の赤バスはクラブ活動がある日のみ運行します。それ以外の日は、午後の下校時に青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
         </is>
       </c>
       <c r="M64" t="inlineStr" s="2">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="O64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-01-23-alumni-talk.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P64" t="inlineStr" s="2">
@@ -6290,17 +6290,17 @@
     <row r="65">
       <c r="A65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-27-natural-disaster-field-trip</t>
+          <t xml:space="preserve">2027-01-22-open-campus</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-27</t>
+          <t xml:space="preserve">2027-01-22</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-27</t>
+          <t xml:space="preserve">2027-01-22</t>
         </is>
       </c>
       <c r="D65" t="inlineStr" s="3">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="E65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F65" t="inlineStr" s="2">
@@ -6330,22 +6330,22 @@
       </c>
       <c r="I65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Natural Disaster Field Trip</t>
+          <t xml:space="preserve">Open Campus</t>
         </is>
       </c>
       <c r="J65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">防災校外学習</t>
+          <t xml:space="preserve">オープンキャンパス</t>
         </is>
       </c>
       <c r="K65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students explore disaster preparedness and safety through interactive learning experiences related to natural disasters and emergency response.</t>
+          <t xml:space="preserve">Any person interested in seeing the daily operation of the school is invited to join a tour of the school during its regular hours.</t>
         </is>
       </c>
       <c r="L65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">自然災害や緊急時の対応に関する体験型学習を通して、防災と安全について学びます。</t>
+          <t xml:space="preserve">学校の日常の様子にご関心のある方は、通常授業時間中の校内見学にご参加いただけます。</t>
         </is>
       </c>
       <c r="M65" t="inlineStr" s="2">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="O65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-01-27-natural-disaster-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-01-22-open-campus.webp</t>
         </is>
       </c>
       <c r="P65" t="inlineStr" s="2">
@@ -6387,17 +6387,17 @@
     <row r="66">
       <c r="A66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-30-model-united-nations-event-mun</t>
+          <t xml:space="preserve">2027-01-23-alumni-talk</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-30</t>
+          <t xml:space="preserve">2027-01-23</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-30</t>
+          <t xml:space="preserve">2027-01-23</t>
         </is>
       </c>
       <c r="D66" t="inlineStr" s="3">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="E66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F66" t="inlineStr" s="2">
@@ -6427,22 +6427,22 @@
       </c>
       <c r="I66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Model United Nations Event (MUN)</t>
+          <t xml:space="preserve">Alumni Talk</t>
         </is>
       </c>
       <c r="J66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">模擬国連（MUN）</t>
+          <t xml:space="preserve">卒業生トーク</t>
         </is>
       </c>
       <c r="K66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will participate in Model United Nations, developing public speaking, research, collaboration, and global awareness through discussion of real-world issues.</t>
+          <t xml:space="preserve">Alumni will share their experiences and advice with students, offering insight into life after School and future pathways.</t>
         </is>
       </c>
       <c r="L66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">模擬国連に参加し、現実の課題について議論することで、スピーチ力、調査力、協働する力、国際的な意識を育みます。</t>
+          <t xml:space="preserve">卒業生が自身の経験やアドバイスを生徒に伝え、卒業後の生活や将来の進路について話します。</t>
         </is>
       </c>
       <c r="M66" t="inlineStr" s="2">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="O66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-01-30-model-united-nations-event-mun.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-01-23-alumni-talk.webp</t>
         </is>
       </c>
       <c r="P66" t="inlineStr" s="2">
@@ -6484,17 +6484,17 @@
     <row r="67">
       <c r="A67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-01-friendly-volleyball-tournament-internal</t>
+          <t xml:space="preserve">2027-01-27-natural-disaster-field-trip</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-01</t>
+          <t xml:space="preserve">2027-01-27</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-05</t>
+          <t xml:space="preserve">2027-01-27</t>
         </is>
       </c>
       <c r="D67" t="inlineStr" s="3">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="E67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">ELC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr" s="2">
@@ -6524,22 +6524,22 @@
       </c>
       <c r="I67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Friendly Volleyball Tournament (Internal)</t>
+          <t xml:space="preserve">Natural Disaster Field Trip</t>
         </is>
       </c>
       <c r="J67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内バレーボール大会</t>
+          <t xml:space="preserve">防災校外学習</t>
         </is>
       </c>
       <c r="K67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in a friendly internal volleyball tournament, promoting teamwork, sportsmanship, and school spirit.</t>
+          <t xml:space="preserve">Students explore disaster preparedness and safety through interactive learning experiences related to natural disasters and emergency response.</t>
         </is>
       </c>
       <c r="L67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内バレーボール大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
+          <t xml:space="preserve">自然災害や緊急時の対応に関する体験型学習を通して、防災と安全について学びます。</t>
         </is>
       </c>
       <c r="M67" t="inlineStr" s="2">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="O67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-01-friendly-volleyball-tournament-internal.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-01-27-natural-disaster-field-trip.webp</t>
         </is>
       </c>
       <c r="P67" t="inlineStr" s="2">
@@ -6581,17 +6581,17 @@
     <row r="68">
       <c r="A68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-01-concept-con-language</t>
+          <t xml:space="preserve">2027-01-30-model-united-nations-event-mun</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-01</t>
+          <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-05</t>
+          <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
       <c r="D68" t="inlineStr" s="3">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="E68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F68" t="inlineStr" s="2">
@@ -6621,22 +6621,22 @@
       </c>
       <c r="I68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Concept Con (Language)</t>
+          <t xml:space="preserve">Model United Nations Event (MUN)</t>
         </is>
       </c>
       <c r="J68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">コンセプト・コン（言語）</t>
+          <t xml:space="preserve">模擬国連（MUN）</t>
         </is>
       </c>
       <c r="K68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students celebrate language and communication through presentations, performances, and projects that showcase their learning and creativity.</t>
+          <t xml:space="preserve">Students will participate in Model United Nations, developing public speaking, research, collaboration, and global awareness through discussion of real-world issues.</t>
         </is>
       </c>
       <c r="L68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学びと創造性を示す発表、パフォーマンス、プロジェクトを通して、言語とコミュニケーションを祝います。</t>
+          <t xml:space="preserve">模擬国連に参加し、現実の課題について議論することで、スピーチ力、調査力、協働する力、国際的な意識を育みます。</t>
         </is>
       </c>
       <c r="M68" t="inlineStr" s="2">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="O68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-01-concept-con-language.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-01-30-model-united-nations-event-mun.webp</t>
         </is>
       </c>
       <c r="P68" t="inlineStr" s="2">
@@ -6678,17 +6678,17 @@
     <row r="69">
       <c r="A69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-18-career-support-second-career-roundtable-and-care</t>
+          <t xml:space="preserve">2027-02-01-friendly-volleyball-tournament-internal</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-18</t>
+          <t xml:space="preserve">2027-02-01</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-18</t>
+          <t xml:space="preserve">2027-02-05</t>
         </is>
       </c>
       <c r="D69" t="inlineStr" s="3">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="E69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G69" t="inlineStr" s="2">
@@ -6718,22 +6718,22 @@
       </c>
       <c r="I69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Career Support: Second Career Roundtable and Career Fair</t>
+          <t xml:space="preserve">Friendly Volleyball Tournament (Internal)</t>
         </is>
       </c>
       <c r="J69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">進路支援：第2回キャリア座談会・キャリアフェア</t>
+          <t xml:space="preserve">校内バレーボール大会</t>
         </is>
       </c>
       <c r="K69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An informative event where students and parents can learn about IB university admissions, holistic admissions strategies in Japan and abroad, and explore future academic and career opportunities through discussions with experts and representatives.</t>
+          <t xml:space="preserve">Students will take part in a friendly internal volleyball tournament, promoting teamwork, sportsmanship, and school spirit.</t>
         </is>
       </c>
       <c r="L69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">専門家や関係者との対話を通して、生徒と保護者の皆様がIBでの大学入試、国内外の総合型選抜の戦略について学び、将来の進学やキャリアの可能性を探る説明会です。</t>
+          <t xml:space="preserve">校内バレーボール大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
         </is>
       </c>
       <c r="M69" t="inlineStr" s="2">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="O69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-18-career-support-second-career-roundtable-and-care.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-01-friendly-volleyball-tournament-internal.webp</t>
         </is>
       </c>
       <c r="P69" t="inlineStr" s="2">
@@ -6775,17 +6775,17 @@
     <row r="70">
       <c r="A70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-19-collective-field-trip</t>
+          <t xml:space="preserve">2027-02-01-concept-con-language</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-19</t>
+          <t xml:space="preserve">2027-02-01</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-19</t>
+          <t xml:space="preserve">2027-02-05</t>
         </is>
       </c>
       <c r="D70" t="inlineStr" s="3">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="E70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr" s="2">
@@ -6815,22 +6815,22 @@
       </c>
       <c r="I70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Collective Field Trip</t>
+          <t xml:space="preserve">Concept Con (Language)</t>
         </is>
       </c>
       <c r="J70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合同校外学習</t>
+          <t xml:space="preserve">コンセプト・コン（言語）</t>
         </is>
       </c>
       <c r="K70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students participate in an off-campus learning experience that connects classroom learning with real-world exploration and discovery.</t>
+          <t xml:space="preserve">Students celebrate language and communication through presentations, performances, and projects that showcase their learning and creativity.</t>
         </is>
       </c>
       <c r="L70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校外での学習体験を通して、教室での学びを実社会での探究や発見と結びつけます。</t>
+          <t xml:space="preserve">学びと創造性を示す発表、パフォーマンス、プロジェクトを通して、言語とコミュニケーションを祝います。</t>
         </is>
       </c>
       <c r="M70" t="inlineStr" s="2">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-19-collective-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-01-concept-con-language.webp</t>
         </is>
       </c>
       <c r="P70" t="inlineStr" s="2">
@@ -6872,17 +6872,17 @@
     <row r="71">
       <c r="A71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-22-world-thinking-day</t>
+          <t xml:space="preserve">2027-02-18-career-support-second-career-roundtable-and-care</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-22</t>
+          <t xml:space="preserve">2027-02-18</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-22</t>
+          <t xml:space="preserve">2027-02-18</t>
         </is>
       </c>
       <c r="D71" t="inlineStr" s="3">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="E71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G71" t="inlineStr" s="2">
@@ -6912,22 +6912,22 @@
       </c>
       <c r="I71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">World Thinking Day</t>
+          <t xml:space="preserve">Career Support: Second Career Roundtable and Career Fair</t>
         </is>
       </c>
       <c r="J71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ワールド・シンキング・デー</t>
+          <t xml:space="preserve">進路支援：第2回キャリア座談会・キャリアフェア</t>
         </is>
       </c>
       <c r="K71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students learn about cultures, traditions, and global citizenship while celebrating international understanding and connection.</t>
+          <t xml:space="preserve">An informative event where students and parents can learn about IB university admissions, holistic admissions strategies in Japan and abroad, and explore future academic and career opportunities through discussions with experts and representatives.</t>
         </is>
       </c>
       <c r="L71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国際理解とつながりを祝いながら、さまざまな文化や伝統、地球市民としてのあり方について学びます。</t>
+          <t xml:space="preserve">専門家や関係者との対話を通して、生徒と保護者の皆様がIBでの大学入試、国内外の総合型選抜の戦略について学び、将来の進学やキャリアの可能性を探る説明会です。</t>
         </is>
       </c>
       <c r="M71" t="inlineStr" s="2">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="O71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-22-world-thinking-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-18-career-support-second-career-roundtable-and-care.webp</t>
         </is>
       </c>
       <c r="P71" t="inlineStr" s="2">
@@ -6969,17 +6969,17 @@
     <row r="72">
       <c r="A72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-22-secondary-sports-day-rehearsal-1</t>
+          <t xml:space="preserve">2027-02-19-collective-field-trip</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-22</t>
+          <t xml:space="preserve">2027-02-19</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-22</t>
+          <t xml:space="preserve">2027-02-19</t>
         </is>
       </c>
       <c r="D72" t="inlineStr" s="3">
@@ -6989,7 +6989,7 @@
       </c>
       <c r="E72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F72" t="inlineStr" s="2">
@@ -7009,22 +7009,22 @@
       </c>
       <c r="I72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary Sports Day Rehearsal #1</t>
+          <t xml:space="preserve">Collective Field Trip</t>
         </is>
       </c>
       <c r="J72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部運動会リハーサル #1</t>
+          <t xml:space="preserve">合同校外学習</t>
         </is>
       </c>
       <c r="K72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
+          <t xml:space="preserve">Students participate in an off-campus learning experience that connects classroom learning with real-world exploration and discovery.</t>
         </is>
       </c>
       <c r="L72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
+          <t xml:space="preserve">校外での学習体験を通して、教室での学びを実社会での探究や発見と結びつけます。</t>
         </is>
       </c>
       <c r="M72" t="inlineStr" s="2">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="O72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-22-secondary-sports-day-rehearsal-1.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-19-collective-field-trip.webp</t>
         </is>
       </c>
       <c r="P72" t="inlineStr" s="2">
@@ -7066,17 +7066,17 @@
     <row r="73">
       <c r="A73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-25-primary-sports-day-rehearsal-1</t>
+          <t xml:space="preserve">2027-02-22-world-thinking-day</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-25</t>
+          <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-25</t>
+          <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
       <c r="D73" t="inlineStr" s="3">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="E73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr" s="2">
@@ -7106,22 +7106,22 @@
       </c>
       <c r="I73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary Sports Day Rehearsal #1</t>
+          <t xml:space="preserve">World Thinking Day</t>
         </is>
       </c>
       <c r="J73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小学部運動会リハーサル #1</t>
+          <t xml:space="preserve">ワールド・シンキング・デー</t>
         </is>
       </c>
       <c r="K73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students begin preparing for Sports Day by practicing events, routines, and teamwork activities.</t>
+          <t xml:space="preserve">Students learn about cultures, traditions, and global citizenship while celebrating international understanding and connection.</t>
         </is>
       </c>
       <c r="L73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">種目、流れ、チームワークの練習を通して、運動会に向けた準備を始めます。</t>
+          <t xml:space="preserve">国際理解とつながりを祝いながら、さまざまな文化や伝統、地球市民としてのあり方について学びます。</t>
         </is>
       </c>
       <c r="M73" t="inlineStr" s="2">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="O73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-25-primary-sports-day-rehearsal-1.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-22-world-thinking-day.webp</t>
         </is>
       </c>
       <c r="P73" t="inlineStr" s="2">
@@ -7163,17 +7163,17 @@
     <row r="74">
       <c r="A74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-26-parents-morning-2</t>
+          <t xml:space="preserve">2027-02-22-secondary-sports-day-rehearsal-1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-26</t>
+          <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-26</t>
+          <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
       <c r="D74" t="inlineStr" s="3">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="E74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G74" t="inlineStr" s="2">
@@ -7203,22 +7203,22 @@
       </c>
       <c r="I74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parents Morning #2</t>
+          <t xml:space="preserve">Secondary Sports Day Rehearsal #1</t>
         </is>
       </c>
       <c r="J74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">朝の授業参観 #2</t>
+          <t xml:space="preserve">中等部運動会リハーサル #1</t>
         </is>
       </c>
       <c r="K74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC and Primary Parents are invited to come and see the lessons in the morning and experience the morning routines with their child.</t>
+          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
         </is>
       </c>
       <c r="L74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部・小学部の保護者の皆様をお招きし、朝の授業をご参観いただき、お子様と一緒に朝の日課を体験していただきます。</t>
+          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
         </is>
       </c>
       <c r="M74" t="inlineStr" s="2">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="O74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-26-parents-morning-2.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-22-secondary-sports-day-rehearsal-1.webp</t>
         </is>
       </c>
       <c r="P74" t="inlineStr" s="2">
@@ -7260,17 +7260,17 @@
     <row r="75">
       <c r="A75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-26-eagle-talks</t>
+          <t xml:space="preserve">2027-02-25-primary-sports-day-rehearsal-1</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-26</t>
+          <t xml:space="preserve">2027-02-25</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-26</t>
+          <t xml:space="preserve">2027-02-25</t>
         </is>
       </c>
       <c r="D75" t="inlineStr" s="3">
@@ -7280,12 +7280,12 @@
       </c>
       <c r="E75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G75" t="inlineStr" s="2">
@@ -7300,22 +7300,22 @@
       </c>
       <c r="I75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Eagle Talks</t>
+          <t xml:space="preserve">Primary Sports Day Rehearsal #1</t>
         </is>
       </c>
       <c r="J75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">イーグル・トーク</t>
+          <t xml:space="preserve">小学部運動会リハーサル #1</t>
         </is>
       </c>
       <c r="K75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students share ideas, experiences, and learning through short presentations designed to build confidence, communication, and leadership skills.</t>
+          <t xml:space="preserve">Students begin preparing for Sports Day by practicing events, routines, and teamwork activities.</t>
         </is>
       </c>
       <c r="L75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">短いプレゼンテーションを通して考えや経験、学びを共有し、自信、コミュニケーション力、リーダーシップを育みます。</t>
+          <t xml:space="preserve">種目、流れ、チームワークの練習を通して、運動会に向けた準備を始めます。</t>
         </is>
       </c>
       <c r="M75" t="inlineStr" s="2">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="O75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-26-eagle-talks.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-25-primary-sports-day-rehearsal-1.webp</t>
         </is>
       </c>
       <c r="P75" t="inlineStr" s="2">
@@ -7357,17 +7357,17 @@
     <row r="76">
       <c r="A76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-04-grade-1-2-musical</t>
+          <t xml:space="preserve">2027-02-26-parents-morning-2</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-04</t>
+          <t xml:space="preserve">2027-02-26</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-05</t>
+          <t xml:space="preserve">2027-02-26</t>
         </is>
       </c>
       <c r="D76" t="inlineStr" s="3">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="E76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr" s="2">
@@ -7397,22 +7397,22 @@
       </c>
       <c r="I76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 1, 2 Musical</t>
+          <t xml:space="preserve">Parents Morning #2</t>
         </is>
       </c>
       <c r="J76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1・2年生ミュージカル</t>
+          <t xml:space="preserve">朝の授業参観 #2</t>
         </is>
       </c>
       <c r="K76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students showcase their creativity and confidence through a musical performance featuring songs, acting, and teamwork.</t>
+          <t xml:space="preserve">ELC and Primary Parents are invited to come and see the lessons in the morning and experience the morning routines with their child.</t>
         </is>
       </c>
       <c r="L76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">歌、演技、チームワークによるミュージカルを通して、創造性と自信あふれる姿を披露します。</t>
+          <t xml:space="preserve">幼稚部・小学部の保護者の皆様をお招きし、朝の授業をご参観いただき、お子様と一緒に朝の日課を体験していただきます。</t>
         </is>
       </c>
       <c r="M76" t="inlineStr" s="2">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="O76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-04-grade-1-2-musical.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-26-parents-morning-2.webp</t>
         </is>
       </c>
       <c r="P76" t="inlineStr" s="2">
@@ -7454,17 +7454,17 @@
     <row r="77">
       <c r="A77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-05-higashiyama-zoo-botanical-garden</t>
+          <t xml:space="preserve">2027-02-26-eagle-talks</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-05</t>
+          <t xml:space="preserve">2027-02-26</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-05</t>
+          <t xml:space="preserve">2027-02-26</t>
         </is>
       </c>
       <c r="D77" t="inlineStr" s="3">
@@ -7474,12 +7474,12 @@
       </c>
       <c r="E77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G77" t="inlineStr" s="2">
@@ -7494,22 +7494,22 @@
       </c>
       <c r="I77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Higashiyama Zoo &amp; Botanical Garden</t>
+          <t xml:space="preserve">Eagle Talks</t>
         </is>
       </c>
       <c r="J77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">東山動植物園</t>
+          <t xml:space="preserve">イーグル・トーク</t>
         </is>
       </c>
       <c r="K77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 7 Science students will visit Higashiyama Zoo and Botanical Gardens to support their learning through observation and real-world examples.</t>
+          <t xml:space="preserve">Students share ideas, experiences, and learning through short presentations designed to build confidence, communication, and leadership skills.</t>
         </is>
       </c>
       <c r="L77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7年生が理科の学習の一環として東山動植物園を訪れ、観察や実物を通して学びを深めます。</t>
+          <t xml:space="preserve">短いプレゼンテーションを通して考えや経験、学びを共有し、自信、コミュニケーション力、リーダーシップを育みます。</t>
         </is>
       </c>
       <c r="M77" t="inlineStr" s="2">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="O77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-05-higashiyama-zoo-botanical-garden.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-26-eagle-talks.webp</t>
         </is>
       </c>
       <c r="P77" t="inlineStr" s="2">
@@ -7551,17 +7551,17 @@
     <row r="78">
       <c r="A78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-06-sat-test-6</t>
+          <t xml:space="preserve">2027-03-04-grade-1-2-musical</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-06</t>
+          <t xml:space="preserve">2027-03-04</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-06</t>
+          <t xml:space="preserve">2027-03-05</t>
         </is>
       </c>
       <c r="D78" t="inlineStr" s="3">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="E78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G78" t="inlineStr" s="2">
@@ -7591,22 +7591,22 @@
       </c>
       <c r="I78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT Test #6</t>
+          <t xml:space="preserve">Grade 1, 2 Musical</t>
         </is>
       </c>
       <c r="J78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT試験 第6回</t>
+          <t xml:space="preserve">1・2年生ミュージカル</t>
         </is>
       </c>
       <c r="K78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
+          <t xml:space="preserve">Students showcase their creativity and confidence through a musical performance featuring songs, acting, and teamwork.</t>
         </is>
       </c>
       <c r="L78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
+          <t xml:space="preserve">歌、演技、チームワークによるミュージカルを通して、創造性と自信あふれる姿を披露します。</t>
         </is>
       </c>
       <c r="M78" t="inlineStr" s="2">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="O78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-06-sat-test-6.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-04-grade-1-2-musical.webp</t>
         </is>
       </c>
       <c r="P78" t="inlineStr" s="2">
@@ -7648,17 +7648,17 @@
     <row r="79">
       <c r="A79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-09-primary-sports-day-rehearsal-2</t>
+          <t xml:space="preserve">2027-03-05-higashiyama-zoo-botanical-garden</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-09</t>
+          <t xml:space="preserve">2027-03-05</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-09</t>
+          <t xml:space="preserve">2027-03-05</t>
         </is>
       </c>
       <c r="D79" t="inlineStr" s="3">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="E79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F79" t="inlineStr" s="2">
@@ -7688,22 +7688,22 @@
       </c>
       <c r="I79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary Sports Day Rehearsal #2</t>
+          <t xml:space="preserve">Higashiyama Zoo &amp; Botanical Garden</t>
         </is>
       </c>
       <c r="J79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小学部運動会リハーサル #2</t>
+          <t xml:space="preserve">東山動植物園</t>
         </is>
       </c>
       <c r="K79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students continue building skills and confidence as they prepare for Sports Day events and activities.</t>
+          <t xml:space="preserve">Grade 7 Science students will visit Higashiyama Zoo and Botanical Gardens to support their learning through observation and real-world examples.</t>
         </is>
       </c>
       <c r="L79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会の種目や活動に向けて準備を進めながら、技能と自信をさらに高めます。</t>
+          <t xml:space="preserve">7年生が理科の学習の一環として東山動植物園を訪れ、観察や実物を通して学びを深めます。</t>
         </is>
       </c>
       <c r="M79" t="inlineStr" s="2">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="O79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-09-primary-sports-day-rehearsal-2.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-05-higashiyama-zoo-botanical-garden.webp</t>
         </is>
       </c>
       <c r="P79" t="inlineStr" s="2">
@@ -7745,17 +7745,17 @@
     <row r="80">
       <c r="A80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-12-secondary-sports-day-rehearsal-2</t>
+          <t xml:space="preserve">2027-03-06-sat-test-6</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-12</t>
+          <t xml:space="preserve">2027-03-06</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-12</t>
+          <t xml:space="preserve">2027-03-06</t>
         </is>
       </c>
       <c r="D80" t="inlineStr" s="3">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="E80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F80" t="inlineStr" s="2">
@@ -7785,22 +7785,22 @@
       </c>
       <c r="I80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary Sports Day Rehearsal #2</t>
+          <t xml:space="preserve">SAT Test #6</t>
         </is>
       </c>
       <c r="J80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部運動会リハーサル #2</t>
+          <t xml:space="preserve">SAT試験 第6回</t>
         </is>
       </c>
       <c r="K80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
+          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
         </is>
       </c>
       <c r="L80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
+          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
         </is>
       </c>
       <c r="M80" t="inlineStr" s="2">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="O80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-12-secondary-sports-day-rehearsal-2.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-06-sat-test-6.webp</t>
         </is>
       </c>
       <c r="P80" t="inlineStr" s="2">
@@ -7842,17 +7842,17 @@
     <row r="81">
       <c r="A81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-15-clubs-pause</t>
+          <t xml:space="preserve">2027-03-09-primary-sports-day-rehearsal-2</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-15</t>
+          <t xml:space="preserve">2027-03-09</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-02</t>
+          <t xml:space="preserve">2027-03-09</t>
         </is>
       </c>
       <c r="D81" t="inlineStr" s="3">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="E81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F81" t="inlineStr" s="2">
@@ -7882,22 +7882,22 @@
       </c>
       <c r="I81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Clubs Pause</t>
+          <t xml:space="preserve">Primary Sports Day Rehearsal #2</t>
         </is>
       </c>
       <c r="J81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クラブ活動休止</t>
+          <t xml:space="preserve">小学部運動会リハーサル #2</t>
         </is>
       </c>
       <c r="K81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">After-school clubs are paused during this period. Bus reminder: the afternoon Red bus runs only on club days, so it does not run while clubs are paused. Please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
+          <t xml:space="preserve">Students continue building skills and confidence as they prepare for Sports Day events and activities.</t>
         </is>
       </c>
       <c r="L81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">この期間、放課後のクラブ活動はお休みです。【バスについて】午後の赤バスはクラブ活動がある日のみ運行するため、休止期間中は運行しません。午後の下校時は青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
+          <t xml:space="preserve">運動会の種目や活動に向けて準備を進めながら、技能と自信をさらに高めます。</t>
         </is>
       </c>
       <c r="M81" t="inlineStr" s="2">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">compass/images/events/2027-03-09-primary-sports-day-rehearsal-2.webp</t>
         </is>
       </c>
       <c r="P81" t="inlineStr" s="2">
@@ -7939,17 +7939,17 @@
     <row r="82">
       <c r="A82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-18-japanese-culture-day</t>
+          <t xml:space="preserve">2027-03-12-secondary-sports-day-rehearsal-2</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-18</t>
+          <t xml:space="preserve">2027-03-12</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-18</t>
+          <t xml:space="preserve">2027-03-12</t>
         </is>
       </c>
       <c r="D82" t="inlineStr" s="3">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="E82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G82" t="inlineStr" s="2">
@@ -7979,22 +7979,22 @@
       </c>
       <c r="I82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Japanese Culture Day</t>
+          <t xml:space="preserve">Secondary Sports Day Rehearsal #2</t>
         </is>
       </c>
       <c r="J82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">日本文化デー</t>
+          <t xml:space="preserve">中等部運動会リハーサル #2</t>
         </is>
       </c>
       <c r="K82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will deepen their understanding and appreciation of Japanese culture through a variety of interactive activities with school community.</t>
+          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
         </is>
       </c>
       <c r="L82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学校コミュニティとともにさまざまな体験型の活動に取り組み、日本文化への理解と関心を深めます。</t>
+          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
         </is>
       </c>
       <c r="M82" t="inlineStr" s="2">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="O82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-18-japanese-culture-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-12-secondary-sports-day-rehearsal-2.webp</t>
         </is>
       </c>
       <c r="P82" t="inlineStr" s="2">
@@ -8036,19 +8036,19 @@
     <row r="83">
       <c r="A83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-19-eagle-bucks-store</t>
+          <t xml:space="preserve">2027-03-15-clubs-pause</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="3">
         <is>
+          <t xml:space="preserve">2027-03-15</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr" s="3">
+        <is>
           <t xml:space="preserve">2027-03-19</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">2027-03-19</t>
-        </is>
-      </c>
       <c r="D83" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve"/>
@@ -8056,7 +8056,7 @@
       </c>
       <c r="E83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F83" t="inlineStr" s="2">
@@ -8076,22 +8076,22 @@
       </c>
       <c r="I83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Eagle Bucks Store</t>
+          <t xml:space="preserve">Clubs Pause</t>
         </is>
       </c>
       <c r="J83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">イーグルバックス・ストア</t>
+          <t xml:space="preserve">クラブ活動休止</t>
         </is>
       </c>
       <c r="K83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
+          <t xml:space="preserve">After-school clubs are paused during this period. Bus reminder: the afternoon Red bus runs only on club days, so it does not run while clubs are paused. Please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
         </is>
       </c>
       <c r="L83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
+          <t xml:space="preserve">この期間、放課後のクラブ活動はお休みです。【バスについて】午後の赤バスはクラブ活動がある日のみ運行するため、休止期間中は運行しません。午後の下校時は青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
         </is>
       </c>
       <c r="M83" t="inlineStr" s="2">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="O83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-19-eagle-bucks-store.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P83" t="inlineStr" s="2">
@@ -8133,17 +8133,17 @@
     <row r="84">
       <c r="A84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-19-tea-party-pta-for-all</t>
+          <t xml:space="preserve">2027-03-18-japanese-culture-day</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-19</t>
+          <t xml:space="preserve">2027-03-18</t>
         </is>
       </c>
       <c r="C84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-19</t>
+          <t xml:space="preserve">2027-03-18</t>
         </is>
       </c>
       <c r="D84" t="inlineStr" s="3">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="E84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTA</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F84" t="inlineStr" s="2">
@@ -8173,22 +8173,22 @@
       </c>
       <c r="I84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Tea Party / PTA for all</t>
+          <t xml:space="preserve">Japanese Culture Day</t>
         </is>
       </c>
       <c r="J84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTAティーパーティー（どなたでも参加できます）</t>
+          <t xml:space="preserve">日本文化デー</t>
         </is>
       </c>
       <c r="K84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A social gathering organized by the PTA and Community Club where staff and students are welcome to enjoy a variety of teas, snacks, and friendly conversation together.</t>
+          <t xml:space="preserve">Students will deepen their understanding and appreciation of Japanese culture through a variety of interactive activities with school community.</t>
         </is>
       </c>
       <c r="L84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTAとコミュニティクラブが主催する交流会です。教職員や生徒も参加でき、さまざまなお茶や軽食、和やかな会話を楽しめます。</t>
+          <t xml:space="preserve">学校コミュニティとともにさまざまな体験型の活動に取り組み、日本文化への理解と関心を深めます。</t>
         </is>
       </c>
       <c r="M84" t="inlineStr" s="2">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="O84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-19-tea-party-pta-for-all.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-18-japanese-culture-day.webp</t>
         </is>
       </c>
       <c r="P84" t="inlineStr" s="2">
@@ -8230,7 +8230,7 @@
     <row r="85">
       <c r="A85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-19-end-of-term-2-activity-g9-12</t>
+          <t xml:space="preserve">2027-03-19-eagle-bucks-store</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="3">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="C85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-20</t>
+          <t xml:space="preserve">2027-03-19</t>
         </is>
       </c>
       <c r="D85" t="inlineStr" s="3">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="E85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr" s="2">
@@ -8270,22 +8270,22 @@
       </c>
       <c r="I85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">End of Term 2 Activity: G9-12</t>
+          <t xml:space="preserve">Eagle Bucks Store</t>
         </is>
       </c>
       <c r="J85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第2学期末行事：G9–12</t>
+          <t xml:space="preserve">イーグルバックス・ストア</t>
         </is>
       </c>
       <c r="K85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in an off-campus day trip activity to celebrate the end of Term 2.</t>
+          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
         </is>
       </c>
       <c r="L85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第2学期の終わりを祝い、校外への日帰り活動に参加します。</t>
+          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
         </is>
       </c>
       <c r="M85" t="inlineStr" s="2">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="O85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-19-end-of-term-2-activity-g9-12.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-19-eagle-bucks-store.webp</t>
         </is>
       </c>
       <c r="P85" t="inlineStr" s="2">
@@ -8327,17 +8327,17 @@
     <row r="86">
       <c r="A86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-20-end-of-term-2-activity-g6-8</t>
+          <t xml:space="preserve">2027-03-19-tea-party-pta-for-all</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-20</t>
+          <t xml:space="preserve">2027-03-19</t>
         </is>
       </c>
       <c r="C86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-21</t>
+          <t xml:space="preserve">2027-03-19</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="3">
@@ -8347,12 +8347,12 @@
       </c>
       <c r="E86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">PTA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G86" t="inlineStr" s="2">
@@ -8367,22 +8367,22 @@
       </c>
       <c r="I86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">End of Term 2 Activity: G6-8</t>
+          <t xml:space="preserve">Tea Party / PTA for all</t>
         </is>
       </c>
       <c r="J86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第2学期末行事：G6–8</t>
+          <t xml:space="preserve">PTAティーパーティー（どなたでも参加できます）</t>
         </is>
       </c>
       <c r="K86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in an overnight camp at an off-campus camping facility to celebrate the end of Term 2.</t>
+          <t xml:space="preserve">A social gathering organized by the PTA and Community Club where staff and students are welcome to enjoy a variety of teas, snacks, and friendly conversation together.</t>
         </is>
       </c>
       <c r="L86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第2学期の終わりを祝い、校外のキャンプ施設での一泊キャンプに参加します。</t>
+          <t xml:space="preserve">PTAとコミュニティクラブが主催する交流会です。教職員や生徒も参加でき、さまざまなお茶や軽食、和やかな会話を楽しめます。</t>
         </is>
       </c>
       <c r="M86" t="inlineStr" s="2">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="O86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-20-end-of-term-2-activity-g6-8.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-19-tea-party-pta-for-all.webp</t>
         </is>
       </c>
       <c r="P86" t="inlineStr" s="2">
@@ -8424,17 +8424,17 @@
     <row r="87">
       <c r="A87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-30-parent-teacher-conferences</t>
+          <t xml:space="preserve">2027-03-19-end-of-term-2-activity-g9-12</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-30</t>
+          <t xml:space="preserve">2027-03-19</t>
         </is>
       </c>
       <c r="C87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-30</t>
+          <t xml:space="preserve">2027-03-20</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="3">
@@ -8444,17 +8444,17 @@
       </c>
       <c r="E87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H87" t="inlineStr" s="2">
@@ -8464,22 +8464,22 @@
       </c>
       <c r="I87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parent Teacher Conferences</t>
+          <t xml:space="preserve">End of Term 2 Activity: G9-12</t>
         </is>
       </c>
       <c r="J87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者面談</t>
+          <t xml:space="preserve">第2学期末行事：G9–12</t>
         </is>
       </c>
       <c r="K87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on this day.</t>
+          <t xml:space="preserve">Students will take part in an off-campus day trip activity to celebrate the end of Term 2.</t>
         </is>
       </c>
       <c r="L87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。当日、生徒は登校しません。</t>
+          <t xml:space="preserve">第2学期の終わりを祝い、校外への日帰り活動に参加します。</t>
         </is>
       </c>
       <c r="M87" t="inlineStr" s="2">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="O87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-30-parent-teacher-conferences.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-19-end-of-term-2-activity-g9-12.webp</t>
         </is>
       </c>
       <c r="P87" t="inlineStr" s="2">
@@ -8521,17 +8521,17 @@
     <row r="88">
       <c r="A88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-31-secondary-sports-day-rehearsal-3</t>
+          <t xml:space="preserve">2027-03-20-end-of-term-2-activity-g6-8</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-31</t>
+          <t xml:space="preserve">2027-03-20</t>
         </is>
       </c>
       <c r="C88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-31</t>
+          <t xml:space="preserve">2027-03-21</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="3">
@@ -8561,22 +8561,22 @@
       </c>
       <c r="I88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary Sports Day Rehearsal #3</t>
+          <t xml:space="preserve">End of Term 2 Activity: G6-8</t>
         </is>
       </c>
       <c r="J88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部運動会リハーサル #3</t>
+          <t xml:space="preserve">第2学期末行事：G6–8</t>
         </is>
       </c>
       <c r="K88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
+          <t xml:space="preserve">Students will take part in an overnight camp at an off-campus camping facility to celebrate the end of Term 2.</t>
         </is>
       </c>
       <c r="L88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
+          <t xml:space="preserve">第2学期の終わりを祝い、校外のキャンプ施設での一泊キャンプに参加します。</t>
         </is>
       </c>
       <c r="M88" t="inlineStr" s="2">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="O88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-31-secondary-sports-day-rehearsal-3.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-20-end-of-term-2-activity-g6-8.webp</t>
         </is>
       </c>
       <c r="P88" t="inlineStr" s="2">
@@ -8618,17 +8618,17 @@
     <row r="89">
       <c r="A89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-01-primary-sports-day-rehearsal-3</t>
+          <t xml:space="preserve">2027-03-30-parent-teacher-conferences</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-01</t>
+          <t xml:space="preserve">2027-03-30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-01</t>
+          <t xml:space="preserve">2027-03-30</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="3">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="E89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="H89" t="inlineStr" s="2">
@@ -8658,22 +8658,22 @@
       </c>
       <c r="I89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary Sports Day Rehearsal #3</t>
+          <t xml:space="preserve">Parent Teacher Conferences</t>
         </is>
       </c>
       <c r="J89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小学部運動会リハーサル #3</t>
+          <t xml:space="preserve">保護者面談</t>
         </is>
       </c>
       <c r="K89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The final rehearsal provides students with an opportunity to practice events and ensure they are ready for Sports Day.</t>
+          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on this day.</t>
         </is>
       </c>
       <c r="L89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">最終リハーサルで各種目を練習し、運動会当日に向けて準備を整えます。</t>
+          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。当日、生徒は登校しません。</t>
         </is>
       </c>
       <c r="M89" t="inlineStr" s="2">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="O89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-01-primary-sports-day-rehearsal-3.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-30-parent-teacher-conferences.webp</t>
         </is>
       </c>
       <c r="P89" t="inlineStr" s="2">
@@ -8715,17 +8715,17 @@
     <row r="90">
       <c r="A90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-03-sports-day</t>
+          <t xml:space="preserve">2027-03-31-secondary-sports-day-rehearsal-3</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-03</t>
+          <t xml:space="preserve">2027-03-31</t>
         </is>
       </c>
       <c r="C90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-03</t>
+          <t xml:space="preserve">2027-03-31</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="3">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="F90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G90" t="inlineStr" s="2">
@@ -8755,22 +8755,22 @@
       </c>
       <c r="I90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sports Day</t>
+          <t xml:space="preserve">Secondary Sports Day Rehearsal #3</t>
         </is>
       </c>
       <c r="J90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会</t>
+          <t xml:space="preserve">中等部運動会リハーサル #3</t>
         </is>
       </c>
       <c r="K90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in Sports Day activities, participating in team games, athletic challenges, and school spirit events.</t>
+          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
         </is>
       </c>
       <c r="L90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会に参加し、チームゲーム、運動競技、応援などの行事に取り組みます。</t>
+          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
         </is>
       </c>
       <c r="M90" t="inlineStr" s="2">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="O90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-03-sports-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-31-secondary-sports-day-rehearsal-3.webp</t>
         </is>
       </c>
       <c r="P90" t="inlineStr" s="2">
@@ -8812,17 +8812,17 @@
     <row r="91">
       <c r="A91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-03-primary-sports-day-2027</t>
+          <t xml:space="preserve">2027-03-31-clubs-pause</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-03</t>
+          <t xml:space="preserve">2027-03-31</t>
         </is>
       </c>
       <c r="C91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-03</t>
+          <t xml:space="preserve">2027-04-02</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="3">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="E91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G91" t="inlineStr" s="2">
@@ -8852,22 +8852,22 @@
       </c>
       <c r="I91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary Sports Day 2027</t>
+          <t xml:space="preserve">Clubs Pause</t>
         </is>
       </c>
       <c r="J91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小学部運動会 2027</t>
+          <t xml:space="preserve">クラブ活動休止</t>
         </is>
       </c>
       <c r="K91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students participate in a day of fun, fitness, and friendly competition while demonstrating teamwork, perseverance, and sportsmanship.</t>
+          <t xml:space="preserve">After-school clubs are paused during this period. Bus reminder: the afternoon Red bus runs only on club days, so it does not run while clubs are paused. Please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
         </is>
       </c>
       <c r="L91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">チームワーク、粘り強さ、スポーツマンシップを発揮しながら、楽しく体を動かし、仲間と競い合う一日を過ごします。</t>
+          <t xml:space="preserve">この期間、放課後のクラブ活動はお休みです。【バスについて】午後の赤バスはクラブ活動がある日のみ運行するため、休止期間中は運行しません。午後の下校時は青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
         </is>
       </c>
       <c r="M91" t="inlineStr" s="2">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="O91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-03-primary-sports-day-2027.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P91" t="inlineStr" s="2">
@@ -8909,17 +8909,17 @@
     <row r="92">
       <c r="A92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-05-clubs-resume</t>
+          <t xml:space="preserve">2027-04-01-primary-sports-day-rehearsal-3</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-05</t>
+          <t xml:space="preserve">2027-04-01</t>
         </is>
       </c>
       <c r="C92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-05</t>
+          <t xml:space="preserve">2027-04-01</t>
         </is>
       </c>
       <c r="D92" t="inlineStr" s="3">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="E92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F92" t="inlineStr" s="2">
@@ -8949,22 +8949,22 @@
       </c>
       <c r="I92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Clubs Resume</t>
+          <t xml:space="preserve">Primary Sports Day Rehearsal #3</t>
         </is>
       </c>
       <c r="J92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クラブ活動再開</t>
+          <t xml:space="preserve">小学部運動会リハーサル #3</t>
         </is>
       </c>
       <c r="K92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">After-school clubs start again today. Bus reminder: the afternoon Red bus runs only on club days. On other days, please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
+          <t xml:space="preserve">The final rehearsal provides students with an opportunity to practice events and ensure they are ready for Sports Day.</t>
         </is>
       </c>
       <c r="L92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">本日から放課後のクラブ活動が再開します。【バスについて】午後の赤バスはクラブ活動がある日のみ運行します。それ以外の日は、午後の下校時に青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
+          <t xml:space="preserve">最終リハーサルで各種目を練習し、運動会当日に向けて準備を整えます。</t>
         </is>
       </c>
       <c r="M92" t="inlineStr" s="2">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="O92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">compass/images/events/2027-04-01-primary-sports-day-rehearsal-3.webp</t>
         </is>
       </c>
       <c r="P92" t="inlineStr" s="2">
@@ -9006,17 +9006,17 @@
     <row r="93">
       <c r="A93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-15-world-art-day</t>
+          <t xml:space="preserve">2027-04-03-sports-day</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-15</t>
+          <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
       <c r="C93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-15</t>
+          <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="3">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="E93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F93" t="inlineStr" s="2">
@@ -9046,22 +9046,22 @@
       </c>
       <c r="I93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">World Art Day</t>
+          <t xml:space="preserve">Sports Day</t>
         </is>
       </c>
       <c r="J93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ワールド・アート・デー</t>
+          <t xml:space="preserve">運動会</t>
         </is>
       </c>
       <c r="K93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students celebrate creativity through art activities, exhibitions, and opportunities to explore different artistic styles and cultures.</t>
+          <t xml:space="preserve">Students will take part in Sports Day activities, participating in team games, athletic challenges, and school spirit events.</t>
         </is>
       </c>
       <c r="L93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">アート活動や展示を通して創造性を祝い、さまざまな芸術様式や文化に触れます。</t>
+          <t xml:space="preserve">運動会に参加し、チームゲーム、運動競技、応援などの行事に取り組みます。</t>
         </is>
       </c>
       <c r="M93" t="inlineStr" s="2">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="O93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-15-world-art-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-03-sports-day.webp</t>
         </is>
       </c>
       <c r="P93" t="inlineStr" s="2">
@@ -9103,17 +9103,17 @@
     <row r="94">
       <c r="A94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-16-foundation-field-trip</t>
+          <t xml:space="preserve">2027-04-03-primary-sports-day-2027</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-16</t>
+          <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
       <c r="C94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-16</t>
+          <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="3">
@@ -9143,22 +9143,22 @@
       </c>
       <c r="I94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Foundation Field Trip</t>
+          <t xml:space="preserve">Primary Sports Day 2027</t>
         </is>
       </c>
       <c r="J94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ファウンデーション校外学習</t>
+          <t xml:space="preserve">小学部運動会 2027</t>
         </is>
       </c>
       <c r="K94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Our youngest learners will enjoy an age-appropriate educational excursion that supports classroom learning through hands-on experiences.</t>
+          <t xml:space="preserve">Students participate in a day of fun, fitness, and friendly competition while demonstrating teamwork, perseverance, and sportsmanship.</t>
         </is>
       </c>
       <c r="L94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">年少の子どもたちが、年齢に合った校外学習に出かけ、体験を通して教室での学びを深めます。</t>
+          <t xml:space="preserve">チームワーク、粘り強さ、スポーツマンシップを発揮しながら、楽しく体を動かし、仲間と競い合う一日を過ごします。</t>
         </is>
       </c>
       <c r="M94" t="inlineStr" s="2">
@@ -9173,7 +9173,7 @@
       </c>
       <c r="O94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-16-foundation-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-03-primary-sports-day-2027.webp</t>
         </is>
       </c>
       <c r="P94" t="inlineStr" s="2">
@@ -9200,17 +9200,17 @@
     <row r="95">
       <c r="A95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-21-hackathon-hour-of-code</t>
+          <t xml:space="preserve">2027-04-05-clubs-resume</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-21</t>
+          <t xml:space="preserve">2027-04-05</t>
         </is>
       </c>
       <c r="C95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-21</t>
+          <t xml:space="preserve">2027-04-05</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="3">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="E95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F95" t="inlineStr" s="2">
@@ -9240,22 +9240,22 @@
       </c>
       <c r="I95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hackathon (Hour of Code)</t>
+          <t xml:space="preserve">Clubs Resume</t>
         </is>
       </c>
       <c r="J95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ハッカソン（Hour of Code）</t>
+          <t xml:space="preserve">クラブ活動再開</t>
         </is>
       </c>
       <c r="K95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in an engaging Hour of Code challenge, using creativity and problem-solving skills to build simple coding projects. This event encourages computational thinking, teamwork, and confidence in technology in a fun and supportive environment.</t>
+          <t xml:space="preserve">After-school clubs start again today. Bus reminder: the afternoon Red bus runs only on club days. On other days, please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
         </is>
       </c>
       <c r="L95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hour of Codeチャレンジに参加し、創造性と問題解決力を生かして簡単なプログラミング作品を作ります。楽しく支え合う環境の中で、コンピュテーショナル・シンキング、チームワーク、テクノロジーへの自信を育みます。</t>
+          <t xml:space="preserve">本日から放課後のクラブ活動が再開します。【バスについて】午後の赤バスはクラブ活動がある日のみ運行します。それ以外の日は、午後の下校時に青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
         </is>
       </c>
       <c r="M95" t="inlineStr" s="2">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="O95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-21-hackathon-hour-of-code.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P95" t="inlineStr" s="2">
@@ -9297,17 +9297,17 @@
     <row r="96">
       <c r="A96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-22-biology-ia-prep-field-trip-shore-ecosystem</t>
+          <t xml:space="preserve">2027-04-15-world-art-day</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-22</t>
+          <t xml:space="preserve">2027-04-15</t>
         </is>
       </c>
       <c r="C96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-22</t>
+          <t xml:space="preserve">2027-04-15</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="3">
@@ -9317,12 +9317,12 @@
       </c>
       <c r="E96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G96" t="inlineStr" s="2">
@@ -9337,22 +9337,22 @@
       </c>
       <c r="I96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Biology IA Prep. Field Trip: Shore Ecosystem</t>
+          <t xml:space="preserve">World Art Day</t>
         </is>
       </c>
       <c r="J96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">生物IA準備校外学習：海岸生態系調査</t>
+          <t xml:space="preserve">ワールド・アート・デー</t>
         </is>
       </c>
       <c r="K96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 11 and 12 Biology students will visit a shore ecosystem to prepare for their Biology Internal Assessment by collecting fieldwork data and practicing research methods.</t>
+          <t xml:space="preserve">Students celebrate creativity through art activities, exhibitions, and opportunities to explore different artistic styles and cultures.</t>
         </is>
       </c>
       <c r="L96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11・12年生の生物履修者が海岸の生態系を訪れ、フィールドワークでのデータ収集や研究手法の練習を通して、生物の内部評価（IA）に向けた準備を行います。</t>
+          <t xml:space="preserve">アート活動や展示を通して創造性を祝い、さまざまな芸術様式や文化に触れます。</t>
         </is>
       </c>
       <c r="M96" t="inlineStr" s="2">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="O96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-22-biology-ia-prep-field-trip-shore-ecosystem.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-15-world-art-day.webp</t>
         </is>
       </c>
       <c r="P96" t="inlineStr" s="2">
@@ -9394,17 +9394,17 @@
     <row r="97">
       <c r="A97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-23-g12-celebration</t>
+          <t xml:space="preserve">2027-04-16-foundation-field-trip</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-23</t>
+          <t xml:space="preserve">2027-04-16</t>
         </is>
       </c>
       <c r="C97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-23</t>
+          <t xml:space="preserve">2027-04-16</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="3">
@@ -9414,12 +9414,12 @@
       </c>
       <c r="E97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G97" t="inlineStr" s="2">
@@ -9434,22 +9434,22 @@
       </c>
       <c r="I97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G12 Celebration</t>
+          <t xml:space="preserve">Foundation Field Trip</t>
         </is>
       </c>
       <c r="J97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G12修了記念イベント</t>
+          <t xml:space="preserve">ファウンデーション校外学習</t>
         </is>
       </c>
       <c r="K97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 12 students will take part in a Graduation Walk as the school community celebrates them ahead of graduation.</t>
+          <t xml:space="preserve">Our youngest learners will enjoy an age-appropriate educational excursion that supports classroom learning through hands-on experiences.</t>
         </is>
       </c>
       <c r="L97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">卒業を前に、12年生がグラデュエーション・ウォークに参加し、学校コミュニティ全体でお祝いします。</t>
+          <t xml:space="preserve">年少の子どもたちが、年齢に合った校外学習に出かけ、体験を通して教室での学びを深めます。</t>
         </is>
       </c>
       <c r="M97" t="inlineStr" s="2">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="O97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-23-g12-celebration.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-16-foundation-field-trip.webp</t>
         </is>
       </c>
       <c r="P97" t="inlineStr" s="2">
@@ -9491,17 +9491,17 @@
     <row r="98">
       <c r="A98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-26-grade-4-5-camping-trip</t>
+          <t xml:space="preserve">2027-04-21-hackathon-hour-of-code</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-26</t>
+          <t xml:space="preserve">2027-04-21</t>
         </is>
       </c>
       <c r="C98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-27</t>
+          <t xml:space="preserve">2027-04-21</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="3">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="E98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F98" t="inlineStr" s="2">
@@ -9531,22 +9531,22 @@
       </c>
       <c r="I98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 4, 5 Camping Trip</t>
+          <t xml:space="preserve">Hackathon (Hour of Code)</t>
         </is>
       </c>
       <c r="J98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4・5年生キャンプ</t>
+          <t xml:space="preserve">ハッカソン（Hour of Code）</t>
         </is>
       </c>
       <c r="K98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students enjoy an outdoor learning experience that promotes independence, teamwork, resilience, and a connection with nature.</t>
+          <t xml:space="preserve">Students will take part in an engaging Hour of Code challenge, using creativity and problem-solving skills to build simple coding projects. This event encourages computational thinking, teamwork, and confidence in technology in a fun and supportive environment.</t>
         </is>
       </c>
       <c r="L98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">自立心、チームワーク、たくましさ、自然とのつながりを育む野外学習を楽しみます。</t>
+          <t xml:space="preserve">Hour of Codeチャレンジに参加し、創造性と問題解決力を生かして簡単なプログラミング作品を作ります。楽しく支え合う環境の中で、コンピュテーショナル・シンキング、チームワーク、テクノロジーへの自信を育みます。</t>
         </is>
       </c>
       <c r="M98" t="inlineStr" s="2">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="O98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-26-grade-4-5-camping-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-21-hackathon-hour-of-code.webp</t>
         </is>
       </c>
       <c r="P98" t="inlineStr" s="2">
@@ -9588,17 +9588,17 @@
     <row r="99">
       <c r="A99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-27-choir-and-orchestra-concert</t>
+          <t xml:space="preserve">2027-04-22-biology-ia-prep-field-trip-shore-ecosystem</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-27</t>
+          <t xml:space="preserve">2027-04-22</t>
         </is>
       </c>
       <c r="C99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-27</t>
+          <t xml:space="preserve">2027-04-22</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="3">
@@ -9608,12 +9608,12 @@
       </c>
       <c r="E99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G99" t="inlineStr" s="2">
@@ -9628,22 +9628,22 @@
       </c>
       <c r="I99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choir and Orchestra Concert</t>
+          <t xml:space="preserve">Biology IA Prep. Field Trip: Shore Ecosystem</t>
         </is>
       </c>
       <c r="J99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合唱・オーケストラコンサート</t>
+          <t xml:space="preserve">生物IA準備校外学習：海岸生態系調査</t>
         </is>
       </c>
       <c r="K99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choir class and orchestra club will perform the music repertoire they have been rehearsing for an audience of family, peers and teachers.</t>
+          <t xml:space="preserve">Grade 11 and 12 Biology students will visit a shore ecosystem to prepare for their Biology Internal Assessment by collecting fieldwork data and practicing research methods.</t>
         </is>
       </c>
       <c r="L99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合唱クラスとオーケストラクラブが、練習を重ねてきた曲目をご家族、友人、教員の前で演奏します。</t>
+          <t xml:space="preserve">11・12年生の生物履修者が海岸の生態系を訪れ、フィールドワークでのデータ収集や研究手法の練習を通して、生物の内部評価（IA）に向けた準備を行います。</t>
         </is>
       </c>
       <c r="M99" t="inlineStr" s="2">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="O99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-27-choir-and-orchestra-concert.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-22-biology-ia-prep-field-trip-shore-ecosystem.webp</t>
         </is>
       </c>
       <c r="P99" t="inlineStr" s="2">
@@ -9685,17 +9685,17 @@
     <row r="100">
       <c r="A100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-30-science-fair</t>
+          <t xml:space="preserve">2027-04-23-g12-celebration</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-30</t>
+          <t xml:space="preserve">2027-04-23</t>
         </is>
       </c>
       <c r="C100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-30</t>
+          <t xml:space="preserve">2027-04-23</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="3">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="E100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G100" t="inlineStr" s="2">
@@ -9725,22 +9725,22 @@
       </c>
       <c r="I100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Science Fair</t>
+          <t xml:space="preserve">G12 Celebration</t>
         </is>
       </c>
       <c r="J100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">サイエンスフェア</t>
+          <t xml:space="preserve">G12修了記念イベント</t>
         </is>
       </c>
       <c r="K100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will share their science projects and investigations with the school community, showcasing their research, creativity, and scientific thinking.</t>
+          <t xml:space="preserve">Grade 12 students will take part in a Graduation Walk as the school community celebrates them ahead of graduation.</t>
         </is>
       </c>
       <c r="L100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">理科のプロジェクトや探究の成果を学校コミュニティに発表し、研究、創造性、科学的思考を披露します。</t>
+          <t xml:space="preserve">卒業を前に、12年生がグラデュエーション・ウォークに参加し、学校コミュニティ全体でお祝いします。</t>
         </is>
       </c>
       <c r="M100" t="inlineStr" s="2">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="O100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-30-science-fair.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-23-g12-celebration.webp</t>
         </is>
       </c>
       <c r="P100" t="inlineStr" s="2">
@@ -9782,17 +9782,17 @@
     <row r="101">
       <c r="A101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-17-friendly-basketball-tournament-internal</t>
+          <t xml:space="preserve">2027-04-26-grade-4-5-camping-trip</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-17</t>
+          <t xml:space="preserve">2027-04-26</t>
         </is>
       </c>
       <c r="C101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-21</t>
+          <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="3">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="E101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F101" t="inlineStr" s="2">
@@ -9822,22 +9822,22 @@
       </c>
       <c r="I101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Friendly Basketball Tournament (Internal)</t>
+          <t xml:space="preserve">Grade 4, 5 Camping Trip</t>
         </is>
       </c>
       <c r="J101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内バスケットボール大会</t>
+          <t xml:space="preserve">4・5年生キャンプ</t>
         </is>
       </c>
       <c r="K101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in a friendly internal basketball tournament, promoting teamwork, sportsmanship, and school spirit.</t>
+          <t xml:space="preserve">Students enjoy an outdoor learning experience that promotes independence, teamwork, resilience, and a connection with nature.</t>
         </is>
       </c>
       <c r="L101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内バスケットボール大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
+          <t xml:space="preserve">自立心、チームワーク、たくましさ、自然とのつながりを育む野外学習を楽しみます。</t>
         </is>
       </c>
       <c r="M101" t="inlineStr" s="2">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="O101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-17-friendly-basketball-tournament-internal.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-26-grade-4-5-camping-trip.webp</t>
         </is>
       </c>
       <c r="P101" t="inlineStr" s="2">
@@ -9879,17 +9879,17 @@
     <row r="102">
       <c r="A102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-19-entrepreneurs-day</t>
+          <t xml:space="preserve">2027-04-27-choir-and-orchestra-concert</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-19</t>
+          <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
       <c r="C102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-20</t>
+          <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="3">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="E102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F102" t="inlineStr" s="2">
@@ -9919,22 +9919,22 @@
       </c>
       <c r="I102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Entrepreneurs Day</t>
+          <t xml:space="preserve">Choir and Orchestra Concert</t>
         </is>
       </c>
       <c r="J102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">アントレプレナーシップ・デー</t>
+          <t xml:space="preserve">合唱・オーケストラコンサート</t>
         </is>
       </c>
       <c r="K102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students develop and showcase business ideas while learning about creativity, financial literacy, problem-solving, and entrepreneurship.</t>
+          <t xml:space="preserve">Choir class and orchestra club will perform the music repertoire they have been rehearsing for an audience of family, peers and teachers.</t>
         </is>
       </c>
       <c r="L102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">創造性、金融リテラシー、問題解決、起業家精神について学びながら、ビジネスのアイデアを考え、発表します。</t>
+          <t xml:space="preserve">合唱クラスとオーケストラクラブが、練習を重ねてきた曲目をご家族、友人、教員の前で演奏します。</t>
         </is>
       </c>
       <c r="M102" t="inlineStr" s="2">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="O102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-19-entrepreneurs-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-27-choir-and-orchestra-concert.webp</t>
         </is>
       </c>
       <c r="P102" t="inlineStr" s="2">
@@ -9976,17 +9976,17 @@
     <row r="103">
       <c r="A103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-21-collective-field-trip</t>
+          <t xml:space="preserve">2027-04-30-science-fair</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-21</t>
+          <t xml:space="preserve">2027-04-30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-21</t>
+          <t xml:space="preserve">2027-04-30</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="3">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="E103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G103" t="inlineStr" s="2">
@@ -10016,22 +10016,22 @@
       </c>
       <c r="I103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Collective Field Trip</t>
+          <t xml:space="preserve">Science Fair</t>
         </is>
       </c>
       <c r="J103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合同校外学習</t>
+          <t xml:space="preserve">サイエンスフェア</t>
         </is>
       </c>
       <c r="K103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students participate in a shared educational experience that promotes collaboration, inquiry, and real-world learning.</t>
+          <t xml:space="preserve">Students will share their science projects and investigations with the school community, showcasing their research, creativity, and scientific thinking.</t>
         </is>
       </c>
       <c r="L103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">協働、探究、実社会での学びを促す合同の学習体験に参加します。</t>
+          <t xml:space="preserve">理科のプロジェクトや探究の成果を学校コミュニティに発表し、研究、創造性、科学的思考を披露します。</t>
         </is>
       </c>
       <c r="M103" t="inlineStr" s="2">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="O103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-21-collective-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-30-science-fair.webp</t>
         </is>
       </c>
       <c r="P103" t="inlineStr" s="2">
@@ -10073,17 +10073,17 @@
     <row r="104">
       <c r="A104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-22-saturday-school-last-day-event</t>
+          <t xml:space="preserve">2027-05-17-friendly-basketball-tournament-internal</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-05-17</t>
         </is>
       </c>
       <c r="C104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="3">
@@ -10113,22 +10113,22 @@
       </c>
       <c r="I104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saturday School Last Day Event</t>
+          <t xml:space="preserve">Friendly Basketball Tournament (Internal)</t>
         </is>
       </c>
       <c r="J104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">土曜校最終日イベント</t>
+          <t xml:space="preserve">校内バスケットボール大会</t>
         </is>
       </c>
       <c r="K104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in a relaxed final Saturday School session, with leisure activities at school to celebrate the last day.</t>
+          <t xml:space="preserve">Students will take part in a friendly internal basketball tournament, promoting teamwork, sportsmanship, and school spirit.</t>
         </is>
       </c>
       <c r="L104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">土曜校の最終日を、校内でのレクリエーション活動とともにリラックスして過ごし、お祝いします。</t>
+          <t xml:space="preserve">校内バスケットボール大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
         </is>
       </c>
       <c r="M104" t="inlineStr" s="2">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="O104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-22-saturday-school-last-day-event.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-17-friendly-basketball-tournament-internal.webp</t>
         </is>
       </c>
       <c r="P104" t="inlineStr" s="2">
@@ -10170,17 +10170,17 @@
     <row r="105">
       <c r="A105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-24-concept-con-future-focus</t>
+          <t xml:space="preserve">2027-05-19-entrepreneurs-day</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-24</t>
+          <t xml:space="preserve">2027-05-19</t>
         </is>
       </c>
       <c r="C105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-28</t>
+          <t xml:space="preserve">2027-05-20</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="3">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="F105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G105" t="inlineStr" s="2">
@@ -10210,22 +10210,22 @@
       </c>
       <c r="I105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Concept Con (Future Focus)</t>
+          <t xml:space="preserve">Entrepreneurs Day</t>
         </is>
       </c>
       <c r="J105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">コンセプト・コン（未来を考える）</t>
+          <t xml:space="preserve">アントレプレナーシップ・デー</t>
         </is>
       </c>
       <c r="K105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students investigate future possibilities, innovations, and solutions to real-world challenges through inquiry-based projects and presentations.</t>
+          <t xml:space="preserve">Students develop and showcase business ideas while learning about creativity, financial literacy, problem-solving, and entrepreneurship.</t>
         </is>
       </c>
       <c r="L105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">探究型のプロジェクトや発表を通して、未来の可能性、イノベーション、現実の課題の解決策について考えます。</t>
+          <t xml:space="preserve">創造性、金融リテラシー、問題解決、起業家精神について学びながら、ビジネスのアイデアを考え、発表します。</t>
         </is>
       </c>
       <c r="M105" t="inlineStr" s="2">
@@ -10240,7 +10240,7 @@
       </c>
       <c r="O105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-24-concept-con-future-focus.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-19-entrepreneurs-day.webp</t>
         </is>
       </c>
       <c r="P105" t="inlineStr" s="2">
@@ -10267,17 +10267,17 @@
     <row r="106">
       <c r="A106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-28-g12-graduation-with-performances</t>
+          <t xml:space="preserve">2027-05-21-collective-field-trip</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-29</t>
+          <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
       <c r="C106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-29</t>
+          <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="3">
@@ -10287,12 +10287,12 @@
       </c>
       <c r="E106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G106" t="inlineStr" s="2">
@@ -10302,27 +10302,27 @@
       </c>
       <c r="H106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">changed</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G12 Graduation with Performances</t>
+          <t xml:space="preserve">Collective Field Trip</t>
         </is>
       </c>
       <c r="J106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G12卒業式・記念パフォーマンス</t>
+          <t xml:space="preserve">合同校外学習</t>
         </is>
       </c>
       <c r="K106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 12 students will celebrate their graduation with a formal ceremony featuring student performances and the wider school community.</t>
+          <t xml:space="preserve">Students participate in a shared educational experience that promotes collaboration, inquiry, and real-world learning.</t>
         </is>
       </c>
       <c r="L106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12年生が、生徒によるパフォーマンスを交えた式典で、学校コミュニティ全体とともに卒業を祝います。</t>
+          <t xml:space="preserve">協働、探究、実社会での学びを促す合同の学習体験に参加します。</t>
         </is>
       </c>
       <c r="M106" t="inlineStr" s="2">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="O106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-28-g12-graduation-with-performances.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-21-collective-field-trip.webp</t>
         </is>
       </c>
       <c r="P106" t="inlineStr" s="2">
@@ -10364,17 +10364,17 @@
     <row r="107">
       <c r="A107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-03-celebration-of-learning-prep</t>
+          <t xml:space="preserve">2027-05-22-saturday-school-last-day-event</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-03</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="C107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-03</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="3">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="E107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="2">
@@ -10404,22 +10404,22 @@
       </c>
       <c r="I107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Celebration of Learning Prep</t>
+          <t xml:space="preserve">Saturday School Last Day Event</t>
         </is>
       </c>
       <c r="J107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学びの発表会準備</t>
+          <t xml:space="preserve">土曜校最終日イベント</t>
         </is>
       </c>
       <c r="K107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students help prepare the school for the Celebration of Learning by organizing learning spaces, setting up displays, arranging materials, and ensuring classrooms and common areas are ready to welcome visitors. This preparation helps create an engaging and welcoming environment for families and guests.</t>
+          <t xml:space="preserve">Students will take part in a relaxed final Saturday School session, with leisure activities at school to celebrate the last day.</t>
         </is>
       </c>
       <c r="L107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学びの発表会に向けて、学習スペースの整理、展示の設営、資料の準備を行い、教室や共用エリアで来場者をお迎えできるよう整えます。ご家族やお客様にとって魅力的で温かな空間づくりにつながります。</t>
+          <t xml:space="preserve">土曜校の最終日を、校内でのレクリエーション活動とともにリラックスして過ごし、お祝いします。</t>
         </is>
       </c>
       <c r="M107" t="inlineStr" s="2">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="O107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-03-celebration-of-learning-prep.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-22-saturday-school-last-day-event.webp</t>
         </is>
       </c>
       <c r="P107" t="inlineStr" s="2">
@@ -10461,17 +10461,17 @@
     <row r="108">
       <c r="A108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-03-ukulele-concert</t>
+          <t xml:space="preserve">2027-05-24-concept-con-future-focus</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-03</t>
+          <t xml:space="preserve">2027-05-24</t>
         </is>
       </c>
       <c r="C108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-04</t>
+          <t xml:space="preserve">2027-05-28</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="3">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="E108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G108" t="inlineStr" s="2">
@@ -10501,22 +10501,22 @@
       </c>
       <c r="I108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ukulele Concert</t>
+          <t xml:space="preserve">Concept Con (Future Focus)</t>
         </is>
       </c>
       <c r="J108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ウクレレコンサート</t>
+          <t xml:space="preserve">コンセプト・コン（未来を考える）</t>
         </is>
       </c>
       <c r="K108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students perform musical pieces they have learned throughout the year, demonstrating their growth, confidence, and musical skills.</t>
+          <t xml:space="preserve">Students investigate future possibilities, innovations, and solutions to real-world challenges through inquiry-based projects and presentations.</t>
         </is>
       </c>
       <c r="L108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一年を通して学んだ曲を演奏し、成長、自信、音楽の技能を披露します。</t>
+          <t xml:space="preserve">探究型のプロジェクトや発表を通して、未来の可能性、イノベーション、現実の課題の解決策について考えます。</t>
         </is>
       </c>
       <c r="M108" t="inlineStr" s="2">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="O108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-03-ukulele-concert.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-24-concept-con-future-focus.webp</t>
         </is>
       </c>
       <c r="P108" t="inlineStr" s="2">
@@ -10558,17 +10558,17 @@
     <row r="109">
       <c r="A109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-04-celebration-of-learning</t>
+          <t xml:space="preserve">2027-05-28-g12-graduation-with-performances</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-04</t>
+          <t xml:space="preserve">2027-05-29</t>
         </is>
       </c>
       <c r="C109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-04</t>
+          <t xml:space="preserve">2027-05-29</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="3">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="E109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F109" t="inlineStr" s="2">
@@ -10593,27 +10593,27 @@
       </c>
       <c r="H109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">changed</t>
         </is>
       </c>
       <c r="I109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Celebration of Learning</t>
+          <t xml:space="preserve">G12 Graduation with Performances</t>
         </is>
       </c>
       <c r="J109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学びの発表会</t>
+          <t xml:space="preserve">G12卒業式・記念パフォーマンス</t>
         </is>
       </c>
       <c r="K109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The school community will celebrate learning as students share projects and exhibitions, including PYPX, MYPX, CAS, EE, TOK and Foundation to 4 projects.</t>
+          <t xml:space="preserve">Grade 12 students will celebrate their graduation with a formal ceremony featuring student performances and the wider school community.</t>
         </is>
       </c>
       <c r="L109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PYPX、MYPX、CAS、EE、TOK、ファウンデーション～4年生のプロジェクトなど、生徒の作品や展示を通して学校コミュニティ全体で学びを祝います。</t>
+          <t xml:space="preserve">12年生が、生徒によるパフォーマンスを交えた式典で、学校コミュニティ全体とともに卒業を祝います。</t>
         </is>
       </c>
       <c r="M109" t="inlineStr" s="2">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="O109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-04-celebration-of-learning.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-28-g12-graduation-with-performances.webp</t>
         </is>
       </c>
       <c r="P109" t="inlineStr" s="2">
@@ -10655,17 +10655,17 @@
     <row r="110">
       <c r="A110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-05-sat-test-7</t>
+          <t xml:space="preserve">2027-06-03-celebration-of-learning-prep</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-05</t>
+          <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
       <c r="C110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-05</t>
+          <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="3">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="E110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F110" t="inlineStr" s="2">
@@ -10695,22 +10695,22 @@
       </c>
       <c r="I110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT Test #7</t>
+          <t xml:space="preserve">Celebration of Learning Prep</t>
         </is>
       </c>
       <c r="J110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT試験 第7回</t>
+          <t xml:space="preserve">学びの発表会準備</t>
         </is>
       </c>
       <c r="K110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
+          <t xml:space="preserve">Students help prepare the school for the Celebration of Learning by organizing learning spaces, setting up displays, arranging materials, and ensuring classrooms and common areas are ready to welcome visitors. This preparation helps create an engaging and welcoming environment for families and guests.</t>
         </is>
       </c>
       <c r="L110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
+          <t xml:space="preserve">学びの発表会に向けて、学習スペースの整理、展示の設営、資料の準備を行い、教室や共用エリアで来場者をお迎えできるよう整えます。ご家族やお客様にとって魅力的で温かな空間づくりにつながります。</t>
         </is>
       </c>
       <c r="M110" t="inlineStr" s="2">
@@ -10725,7 +10725,7 @@
       </c>
       <c r="O110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-05-sat-test-7.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-03-celebration-of-learning-prep.webp</t>
         </is>
       </c>
       <c r="P110" t="inlineStr" s="2">
@@ -10752,17 +10752,17 @@
     <row r="111">
       <c r="A111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-11-last-day-of-clubs</t>
+          <t xml:space="preserve">2027-06-03-ukulele-concert</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-11</t>
+          <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
       <c r="C111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-11</t>
+          <t xml:space="preserve">2027-06-04</t>
         </is>
       </c>
       <c r="D111" t="inlineStr" s="3">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="E111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G111" t="inlineStr" s="2">
@@ -10792,22 +10792,22 @@
       </c>
       <c r="I111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Last Day of Clubs</t>
+          <t xml:space="preserve">Ukulele Concert</t>
         </is>
       </c>
       <c r="J111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クラブ活動最終日</t>
+          <t xml:space="preserve">ウクレレコンサート</t>
         </is>
       </c>
       <c r="K111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The last day of after-school clubs for this school year. Bus reminder: the afternoon Red bus runs only on club days, so after today it no longer runs. Please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
+          <t xml:space="preserve">Students perform musical pieces they have learned throughout the year, demonstrating their growth, confidence, and musical skills.</t>
         </is>
       </c>
       <c r="L111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">今年度の放課後クラブ活動の最終日です。【バスについて】午後の赤バスはクラブ活動がある日のみ運行するため、本日で運行を終了します。明日以降、午後の下校時は青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
+          <t xml:space="preserve">一年を通して学んだ曲を演奏し、成長、自信、音楽の技能を披露します。</t>
         </is>
       </c>
       <c r="M111" t="inlineStr" s="2">
@@ -10822,7 +10822,7 @@
       </c>
       <c r="O111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">compass/images/events/2027-06-03-ukulele-concert.webp</t>
         </is>
       </c>
       <c r="P111" t="inlineStr" s="2">
@@ -10849,17 +10849,17 @@
     <row r="112">
       <c r="A112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-17-eagle-bucks-store</t>
+          <t xml:space="preserve">2027-06-04-celebration-of-learning</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-17</t>
+          <t xml:space="preserve">2027-06-04</t>
         </is>
       </c>
       <c r="C112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-17</t>
+          <t xml:space="preserve">2027-06-04</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="3">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G112" t="inlineStr" s="2">
@@ -10889,22 +10889,22 @@
       </c>
       <c r="I112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Eagle Bucks Store</t>
+          <t xml:space="preserve">Celebration of Learning</t>
         </is>
       </c>
       <c r="J112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">イーグルバックス・ストア</t>
+          <t xml:space="preserve">学びの発表会</t>
         </is>
       </c>
       <c r="K112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
+          <t xml:space="preserve">The school community will celebrate learning as students share projects and exhibitions, including PYPX, MYPX, CAS, EE, TOK and Foundation to 4 projects.</t>
         </is>
       </c>
       <c r="L112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
+          <t xml:space="preserve">PYPX、MYPX、CAS、EE、TOK、ファウンデーション～4年生のプロジェクトなど、生徒の作品や展示を通して学校コミュニティ全体で学びを祝います。</t>
         </is>
       </c>
       <c r="M112" t="inlineStr" s="2">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="O112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-17-eagle-bucks-store.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-04-celebration-of-learning.webp</t>
         </is>
       </c>
       <c r="P112" t="inlineStr" s="2">
@@ -10946,17 +10946,17 @@
     <row r="113">
       <c r="A113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-18-kindergarten-and-grade-5-graduation</t>
+          <t xml:space="preserve">2027-06-05-sat-test-7</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-18</t>
+          <t xml:space="preserve">2027-06-05</t>
         </is>
       </c>
       <c r="C113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-18</t>
+          <t xml:space="preserve">2027-06-05</t>
         </is>
       </c>
       <c r="D113" t="inlineStr" s="3">
@@ -10966,12 +10966,12 @@
       </c>
       <c r="E113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G113" t="inlineStr" s="2">
@@ -10986,22 +10986,22 @@
       </c>
       <c r="I113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Kindergarten and Grade 5 Graduation</t>
+          <t xml:space="preserve">SAT Test #7</t>
         </is>
       </c>
       <c r="J113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部・5年生卒業式</t>
+          <t xml:space="preserve">SAT試験 第7回</t>
         </is>
       </c>
       <c r="K113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students participate in graduation ceremonies to celebrate important milestones in their educational journey. The events recognize student growth, achievements, and readiness for the next stage of learning while bringing together families, staff, and the school community in celebration.</t>
+          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
         </is>
       </c>
       <c r="L113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学びの歩みにおける大切な節目を祝う卒業式に参加します。生徒の成長と成果、そして次のステージへの準備が整ったことを、ご家族、教職員、学校コミュニティが一堂に会して祝福します。</t>
+          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
         </is>
       </c>
       <c r="M113" t="inlineStr" s="2">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="O113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-18-kindergarten-and-grade-5-graduation.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-05-sat-test-7.webp</t>
         </is>
       </c>
       <c r="P113" t="inlineStr" s="2">
@@ -11043,17 +11043,17 @@
     <row r="114">
       <c r="A114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-18-primary-elc-year-end-performance</t>
+          <t xml:space="preserve">2027-06-11-last-day-of-clubs</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-18</t>
+          <t xml:space="preserve">2027-06-11</t>
         </is>
       </c>
       <c r="C114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-18</t>
+          <t xml:space="preserve">2027-06-11</t>
         </is>
       </c>
       <c r="D114" t="inlineStr" s="3">
@@ -11063,12 +11063,12 @@
       </c>
       <c r="E114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G114" t="inlineStr" s="2">
@@ -11083,22 +11083,22 @@
       </c>
       <c r="I114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary &amp; ELC Year End Performance</t>
+          <t xml:space="preserve">Last Day of Clubs</t>
         </is>
       </c>
       <c r="J114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小学部・幼稚部年度末発表会</t>
+          <t xml:space="preserve">クラブ活動最終日</t>
         </is>
       </c>
       <c r="K114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students participate in music, dance, drama, and other performance activities to showcase their learning, creativity, and talents. These performances provide an opportunity to celebrate the school year and share achievements with families and the school community.</t>
+          <t xml:space="preserve">The last day of after-school clubs for this school year. Bus reminder: the afternoon Red bus runs only on club days, so after today it no longer runs. Please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
         </is>
       </c>
       <c r="L114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">音楽、ダンス、演劇などのパフォーマンスを通して、学び、創造性、才能を披露します。一年の締めくくりを祝い、その成果をご家族や学校コミュニティと分かち合う機会です。</t>
+          <t xml:space="preserve">今年度の放課後クラブ活動の最終日です。【バスについて】午後の赤バスはクラブ活動がある日のみ運行するため、本日で運行を終了します。明日以降、午後の下校時は青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
         </is>
       </c>
       <c r="M114" t="inlineStr" s="2">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="O114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-18-primary-elc-year-end-performance.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P114" t="inlineStr" s="2">
@@ -11140,17 +11140,17 @@
     <row r="115">
       <c r="A115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-19-end-of-term-3-activity-g6-10</t>
+          <t xml:space="preserve">2027-06-17-eagle-bucks-store</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-19</t>
+          <t xml:space="preserve">2027-06-17</t>
         </is>
       </c>
       <c r="C115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-19</t>
+          <t xml:space="preserve">2027-06-17</t>
         </is>
       </c>
       <c r="D115" t="inlineStr" s="3">
@@ -11160,7 +11160,7 @@
       </c>
       <c r="E115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F115" t="inlineStr" s="2">
@@ -11180,22 +11180,22 @@
       </c>
       <c r="I115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">End of Term 3 Activity: G6-10</t>
+          <t xml:space="preserve">Eagle Bucks Store</t>
         </is>
       </c>
       <c r="J115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第3学期末行事：G6–10</t>
+          <t xml:space="preserve">イーグルバックス・ストア</t>
         </is>
       </c>
       <c r="K115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in an off-campus day trip outside Nagoya to celebrate the end of Term 3.</t>
+          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
         </is>
       </c>
       <c r="L115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第3学期の終わりを祝い、名古屋近郊への日帰り校外活動に参加します。</t>
+          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
         </is>
       </c>
       <c r="M115" t="inlineStr" s="2">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="O115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-19-end-of-term-3-activity-g6-10.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-17-eagle-bucks-store.webp</t>
         </is>
       </c>
       <c r="P115" t="inlineStr" s="2">
@@ -11237,17 +11237,17 @@
     <row r="116">
       <c r="A116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-22-parent-teacher-conferences</t>
+          <t xml:space="preserve">2027-06-18-kindergarten-and-grade-5-graduation</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-22</t>
+          <t xml:space="preserve">2027-06-18</t>
         </is>
       </c>
       <c r="C116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-23</t>
+          <t xml:space="preserve">2027-06-18</t>
         </is>
       </c>
       <c r="D116" t="inlineStr" s="3">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="E116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr" s="2">
@@ -11267,7 +11267,7 @@
       </c>
       <c r="G116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H116" t="inlineStr" s="2">
@@ -11277,22 +11277,22 @@
       </c>
       <c r="I116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parent Teacher Conferences</t>
+          <t xml:space="preserve">Kindergarten and Grade 5 Graduation</t>
         </is>
       </c>
       <c r="J116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者面談</t>
+          <t xml:space="preserve">幼稚部・5年生卒業式</t>
         </is>
       </c>
       <c r="K116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on these days.</t>
+          <t xml:space="preserve">Students participate in graduation ceremonies to celebrate important milestones in their educational journey. The events recognize student growth, achievements, and readiness for the next stage of learning while bringing together families, staff, and the school community in celebration.</t>
         </is>
       </c>
       <c r="L116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。期間中、生徒は登校しません。</t>
+          <t xml:space="preserve">学びの歩みにおける大切な節目を祝う卒業式に参加します。生徒の成長と成果、そして次のステージへの準備が整ったことを、ご家族、教職員、学校コミュニティが一堂に会して祝福します。</t>
         </is>
       </c>
       <c r="M116" t="inlineStr" s="2">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="O116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-22-parent-teacher-conferences.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-18-kindergarten-and-grade-5-graduation.webp</t>
         </is>
       </c>
       <c r="P116" t="inlineStr" s="2">
@@ -11334,17 +11334,17 @@
     <row r="117">
       <c r="A117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-28-summer-school</t>
+          <t xml:space="preserve">2027-06-18-primary-elc-year-end-performance</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-28</t>
+          <t xml:space="preserve">2027-06-18</t>
         </is>
       </c>
       <c r="C117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-07-18</t>
+          <t xml:space="preserve">2027-06-18</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="3">
@@ -11354,12 +11354,12 @@
       </c>
       <c r="E117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G117" t="inlineStr" s="2">
@@ -11374,22 +11374,22 @@
       </c>
       <c r="I117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Summer School</t>
+          <t xml:space="preserve">Primary &amp; ELC Year End Performance</t>
         </is>
       </c>
       <c r="J117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">サマースクール</t>
+          <t xml:space="preserve">小学部・幼稚部年度末発表会</t>
         </is>
       </c>
       <c r="K117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Participate in fun English style summer camps that challenge students and help foster friendships and connections with others.</t>
+          <t xml:space="preserve">Students participate in music, dance, drama, and other performance activities to showcase their learning, creativity, and talents. These performances provide an opportunity to celebrate the school year and share achievements with families and the school community.</t>
         </is>
       </c>
       <c r="L117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">英語で楽しく過ごすサマーキャンプに参加し、新たなことに挑戦しながら友情や人とのつながりを育みます。</t>
+          <t xml:space="preserve">音楽、ダンス、演劇などのパフォーマンスを通して、学び、創造性、才能を披露します。一年の締めくくりを祝い、その成果をご家族や学校コミュニティと分かち合う機会です。</t>
         </is>
       </c>
       <c r="M117" t="inlineStr" s="2">
@@ -11404,7 +11404,7 @@
       </c>
       <c r="O117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-28-summer-school.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-18-primary-elc-year-end-performance.webp</t>
         </is>
       </c>
       <c r="P117" t="inlineStr" s="2">
@@ -11431,95 +11431,386 @@
     <row r="118">
       <c r="A118" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">2027-06-19-end-of-term-3-activity-g6-10</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2027-06-19</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2027-06-19</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Secondary</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">End of Term 3 Activity: G6-10</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">第3学期末行事：G6–10</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Students will take part in an off-campus day trip outside Nagoya to celebrate the end of Term 3.</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">第3学期の終わりを祝い、名古屋近郊への日帰り校外活動に参加します。</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">compass/images/events/2027-06-19-end-of-term-3-activity-g6-10.webp</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">2027-06-22-parent-teacher-conferences</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2027-06-22</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2027-06-23</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Whole School</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parent Teacher Conferences</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">保護者面談</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on these days.</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。期間中、生徒は登校しません。</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">compass/images/events/2027-06-22-parent-teacher-conferences.webp</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">2027-06-28-summer-school</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2027-06-28</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">2027-07-18</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Whole School</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Summer School</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">サマースクール</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Participate in fun English style summer camps that challenge students and help foster friendships and connections with others.</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">英語で楽しく過ごすサマーキャンプに参加し、新たなことに挑戦しながら友情や人とのつながりを育みます。</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">compass/images/events/2027-06-28-summer-school.webp</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">2027-07-20-summer-school</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr" s="3">
+      <c r="B121" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-07-20</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr" s="3">
+      <c r="C121" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2027-07-24</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr" s="2">
+      <c r="D121" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Whole School</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr" s="2">
+      <c r="F121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Summer School</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr" s="2">
+      <c r="J121" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">サマースクール</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr" s="2">
+      <c r="K121" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Participate in fun English style summer camps that challenge students and help foster friendships and connections with others.</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr" s="2">
+      <c r="L121" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">英語で楽しく過ごすサマーキャンプに参加し、新たなことに挑戦しながら友情や人とのつながりを育みます。</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O118" t="inlineStr" s="2">
+      <c r="M121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">compass/images/events/2027-06-28-summer-school.webp</t>
         </is>
       </c>
-      <c r="P118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R118" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="S118" t="inlineStr" s="2">
+      <c r="P121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>

--- a/admin/EIS-Compass-events.xlsx
+++ b/admin/EIS-Compass-events.xlsx
@@ -2798,17 +2798,17 @@
     <row r="29">
       <c r="A29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-25-pta-picnic</t>
+          <t xml:space="preserve">2026-10-26-toyota-college-trip</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-25</t>
+          <t xml:space="preserve">2026-10-26</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-25</t>
+          <t xml:space="preserve">2026-10-26</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="3">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="E29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTA</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="2">
@@ -2838,22 +2838,22 @@
       </c>
       <c r="I29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTA Picnic</t>
+          <t xml:space="preserve">Toyota College Trip</t>
         </is>
       </c>
       <c r="J29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTAピクニック</t>
+          <t xml:space="preserve">豊田高専見学</t>
         </is>
       </c>
       <c r="K29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Families, students, and staff come together for a fun outdoor gathering that strengthens relationships and builds school community.</t>
+          <t xml:space="preserve">Grade 8 Science students will visit Toyota College for a curriculum-based learning experience connected to their science studies.</t>
         </is>
       </c>
       <c r="L29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ご家族、生徒、教職員が集まり、屋外で楽しく交流しながら絆を深め、学校コミュニティを育みます。</t>
+          <t xml:space="preserve">8年生が理科の授業と関連したカリキュラムに基づく学習として、豊田高専を訪問します。</t>
         </is>
       </c>
       <c r="M29" t="inlineStr" s="2">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="O29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-25-pta-picnic.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-26-toyota-college-trip.webp</t>
         </is>
       </c>
       <c r="P29" t="inlineStr" s="2">
@@ -2895,7 +2895,7 @@
     <row r="30">
       <c r="A30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-26-toyota-college-trip</t>
+          <t xml:space="preserve">2026-10-26-clubs-resume</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="3">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="E30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F30" t="inlineStr" s="2">
@@ -2935,22 +2935,22 @@
       </c>
       <c r="I30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Toyota College Trip</t>
+          <t xml:space="preserve">Clubs Resume</t>
         </is>
       </c>
       <c r="J30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">豊田高専見学</t>
+          <t xml:space="preserve">クラブ活動再開</t>
         </is>
       </c>
       <c r="K30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 8 Science students will visit Toyota College for a curriculum-based learning experience connected to their science studies.</t>
+          <t xml:space="preserve">After-school clubs start again today. Bus reminder: the afternoon Red bus runs only on club days. On other days, please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
         </is>
       </c>
       <c r="L30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8年生が理科の授業と関連したカリキュラムに基づく学習として、豊田高専を訪問します。</t>
+          <t xml:space="preserve">本日から放課後のクラブ活動が再開します。【バスについて】午後の赤バスはクラブ活動がある日のみ運行します。それ以外の日は、午後の下校時に青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
         </is>
       </c>
       <c r="M30" t="inlineStr" s="2">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="O30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-26-toyota-college-trip.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P30" t="inlineStr" s="2">
@@ -2992,17 +2992,17 @@
     <row r="31">
       <c r="A31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-26-clubs-resume</t>
+          <t xml:space="preserve">2026-10-30-sensory-wonderland</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-26</t>
+          <t xml:space="preserve">2026-10-30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-26</t>
+          <t xml:space="preserve">2026-10-30</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="3">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="E31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">ELC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr" s="2">
@@ -3032,22 +3032,22 @@
       </c>
       <c r="I31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Clubs Resume</t>
+          <t xml:space="preserve">Sensory Wonderland</t>
         </is>
       </c>
       <c r="J31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クラブ活動再開</t>
+          <t xml:space="preserve">センサリー・ワンダーランド</t>
         </is>
       </c>
       <c r="K31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">After-school clubs start again today. Bus reminder: the afternoon Red bus runs only on club days. On other days, please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
+          <t xml:space="preserve">Students explore a variety of interactive sensory experiences designed to engage curiosity, creativity, and learning through play.</t>
         </is>
       </c>
       <c r="L31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">本日から放課後のクラブ活動が再開します。【バスについて】午後の赤バスはクラブ活動がある日のみ運行します。それ以外の日は、午後の下校時に青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
+          <t xml:space="preserve">好奇心と創造性を刺激し、遊びを通して学ぶ、さまざまな体験型の感覚活動を楽しみます。</t>
         </is>
       </c>
       <c r="M31" t="inlineStr" s="2">
@@ -3089,32 +3089,32 @@
     <row r="32">
       <c r="A32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-30-sensory-wonderland</t>
+          <t xml:space="preserve">2026-10-31-international-mindedness-festival</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-30</t>
+          <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-30</t>
+          <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">10:00-14:00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G32" t="inlineStr" s="2">
@@ -3129,22 +3129,22 @@
       </c>
       <c r="I32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sensory Wonderland</t>
+          <t xml:space="preserve">International Mindedness Festival</t>
         </is>
       </c>
       <c r="J32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">センサリー・ワンダーランド</t>
+          <t xml:space="preserve">インターナショナル・マインデッドネス・フェスティバル</t>
         </is>
       </c>
       <c r="K32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students explore a variety of interactive sensory experiences designed to engage curiosity, creativity, and learning through play.</t>
+          <t xml:space="preserve">This year’s theme is “Festivals and Holidays Around the World”. A Saturday family event celebrating traditions, cultures, stories, arts, music and celebrations from around the world, with student activities, cultural displays, performances, arts and crafts, and interactive booths. Clean-up runs from 14:00 to 15:00, and community members are welcome to help. ELC and Primary students must attend with a parent or guardian and may not be dropped off. School buses will not operate. More details will be shared soon.</t>
         </is>
       </c>
       <c r="L32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">好奇心と創造性を刺激し、遊びを通して学ぶ、さまざまな体験型の感覚活動を楽しみます。</t>
+          <t xml:space="preserve">今年のテーマは「世界の祭りと祝日」です。世界各地の伝統、文化、物語、芸術、音楽、お祝いを紹介する、土曜日のご家族参加型イベントです。児童・生徒の活動、文化展示、パフォーマンス、工作、体験型ブースをお楽しみいただけます。午後2時～3時に片付けを行います（学校コミュニティの皆さまのご協力も歓迎します）。幼稚部・小学部の児童は必ず保護者同伴でご参加ください（お子さまだけを送り届けることはできません）。当日はスクールバスの運行はありません。詳細は近日中にお知らせします。</t>
         </is>
       </c>
       <c r="M32" t="inlineStr" s="2">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="O32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">compass/images/events/2026-10-31-international-mindedness-festival.webp</t>
         </is>
       </c>
       <c r="P32" t="inlineStr" s="2">
@@ -3186,32 +3186,32 @@
     <row r="33">
       <c r="A33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-31-international-mindedness-festival</t>
+          <t xml:space="preserve">2026-11-04-elc-sports-day-rehearsal-1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-31</t>
+          <t xml:space="preserve">2026-11-04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-31</t>
+          <t xml:space="preserve">2026-11-04</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">10:00-14:00</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">ELC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G33" t="inlineStr" s="2">
@@ -3226,22 +3226,22 @@
       </c>
       <c r="I33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">International Mindedness Festival</t>
+          <t xml:space="preserve">ELC Sports Day Rehearsal #1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">インターナショナル・マインデッドネス・フェスティバル</t>
+          <t xml:space="preserve">幼稚部運動会リハーサル #1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This year’s theme is “Festivals and Holidays Around the World”. A Saturday family event celebrating traditions, cultures, stories, arts, music and celebrations from around the world, with student activities, cultural displays, performances, arts and crafts, and interactive booths. Clean-up runs from 14:00 to 15:00, and community members are welcome to help. ELC and Primary students must attend with a parent or guardian and may not be dropped off. School buses will not operate. More details will be shared soon.</t>
+          <t xml:space="preserve">During Sports Day practice, students participate in a variety of physical activities, team games, relays, and event rehearsals in preparation for Sports Day. They develop teamwork, cooperation, sportsmanship, and physical fitness while learning event procedures, safety expectations, and cheering routines. Practice sessions help students build confidence and ensure they are prepared to participate successfully in the Sports Day celebration.</t>
         </is>
       </c>
       <c r="L33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">今年のテーマは「世界の祭りと祝日」です。世界各地の伝統、文化、物語、芸術、音楽、お祝いを紹介する、土曜日のご家族参加型イベントです。児童・生徒の活動、文化展示、パフォーマンス、工作、体験型ブースをお楽しみいただけます。午後2時～3時に片付けを行います（学校コミュニティの皆さまのご協力も歓迎します）。幼稚部・小学部の児童は必ず保護者同伴でご参加ください（お子さまだけを送り届けることはできません）。当日はスクールバスの運行はありません。詳細は近日中にお知らせします。</t>
+          <t xml:space="preserve">運動会に向けた練習では、さまざまな運動、チームゲーム、リレー、種目のリハーサルに取り組みます。進行の流れ、安全面のルール、応援の仕方を学びながら、チームワーク、協調性、スポーツマンシップ、体力を養います。練習を通して自信をつけ、運動会当日に力を発揮できるよう準備します。</t>
         </is>
       </c>
       <c r="M33" t="inlineStr" s="2">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="O33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-31-international-mindedness-festival.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-04-elc-sports-day-rehearsal-1.webp</t>
         </is>
       </c>
       <c r="P33" t="inlineStr" s="2">
@@ -3283,17 +3283,17 @@
     <row r="34">
       <c r="A34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-04-elc-sports-day-rehearsal-1</t>
+          <t xml:space="preserve">2026-11-05-toyota-museum-field-trip</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-04</t>
+          <t xml:space="preserve">2026-11-05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-04</t>
+          <t xml:space="preserve">2026-11-05</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="3">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="E34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F34" t="inlineStr" s="2">
@@ -3323,22 +3323,22 @@
       </c>
       <c r="I34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC Sports Day Rehearsal #1</t>
+          <t xml:space="preserve">Toyota Museum Field Trip</t>
         </is>
       </c>
       <c r="J34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部運動会リハーサル #1</t>
+          <t xml:space="preserve">トヨタ博物館校外学習</t>
         </is>
       </c>
       <c r="K34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">During Sports Day practice, students participate in a variety of physical activities, team games, relays, and event rehearsals in preparation for Sports Day. They develop teamwork, cooperation, sportsmanship, and physical fitness while learning event procedures, safety expectations, and cheering routines. Practice sessions help students build confidence and ensure they are prepared to participate successfully in the Sports Day celebration.</t>
+          <t xml:space="preserve">Grade 9 students go to the Toyota museum down the road and view the exhibits taking some notes on machines they learned about.</t>
         </is>
       </c>
       <c r="L34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会に向けた練習では、さまざまな運動、チームゲーム、リレー、種目のリハーサルに取り組みます。進行の流れ、安全面のルール、応援の仕方を学びながら、チームワーク、協調性、スポーツマンシップ、体力を養います。練習を通して自信をつけ、運動会当日に力を発揮できるよう準備します。</t>
+          <t xml:space="preserve">9年生が近くのトヨタの博物館を訪れ、授業で学んだ機械について展示を見学しながらメモを取ります。</t>
         </is>
       </c>
       <c r="M34" t="inlineStr" s="2">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="O34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-04-elc-sports-day-rehearsal-1.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-05-toyota-museum-field-trip.webp</t>
         </is>
       </c>
       <c r="P34" t="inlineStr" s="2">
@@ -3380,17 +3380,17 @@
     <row r="35">
       <c r="A35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-05-toyota-museum-field-trip</t>
+          <t xml:space="preserve">2026-11-06-extracurricular-activities-autumn-cas-project-su</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-05</t>
+          <t xml:space="preserve">2026-11-06</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-05</t>
+          <t xml:space="preserve">2026-11-06</t>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="3">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="F35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G35" t="inlineStr" s="2">
@@ -3420,22 +3420,22 @@
       </c>
       <c r="I35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Toyota Museum Field Trip</t>
+          <t xml:space="preserve">Extracurricular Activities: Autumn CAS &amp; Project Support Fair</t>
         </is>
       </c>
       <c r="J35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">トヨタ博物館校外学習</t>
+          <t xml:space="preserve">課外活動：秋のCAS・プロジェクトサポートフェア</t>
         </is>
       </c>
       <c r="K35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 9 students go to the Toyota museum down the road and view the exhibits taking some notes on machines they learned about.</t>
+          <t xml:space="preserve">Secondary PTA Supported Event to help students understand various volunteering and CAS project opportunities in the community. Open to MYP and DP Students.</t>
         </is>
       </c>
       <c r="L35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">9年生が近くのトヨタの博物館を訪れ、授業で学んだ機械について展示を見学しながらメモを取ります。</t>
+          <t xml:space="preserve">中等部PTAの支援による行事で、地域でのさまざまなボランティアやCASプロジェクトの機会について知ることができます。MYP・DP生徒が対象です。</t>
         </is>
       </c>
       <c r="M35" t="inlineStr" s="2">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="O35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-05-toyota-museum-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-06-extracurricular-activities-autumn-cas-project-su.webp</t>
         </is>
       </c>
       <c r="P35" t="inlineStr" s="2">
@@ -3477,17 +3477,17 @@
     <row r="36">
       <c r="A36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-06-extracurricular-activities-autumn-cas-project-su</t>
+          <t xml:space="preserve">2026-11-07-sat-test-4</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-06</t>
+          <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-06</t>
+          <t xml:space="preserve">2026-11-07</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="3">
@@ -3497,12 +3497,12 @@
       </c>
       <c r="E36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G36" t="inlineStr" s="2">
@@ -3517,22 +3517,22 @@
       </c>
       <c r="I36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Extracurricular Activities: Autumn CAS &amp; Project Support Fair</t>
+          <t xml:space="preserve">SAT Test #4</t>
         </is>
       </c>
       <c r="J36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">課外活動：秋のCAS・プロジェクトサポートフェア</t>
+          <t xml:space="preserve">SAT試験 第4回</t>
         </is>
       </c>
       <c r="K36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary PTA Supported Event to help students understand various volunteering and CAS project opportunities in the community. Open to MYP and DP Students.</t>
+          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
         </is>
       </c>
       <c r="L36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部PTAの支援による行事で、地域でのさまざまなボランティアやCASプロジェクトの機会について知ることができます。MYP・DP生徒が対象です。</t>
+          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
         </is>
       </c>
       <c r="M36" t="inlineStr" s="2">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="O36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-06-extracurricular-activities-autumn-cas-project-su.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-07-sat-test-4.webp</t>
         </is>
       </c>
       <c r="P36" t="inlineStr" s="2">
@@ -3574,17 +3574,17 @@
     <row r="37">
       <c r="A37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-07-sat-test-4</t>
+          <t xml:space="preserve">2026-11-09-wellbeing-week</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-07</t>
+          <t xml:space="preserve">2026-11-09</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-07</t>
+          <t xml:space="preserve">2026-11-13</t>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="3">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="E37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F37" t="inlineStr" s="2">
@@ -3614,22 +3614,22 @@
       </c>
       <c r="I37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT Test #4</t>
+          <t xml:space="preserve">Wellbeing Week</t>
         </is>
       </c>
       <c r="J37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT試験 第4回</t>
+          <t xml:space="preserve">ウェルビーイング週間</t>
         </is>
       </c>
       <c r="K37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
+          <t xml:space="preserve">A school wide event focused on raising awareness for wellbeing.</t>
         </is>
       </c>
       <c r="L37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
+          <t xml:space="preserve">ウェルビーイング（心身の健康）への意識を高めることを目的とした全校行事です。</t>
         </is>
       </c>
       <c r="M37" t="inlineStr" s="2">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-07-sat-test-4.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-09-wellbeing-week.webp</t>
         </is>
       </c>
       <c r="P37" t="inlineStr" s="2">
@@ -3671,7 +3671,7 @@
     <row r="38">
       <c r="A38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-09-wellbeing-week</t>
+          <t xml:space="preserve">2026-11-09-concept-con-wellbeing</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="3">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="E38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F38" t="inlineStr" s="2">
@@ -3711,22 +3711,22 @@
       </c>
       <c r="I38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Wellbeing Week</t>
+          <t xml:space="preserve">Concept Con (Wellbeing)</t>
         </is>
       </c>
       <c r="J38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ウェルビーイング週間</t>
+          <t xml:space="preserve">コンセプト・コン（ウェルビーイング）</t>
         </is>
       </c>
       <c r="K38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A school wide event focused on raising awareness for wellbeing.</t>
+          <t xml:space="preserve">The Primary Concept Conference on the theme of wellbeing, held during Wellbeing Week.</t>
         </is>
       </c>
       <c r="L38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ウェルビーイング（心身の健康）への意識を高めることを目的とした全校行事です。</t>
+          <t xml:space="preserve">ウェルビーイング週間に合わせて行う、小学部のコンセプト・カンファレンス（テーマ：ウェルビーイング）です。</t>
         </is>
       </c>
       <c r="M38" t="inlineStr" s="2">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="O38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-09-wellbeing-week.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P38" t="inlineStr" s="2">
@@ -3768,17 +3768,17 @@
     <row r="39">
       <c r="A39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-09-concept-con-wellbeing</t>
+          <t xml:space="preserve">2026-11-11-elc-sports-day-rehearsal-2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-09</t>
+          <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-13</t>
+          <t xml:space="preserve">2026-11-11</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="3">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="E39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">ELC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr" s="2">
@@ -3808,22 +3808,22 @@
       </c>
       <c r="I39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Concept Con (Wellbeing)</t>
+          <t xml:space="preserve">ELC Sports Day Rehearsal #2</t>
         </is>
       </c>
       <c r="J39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">コンセプト・コン（ウェルビーイング）</t>
+          <t xml:space="preserve">幼稚部運動会リハーサル #2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The Primary Concept Conference on the theme of wellbeing, held during Wellbeing Week.</t>
+          <t xml:space="preserve">During Sports Day practice, students participate in a variety of physical activities, team games, relays, and event rehearsals in preparation for Sports Day. They develop teamwork, cooperation, sportsmanship, and physical fitness while learning event procedures, safety expectations, and cheering routines. Practice sessions help students build confidence and ensure they are prepared to participate successfully in the Sports Day celebration.</t>
         </is>
       </c>
       <c r="L39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ウェルビーイング週間に合わせて行う、小学部のコンセプト・カンファレンス（テーマ：ウェルビーイング）です。</t>
+          <t xml:space="preserve">運動会に向けた練習では、さまざまな運動、チームゲーム、リレー、種目のリハーサルに取り組みます。進行の流れ、安全面のルール、応援の仕方を学びながら、チームワーク、協調性、スポーツマンシップ、体力を養います。練習を通して自信をつけ、運動会当日に力を発揮できるよう準備します。</t>
         </is>
       </c>
       <c r="M39" t="inlineStr" s="2">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="O39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">compass/images/events/2026-11-11-elc-sports-day-rehearsal-2.webp</t>
         </is>
       </c>
       <c r="P39" t="inlineStr" s="2">
@@ -3865,17 +3865,17 @@
     <row r="40">
       <c r="A40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-11-elc-sports-day-rehearsal-2</t>
+          <t xml:space="preserve">2026-11-14-elc-sports-day</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-11</t>
+          <t xml:space="preserve">2026-11-14</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-11</t>
+          <t xml:space="preserve">2026-11-14</t>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="3">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="I40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC Sports Day Rehearsal #2</t>
+          <t xml:space="preserve">ELC Sports Day</t>
         </is>
       </c>
       <c r="J40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部運動会リハーサル #2</t>
+          <t xml:space="preserve">幼稚部運動会</t>
         </is>
       </c>
       <c r="K40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">During Sports Day practice, students participate in a variety of physical activities, team games, relays, and event rehearsals in preparation for Sports Day. They develop teamwork, cooperation, sportsmanship, and physical fitness while learning event procedures, safety expectations, and cheering routines. Practice sessions help students build confidence and ensure they are prepared to participate successfully in the Sports Day celebration.</t>
+          <t xml:space="preserve">During Sports Day, students participate in a variety of athletic events, relay races, team challenges, and cooperative games. They demonstrate teamwork, perseverance, sportsmanship, and school spirit while celebrating physical activity and healthy competition. Sports Day provides an opportunity for students to challenge themselves, support their peers, and enjoy a fun day of community participation and achievement.</t>
         </is>
       </c>
       <c r="L40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会に向けた練習では、さまざまな運動、チームゲーム、リレー、種目のリハーサルに取り組みます。進行の流れ、安全面のルール、応援の仕方を学びながら、チームワーク、協調性、スポーツマンシップ、体力を養います。練習を通して自信をつけ、運動会当日に力を発揮できるよう準備します。</t>
+          <t xml:space="preserve">運動会では、さまざまな競技、リレー、チーム対抗戦、協力ゲームに参加します。体を動かすことと健全な競争を楽しみながら、チームワーク、粘り強さ、スポーツマンシップ、愛校心を発揮します。自分に挑戦し、仲間を応援し、コミュニティ全体で達成感を味わう楽しい一日です。</t>
         </is>
       </c>
       <c r="M40" t="inlineStr" s="2">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="O40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-11-elc-sports-day-rehearsal-2.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-14-elc-sports-day.webp</t>
         </is>
       </c>
       <c r="P40" t="inlineStr" s="2">
@@ -3962,17 +3962,17 @@
     <row r="41">
       <c r="A41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-14-elc-sports-day</t>
+          <t xml:space="preserve">2026-11-16-friendly-soccer-tournament-internal</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-14</t>
+          <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-14</t>
+          <t xml:space="preserve">2026-11-20</t>
         </is>
       </c>
       <c r="D41" t="inlineStr" s="3">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="E41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F41" t="inlineStr" s="2">
@@ -4002,22 +4002,22 @@
       </c>
       <c r="I41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC Sports Day</t>
+          <t xml:space="preserve">Friendly Soccer Tournament (Internal)</t>
         </is>
       </c>
       <c r="J41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部運動会</t>
+          <t xml:space="preserve">校内サッカー大会</t>
         </is>
       </c>
       <c r="K41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">During Sports Day, students participate in a variety of athletic events, relay races, team challenges, and cooperative games. They demonstrate teamwork, perseverance, sportsmanship, and school spirit while celebrating physical activity and healthy competition. Sports Day provides an opportunity for students to challenge themselves, support their peers, and enjoy a fun day of community participation and achievement.</t>
+          <t xml:space="preserve">Students will take part in a friendly internal soccer tournament, promoting teamwork, sportsmanship, and school spirit.</t>
         </is>
       </c>
       <c r="L41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会では、さまざまな競技、リレー、チーム対抗戦、協力ゲームに参加します。体を動かすことと健全な競争を楽しみながら、チームワーク、粘り強さ、スポーツマンシップ、愛校心を発揮します。自分に挑戦し、仲間を応援し、コミュニティ全体で達成感を味わう楽しい一日です。</t>
+          <t xml:space="preserve">校内サッカー大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
         </is>
       </c>
       <c r="M41" t="inlineStr" s="2">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="O41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-14-elc-sports-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-16-friendly-soccer-tournament-internal.webp</t>
         </is>
       </c>
       <c r="P41" t="inlineStr" s="2">
@@ -4059,17 +4059,17 @@
     <row r="42">
       <c r="A42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-16-friendly-soccer-tournament-internal</t>
+          <t xml:space="preserve">2026-11-17-foundation-field-trip</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-16</t>
+          <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-20</t>
+          <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="3">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="E42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">ELC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G42" t="inlineStr" s="2">
@@ -4099,22 +4099,22 @@
       </c>
       <c r="I42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Friendly Soccer Tournament (Internal)</t>
+          <t xml:space="preserve">Foundation Field Trip</t>
         </is>
       </c>
       <c r="J42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内サッカー大会</t>
+          <t xml:space="preserve">ファウンデーション校外学習</t>
         </is>
       </c>
       <c r="K42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in a friendly internal soccer tournament, promoting teamwork, sportsmanship, and school spirit.</t>
+          <t xml:space="preserve">Our youngest learners will enjoy an age-appropriate educational excursion that supports classroom learning through hands-on experiences.</t>
         </is>
       </c>
       <c r="L42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内サッカー大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
+          <t xml:space="preserve">年少の子どもたちが、年齢に合った校外学習に出かけ、体験を通して教室での学びを深めます。</t>
         </is>
       </c>
       <c r="M42" t="inlineStr" s="2">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="O42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-16-friendly-soccer-tournament-internal.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-17-foundation-field-trip.webp</t>
         </is>
       </c>
       <c r="P42" t="inlineStr" s="2">
@@ -4156,17 +4156,17 @@
     <row r="43">
       <c r="A43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-17-foundation-field-trip</t>
+          <t xml:space="preserve">2026-11-20-gifu-kakamigahara-air-and-space-museum</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-17</t>
+          <t xml:space="preserve">2026-11-20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-17</t>
+          <t xml:space="preserve">2026-11-20</t>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="3">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="E43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G43" t="inlineStr" s="2">
@@ -4196,22 +4196,22 @@
       </c>
       <c r="I43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Foundation Field Trip</t>
+          <t xml:space="preserve">Gifu Kakamigahara Air and Space Museum</t>
         </is>
       </c>
       <c r="J43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ファウンデーション校外学習</t>
+          <t xml:space="preserve">岐阜かかみがはら航空宇宙博物館</t>
         </is>
       </c>
       <c r="K43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Our youngest learners will enjoy an age-appropriate educational excursion that supports classroom learning through hands-on experiences.</t>
+          <t xml:space="preserve">Students will be going to the air and space museum to complete a practical where they will be analyzing plane design throughout history.</t>
         </is>
       </c>
       <c r="L43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">年少の子どもたちが、年齢に合った校外学習に出かけ、体験を通して教室での学びを深めます。</t>
+          <t xml:space="preserve">航空宇宙博物館を訪れ、歴史を通じた飛行機のデザインを分析する実習に取り組みます。</t>
         </is>
       </c>
       <c r="M43" t="inlineStr" s="2">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="O43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-17-foundation-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-20-gifu-kakamigahara-air-and-space-museum.webp</t>
         </is>
       </c>
       <c r="P43" t="inlineStr" s="2">
@@ -4253,32 +4253,32 @@
     <row r="44">
       <c r="A44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-20-gifu-kakamigahara-air-and-space-museum</t>
+          <t xml:space="preserve">2026-11-24-winter-art-contest</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-20</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-20</t>
+          <t xml:space="preserve">2026-11-24</t>
         </is>
       </c>
       <c r="D44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">13:10-14:55</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G44" t="inlineStr" s="2">
@@ -4293,37 +4293,37 @@
       </c>
       <c r="I44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Gifu Kakamigahara Air and Space Museum</t>
+          <t xml:space="preserve">Gallery Day: ELC &amp; Primary Art Showcase</t>
         </is>
       </c>
       <c r="J44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">岐阜かかみがはら航空宇宙博物館</t>
+          <t xml:space="preserve">ギャラリーデー：幼稚部・小学部アート展</t>
         </is>
       </c>
       <c r="K44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will be going to the air and space museum to complete a practical where they will be analyzing plane design throughout history.</t>
+          <t xml:space="preserve">ELC and Primary students display the artwork they have created with the visual arts teacher. Parents are welcome to view the gallery from 13:10 to 14:55. Students vote for their favourite artworks, and the winners for each grade are announced.</t>
         </is>
       </c>
       <c r="L44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">航空宇宙博物館を訪れ、歴史を通じた飛行機のデザインを分析する実習に取り組みます。</t>
+          <t xml:space="preserve">幼稚部・小学部の児童が美術の授業で制作した作品を展示します。保護者の皆さまは13:10～14:55にご鑑賞いただけます。児童による投票を行い、学年ごとの受賞作品を発表します。</t>
         </is>
       </c>
       <c r="M44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Gym</t>
         </is>
       </c>
       <c r="N44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">体育館</t>
         </is>
       </c>
       <c r="O44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-20-gifu-kakamigahara-air-and-space-museum.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-24-winter-art-contest.webp</t>
         </is>
       </c>
       <c r="P44" t="inlineStr" s="2">
@@ -4350,22 +4350,22 @@
     <row r="45">
       <c r="A45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-24-winter-art-contest</t>
+          <t xml:space="preserve">2026-11-27-parents-morning-1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-24</t>
+          <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-24</t>
+          <t xml:space="preserve">2026-11-27</t>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">13:10-14:55</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -4390,37 +4390,37 @@
       </c>
       <c r="I45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Gallery Day: ELC &amp; Primary Art Showcase</t>
+          <t xml:space="preserve">Parents Morning #1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ギャラリーデー：幼稚部・小学部アート展</t>
+          <t xml:space="preserve">朝の授業参観 #1</t>
         </is>
       </c>
       <c r="K45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC and Primary students display the artwork they have created with the visual arts teacher. Parents are welcome to view the gallery from 13:10 to 14:55. Students vote for their favourite artworks, and the winners for each grade are announced.</t>
+          <t xml:space="preserve">ELC and Primary Parents are invited to come and see the lessons in the morning and experience the morning routines with their child.</t>
         </is>
       </c>
       <c r="L45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部・小学部の児童が美術の授業で制作した作品を展示します。保護者の皆さまは13:10～14:55にご鑑賞いただけます。児童による投票を行い、学年ごとの受賞作品を発表します。</t>
+          <t xml:space="preserve">幼稚部・小学部の保護者の皆様をお招きし、朝の授業をご参観いただき、お子様と一緒に朝の日課を体験していただきます。</t>
         </is>
       </c>
       <c r="M45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Gym</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="N45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">体育館</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="O45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-24-winter-art-contest.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-27-parents-morning-1.webp</t>
         </is>
       </c>
       <c r="P45" t="inlineStr" s="2">
@@ -4447,7 +4447,7 @@
     <row r="46">
       <c r="A46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-27-parents-morning-1</t>
+          <t xml:space="preserve">2026-11-27-teacher-appreciation-day</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="3">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="E46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G46" t="inlineStr" s="2">
@@ -4487,22 +4487,22 @@
       </c>
       <c r="I46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parents Morning #1</t>
+          <t xml:space="preserve">Teacher Appreciation Day</t>
         </is>
       </c>
       <c r="J46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">朝の授業参観 #1</t>
+          <t xml:space="preserve">教職員感謝デー</t>
         </is>
       </c>
       <c r="K46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC and Primary Parents are invited to come and see the lessons in the morning and experience the morning routines with their child.</t>
+          <t xml:space="preserve">The school community will celebrate Teacher Appreciation Day by recognizing and thanking teachers for their dedication, care, and support.</t>
         </is>
       </c>
       <c r="L46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部・小学部の保護者の皆様をお招きし、朝の授業をご参観いただき、お子様と一緒に朝の日課を体験していただきます。</t>
+          <t xml:space="preserve">学校コミュニティ全体で、教員の献身、思いやり、支えに感謝を伝える日です。</t>
         </is>
       </c>
       <c r="M46" t="inlineStr" s="2">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="O46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-27-parents-morning-1.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-27-teacher-appreciation-day.webp</t>
         </is>
       </c>
       <c r="P46" t="inlineStr" s="2">
@@ -4544,17 +4544,17 @@
     <row r="47">
       <c r="A47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-27-teacher-appreciation-day</t>
+          <t xml:space="preserve">2026-11-28-2026-enishi-futsal-tournament</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-27</t>
+          <t xml:space="preserve">2026-11-28</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-27</t>
+          <t xml:space="preserve">2026-11-28</t>
         </is>
       </c>
       <c r="D47" t="inlineStr" s="3">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="E47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F47" t="inlineStr" s="2">
@@ -4584,22 +4584,22 @@
       </c>
       <c r="I47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Teacher Appreciation Day</t>
+          <t xml:space="preserve">2026 - Enishi Futsal Tournament</t>
         </is>
       </c>
       <c r="J47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">教職員感謝デー</t>
+          <t xml:space="preserve">2026 Enishiフットサル大会</t>
         </is>
       </c>
       <c r="K47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The school community will celebrate Teacher Appreciation Day by recognizing and thanking teachers for their dedication, care, and support.</t>
+          <t xml:space="preserve">Enishi will host a Middle School Futsal tournament at our school with multiple schools participating.</t>
         </is>
       </c>
       <c r="L47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学校コミュニティ全体で、教員の献身、思いやり、支えに感謝を伝える日です。</t>
+          <t xml:space="preserve">本校にて複数校が参加する中学生フットサル大会を開催します。</t>
         </is>
       </c>
       <c r="M47" t="inlineStr" s="2">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="O47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-27-teacher-appreciation-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-11-28-2026-enishi-futsal-tournament.webp</t>
         </is>
       </c>
       <c r="P47" t="inlineStr" s="2">
@@ -4641,32 +4641,32 @@
     <row r="48">
       <c r="A48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-11-28-2026-enishi-futsal-tournament</t>
+          <t xml:space="preserve">2026-12-03-grade-3-4-musical</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-28</t>
+          <t xml:space="preserve">2026-12-03</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-11-28</t>
+          <t xml:space="preserve">2026-12-03</t>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">17:30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G48" t="inlineStr" s="2">
@@ -4681,22 +4681,22 @@
       </c>
       <c r="I48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026 - Enishi Futsal Tournament</t>
+          <t xml:space="preserve">Grade 3, 4 Musical</t>
         </is>
       </c>
       <c r="J48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026 Enishiフットサル大会</t>
+          <t xml:space="preserve">3・4年生ミュージカル</t>
         </is>
       </c>
       <c r="K48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Enishi will host a Middle School Futsal tournament at our school with multiple schools participating.</t>
+          <t xml:space="preserve">Students present a musical performance showcasing their talents in singing, acting, and teamwork. Families are invited to enjoy this special production.</t>
         </is>
       </c>
       <c r="L48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">本校にて複数校が参加する中学生フットサル大会を開催します。</t>
+          <t xml:space="preserve">歌、演技、チームワークを披露するミュージカルを上演します。ご家族の皆様もぜひこの特別な公演をお楽しみください。</t>
         </is>
       </c>
       <c r="M48" t="inlineStr" s="2">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-11-28-2026-enishi-futsal-tournament.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-03-grade-3-4-musical.webp</t>
         </is>
       </c>
       <c r="P48" t="inlineStr" s="2">
@@ -4738,32 +4738,32 @@
     <row r="49">
       <c r="A49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-03-grade-3-4-musical</t>
+          <t xml:space="preserve">2026-12-05-sat-test-5</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-03</t>
+          <t xml:space="preserve">2026-12-05</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-03</t>
+          <t xml:space="preserve">2026-12-05</t>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">17:30</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G49" t="inlineStr" s="2">
@@ -4778,22 +4778,22 @@
       </c>
       <c r="I49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 3, 4 Musical</t>
+          <t xml:space="preserve">SAT Test #5</t>
         </is>
       </c>
       <c r="J49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">3・4年生ミュージカル</t>
+          <t xml:space="preserve">SAT試験 第5回</t>
         </is>
       </c>
       <c r="K49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students present a musical performance showcasing their talents in singing, acting, and teamwork. Families are invited to enjoy this special production.</t>
+          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
         </is>
       </c>
       <c r="L49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">歌、演技、チームワークを披露するミュージカルを上演します。ご家族の皆様もぜひこの特別な公演をお楽しみください。</t>
+          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
         </is>
       </c>
       <c r="M49" t="inlineStr" s="2">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="O49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-03-grade-3-4-musical.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-05-sat-test-5.webp</t>
         </is>
       </c>
       <c r="P49" t="inlineStr" s="2">
@@ -4835,17 +4835,17 @@
     <row r="50">
       <c r="A50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-05-sat-test-5</t>
+          <t xml:space="preserve">2026-12-10-choir-and-orchestra-concert</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-05</t>
+          <t xml:space="preserve">2026-12-10</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-05</t>
+          <t xml:space="preserve">2026-12-10</t>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="3">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G50" t="inlineStr" s="2">
@@ -4875,22 +4875,22 @@
       </c>
       <c r="I50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT Test #5</t>
+          <t xml:space="preserve">Choir and Orchestra Concert</t>
         </is>
       </c>
       <c r="J50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT試験 第5回</t>
+          <t xml:space="preserve">合唱・オーケストラコンサート</t>
         </is>
       </c>
       <c r="K50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
+          <t xml:space="preserve">Choir class and orchestra club will perform the music repertoire they have been rehearsing for an audience of family, peers and teachers.</t>
         </is>
       </c>
       <c r="L50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
+          <t xml:space="preserve">合唱クラスとオーケストラクラブが、練習を重ねてきた曲目をご家族、友人、教員の前で演奏します。</t>
         </is>
       </c>
       <c r="M50" t="inlineStr" s="2">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-05-sat-test-5.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-10-choir-and-orchestra-concert.webp</t>
         </is>
       </c>
       <c r="P50" t="inlineStr" s="2">
@@ -4932,17 +4932,17 @@
     <row r="51">
       <c r="A51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-10-choir-and-orchestra-concert</t>
+          <t xml:space="preserve">2026-12-11-silent-auction</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-10</t>
+          <t xml:space="preserve">2026-12-11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-10</t>
+          <t xml:space="preserve">2026-12-11</t>
         </is>
       </c>
       <c r="D51" t="inlineStr" s="3">
@@ -4952,7 +4952,7 @@
       </c>
       <c r="E51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F51" t="inlineStr" s="2">
@@ -4972,22 +4972,22 @@
       </c>
       <c r="I51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choir and Orchestra Concert</t>
+          <t xml:space="preserve">Silent Auction</t>
         </is>
       </c>
       <c r="J51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合唱・オーケストラコンサート</t>
+          <t xml:space="preserve">サイレントオークション</t>
         </is>
       </c>
       <c r="K51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choir class and orchestra club will perform the music repertoire they have been rehearsing for an audience of family, peers and teachers.</t>
+          <t xml:space="preserve">Families and community members can bid on donated items and experiences to support initiatives chosen by the primary student council.</t>
         </is>
       </c>
       <c r="L51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合唱クラスとオーケストラクラブが、練習を重ねてきた曲目をご家族、友人、教員の前で演奏します。</t>
+          <t xml:space="preserve">ご家族や地域の皆様が寄付された品物や体験に入札し、小学部生徒会が選んだ取り組みを支援します。</t>
         </is>
       </c>
       <c r="M51" t="inlineStr" s="2">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="O51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-10-choir-and-orchestra-concert.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-11-silent-auction.webp</t>
         </is>
       </c>
       <c r="P51" t="inlineStr" s="2">
@@ -5029,17 +5029,17 @@
     <row r="52">
       <c r="A52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-11-silent-auction</t>
+          <t xml:space="preserve">2026-12-14-clubs-pause</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-11</t>
+          <t xml:space="preserve">2026-12-14</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-11</t>
+          <t xml:space="preserve">2026-12-18</t>
         </is>
       </c>
       <c r="D52" t="inlineStr" s="3">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G52" t="inlineStr" s="2">
@@ -5069,22 +5069,22 @@
       </c>
       <c r="I52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Silent Auction</t>
+          <t xml:space="preserve">Clubs Pause</t>
         </is>
       </c>
       <c r="J52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">サイレントオークション</t>
+          <t xml:space="preserve">クラブ活動休止</t>
         </is>
       </c>
       <c r="K52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Families and community members can bid on donated items and experiences to support initiatives chosen by the primary student council.</t>
+          <t xml:space="preserve">After-school clubs are paused during this period. Bus reminder: the afternoon Red bus runs only on club days, so it does not run while clubs are paused. Please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
         </is>
       </c>
       <c r="L52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ご家族や地域の皆様が寄付された品物や体験に入札し、小学部生徒会が選んだ取り組みを支援します。</t>
+          <t xml:space="preserve">この期間、放課後のクラブ活動はお休みです。【バスについて】午後の赤バスはクラブ活動がある日のみ運行するため、休止期間中は運行しません。午後の下校時は青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
         </is>
       </c>
       <c r="M52" t="inlineStr" s="2">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="O52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-11-silent-auction.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P52" t="inlineStr" s="2">
@@ -5126,17 +5126,17 @@
     <row r="53">
       <c r="A53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-14-clubs-pause</t>
+          <t xml:space="preserve">2026-12-16-industry-visit-tech-company</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-14</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-18</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="D53" t="inlineStr" s="3">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="E53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F53" t="inlineStr" s="2">
@@ -5166,22 +5166,22 @@
       </c>
       <c r="I53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Clubs Pause</t>
+          <t xml:space="preserve">Industry Visit (Tech Company)</t>
         </is>
       </c>
       <c r="J53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クラブ活動休止</t>
+          <t xml:space="preserve">企業訪問（テクノロジー企業）</t>
         </is>
       </c>
       <c r="K53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">After-school clubs are paused during this period. Bus reminder: the afternoon Red bus runs only on club days, so it does not run while clubs are paused. Please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
+          <t xml:space="preserve">Students will visit a local technology company to gain firsthand insight into the modern workplace and explore careers in technology and innovation.</t>
         </is>
       </c>
       <c r="L53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">この期間、放課後のクラブ活動はお休みです。【バスについて】午後の赤バスはクラブ活動がある日のみ運行するため、休止期間中は運行しません。午後の下校時は青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
+          <t xml:space="preserve">地元のテクノロジー企業を訪問し、現代の職場を直接知るとともに、テクノロジーやイノベーション分野のキャリアについて考えます。</t>
         </is>
       </c>
       <c r="M53" t="inlineStr" s="2">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="O53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">compass/images/events/2026-12-16-industry-visit-tech-company.webp</t>
         </is>
       </c>
       <c r="P53" t="inlineStr" s="2">
@@ -5223,7 +5223,7 @@
     <row r="54">
       <c r="A54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-16-industry-visit-tech-company</t>
+          <t xml:space="preserve">2026-12-16-winter-party-eagle-nest</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="3">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="E54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr" s="2">
@@ -5263,22 +5263,22 @@
       </c>
       <c r="I54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Industry Visit (Tech Company)</t>
+          <t xml:space="preserve">Winter Party (Eagle Nest)</t>
         </is>
       </c>
       <c r="J54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">企業訪問（テクノロジー企業）</t>
+          <t xml:space="preserve">ウィンターパーティー（イーグルネスト）</t>
         </is>
       </c>
       <c r="K54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will visit a local technology company to gain firsthand insight into the modern workplace and explore careers in technology and innovation.</t>
+          <t xml:space="preserve">Students celebrate the season with fun activities, games, and opportunities to connect with peers in their Eagle Nests. This is led by the primary student council.</t>
         </is>
       </c>
       <c r="L54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">地元のテクノロジー企業を訪問し、現代の職場を直接知るとともに、テクノロジーやイノベーション分野のキャリアについて考えます。</t>
+          <t xml:space="preserve">イーグルネストごとに、楽しい活動やゲームを通して仲間と交流し、季節を祝います。小学部生徒会が主催します。</t>
         </is>
       </c>
       <c r="M54" t="inlineStr" s="2">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="O54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-16-industry-visit-tech-company.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-16-winter-party-eagle-nest.webp</t>
         </is>
       </c>
       <c r="P54" t="inlineStr" s="2">
@@ -5320,17 +5320,17 @@
     <row r="55">
       <c r="A55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-16-winter-party-eagle-nest</t>
+          <t xml:space="preserve">2026-12-17-talent-day</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-16</t>
+          <t xml:space="preserve">2026-12-17</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-16</t>
+          <t xml:space="preserve">2026-12-17</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="3">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="E55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G55" t="inlineStr" s="2">
@@ -5360,22 +5360,22 @@
       </c>
       <c r="I55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Winter Party (Eagle Nest)</t>
+          <t xml:space="preserve">Talent Day</t>
         </is>
       </c>
       <c r="J55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ウィンターパーティー（イーグルネスト）</t>
+          <t xml:space="preserve">タレントデー</t>
         </is>
       </c>
       <c r="K55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students celebrate the season with fun activities, games, and opportunities to connect with peers in their Eagle Nests. This is led by the primary student council.</t>
+          <t xml:space="preserve">Students have the opportunity to showcase their unique talents and interests in a supportive and encouraging environment led by the performing arts teacher.</t>
         </is>
       </c>
       <c r="L55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">イーグルネストごとに、楽しい活動やゲームを通して仲間と交流し、季節を祝います。小学部生徒会が主催します。</t>
+          <t xml:space="preserve">舞台芸術の先生のもと、温かく励まし合う雰囲気の中で、一人ひとりの特技や興味を披露します。</t>
         </is>
       </c>
       <c r="M55" t="inlineStr" s="2">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="O55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-16-winter-party-eagle-nest.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-17-talent-day.webp</t>
         </is>
       </c>
       <c r="P55" t="inlineStr" s="2">
@@ -5417,17 +5417,17 @@
     <row r="56">
       <c r="A56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-17-talent-day</t>
+          <t xml:space="preserve">2026-12-18-tea-party-pta-for-all</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-17</t>
+          <t xml:space="preserve">2026-12-18</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-17</t>
+          <t xml:space="preserve">2026-12-18</t>
         </is>
       </c>
       <c r="D56" t="inlineStr" s="3">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="E56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">PTA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr" s="2">
@@ -5457,22 +5457,22 @@
       </c>
       <c r="I56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Talent Day</t>
+          <t xml:space="preserve">Tea Party / PTA for all</t>
         </is>
       </c>
       <c r="J56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">タレントデー</t>
+          <t xml:space="preserve">PTAティーパーティー（どなたでも参加できます）</t>
         </is>
       </c>
       <c r="K56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students have the opportunity to showcase their unique talents and interests in a supportive and encouraging environment led by the performing arts teacher.</t>
+          <t xml:space="preserve">Families are invited to enjoy refreshments while connecting with the PTA, school staff, and other members of the community.</t>
         </is>
       </c>
       <c r="L56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">舞台芸術の先生のもと、温かく励まし合う雰囲気の中で、一人ひとりの特技や興味を披露します。</t>
+          <t xml:space="preserve">軽食を楽しみながら、PTA、教職員、コミュニティの皆様と交流していただける集いです。</t>
         </is>
       </c>
       <c r="M56" t="inlineStr" s="2">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="O56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-17-talent-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-18-tea-party-pta-for-all.webp</t>
         </is>
       </c>
       <c r="P56" t="inlineStr" s="2">
@@ -5514,7 +5514,7 @@
     <row r="57">
       <c r="A57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-18-tea-party-pta-for-all</t>
+          <t xml:space="preserve">2026-12-18-eagle-bucks-store</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="3">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="E57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTA</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G57" t="inlineStr" s="2">
@@ -5554,22 +5554,22 @@
       </c>
       <c r="I57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Tea Party / PTA for all</t>
+          <t xml:space="preserve">Eagle Bucks Store</t>
         </is>
       </c>
       <c r="J57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTAティーパーティー（どなたでも参加できます）</t>
+          <t xml:space="preserve">イーグルバックス・ストア</t>
         </is>
       </c>
       <c r="K57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Families are invited to enjoy refreshments while connecting with the PTA, school staff, and other members of the community.</t>
+          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
         </is>
       </c>
       <c r="L57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">軽食を楽しみながら、PTA、教職員、コミュニティの皆様と交流していただける集いです。</t>
+          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
         </is>
       </c>
       <c r="M57" t="inlineStr" s="2">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="O57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-18-tea-party-pta-for-all.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-18-eagle-bucks-store.webp</t>
         </is>
       </c>
       <c r="P57" t="inlineStr" s="2">
@@ -5611,17 +5611,17 @@
     <row r="58">
       <c r="A58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-18-eagle-bucks-store</t>
+          <t xml:space="preserve">2026-12-19-end-of-term-1-activity-sleep-over-program-g6-10</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-18</t>
+          <t xml:space="preserve">2026-12-19</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-18</t>
+          <t xml:space="preserve">2026-12-19</t>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="3">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F58" t="inlineStr" s="2">
@@ -5651,22 +5651,22 @@
       </c>
       <c r="I58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Eagle Bucks Store</t>
+          <t xml:space="preserve">End of Term 1 Activity-Sleep Over Program: G6-10</t>
         </is>
       </c>
       <c r="J58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">イーグルバックス・ストア</t>
+          <t xml:space="preserve">第1学期末行事：宿泊プログラム（G6–10）</t>
         </is>
       </c>
       <c r="K58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
+          <t xml:space="preserve">Grade 6 to 10 students will take part in a school sleepover program to celebrate the end of Term 1 through shared activities and community building.</t>
         </is>
       </c>
       <c r="L58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
+          <t xml:space="preserve">6～10年生が校内での宿泊プログラムに参加し、共に活動しながら仲間づくりを行い、第1学期の終わりを祝います。</t>
         </is>
       </c>
       <c r="M58" t="inlineStr" s="2">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="O58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-18-eagle-bucks-store.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-19-end-of-term-1-activity-sleep-over-program-g6-10.webp</t>
         </is>
       </c>
       <c r="P58" t="inlineStr" s="2">
@@ -5708,17 +5708,17 @@
     <row r="59">
       <c r="A59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-19-end-of-term-1-activity-sleep-over-program-g6-10</t>
+          <t xml:space="preserve">2026-12-21-winter-study-camp-g11-12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-19</t>
+          <t xml:space="preserve">2026-12-21</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-19</t>
+          <t xml:space="preserve">2026-12-23</t>
         </is>
       </c>
       <c r="D59" t="inlineStr" s="3">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="E59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F59" t="inlineStr" s="2">
@@ -5748,22 +5748,22 @@
       </c>
       <c r="I59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">End of Term 1 Activity-Sleep Over Program: G6-10</t>
+          <t xml:space="preserve">Winter Study Camp: G11-12</t>
         </is>
       </c>
       <c r="J59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第1学期末行事：宿泊プログラム（G6–10）</t>
+          <t xml:space="preserve">冬季学習合宿：G11–12</t>
         </is>
       </c>
       <c r="K59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 6 to 10 students will take part in a school sleepover program to celebrate the end of Term 1 through shared activities and community building.</t>
+          <t xml:space="preserve">Grade 11 and 12 students will take part in an off-campus Winter Study Camp focused on concentrated study, academic review, and exam preparation.</t>
         </is>
       </c>
       <c r="L59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">6～10年生が校内での宿泊プログラムに参加し、共に活動しながら仲間づくりを行い、第1学期の終わりを祝います。</t>
+          <t xml:space="preserve">11・12年生が校外での冬季学習合宿に参加し、集中学習、復習、試験対策に取り組みます。</t>
         </is>
       </c>
       <c r="M59" t="inlineStr" s="2">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-19-end-of-term-1-activity-sleep-over-program-g6-10.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-12-21-winter-study-camp-g11-12.webp</t>
         </is>
       </c>
       <c r="P59" t="inlineStr" s="2">
@@ -5805,17 +5805,17 @@
     <row r="60">
       <c r="A60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-12-21-winter-study-camp-g11-12</t>
+          <t xml:space="preserve">2027-01-08-parent-teacher-conferences</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-21</t>
+          <t xml:space="preserve">2027-01-08</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-12-23</t>
+          <t xml:space="preserve">2027-01-08</t>
         </is>
       </c>
       <c r="D60" t="inlineStr" s="3">
@@ -5825,17 +5825,17 @@
       </c>
       <c r="E60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="H60" t="inlineStr" s="2">
@@ -5845,22 +5845,22 @@
       </c>
       <c r="I60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Winter Study Camp: G11-12</t>
+          <t xml:space="preserve">Parent Teacher Conferences</t>
         </is>
       </c>
       <c r="J60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">冬季学習合宿：G11–12</t>
+          <t xml:space="preserve">保護者面談</t>
         </is>
       </c>
       <c r="K60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 11 and 12 students will take part in an off-campus Winter Study Camp focused on concentrated study, academic review, and exam preparation.</t>
+          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on this day.</t>
         </is>
       </c>
       <c r="L60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11・12年生が校外での冬季学習合宿に参加し、集中学習、復習、試験対策に取り組みます。</t>
+          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。当日、生徒は登校しません。</t>
         </is>
       </c>
       <c r="M60" t="inlineStr" s="2">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="O60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-12-21-winter-study-camp-g11-12.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-19-parent-teacher-conferences.webp</t>
         </is>
       </c>
       <c r="P60" t="inlineStr" s="2">
@@ -5902,17 +5902,17 @@
     <row r="61">
       <c r="A61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-08-parent-teacher-conferences</t>
+          <t xml:space="preserve">2027-01-11-clubs-pause</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-08</t>
+          <t xml:space="preserve">2027-01-11</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-08</t>
+          <t xml:space="preserve">2027-01-15</t>
         </is>
       </c>
       <c r="D61" t="inlineStr" s="3">
@@ -5927,12 +5927,12 @@
       </c>
       <c r="F61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H61" t="inlineStr" s="2">
@@ -5942,22 +5942,22 @@
       </c>
       <c r="I61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parent Teacher Conferences</t>
+          <t xml:space="preserve">Clubs Pause</t>
         </is>
       </c>
       <c r="J61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者面談</t>
+          <t xml:space="preserve">クラブ活動休止</t>
         </is>
       </c>
       <c r="K61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on this day.</t>
+          <t xml:space="preserve">After-school clubs are paused during this period. Bus reminder: the afternoon Red bus runs only on club days, so it does not run while clubs are paused. Please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
         </is>
       </c>
       <c r="L61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。当日、生徒は登校しません。</t>
+          <t xml:space="preserve">この期間、放課後のクラブ活動はお休みです。【バスについて】午後の赤バスはクラブ活動がある日のみ運行するため、休止期間中は運行しません。午後の下校時は青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
         </is>
       </c>
       <c r="M61" t="inlineStr" s="2">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="O61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-19-parent-teacher-conferences.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P61" t="inlineStr" s="2">
@@ -5999,17 +5999,17 @@
     <row r="62">
       <c r="A62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-11-clubs-pause</t>
+          <t xml:space="preserve">2027-01-14-g10-parent-info-session-high-school-subject-choi</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-11</t>
+          <t xml:space="preserve">2027-01-14</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-15</t>
+          <t xml:space="preserve">2027-01-14</t>
         </is>
       </c>
       <c r="D62" t="inlineStr" s="3">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="E62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G62" t="inlineStr" s="2">
@@ -6039,22 +6039,22 @@
       </c>
       <c r="I62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Clubs Pause</t>
+          <t xml:space="preserve">G10 Parent info Session (High School Subject Choice)</t>
         </is>
       </c>
       <c r="J62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クラブ活動休止</t>
+          <t xml:space="preserve">G10保護者向け説明会（高等部科目選択）</t>
         </is>
       </c>
       <c r="K62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">After-school clubs are paused during this period. Bus reminder: the afternoon Red bus runs only on club days, so it does not run while clubs are paused. Please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
+          <t xml:space="preserve">Grade 10 parents are invited to an information session about DP subject choices and guidance for planning the next stage of their child’s learning.</t>
         </is>
       </c>
       <c r="L62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">この期間、放課後のクラブ活動はお休みです。【バスについて】午後の赤バスはクラブ活動がある日のみ運行するため、休止期間中は運行しません。午後の下校時は青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
+          <t xml:space="preserve">10年生の保護者の皆様を対象に、DPの科目選択と、お子様の次のステージの学びを計画するためのガイダンスを行います。</t>
         </is>
       </c>
       <c r="M62" t="inlineStr" s="2">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="O62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">compass/images/events/2027-01-14-g10-parent-info-session-high-school-subject-choi.webp</t>
         </is>
       </c>
       <c r="P62" t="inlineStr" s="2">
@@ -6096,17 +6096,17 @@
     <row r="63">
       <c r="A63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-14-g10-parent-info-session-high-school-subject-choi</t>
+          <t xml:space="preserve">2027-01-18-clubs-resume</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-14</t>
+          <t xml:space="preserve">2027-01-18</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-14</t>
+          <t xml:space="preserve">2027-01-18</t>
         </is>
       </c>
       <c r="D63" t="inlineStr" s="3">
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G63" t="inlineStr" s="2">
@@ -6136,22 +6136,22 @@
       </c>
       <c r="I63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G10 Parent info Session (High School Subject Choice)</t>
+          <t xml:space="preserve">Clubs Resume</t>
         </is>
       </c>
       <c r="J63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G10保護者向け説明会（高等部科目選択）</t>
+          <t xml:space="preserve">クラブ活動再開</t>
         </is>
       </c>
       <c r="K63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 10 parents are invited to an information session about DP subject choices and guidance for planning the next stage of their child’s learning.</t>
+          <t xml:space="preserve">After-school clubs start again today. Bus reminder: the afternoon Red bus runs only on club days. On other days, please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
         </is>
       </c>
       <c r="L63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10年生の保護者の皆様を対象に、DPの科目選択と、お子様の次のステージの学びを計画するためのガイダンスを行います。</t>
+          <t xml:space="preserve">本日から放課後のクラブ活動が再開します。【バスについて】午後の赤バスはクラブ活動がある日のみ運行します。それ以外の日は、午後の下校時に青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
         </is>
       </c>
       <c r="M63" t="inlineStr" s="2">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-01-14-g10-parent-info-session-high-school-subject-choi.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P63" t="inlineStr" s="2">
@@ -6193,17 +6193,17 @@
     <row r="64">
       <c r="A64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-18-clubs-resume</t>
+          <t xml:space="preserve">2027-01-22-open-campus</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-18</t>
+          <t xml:space="preserve">2027-01-22</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-18</t>
+          <t xml:space="preserve">2027-01-22</t>
         </is>
       </c>
       <c r="D64" t="inlineStr" s="3">
@@ -6233,22 +6233,22 @@
       </c>
       <c r="I64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Clubs Resume</t>
+          <t xml:space="preserve">Open Campus</t>
         </is>
       </c>
       <c r="J64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クラブ活動再開</t>
+          <t xml:space="preserve">オープンキャンパス</t>
         </is>
       </c>
       <c r="K64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">After-school clubs start again today. Bus reminder: the afternoon Red bus runs only on club days. On other days, please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
+          <t xml:space="preserve">Any person interested in seeing the daily operation of the school is invited to join a tour of the school during its regular hours.</t>
         </is>
       </c>
       <c r="L64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">本日から放課後のクラブ活動が再開します。【バスについて】午後の赤バスはクラブ活動がある日のみ運行します。それ以外の日は、午後の下校時に青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
+          <t xml:space="preserve">学校の日常の様子にご関心のある方は、通常授業時間中の校内見学にご参加いただけます。</t>
         </is>
       </c>
       <c r="M64" t="inlineStr" s="2">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="O64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">compass/images/events/2027-01-22-open-campus.webp</t>
         </is>
       </c>
       <c r="P64" t="inlineStr" s="2">
@@ -6290,17 +6290,17 @@
     <row r="65">
       <c r="A65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-22-open-campus</t>
+          <t xml:space="preserve">2027-01-23-alumni-talk</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-22</t>
+          <t xml:space="preserve">2027-01-23</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-22</t>
+          <t xml:space="preserve">2027-01-23</t>
         </is>
       </c>
       <c r="D65" t="inlineStr" s="3">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="E65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F65" t="inlineStr" s="2">
@@ -6330,22 +6330,22 @@
       </c>
       <c r="I65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Open Campus</t>
+          <t xml:space="preserve">Alumni Talk</t>
         </is>
       </c>
       <c r="J65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">オープンキャンパス</t>
+          <t xml:space="preserve">卒業生トーク</t>
         </is>
       </c>
       <c r="K65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Any person interested in seeing the daily operation of the school is invited to join a tour of the school during its regular hours.</t>
+          <t xml:space="preserve">Alumni will share their experiences and advice with students, offering insight into life after School and future pathways.</t>
         </is>
       </c>
       <c r="L65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学校の日常の様子にご関心のある方は、通常授業時間中の校内見学にご参加いただけます。</t>
+          <t xml:space="preserve">卒業生が自身の経験やアドバイスを生徒に伝え、卒業後の生活や将来の進路について話します。</t>
         </is>
       </c>
       <c r="M65" t="inlineStr" s="2">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="O65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-01-22-open-campus.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-01-23-alumni-talk.webp</t>
         </is>
       </c>
       <c r="P65" t="inlineStr" s="2">
@@ -6387,17 +6387,17 @@
     <row r="66">
       <c r="A66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-23-alumni-talk</t>
+          <t xml:space="preserve">2027-01-27-natural-disaster-field-trip</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-23</t>
+          <t xml:space="preserve">2027-01-27</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-23</t>
+          <t xml:space="preserve">2027-01-27</t>
         </is>
       </c>
       <c r="D66" t="inlineStr" s="3">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="E66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">ELC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr" s="2">
@@ -6427,22 +6427,22 @@
       </c>
       <c r="I66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Alumni Talk</t>
+          <t xml:space="preserve">Natural Disaster Field Trip</t>
         </is>
       </c>
       <c r="J66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">卒業生トーク</t>
+          <t xml:space="preserve">防災校外学習</t>
         </is>
       </c>
       <c r="K66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Alumni will share their experiences and advice with students, offering insight into life after School and future pathways.</t>
+          <t xml:space="preserve">Students explore disaster preparedness and safety through interactive learning experiences related to natural disasters and emergency response.</t>
         </is>
       </c>
       <c r="L66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">卒業生が自身の経験やアドバイスを生徒に伝え、卒業後の生活や将来の進路について話します。</t>
+          <t xml:space="preserve">自然災害や緊急時の対応に関する体験型学習を通して、防災と安全について学びます。</t>
         </is>
       </c>
       <c r="M66" t="inlineStr" s="2">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="O66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-01-23-alumni-talk.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-01-27-natural-disaster-field-trip.webp</t>
         </is>
       </c>
       <c r="P66" t="inlineStr" s="2">
@@ -6484,17 +6484,17 @@
     <row r="67">
       <c r="A67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-27-natural-disaster-field-trip</t>
+          <t xml:space="preserve">2027-01-30-model-united-nations-event-mun</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-27</t>
+          <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-27</t>
+          <t xml:space="preserve">2027-01-30</t>
         </is>
       </c>
       <c r="D67" t="inlineStr" s="3">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="E67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F67" t="inlineStr" s="2">
@@ -6524,22 +6524,22 @@
       </c>
       <c r="I67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Natural Disaster Field Trip</t>
+          <t xml:space="preserve">Model United Nations Event (MUN)</t>
         </is>
       </c>
       <c r="J67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">防災校外学習</t>
+          <t xml:space="preserve">模擬国連（MUN）</t>
         </is>
       </c>
       <c r="K67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students explore disaster preparedness and safety through interactive learning experiences related to natural disasters and emergency response.</t>
+          <t xml:space="preserve">Students will participate in Model United Nations, developing public speaking, research, collaboration, and global awareness through discussion of real-world issues.</t>
         </is>
       </c>
       <c r="L67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">自然災害や緊急時の対応に関する体験型学習を通して、防災と安全について学びます。</t>
+          <t xml:space="preserve">模擬国連に参加し、現実の課題について議論することで、スピーチ力、調査力、協働する力、国際的な意識を育みます。</t>
         </is>
       </c>
       <c r="M67" t="inlineStr" s="2">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="O67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-01-27-natural-disaster-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-01-30-model-united-nations-event-mun.webp</t>
         </is>
       </c>
       <c r="P67" t="inlineStr" s="2">
@@ -6581,17 +6581,17 @@
     <row r="68">
       <c r="A68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-01-30-model-united-nations-event-mun</t>
+          <t xml:space="preserve">2027-02-01-friendly-volleyball-tournament-internal</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-30</t>
+          <t xml:space="preserve">2027-02-01</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-01-30</t>
+          <t xml:space="preserve">2027-02-05</t>
         </is>
       </c>
       <c r="D68" t="inlineStr" s="3">
@@ -6621,22 +6621,22 @@
       </c>
       <c r="I68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Model United Nations Event (MUN)</t>
+          <t xml:space="preserve">Friendly Volleyball Tournament (Internal)</t>
         </is>
       </c>
       <c r="J68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">模擬国連（MUN）</t>
+          <t xml:space="preserve">校内バレーボール大会</t>
         </is>
       </c>
       <c r="K68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will participate in Model United Nations, developing public speaking, research, collaboration, and global awareness through discussion of real-world issues.</t>
+          <t xml:space="preserve">Students will take part in a friendly internal volleyball tournament, promoting teamwork, sportsmanship, and school spirit.</t>
         </is>
       </c>
       <c r="L68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">模擬国連に参加し、現実の課題について議論することで、スピーチ力、調査力、協働する力、国際的な意識を育みます。</t>
+          <t xml:space="preserve">校内バレーボール大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
         </is>
       </c>
       <c r="M68" t="inlineStr" s="2">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="O68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-01-30-model-united-nations-event-mun.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-01-friendly-volleyball-tournament-internal.webp</t>
         </is>
       </c>
       <c r="P68" t="inlineStr" s="2">
@@ -6678,7 +6678,7 @@
     <row r="69">
       <c r="A69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-01-friendly-volleyball-tournament-internal</t>
+          <t xml:space="preserve">2027-02-01-concept-con-language</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="3">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="E69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr" s="2">
@@ -6718,22 +6718,22 @@
       </c>
       <c r="I69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Friendly Volleyball Tournament (Internal)</t>
+          <t xml:space="preserve">Concept Con (Language)</t>
         </is>
       </c>
       <c r="J69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内バレーボール大会</t>
+          <t xml:space="preserve">コンセプト・コン（言語）</t>
         </is>
       </c>
       <c r="K69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in a friendly internal volleyball tournament, promoting teamwork, sportsmanship, and school spirit.</t>
+          <t xml:space="preserve">Students celebrate language and communication through presentations, performances, and projects that showcase their learning and creativity.</t>
         </is>
       </c>
       <c r="L69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内バレーボール大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
+          <t xml:space="preserve">学びと創造性を示す発表、パフォーマンス、プロジェクトを通して、言語とコミュニケーションを祝います。</t>
         </is>
       </c>
       <c r="M69" t="inlineStr" s="2">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="O69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-01-friendly-volleyball-tournament-internal.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-01-concept-con-language.webp</t>
         </is>
       </c>
       <c r="P69" t="inlineStr" s="2">
@@ -6775,17 +6775,17 @@
     <row r="70">
       <c r="A70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-01-concept-con-language</t>
+          <t xml:space="preserve">2027-02-18-career-support-second-career-roundtable-and-care</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-01</t>
+          <t xml:space="preserve">2027-02-18</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-05</t>
+          <t xml:space="preserve">2027-02-18</t>
         </is>
       </c>
       <c r="D70" t="inlineStr" s="3">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="E70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G70" t="inlineStr" s="2">
@@ -6815,22 +6815,22 @@
       </c>
       <c r="I70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Concept Con (Language)</t>
+          <t xml:space="preserve">Career Support: Second Career Roundtable and Career Fair</t>
         </is>
       </c>
       <c r="J70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">コンセプト・コン（言語）</t>
+          <t xml:space="preserve">進路支援：第2回キャリア座談会・キャリアフェア</t>
         </is>
       </c>
       <c r="K70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students celebrate language and communication through presentations, performances, and projects that showcase their learning and creativity.</t>
+          <t xml:space="preserve">An informative event where students and parents can learn about IB university admissions, holistic admissions strategies in Japan and abroad, and explore future academic and career opportunities through discussions with experts and representatives.</t>
         </is>
       </c>
       <c r="L70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学びと創造性を示す発表、パフォーマンス、プロジェクトを通して、言語とコミュニケーションを祝います。</t>
+          <t xml:space="preserve">専門家や関係者との対話を通して、生徒と保護者の皆様がIBでの大学入試、国内外の総合型選抜の戦略について学び、将来の進学やキャリアの可能性を探る説明会です。</t>
         </is>
       </c>
       <c r="M70" t="inlineStr" s="2">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-01-concept-con-language.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-18-career-support-second-career-roundtable-and-care.webp</t>
         </is>
       </c>
       <c r="P70" t="inlineStr" s="2">
@@ -6872,17 +6872,17 @@
     <row r="71">
       <c r="A71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-18-career-support-second-career-roundtable-and-care</t>
+          <t xml:space="preserve">2027-02-19-collective-field-trip</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-18</t>
+          <t xml:space="preserve">2027-02-19</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-18</t>
+          <t xml:space="preserve">2027-02-19</t>
         </is>
       </c>
       <c r="D71" t="inlineStr" s="3">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="E71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G71" t="inlineStr" s="2">
@@ -6912,22 +6912,22 @@
       </c>
       <c r="I71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Career Support: Second Career Roundtable and Career Fair</t>
+          <t xml:space="preserve">Collective Field Trip</t>
         </is>
       </c>
       <c r="J71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">進路支援：第2回キャリア座談会・キャリアフェア</t>
+          <t xml:space="preserve">合同校外学習</t>
         </is>
       </c>
       <c r="K71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An informative event where students and parents can learn about IB university admissions, holistic admissions strategies in Japan and abroad, and explore future academic and career opportunities through discussions with experts and representatives.</t>
+          <t xml:space="preserve">Students participate in an off-campus learning experience that connects classroom learning with real-world exploration and discovery.</t>
         </is>
       </c>
       <c r="L71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">専門家や関係者との対話を通して、生徒と保護者の皆様がIBでの大学入試、国内外の総合型選抜の戦略について学び、将来の進学やキャリアの可能性を探る説明会です。</t>
+          <t xml:space="preserve">校外での学習体験を通して、教室での学びを実社会での探究や発見と結びつけます。</t>
         </is>
       </c>
       <c r="M71" t="inlineStr" s="2">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="O71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-18-career-support-second-career-roundtable-and-care.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-19-collective-field-trip.webp</t>
         </is>
       </c>
       <c r="P71" t="inlineStr" s="2">
@@ -6969,17 +6969,17 @@
     <row r="72">
       <c r="A72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-19-collective-field-trip</t>
+          <t xml:space="preserve">2027-02-22-world-thinking-day</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-19</t>
+          <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-19</t>
+          <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
       <c r="D72" t="inlineStr" s="3">
@@ -6989,7 +6989,7 @@
       </c>
       <c r="E72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr" s="2">
@@ -7009,22 +7009,22 @@
       </c>
       <c r="I72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Collective Field Trip</t>
+          <t xml:space="preserve">World Thinking Day</t>
         </is>
       </c>
       <c r="J72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合同校外学習</t>
+          <t xml:space="preserve">ワールド・シンキング・デー</t>
         </is>
       </c>
       <c r="K72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students participate in an off-campus learning experience that connects classroom learning with real-world exploration and discovery.</t>
+          <t xml:space="preserve">Students learn about cultures, traditions, and global citizenship while celebrating international understanding and connection.</t>
         </is>
       </c>
       <c r="L72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校外での学習体験を通して、教室での学びを実社会での探究や発見と結びつけます。</t>
+          <t xml:space="preserve">国際理解とつながりを祝いながら、さまざまな文化や伝統、地球市民としてのあり方について学びます。</t>
         </is>
       </c>
       <c r="M72" t="inlineStr" s="2">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="O72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-19-collective-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-22-world-thinking-day.webp</t>
         </is>
       </c>
       <c r="P72" t="inlineStr" s="2">
@@ -7066,7 +7066,7 @@
     <row r="73">
       <c r="A73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-22-world-thinking-day</t>
+          <t xml:space="preserve">2027-02-22-secondary-sports-day-rehearsal-1</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="3">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="E73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F73" t="inlineStr" s="2">
@@ -7106,22 +7106,22 @@
       </c>
       <c r="I73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">World Thinking Day</t>
+          <t xml:space="preserve">Secondary Sports Day Rehearsal #1</t>
         </is>
       </c>
       <c r="J73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ワールド・シンキング・デー</t>
+          <t xml:space="preserve">中等部運動会リハーサル #1</t>
         </is>
       </c>
       <c r="K73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students learn about cultures, traditions, and global citizenship while celebrating international understanding and connection.</t>
+          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
         </is>
       </c>
       <c r="L73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国際理解とつながりを祝いながら、さまざまな文化や伝統、地球市民としてのあり方について学びます。</t>
+          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
         </is>
       </c>
       <c r="M73" t="inlineStr" s="2">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="O73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-22-world-thinking-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-22-secondary-sports-day-rehearsal-1.webp</t>
         </is>
       </c>
       <c r="P73" t="inlineStr" s="2">
@@ -7163,17 +7163,17 @@
     <row r="74">
       <c r="A74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-22-secondary-sports-day-rehearsal-1</t>
+          <t xml:space="preserve">2027-02-25-primary-sports-day-rehearsal-1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-22</t>
+          <t xml:space="preserve">2027-02-25</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-22</t>
+          <t xml:space="preserve">2027-02-25</t>
         </is>
       </c>
       <c r="D74" t="inlineStr" s="3">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="E74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F74" t="inlineStr" s="2">
@@ -7203,22 +7203,22 @@
       </c>
       <c r="I74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary Sports Day Rehearsal #1</t>
+          <t xml:space="preserve">Primary Sports Day Rehearsal #1</t>
         </is>
       </c>
       <c r="J74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部運動会リハーサル #1</t>
+          <t xml:space="preserve">小学部運動会リハーサル #1</t>
         </is>
       </c>
       <c r="K74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
+          <t xml:space="preserve">Students begin preparing for Sports Day by practicing events, routines, and teamwork activities.</t>
         </is>
       </c>
       <c r="L74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
+          <t xml:space="preserve">種目、流れ、チームワークの練習を通して、運動会に向けた準備を始めます。</t>
         </is>
       </c>
       <c r="M74" t="inlineStr" s="2">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="O74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-22-secondary-sports-day-rehearsal-1.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-25-primary-sports-day-rehearsal-1.webp</t>
         </is>
       </c>
       <c r="P74" t="inlineStr" s="2">
@@ -7260,17 +7260,17 @@
     <row r="75">
       <c r="A75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-25-primary-sports-day-rehearsal-1</t>
+          <t xml:space="preserve">2027-02-26-parents-morning-2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-25</t>
+          <t xml:space="preserve">2027-02-26</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-25</t>
+          <t xml:space="preserve">2027-02-26</t>
         </is>
       </c>
       <c r="D75" t="inlineStr" s="3">
@@ -7280,12 +7280,12 @@
       </c>
       <c r="E75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G75" t="inlineStr" s="2">
@@ -7300,22 +7300,22 @@
       </c>
       <c r="I75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary Sports Day Rehearsal #1</t>
+          <t xml:space="preserve">Parents Morning #2</t>
         </is>
       </c>
       <c r="J75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小学部運動会リハーサル #1</t>
+          <t xml:space="preserve">朝の授業参観 #2</t>
         </is>
       </c>
       <c r="K75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students begin preparing for Sports Day by practicing events, routines, and teamwork activities.</t>
+          <t xml:space="preserve">ELC and Primary Parents are invited to come and see the lessons in the morning and experience the morning routines with their child.</t>
         </is>
       </c>
       <c r="L75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">種目、流れ、チームワークの練習を通して、運動会に向けた準備を始めます。</t>
+          <t xml:space="preserve">幼稚部・小学部の保護者の皆様をお招きし、朝の授業をご参観いただき、お子様と一緒に朝の日課を体験していただきます。</t>
         </is>
       </c>
       <c r="M75" t="inlineStr" s="2">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="O75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-25-primary-sports-day-rehearsal-1.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-26-parents-morning-2.webp</t>
         </is>
       </c>
       <c r="P75" t="inlineStr" s="2">
@@ -7357,7 +7357,7 @@
     <row r="76">
       <c r="A76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-26-parents-morning-2</t>
+          <t xml:space="preserve">2027-02-26-eagle-talks</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="3">
@@ -7397,22 +7397,22 @@
       </c>
       <c r="I76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parents Morning #2</t>
+          <t xml:space="preserve">Eagle Talks</t>
         </is>
       </c>
       <c r="J76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">朝の授業参観 #2</t>
+          <t xml:space="preserve">イーグル・トーク</t>
         </is>
       </c>
       <c r="K76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC and Primary Parents are invited to come and see the lessons in the morning and experience the morning routines with their child.</t>
+          <t xml:space="preserve">Students share ideas, experiences, and learning through short presentations designed to build confidence, communication, and leadership skills.</t>
         </is>
       </c>
       <c r="L76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部・小学部の保護者の皆様をお招きし、朝の授業をご参観いただき、お子様と一緒に朝の日課を体験していただきます。</t>
+          <t xml:space="preserve">短いプレゼンテーションを通して考えや経験、学びを共有し、自信、コミュニケーション力、リーダーシップを育みます。</t>
         </is>
       </c>
       <c r="M76" t="inlineStr" s="2">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="O76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-26-parents-morning-2.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-02-26-eagle-talks.webp</t>
         </is>
       </c>
       <c r="P76" t="inlineStr" s="2">
@@ -7454,17 +7454,17 @@
     <row r="77">
       <c r="A77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-02-26-eagle-talks</t>
+          <t xml:space="preserve">2027-03-04-grade-1-2-musical</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-26</t>
+          <t xml:space="preserve">2027-03-04</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-02-26</t>
+          <t xml:space="preserve">2027-03-05</t>
         </is>
       </c>
       <c r="D77" t="inlineStr" s="3">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="E77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F77" t="inlineStr" s="2">
@@ -7494,22 +7494,22 @@
       </c>
       <c r="I77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Eagle Talks</t>
+          <t xml:space="preserve">Grade 1, 2 Musical</t>
         </is>
       </c>
       <c r="J77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">イーグル・トーク</t>
+          <t xml:space="preserve">1・2年生ミュージカル</t>
         </is>
       </c>
       <c r="K77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students share ideas, experiences, and learning through short presentations designed to build confidence, communication, and leadership skills.</t>
+          <t xml:space="preserve">Students showcase their creativity and confidence through a musical performance featuring songs, acting, and teamwork.</t>
         </is>
       </c>
       <c r="L77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">短いプレゼンテーションを通して考えや経験、学びを共有し、自信、コミュニケーション力、リーダーシップを育みます。</t>
+          <t xml:space="preserve">歌、演技、チームワークによるミュージカルを通して、創造性と自信あふれる姿を披露します。</t>
         </is>
       </c>
       <c r="M77" t="inlineStr" s="2">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="O77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-02-26-eagle-talks.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-04-grade-1-2-musical.webp</t>
         </is>
       </c>
       <c r="P77" t="inlineStr" s="2">
@@ -7551,12 +7551,12 @@
     <row r="78">
       <c r="A78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-04-grade-1-2-musical</t>
+          <t xml:space="preserve">2027-03-05-higashiyama-zoo-botanical-garden</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-04</t>
+          <t xml:space="preserve">2027-03-05</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="3">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="E78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G78" t="inlineStr" s="2">
@@ -7591,22 +7591,22 @@
       </c>
       <c r="I78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 1, 2 Musical</t>
+          <t xml:space="preserve">Higashiyama Zoo &amp; Botanical Garden</t>
         </is>
       </c>
       <c r="J78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1・2年生ミュージカル</t>
+          <t xml:space="preserve">東山動植物園</t>
         </is>
       </c>
       <c r="K78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students showcase their creativity and confidence through a musical performance featuring songs, acting, and teamwork.</t>
+          <t xml:space="preserve">Grade 7 Science students will visit Higashiyama Zoo and Botanical Gardens to support their learning through observation and real-world examples.</t>
         </is>
       </c>
       <c r="L78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">歌、演技、チームワークによるミュージカルを通して、創造性と自信あふれる姿を披露します。</t>
+          <t xml:space="preserve">7年生が理科の学習の一環として東山動植物園を訪れ、観察や実物を通して学びを深めます。</t>
         </is>
       </c>
       <c r="M78" t="inlineStr" s="2">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="O78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-04-grade-1-2-musical.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-05-higashiyama-zoo-botanical-garden.webp</t>
         </is>
       </c>
       <c r="P78" t="inlineStr" s="2">
@@ -7648,17 +7648,17 @@
     <row r="79">
       <c r="A79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-05-higashiyama-zoo-botanical-garden</t>
+          <t xml:space="preserve">2027-03-06-sat-test-6</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-05</t>
+          <t xml:space="preserve">2027-03-06</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-05</t>
+          <t xml:space="preserve">2027-03-06</t>
         </is>
       </c>
       <c r="D79" t="inlineStr" s="3">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="E79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F79" t="inlineStr" s="2">
@@ -7688,22 +7688,22 @@
       </c>
       <c r="I79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Higashiyama Zoo &amp; Botanical Garden</t>
+          <t xml:space="preserve">SAT Test #6</t>
         </is>
       </c>
       <c r="J79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">東山動植物園</t>
+          <t xml:space="preserve">SAT試験 第6回</t>
         </is>
       </c>
       <c r="K79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 7 Science students will visit Higashiyama Zoo and Botanical Gardens to support their learning through observation and real-world examples.</t>
+          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
         </is>
       </c>
       <c r="L79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">7年生が理科の学習の一環として東山動植物園を訪れ、観察や実物を通して学びを深めます。</t>
+          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
         </is>
       </c>
       <c r="M79" t="inlineStr" s="2">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="O79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-05-higashiyama-zoo-botanical-garden.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-06-sat-test-6.webp</t>
         </is>
       </c>
       <c r="P79" t="inlineStr" s="2">
@@ -7745,17 +7745,17 @@
     <row r="80">
       <c r="A80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-06-sat-test-6</t>
+          <t xml:space="preserve">2027-03-09-primary-sports-day-rehearsal-2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-06</t>
+          <t xml:space="preserve">2027-03-09</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-06</t>
+          <t xml:space="preserve">2027-03-09</t>
         </is>
       </c>
       <c r="D80" t="inlineStr" s="3">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="E80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F80" t="inlineStr" s="2">
@@ -7785,22 +7785,22 @@
       </c>
       <c r="I80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT Test #6</t>
+          <t xml:space="preserve">Primary Sports Day Rehearsal #2</t>
         </is>
       </c>
       <c r="J80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT試験 第6回</t>
+          <t xml:space="preserve">小学部運動会リハーサル #2</t>
         </is>
       </c>
       <c r="K80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
+          <t xml:space="preserve">Students continue building skills and confidence as they prepare for Sports Day events and activities.</t>
         </is>
       </c>
       <c r="L80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
+          <t xml:space="preserve">運動会の種目や活動に向けて準備を進めながら、技能と自信をさらに高めます。</t>
         </is>
       </c>
       <c r="M80" t="inlineStr" s="2">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="O80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-06-sat-test-6.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-09-primary-sports-day-rehearsal-2.webp</t>
         </is>
       </c>
       <c r="P80" t="inlineStr" s="2">
@@ -7842,17 +7842,17 @@
     <row r="81">
       <c r="A81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-09-primary-sports-day-rehearsal-2</t>
+          <t xml:space="preserve">2027-03-12-secondary-sports-day-rehearsal-2</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-09</t>
+          <t xml:space="preserve">2027-03-12</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-09</t>
+          <t xml:space="preserve">2027-03-12</t>
         </is>
       </c>
       <c r="D81" t="inlineStr" s="3">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="E81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F81" t="inlineStr" s="2">
@@ -7882,22 +7882,22 @@
       </c>
       <c r="I81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary Sports Day Rehearsal #2</t>
+          <t xml:space="preserve">Secondary Sports Day Rehearsal #2</t>
         </is>
       </c>
       <c r="J81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小学部運動会リハーサル #2</t>
+          <t xml:space="preserve">中等部運動会リハーサル #2</t>
         </is>
       </c>
       <c r="K81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students continue building skills and confidence as they prepare for Sports Day events and activities.</t>
+          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
         </is>
       </c>
       <c r="L81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会の種目や活動に向けて準備を進めながら、技能と自信をさらに高めます。</t>
+          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
         </is>
       </c>
       <c r="M81" t="inlineStr" s="2">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-09-primary-sports-day-rehearsal-2.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-12-secondary-sports-day-rehearsal-2.webp</t>
         </is>
       </c>
       <c r="P81" t="inlineStr" s="2">
@@ -7939,17 +7939,17 @@
     <row r="82">
       <c r="A82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-12-secondary-sports-day-rehearsal-2</t>
+          <t xml:space="preserve">2027-03-15-clubs-pause</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-12</t>
+          <t xml:space="preserve">2027-03-15</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-12</t>
+          <t xml:space="preserve">2027-03-19</t>
         </is>
       </c>
       <c r="D82" t="inlineStr" s="3">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="E82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F82" t="inlineStr" s="2">
@@ -7979,22 +7979,22 @@
       </c>
       <c r="I82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary Sports Day Rehearsal #2</t>
+          <t xml:space="preserve">Clubs Pause</t>
         </is>
       </c>
       <c r="J82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部運動会リハーサル #2</t>
+          <t xml:space="preserve">クラブ活動休止</t>
         </is>
       </c>
       <c r="K82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
+          <t xml:space="preserve">After-school clubs are paused during this period. Bus reminder: the afternoon Red bus runs only on club days, so it does not run while clubs are paused. Please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
         </is>
       </c>
       <c r="L82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
+          <t xml:space="preserve">この期間、放課後のクラブ活動はお休みです。【バスについて】午後の赤バスはクラブ活動がある日のみ運行するため、休止期間中は運行しません。午後の下校時は青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
         </is>
       </c>
       <c r="M82" t="inlineStr" s="2">
@@ -8009,7 +8009,7 @@
       </c>
       <c r="O82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-12-secondary-sports-day-rehearsal-2.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P82" t="inlineStr" s="2">
@@ -8036,17 +8036,17 @@
     <row r="83">
       <c r="A83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-15-clubs-pause</t>
+          <t xml:space="preserve">2027-03-18-japanese-culture-day</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-15</t>
+          <t xml:space="preserve">2027-03-18</t>
         </is>
       </c>
       <c r="C83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-19</t>
+          <t xml:space="preserve">2027-03-18</t>
         </is>
       </c>
       <c r="D83" t="inlineStr" s="3">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="F83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G83" t="inlineStr" s="2">
@@ -8076,22 +8076,22 @@
       </c>
       <c r="I83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Clubs Pause</t>
+          <t xml:space="preserve">Japanese Culture Day</t>
         </is>
       </c>
       <c r="J83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クラブ活動休止</t>
+          <t xml:space="preserve">日本文化デー</t>
         </is>
       </c>
       <c r="K83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">After-school clubs are paused during this period. Bus reminder: the afternoon Red bus runs only on club days, so it does not run while clubs are paused. Please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
+          <t xml:space="preserve">Students will deepen their understanding and appreciation of Japanese culture through a variety of interactive activities with school community.</t>
         </is>
       </c>
       <c r="L83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">この期間、放課後のクラブ活動はお休みです。【バスについて】午後の赤バスはクラブ活動がある日のみ運行するため、休止期間中は運行しません。午後の下校時は青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
+          <t xml:space="preserve">学校コミュニティとともにさまざまな体験型の活動に取り組み、日本文化への理解と関心を深めます。</t>
         </is>
       </c>
       <c r="M83" t="inlineStr" s="2">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="O83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">compass/images/events/2027-03-18-japanese-culture-day.webp</t>
         </is>
       </c>
       <c r="P83" t="inlineStr" s="2">
@@ -8133,17 +8133,17 @@
     <row r="84">
       <c r="A84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-18-japanese-culture-day</t>
+          <t xml:space="preserve">2027-03-19-eagle-bucks-store</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-18</t>
+          <t xml:space="preserve">2027-03-19</t>
         </is>
       </c>
       <c r="C84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-18</t>
+          <t xml:space="preserve">2027-03-19</t>
         </is>
       </c>
       <c r="D84" t="inlineStr" s="3">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="E84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G84" t="inlineStr" s="2">
@@ -8173,22 +8173,22 @@
       </c>
       <c r="I84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Japanese Culture Day</t>
+          <t xml:space="preserve">Eagle Bucks Store</t>
         </is>
       </c>
       <c r="J84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">日本文化デー</t>
+          <t xml:space="preserve">イーグルバックス・ストア</t>
         </is>
       </c>
       <c r="K84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will deepen their understanding and appreciation of Japanese culture through a variety of interactive activities with school community.</t>
+          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
         </is>
       </c>
       <c r="L84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学校コミュニティとともにさまざまな体験型の活動に取り組み、日本文化への理解と関心を深めます。</t>
+          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
         </is>
       </c>
       <c r="M84" t="inlineStr" s="2">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="O84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-18-japanese-culture-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-19-eagle-bucks-store.webp</t>
         </is>
       </c>
       <c r="P84" t="inlineStr" s="2">
@@ -8230,7 +8230,7 @@
     <row r="85">
       <c r="A85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-19-eagle-bucks-store</t>
+          <t xml:space="preserve">2027-03-19-tea-party-pta-for-all</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="3">
@@ -8250,12 +8250,12 @@
       </c>
       <c r="E85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">PTA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G85" t="inlineStr" s="2">
@@ -8270,22 +8270,22 @@
       </c>
       <c r="I85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Eagle Bucks Store</t>
+          <t xml:space="preserve">Tea Party / PTA for all</t>
         </is>
       </c>
       <c r="J85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">イーグルバックス・ストア</t>
+          <t xml:space="preserve">PTAティーパーティー（どなたでも参加できます）</t>
         </is>
       </c>
       <c r="K85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
+          <t xml:space="preserve">A social gathering organized by the PTA and Community Club where staff and students are welcome to enjoy a variety of teas, snacks, and friendly conversation together.</t>
         </is>
       </c>
       <c r="L85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
+          <t xml:space="preserve">PTAとコミュニティクラブが主催する交流会です。教職員や生徒も参加でき、さまざまなお茶や軽食、和やかな会話を楽しめます。</t>
         </is>
       </c>
       <c r="M85" t="inlineStr" s="2">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="O85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-19-eagle-bucks-store.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-19-tea-party-pta-for-all.webp</t>
         </is>
       </c>
       <c r="P85" t="inlineStr" s="2">
@@ -8327,7 +8327,7 @@
     <row r="86">
       <c r="A86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-19-tea-party-pta-for-all</t>
+          <t xml:space="preserve">2027-03-19-end-of-term-2-activity-g9-12</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="3">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="C86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-19</t>
+          <t xml:space="preserve">2027-03-20</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="3">
@@ -8347,12 +8347,12 @@
       </c>
       <c r="E86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTA</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G86" t="inlineStr" s="2">
@@ -8367,22 +8367,22 @@
       </c>
       <c r="I86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Tea Party / PTA for all</t>
+          <t xml:space="preserve">End of Term 2 Activity: G9-12</t>
         </is>
       </c>
       <c r="J86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTAティーパーティー（どなたでも参加できます）</t>
+          <t xml:space="preserve">第2学期末行事：G9–12</t>
         </is>
       </c>
       <c r="K86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A social gathering organized by the PTA and Community Club where staff and students are welcome to enjoy a variety of teas, snacks, and friendly conversation together.</t>
+          <t xml:space="preserve">Students will take part in an off-campus day trip activity to celebrate the end of Term 2.</t>
         </is>
       </c>
       <c r="L86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PTAとコミュニティクラブが主催する交流会です。教職員や生徒も参加でき、さまざまなお茶や軽食、和やかな会話を楽しめます。</t>
+          <t xml:space="preserve">第2学期の終わりを祝い、校外への日帰り活動に参加します。</t>
         </is>
       </c>
       <c r="M86" t="inlineStr" s="2">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="O86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-19-tea-party-pta-for-all.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-19-end-of-term-2-activity-g9-12.webp</t>
         </is>
       </c>
       <c r="P86" t="inlineStr" s="2">
@@ -8424,17 +8424,17 @@
     <row r="87">
       <c r="A87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-19-end-of-term-2-activity-g9-12</t>
+          <t xml:space="preserve">2027-03-20-end-of-term-2-activity-g6-8</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-19</t>
+          <t xml:space="preserve">2027-03-20</t>
         </is>
       </c>
       <c r="C87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-20</t>
+          <t xml:space="preserve">2027-03-21</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="3">
@@ -8444,7 +8444,7 @@
       </c>
       <c r="E87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F87" t="inlineStr" s="2">
@@ -8464,22 +8464,22 @@
       </c>
       <c r="I87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">End of Term 2 Activity: G9-12</t>
+          <t xml:space="preserve">End of Term 2 Activity: G6-8</t>
         </is>
       </c>
       <c r="J87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第2学期末行事：G9–12</t>
+          <t xml:space="preserve">第2学期末行事：G6–8</t>
         </is>
       </c>
       <c r="K87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in an off-campus day trip activity to celebrate the end of Term 2.</t>
+          <t xml:space="preserve">Students will take part in an overnight camp at an off-campus camping facility to celebrate the end of Term 2.</t>
         </is>
       </c>
       <c r="L87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第2学期の終わりを祝い、校外への日帰り活動に参加します。</t>
+          <t xml:space="preserve">第2学期の終わりを祝い、校外のキャンプ施設での一泊キャンプに参加します。</t>
         </is>
       </c>
       <c r="M87" t="inlineStr" s="2">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="O87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-19-end-of-term-2-activity-g9-12.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-20-end-of-term-2-activity-g6-8.webp</t>
         </is>
       </c>
       <c r="P87" t="inlineStr" s="2">
@@ -8521,17 +8521,17 @@
     <row r="88">
       <c r="A88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-20-end-of-term-2-activity-g6-8</t>
+          <t xml:space="preserve">2027-03-30-parent-teacher-conferences</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-20</t>
+          <t xml:space="preserve">2027-03-30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-21</t>
+          <t xml:space="preserve">2027-03-30</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="3">
@@ -8541,17 +8541,17 @@
       </c>
       <c r="E88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="H88" t="inlineStr" s="2">
@@ -8561,22 +8561,22 @@
       </c>
       <c r="I88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">End of Term 2 Activity: G6-8</t>
+          <t xml:space="preserve">Parent Teacher Conferences</t>
         </is>
       </c>
       <c r="J88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第2学期末行事：G6–8</t>
+          <t xml:space="preserve">保護者面談</t>
         </is>
       </c>
       <c r="K88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in an overnight camp at an off-campus camping facility to celebrate the end of Term 2.</t>
+          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on this day.</t>
         </is>
       </c>
       <c r="L88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第2学期の終わりを祝い、校外のキャンプ施設での一泊キャンプに参加します。</t>
+          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。当日、生徒は登校しません。</t>
         </is>
       </c>
       <c r="M88" t="inlineStr" s="2">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="O88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-20-end-of-term-2-activity-g6-8.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-30-parent-teacher-conferences.webp</t>
         </is>
       </c>
       <c r="P88" t="inlineStr" s="2">
@@ -8618,17 +8618,17 @@
     <row r="89">
       <c r="A89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-30-parent-teacher-conferences</t>
+          <t xml:space="preserve">2027-03-31-secondary-sports-day-rehearsal-3</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-30</t>
+          <t xml:space="preserve">2027-03-31</t>
         </is>
       </c>
       <c r="C89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-30</t>
+          <t xml:space="preserve">2027-03-31</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="3">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="E89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H89" t="inlineStr" s="2">
@@ -8658,22 +8658,22 @@
       </c>
       <c r="I89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parent Teacher Conferences</t>
+          <t xml:space="preserve">Secondary Sports Day Rehearsal #3</t>
         </is>
       </c>
       <c r="J89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者面談</t>
+          <t xml:space="preserve">中等部運動会リハーサル #3</t>
         </is>
       </c>
       <c r="K89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on this day.</t>
+          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
         </is>
       </c>
       <c r="L89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。当日、生徒は登校しません。</t>
+          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
         </is>
       </c>
       <c r="M89" t="inlineStr" s="2">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="O89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-30-parent-teacher-conferences.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-03-31-secondary-sports-day-rehearsal-3.webp</t>
         </is>
       </c>
       <c r="P89" t="inlineStr" s="2">
@@ -8715,7 +8715,7 @@
     <row r="90">
       <c r="A90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-31-secondary-sports-day-rehearsal-3</t>
+          <t xml:space="preserve">2027-03-31-clubs-pause</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="3">
@@ -8725,7 +8725,7 @@
       </c>
       <c r="C90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-31</t>
+          <t xml:space="preserve">2027-04-02</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="3">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="E90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F90" t="inlineStr" s="2">
@@ -8755,22 +8755,22 @@
       </c>
       <c r="I90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary Sports Day Rehearsal #3</t>
+          <t xml:space="preserve">Clubs Pause</t>
         </is>
       </c>
       <c r="J90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部運動会リハーサル #3</t>
+          <t xml:space="preserve">クラブ活動休止</t>
         </is>
       </c>
       <c r="K90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary students will prepare for Sports Day by practicing event routines, team organization, and activity expectations.</t>
+          <t xml:space="preserve">After-school clubs are paused during this period. Bus reminder: the afternoon Red bus runs only on club days, so it does not run while clubs are paused. Please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
         </is>
       </c>
       <c r="L90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">中等部の生徒が、種目の流れ、チーム編成、活動のルールを練習し、運動会に向けて準備します。</t>
+          <t xml:space="preserve">この期間、放課後のクラブ活動はお休みです。【バスについて】午後の赤バスはクラブ活動がある日のみ運行するため、休止期間中は運行しません。午後の下校時は青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
         </is>
       </c>
       <c r="M90" t="inlineStr" s="2">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="O90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-03-31-secondary-sports-day-rehearsal-3.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P90" t="inlineStr" s="2">
@@ -8812,17 +8812,17 @@
     <row r="91">
       <c r="A91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-03-31-clubs-pause</t>
+          <t xml:space="preserve">2027-04-01-primary-sports-day-rehearsal-3</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-03-31</t>
+          <t xml:space="preserve">2027-04-01</t>
         </is>
       </c>
       <c r="C91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-02</t>
+          <t xml:space="preserve">2027-04-01</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="3">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="E91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F91" t="inlineStr" s="2">
@@ -8852,22 +8852,22 @@
       </c>
       <c r="I91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Clubs Pause</t>
+          <t xml:space="preserve">Primary Sports Day Rehearsal #3</t>
         </is>
       </c>
       <c r="J91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クラブ活動休止</t>
+          <t xml:space="preserve">小学部運動会リハーサル #3</t>
         </is>
       </c>
       <c r="K91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">After-school clubs are paused during this period. Bus reminder: the afternoon Red bus runs only on club days, so it does not run while clubs are paused. Please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
+          <t xml:space="preserve">The final rehearsal provides students with an opportunity to practice events and ensure they are ready for Sports Day.</t>
         </is>
       </c>
       <c r="L91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">この期間、放課後のクラブ活動はお休みです。【バスについて】午後の赤バスはクラブ活動がある日のみ運行するため、休止期間中は運行しません。午後の下校時は青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
+          <t xml:space="preserve">最終リハーサルで各種目を練習し、運動会当日に向けて準備を整えます。</t>
         </is>
       </c>
       <c r="M91" t="inlineStr" s="2">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="O91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">compass/images/events/2027-04-01-primary-sports-day-rehearsal-3.webp</t>
         </is>
       </c>
       <c r="P91" t="inlineStr" s="2">
@@ -8909,17 +8909,17 @@
     <row r="92">
       <c r="A92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-01-primary-sports-day-rehearsal-3</t>
+          <t xml:space="preserve">2027-04-03-sports-day</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-01</t>
+          <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
       <c r="C92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-01</t>
+          <t xml:space="preserve">2027-04-03</t>
         </is>
       </c>
       <c r="D92" t="inlineStr" s="3">
@@ -8929,12 +8929,12 @@
       </c>
       <c r="E92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G92" t="inlineStr" s="2">
@@ -8949,22 +8949,22 @@
       </c>
       <c r="I92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary Sports Day Rehearsal #3</t>
+          <t xml:space="preserve">Sports Day</t>
         </is>
       </c>
       <c r="J92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小学部運動会リハーサル #3</t>
+          <t xml:space="preserve">運動会</t>
         </is>
       </c>
       <c r="K92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The final rehearsal provides students with an opportunity to practice events and ensure they are ready for Sports Day.</t>
+          <t xml:space="preserve">Students will take part in Sports Day activities, participating in team games, athletic challenges, and school spirit events.</t>
         </is>
       </c>
       <c r="L92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">最終リハーサルで各種目を練習し、運動会当日に向けて準備を整えます。</t>
+          <t xml:space="preserve">運動会に参加し、チームゲーム、運動競技、応援などの行事に取り組みます。</t>
         </is>
       </c>
       <c r="M92" t="inlineStr" s="2">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="O92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-01-primary-sports-day-rehearsal-3.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-03-sports-day.webp</t>
         </is>
       </c>
       <c r="P92" t="inlineStr" s="2">
@@ -9006,7 +9006,7 @@
     <row r="93">
       <c r="A93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-03-sports-day</t>
+          <t xml:space="preserve">2027-04-03-primary-sports-day-2027</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="3">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="E93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F93" t="inlineStr" s="2">
@@ -9046,22 +9046,22 @@
       </c>
       <c r="I93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Sports Day</t>
+          <t xml:space="preserve">Primary Sports Day 2027</t>
         </is>
       </c>
       <c r="J93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会</t>
+          <t xml:space="preserve">小学部運動会 2027</t>
         </is>
       </c>
       <c r="K93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in Sports Day activities, participating in team games, athletic challenges, and school spirit events.</t>
+          <t xml:space="preserve">Students participate in a day of fun, fitness, and friendly competition while demonstrating teamwork, perseverance, and sportsmanship.</t>
         </is>
       </c>
       <c r="L93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">運動会に参加し、チームゲーム、運動競技、応援などの行事に取り組みます。</t>
+          <t xml:space="preserve">チームワーク、粘り強さ、スポーツマンシップを発揮しながら、楽しく体を動かし、仲間と競い合う一日を過ごします。</t>
         </is>
       </c>
       <c r="M93" t="inlineStr" s="2">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="O93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-03-sports-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-03-primary-sports-day-2027.webp</t>
         </is>
       </c>
       <c r="P93" t="inlineStr" s="2">
@@ -9103,17 +9103,17 @@
     <row r="94">
       <c r="A94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-03-primary-sports-day-2027</t>
+          <t xml:space="preserve">2027-04-05-clubs-resume</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-03</t>
+          <t xml:space="preserve">2027-04-05</t>
         </is>
       </c>
       <c r="C94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-03</t>
+          <t xml:space="preserve">2027-04-05</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="3">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="E94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G94" t="inlineStr" s="2">
@@ -9143,22 +9143,22 @@
       </c>
       <c r="I94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary Sports Day 2027</t>
+          <t xml:space="preserve">Clubs Resume</t>
         </is>
       </c>
       <c r="J94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小学部運動会 2027</t>
+          <t xml:space="preserve">クラブ活動再開</t>
         </is>
       </c>
       <c r="K94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students participate in a day of fun, fitness, and friendly competition while demonstrating teamwork, perseverance, and sportsmanship.</t>
+          <t xml:space="preserve">After-school clubs start again today. Bus reminder: the afternoon Red bus runs only on club days. On other days, please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
         </is>
       </c>
       <c r="L94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">チームワーク、粘り強さ、スポーツマンシップを発揮しながら、楽しく体を動かし、仲間と競い合う一日を過ごします。</t>
+          <t xml:space="preserve">本日から放課後のクラブ活動が再開します。【バスについて】午後の赤バスはクラブ活動がある日のみ運行します。それ以外の日は、午後の下校時に青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
         </is>
       </c>
       <c r="M94" t="inlineStr" s="2">
@@ -9173,7 +9173,7 @@
       </c>
       <c r="O94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-03-primary-sports-day-2027.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P94" t="inlineStr" s="2">
@@ -9200,17 +9200,17 @@
     <row r="95">
       <c r="A95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-05-clubs-resume</t>
+          <t xml:space="preserve">2027-04-15-world-art-day</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-05</t>
+          <t xml:space="preserve">2027-04-15</t>
         </is>
       </c>
       <c r="C95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-05</t>
+          <t xml:space="preserve">2027-04-15</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="3">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="E95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G95" t="inlineStr" s="2">
@@ -9240,22 +9240,22 @@
       </c>
       <c r="I95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Clubs Resume</t>
+          <t xml:space="preserve">World Art Day</t>
         </is>
       </c>
       <c r="J95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クラブ活動再開</t>
+          <t xml:space="preserve">ワールド・アート・デー</t>
         </is>
       </c>
       <c r="K95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">After-school clubs start again today. Bus reminder: the afternoon Red bus runs only on club days. On other days, please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
+          <t xml:space="preserve">Students celebrate creativity through art activities, exhibitions, and opportunities to explore different artistic styles and cultures.</t>
         </is>
       </c>
       <c r="L95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">本日から放課後のクラブ活動が再開します。【バスについて】午後の赤バスはクラブ活動がある日のみ運行します。それ以外の日は、午後の下校時に青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
+          <t xml:space="preserve">アート活動や展示を通して創造性を祝い、さまざまな芸術様式や文化に触れます。</t>
         </is>
       </c>
       <c r="M95" t="inlineStr" s="2">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="O95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">compass/images/events/2027-04-15-world-art-day.webp</t>
         </is>
       </c>
       <c r="P95" t="inlineStr" s="2">
@@ -9297,17 +9297,17 @@
     <row r="96">
       <c r="A96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-15-world-art-day</t>
+          <t xml:space="preserve">2027-04-16-foundation-field-trip</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-15</t>
+          <t xml:space="preserve">2027-04-16</t>
         </is>
       </c>
       <c r="C96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-15</t>
+          <t xml:space="preserve">2027-04-16</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="3">
@@ -9317,7 +9317,7 @@
       </c>
       <c r="E96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F96" t="inlineStr" s="2">
@@ -9337,22 +9337,22 @@
       </c>
       <c r="I96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">World Art Day</t>
+          <t xml:space="preserve">Foundation Field Trip</t>
         </is>
       </c>
       <c r="J96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ワールド・アート・デー</t>
+          <t xml:space="preserve">ファウンデーション校外学習</t>
         </is>
       </c>
       <c r="K96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students celebrate creativity through art activities, exhibitions, and opportunities to explore different artistic styles and cultures.</t>
+          <t xml:space="preserve">Our youngest learners will enjoy an age-appropriate educational excursion that supports classroom learning through hands-on experiences.</t>
         </is>
       </c>
       <c r="L96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">アート活動や展示を通して創造性を祝い、さまざまな芸術様式や文化に触れます。</t>
+          <t xml:space="preserve">年少の子どもたちが、年齢に合った校外学習に出かけ、体験を通して教室での学びを深めます。</t>
         </is>
       </c>
       <c r="M96" t="inlineStr" s="2">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="O96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-15-world-art-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-16-foundation-field-trip.webp</t>
         </is>
       </c>
       <c r="P96" t="inlineStr" s="2">
@@ -9394,17 +9394,17 @@
     <row r="97">
       <c r="A97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-16-foundation-field-trip</t>
+          <t xml:space="preserve">2027-04-21-hackathon-hour-of-code</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-16</t>
+          <t xml:space="preserve">2027-04-21</t>
         </is>
       </c>
       <c r="C97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-16</t>
+          <t xml:space="preserve">2027-04-21</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="3">
@@ -9414,12 +9414,12 @@
       </c>
       <c r="E97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G97" t="inlineStr" s="2">
@@ -9434,22 +9434,22 @@
       </c>
       <c r="I97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Foundation Field Trip</t>
+          <t xml:space="preserve">Hackathon (Hour of Code)</t>
         </is>
       </c>
       <c r="J97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ファウンデーション校外学習</t>
+          <t xml:space="preserve">ハッカソン（Hour of Code）</t>
         </is>
       </c>
       <c r="K97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Our youngest learners will enjoy an age-appropriate educational excursion that supports classroom learning through hands-on experiences.</t>
+          <t xml:space="preserve">Students will take part in an engaging Hour of Code challenge, using creativity and problem-solving skills to build simple coding projects. This event encourages computational thinking, teamwork, and confidence in technology in a fun and supportive environment.</t>
         </is>
       </c>
       <c r="L97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">年少の子どもたちが、年齢に合った校外学習に出かけ、体験を通して教室での学びを深めます。</t>
+          <t xml:space="preserve">Hour of Codeチャレンジに参加し、創造性と問題解決力を生かして簡単なプログラミング作品を作ります。楽しく支え合う環境の中で、コンピュテーショナル・シンキング、チームワーク、テクノロジーへの自信を育みます。</t>
         </is>
       </c>
       <c r="M97" t="inlineStr" s="2">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="O97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-16-foundation-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-21-hackathon-hour-of-code.webp</t>
         </is>
       </c>
       <c r="P97" t="inlineStr" s="2">
@@ -9491,17 +9491,17 @@
     <row r="98">
       <c r="A98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-21-hackathon-hour-of-code</t>
+          <t xml:space="preserve">2027-04-22-biology-ia-prep-field-trip-shore-ecosystem</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-21</t>
+          <t xml:space="preserve">2027-04-22</t>
         </is>
       </c>
       <c r="C98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-21</t>
+          <t xml:space="preserve">2027-04-22</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="3">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="E98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F98" t="inlineStr" s="2">
@@ -9531,22 +9531,22 @@
       </c>
       <c r="I98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hackathon (Hour of Code)</t>
+          <t xml:space="preserve">Biology IA Prep. Field Trip: Shore Ecosystem</t>
         </is>
       </c>
       <c r="J98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ハッカソン（Hour of Code）</t>
+          <t xml:space="preserve">生物IA準備校外学習：海岸生態系調査</t>
         </is>
       </c>
       <c r="K98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in an engaging Hour of Code challenge, using creativity and problem-solving skills to build simple coding projects. This event encourages computational thinking, teamwork, and confidence in technology in a fun and supportive environment.</t>
+          <t xml:space="preserve">Grade 11 and 12 Biology students will visit a shore ecosystem to prepare for their Biology Internal Assessment by collecting fieldwork data and practicing research methods.</t>
         </is>
       </c>
       <c r="L98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hour of Codeチャレンジに参加し、創造性と問題解決力を生かして簡単なプログラミング作品を作ります。楽しく支え合う環境の中で、コンピュテーショナル・シンキング、チームワーク、テクノロジーへの自信を育みます。</t>
+          <t xml:space="preserve">11・12年生の生物履修者が海岸の生態系を訪れ、フィールドワークでのデータ収集や研究手法の練習を通して、生物の内部評価（IA）に向けた準備を行います。</t>
         </is>
       </c>
       <c r="M98" t="inlineStr" s="2">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="O98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-21-hackathon-hour-of-code.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-22-biology-ia-prep-field-trip-shore-ecosystem.webp</t>
         </is>
       </c>
       <c r="P98" t="inlineStr" s="2">
@@ -9588,17 +9588,17 @@
     <row r="99">
       <c r="A99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-22-biology-ia-prep-field-trip-shore-ecosystem</t>
+          <t xml:space="preserve">2027-04-23-g12-celebration</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-22</t>
+          <t xml:space="preserve">2027-04-23</t>
         </is>
       </c>
       <c r="C99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-22</t>
+          <t xml:space="preserve">2027-04-23</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="3">
@@ -9628,22 +9628,22 @@
       </c>
       <c r="I99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Biology IA Prep. Field Trip: Shore Ecosystem</t>
+          <t xml:space="preserve">G12 Celebration</t>
         </is>
       </c>
       <c r="J99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">生物IA準備校外学習：海岸生態系調査</t>
+          <t xml:space="preserve">G12修了記念イベント</t>
         </is>
       </c>
       <c r="K99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 11 and 12 Biology students will visit a shore ecosystem to prepare for their Biology Internal Assessment by collecting fieldwork data and practicing research methods.</t>
+          <t xml:space="preserve">Grade 12 students will take part in a Graduation Walk as the school community celebrates them ahead of graduation.</t>
         </is>
       </c>
       <c r="L99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11・12年生の生物履修者が海岸の生態系を訪れ、フィールドワークでのデータ収集や研究手法の練習を通して、生物の内部評価（IA）に向けた準備を行います。</t>
+          <t xml:space="preserve">卒業を前に、12年生がグラデュエーション・ウォークに参加し、学校コミュニティ全体でお祝いします。</t>
         </is>
       </c>
       <c r="M99" t="inlineStr" s="2">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="O99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-22-biology-ia-prep-field-trip-shore-ecosystem.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-23-g12-celebration.webp</t>
         </is>
       </c>
       <c r="P99" t="inlineStr" s="2">
@@ -9685,17 +9685,17 @@
     <row r="100">
       <c r="A100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-23-g12-celebration</t>
+          <t xml:space="preserve">2027-04-26-grade-4-5-camping-trip</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-23</t>
+          <t xml:space="preserve">2027-04-26</t>
         </is>
       </c>
       <c r="C100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-23</t>
+          <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="3">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="E100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F100" t="inlineStr" s="2">
@@ -9725,22 +9725,22 @@
       </c>
       <c r="I100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G12 Celebration</t>
+          <t xml:space="preserve">Grade 4, 5 Camping Trip</t>
         </is>
       </c>
       <c r="J100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G12修了記念イベント</t>
+          <t xml:space="preserve">4・5年生キャンプ</t>
         </is>
       </c>
       <c r="K100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 12 students will take part in a Graduation Walk as the school community celebrates them ahead of graduation.</t>
+          <t xml:space="preserve">Students enjoy an outdoor learning experience that promotes independence, teamwork, resilience, and a connection with nature.</t>
         </is>
       </c>
       <c r="L100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">卒業を前に、12年生がグラデュエーション・ウォークに参加し、学校コミュニティ全体でお祝いします。</t>
+          <t xml:space="preserve">自立心、チームワーク、たくましさ、自然とのつながりを育む野外学習を楽しみます。</t>
         </is>
       </c>
       <c r="M100" t="inlineStr" s="2">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="O100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-23-g12-celebration.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-26-grade-4-5-camping-trip.webp</t>
         </is>
       </c>
       <c r="P100" t="inlineStr" s="2">
@@ -9782,12 +9782,12 @@
     <row r="101">
       <c r="A101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-26-grade-4-5-camping-trip</t>
+          <t xml:space="preserve">2027-04-27-choir-and-orchestra-concert</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-26</t>
+          <t xml:space="preserve">2027-04-27</t>
         </is>
       </c>
       <c r="C101" t="inlineStr" s="3">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G101" t="inlineStr" s="2">
@@ -9822,22 +9822,22 @@
       </c>
       <c r="I101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 4, 5 Camping Trip</t>
+          <t xml:space="preserve">Choir and Orchestra Concert</t>
         </is>
       </c>
       <c r="J101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">4・5年生キャンプ</t>
+          <t xml:space="preserve">合唱・オーケストラコンサート</t>
         </is>
       </c>
       <c r="K101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students enjoy an outdoor learning experience that promotes independence, teamwork, resilience, and a connection with nature.</t>
+          <t xml:space="preserve">Choir class and orchestra club will perform the music repertoire they have been rehearsing for an audience of family, peers and teachers.</t>
         </is>
       </c>
       <c r="L101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">自立心、チームワーク、たくましさ、自然とのつながりを育む野外学習を楽しみます。</t>
+          <t xml:space="preserve">合唱クラスとオーケストラクラブが、練習を重ねてきた曲目をご家族、友人、教員の前で演奏します。</t>
         </is>
       </c>
       <c r="M101" t="inlineStr" s="2">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="O101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-26-grade-4-5-camping-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-27-choir-and-orchestra-concert.webp</t>
         </is>
       </c>
       <c r="P101" t="inlineStr" s="2">
@@ -9879,17 +9879,17 @@
     <row r="102">
       <c r="A102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-27-choir-and-orchestra-concert</t>
+          <t xml:space="preserve">2027-04-30-science-fair</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-27</t>
+          <t xml:space="preserve">2027-04-30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-27</t>
+          <t xml:space="preserve">2027-04-30</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="3">
@@ -9919,22 +9919,22 @@
       </c>
       <c r="I102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choir and Orchestra Concert</t>
+          <t xml:space="preserve">Science Fair</t>
         </is>
       </c>
       <c r="J102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合唱・オーケストラコンサート</t>
+          <t xml:space="preserve">サイエンスフェア</t>
         </is>
       </c>
       <c r="K102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Choir class and orchestra club will perform the music repertoire they have been rehearsing for an audience of family, peers and teachers.</t>
+          <t xml:space="preserve">Students will share their science projects and investigations with the school community, showcasing their research, creativity, and scientific thinking.</t>
         </is>
       </c>
       <c r="L102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合唱クラスとオーケストラクラブが、練習を重ねてきた曲目をご家族、友人、教員の前で演奏します。</t>
+          <t xml:space="preserve">理科のプロジェクトや探究の成果を学校コミュニティに発表し、研究、創造性、科学的思考を披露します。</t>
         </is>
       </c>
       <c r="M102" t="inlineStr" s="2">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="O102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-27-choir-and-orchestra-concert.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-04-30-science-fair.webp</t>
         </is>
       </c>
       <c r="P102" t="inlineStr" s="2">
@@ -9976,17 +9976,17 @@
     <row r="103">
       <c r="A103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-04-30-science-fair</t>
+          <t xml:space="preserve">2027-05-17-friendly-basketball-tournament-internal</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-30</t>
+          <t xml:space="preserve">2027-05-17</t>
         </is>
       </c>
       <c r="C103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-04-30</t>
+          <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="3">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="F103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G103" t="inlineStr" s="2">
@@ -10016,22 +10016,22 @@
       </c>
       <c r="I103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Science Fair</t>
+          <t xml:space="preserve">Friendly Basketball Tournament (Internal)</t>
         </is>
       </c>
       <c r="J103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">サイエンスフェア</t>
+          <t xml:space="preserve">校内バスケットボール大会</t>
         </is>
       </c>
       <c r="K103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will share their science projects and investigations with the school community, showcasing their research, creativity, and scientific thinking.</t>
+          <t xml:space="preserve">Students will take part in a friendly internal basketball tournament, promoting teamwork, sportsmanship, and school spirit.</t>
         </is>
       </c>
       <c r="L103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">理科のプロジェクトや探究の成果を学校コミュニティに発表し、研究、創造性、科学的思考を披露します。</t>
+          <t xml:space="preserve">校内バスケットボール大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
         </is>
       </c>
       <c r="M103" t="inlineStr" s="2">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="O103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-04-30-science-fair.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-17-friendly-basketball-tournament-internal.webp</t>
         </is>
       </c>
       <c r="P103" t="inlineStr" s="2">
@@ -10073,17 +10073,17 @@
     <row r="104">
       <c r="A104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-17-friendly-basketball-tournament-internal</t>
+          <t xml:space="preserve">2027-05-19-entrepreneurs-day</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-17</t>
+          <t xml:space="preserve">2027-05-19</t>
         </is>
       </c>
       <c r="C104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-21</t>
+          <t xml:space="preserve">2027-05-20</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="3">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G104" t="inlineStr" s="2">
@@ -10113,22 +10113,22 @@
       </c>
       <c r="I104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Friendly Basketball Tournament (Internal)</t>
+          <t xml:space="preserve">Entrepreneurs Day</t>
         </is>
       </c>
       <c r="J104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内バスケットボール大会</t>
+          <t xml:space="preserve">アントレプレナーシップ・デー</t>
         </is>
       </c>
       <c r="K104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in a friendly internal basketball tournament, promoting teamwork, sportsmanship, and school spirit.</t>
+          <t xml:space="preserve">Students develop and showcase business ideas while learning about creativity, financial literacy, problem-solving, and entrepreneurship.</t>
         </is>
       </c>
       <c r="L104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">校内バスケットボール大会に参加し、チームワーク、スポーツマンシップ、愛校心を育みます。</t>
+          <t xml:space="preserve">創造性、金融リテラシー、問題解決、起業家精神について学びながら、ビジネスのアイデアを考え、発表します。</t>
         </is>
       </c>
       <c r="M104" t="inlineStr" s="2">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="O104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-17-friendly-basketball-tournament-internal.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-19-entrepreneurs-day.webp</t>
         </is>
       </c>
       <c r="P104" t="inlineStr" s="2">
@@ -10170,17 +10170,17 @@
     <row r="105">
       <c r="A105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-19-entrepreneurs-day</t>
+          <t xml:space="preserve">2027-05-21-collective-field-trip</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-19</t>
+          <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
       <c r="C105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-20</t>
+          <t xml:space="preserve">2027-05-21</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="3">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="F105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G105" t="inlineStr" s="2">
@@ -10210,22 +10210,22 @@
       </c>
       <c r="I105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Entrepreneurs Day</t>
+          <t xml:space="preserve">Collective Field Trip</t>
         </is>
       </c>
       <c r="J105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">アントレプレナーシップ・デー</t>
+          <t xml:space="preserve">合同校外学習</t>
         </is>
       </c>
       <c r="K105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students develop and showcase business ideas while learning about creativity, financial literacy, problem-solving, and entrepreneurship.</t>
+          <t xml:space="preserve">Students participate in a shared educational experience that promotes collaboration, inquiry, and real-world learning.</t>
         </is>
       </c>
       <c r="L105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">創造性、金融リテラシー、問題解決、起業家精神について学びながら、ビジネスのアイデアを考え、発表します。</t>
+          <t xml:space="preserve">協働、探究、実社会での学びを促す合同の学習体験に参加します。</t>
         </is>
       </c>
       <c r="M105" t="inlineStr" s="2">
@@ -10240,7 +10240,7 @@
       </c>
       <c r="O105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-19-entrepreneurs-day.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-21-collective-field-trip.webp</t>
         </is>
       </c>
       <c r="P105" t="inlineStr" s="2">
@@ -10267,17 +10267,17 @@
     <row r="106">
       <c r="A106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-21-collective-field-trip</t>
+          <t xml:space="preserve">2027-05-22-saturday-school-last-day-event</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-21</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="C106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-21</t>
+          <t xml:space="preserve">2027-05-22</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="3">
@@ -10287,7 +10287,7 @@
       </c>
       <c r="E106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F106" t="inlineStr" s="2">
@@ -10307,22 +10307,22 @@
       </c>
       <c r="I106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Collective Field Trip</t>
+          <t xml:space="preserve">Saturday School Last Day Event</t>
         </is>
       </c>
       <c r="J106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">合同校外学習</t>
+          <t xml:space="preserve">土曜校最終日イベント</t>
         </is>
       </c>
       <c r="K106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students participate in a shared educational experience that promotes collaboration, inquiry, and real-world learning.</t>
+          <t xml:space="preserve">Students will take part in a relaxed final Saturday School session, with leisure activities at school to celebrate the last day.</t>
         </is>
       </c>
       <c r="L106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">協働、探究、実社会での学びを促す合同の学習体験に参加します。</t>
+          <t xml:space="preserve">土曜校の最終日を、校内でのレクリエーション活動とともにリラックスして過ごし、お祝いします。</t>
         </is>
       </c>
       <c r="M106" t="inlineStr" s="2">
@@ -10337,7 +10337,7 @@
       </c>
       <c r="O106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-21-collective-field-trip.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-22-saturday-school-last-day-event.webp</t>
         </is>
       </c>
       <c r="P106" t="inlineStr" s="2">
@@ -10364,17 +10364,17 @@
     <row r="107">
       <c r="A107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-22-saturday-school-last-day-event</t>
+          <t xml:space="preserve">2027-05-24-concept-con-future-focus</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-05-24</t>
         </is>
       </c>
       <c r="C107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-22</t>
+          <t xml:space="preserve">2027-05-28</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="3">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="E107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="2">
@@ -10404,22 +10404,22 @@
       </c>
       <c r="I107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Saturday School Last Day Event</t>
+          <t xml:space="preserve">Concept Con (Future Focus)</t>
         </is>
       </c>
       <c r="J107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">土曜校最終日イベント</t>
+          <t xml:space="preserve">コンセプト・コン（未来を考える）</t>
         </is>
       </c>
       <c r="K107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in a relaxed final Saturday School session, with leisure activities at school to celebrate the last day.</t>
+          <t xml:space="preserve">Students investigate future possibilities, innovations, and solutions to real-world challenges through inquiry-based projects and presentations.</t>
         </is>
       </c>
       <c r="L107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">土曜校の最終日を、校内でのレクリエーション活動とともにリラックスして過ごし、お祝いします。</t>
+          <t xml:space="preserve">探究型のプロジェクトや発表を通して、未来の可能性、イノベーション、現実の課題の解決策について考えます。</t>
         </is>
       </c>
       <c r="M107" t="inlineStr" s="2">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="O107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-22-saturday-school-last-day-event.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-24-concept-con-future-focus.webp</t>
         </is>
       </c>
       <c r="P107" t="inlineStr" s="2">
@@ -10461,17 +10461,17 @@
     <row r="108">
       <c r="A108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-24-concept-con-future-focus</t>
+          <t xml:space="preserve">2027-05-28-g12-graduation-with-performances</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-24</t>
+          <t xml:space="preserve">2027-05-29</t>
         </is>
       </c>
       <c r="C108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-28</t>
+          <t xml:space="preserve">2027-05-29</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="3">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="E108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G108" t="inlineStr" s="2">
@@ -10496,27 +10496,27 @@
       </c>
       <c r="H108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">changed</t>
         </is>
       </c>
       <c r="I108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Concept Con (Future Focus)</t>
+          <t xml:space="preserve">G12 Graduation with Performances</t>
         </is>
       </c>
       <c r="J108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">コンセプト・コン（未来を考える）</t>
+          <t xml:space="preserve">G12卒業式・記念パフォーマンス</t>
         </is>
       </c>
       <c r="K108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students investigate future possibilities, innovations, and solutions to real-world challenges through inquiry-based projects and presentations.</t>
+          <t xml:space="preserve">Grade 12 students will celebrate their graduation with a formal ceremony featuring student performances and the wider school community.</t>
         </is>
       </c>
       <c r="L108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">探究型のプロジェクトや発表を通して、未来の可能性、イノベーション、現実の課題の解決策について考えます。</t>
+          <t xml:space="preserve">12年生が、生徒によるパフォーマンスを交えた式典で、学校コミュニティ全体とともに卒業を祝います。</t>
         </is>
       </c>
       <c r="M108" t="inlineStr" s="2">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="O108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-24-concept-con-future-focus.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-05-28-g12-graduation-with-performances.webp</t>
         </is>
       </c>
       <c r="P108" t="inlineStr" s="2">
@@ -10558,17 +10558,17 @@
     <row r="109">
       <c r="A109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-05-28-g12-graduation-with-performances</t>
+          <t xml:space="preserve">2027-06-03-celebration-of-learning-prep</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-29</t>
+          <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
       <c r="C109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-05-29</t>
+          <t xml:space="preserve">2027-06-03</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="3">
@@ -10578,12 +10578,12 @@
       </c>
       <c r="E109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G109" t="inlineStr" s="2">
@@ -10593,27 +10593,27 @@
       </c>
       <c r="H109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">changed</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G12 Graduation with Performances</t>
+          <t xml:space="preserve">Celebration of Learning Prep</t>
         </is>
       </c>
       <c r="J109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">G12卒業式・記念パフォーマンス</t>
+          <t xml:space="preserve">学びの発表会準備</t>
         </is>
       </c>
       <c r="K109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 12 students will celebrate their graduation with a formal ceremony featuring student performances and the wider school community.</t>
+          <t xml:space="preserve">Students help prepare the school for the Celebration of Learning by organizing learning spaces, setting up displays, arranging materials, and ensuring classrooms and common areas are ready to welcome visitors. This preparation helps create an engaging and welcoming environment for families and guests.</t>
         </is>
       </c>
       <c r="L109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12年生が、生徒によるパフォーマンスを交えた式典で、学校コミュニティ全体とともに卒業を祝います。</t>
+          <t xml:space="preserve">学びの発表会に向けて、学習スペースの整理、展示の設営、資料の準備を行い、教室や共用エリアで来場者をお迎えできるよう整えます。ご家族やお客様にとって魅力的で温かな空間づくりにつながります。</t>
         </is>
       </c>
       <c r="M109" t="inlineStr" s="2">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="O109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-05-28-g12-graduation-with-performances.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-03-celebration-of-learning-prep.webp</t>
         </is>
       </c>
       <c r="P109" t="inlineStr" s="2">
@@ -10655,7 +10655,7 @@
     <row r="110">
       <c r="A110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-03-celebration-of-learning-prep</t>
+          <t xml:space="preserve">2027-06-03-ukulele-concert</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="3">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="C110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-03</t>
+          <t xml:space="preserve">2027-06-04</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="3">
@@ -10675,12 +10675,12 @@
       </c>
       <c r="E110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Primary</t>
         </is>
       </c>
       <c r="F110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G110" t="inlineStr" s="2">
@@ -10695,22 +10695,22 @@
       </c>
       <c r="I110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Celebration of Learning Prep</t>
+          <t xml:space="preserve">Ukulele Concert</t>
         </is>
       </c>
       <c r="J110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学びの発表会準備</t>
+          <t xml:space="preserve">ウクレレコンサート</t>
         </is>
       </c>
       <c r="K110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students help prepare the school for the Celebration of Learning by organizing learning spaces, setting up displays, arranging materials, and ensuring classrooms and common areas are ready to welcome visitors. This preparation helps create an engaging and welcoming environment for families and guests.</t>
+          <t xml:space="preserve">Students perform musical pieces they have learned throughout the year, demonstrating their growth, confidence, and musical skills.</t>
         </is>
       </c>
       <c r="L110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学びの発表会に向けて、学習スペースの整理、展示の設営、資料の準備を行い、教室や共用エリアで来場者をお迎えできるよう整えます。ご家族やお客様にとって魅力的で温かな空間づくりにつながります。</t>
+          <t xml:space="preserve">一年を通して学んだ曲を演奏し、成長、自信、音楽の技能を披露します。</t>
         </is>
       </c>
       <c r="M110" t="inlineStr" s="2">
@@ -10725,7 +10725,7 @@
       </c>
       <c r="O110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-03-celebration-of-learning-prep.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-03-ukulele-concert.webp</t>
         </is>
       </c>
       <c r="P110" t="inlineStr" s="2">
@@ -10752,12 +10752,12 @@
     <row r="111">
       <c r="A111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-03-ukulele-concert</t>
+          <t xml:space="preserve">2027-06-04-celebration-of-learning</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-03</t>
+          <t xml:space="preserve">2027-06-04</t>
         </is>
       </c>
       <c r="C111" t="inlineStr" s="3">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="E111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F111" t="inlineStr" s="2">
@@ -10792,22 +10792,22 @@
       </c>
       <c r="I111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ukulele Concert</t>
+          <t xml:space="preserve">Celebration of Learning</t>
         </is>
       </c>
       <c r="J111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ウクレレコンサート</t>
+          <t xml:space="preserve">学びの発表会</t>
         </is>
       </c>
       <c r="K111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students perform musical pieces they have learned throughout the year, demonstrating their growth, confidence, and musical skills.</t>
+          <t xml:space="preserve">The school community will celebrate learning as students share projects and exhibitions, including PYPX, MYPX, CAS, EE, TOK and Foundation to 4 projects.</t>
         </is>
       </c>
       <c r="L111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一年を通して学んだ曲を演奏し、成長、自信、音楽の技能を披露します。</t>
+          <t xml:space="preserve">PYPX、MYPX、CAS、EE、TOK、ファウンデーション～4年生のプロジェクトなど、生徒の作品や展示を通して学校コミュニティ全体で学びを祝います。</t>
         </is>
       </c>
       <c r="M111" t="inlineStr" s="2">
@@ -10822,7 +10822,7 @@
       </c>
       <c r="O111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-03-ukulele-concert.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-04-celebration-of-learning.webp</t>
         </is>
       </c>
       <c r="P111" t="inlineStr" s="2">
@@ -10849,17 +10849,17 @@
     <row r="112">
       <c r="A112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-04-celebration-of-learning</t>
+          <t xml:space="preserve">2027-06-05-sat-test-7</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-04</t>
+          <t xml:space="preserve">2027-06-05</t>
         </is>
       </c>
       <c r="C112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-04</t>
+          <t xml:space="preserve">2027-06-05</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="3">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="E112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">High School</t>
         </is>
       </c>
       <c r="F112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G112" t="inlineStr" s="2">
@@ -10889,22 +10889,22 @@
       </c>
       <c r="I112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Celebration of Learning</t>
+          <t xml:space="preserve">SAT Test #7</t>
         </is>
       </c>
       <c r="J112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学びの発表会</t>
+          <t xml:space="preserve">SAT試験 第7回</t>
         </is>
       </c>
       <c r="K112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The school community will celebrate learning as students share projects and exhibitions, including PYPX, MYPX, CAS, EE, TOK and Foundation to 4 projects.</t>
+          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
         </is>
       </c>
       <c r="L112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PYPX、MYPX、CAS、EE、TOK、ファウンデーション～4年生のプロジェクトなど、生徒の作品や展示を通して学校コミュニティ全体で学びを祝います。</t>
+          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
         </is>
       </c>
       <c r="M112" t="inlineStr" s="2">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="O112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-04-celebration-of-learning.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-05-sat-test-7.webp</t>
         </is>
       </c>
       <c r="P112" t="inlineStr" s="2">
@@ -10946,17 +10946,17 @@
     <row r="113">
       <c r="A113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-05-sat-test-7</t>
+          <t xml:space="preserve">2027-06-11-last-day-of-clubs</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-05</t>
+          <t xml:space="preserve">2027-06-11</t>
         </is>
       </c>
       <c r="C113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-05</t>
+          <t xml:space="preserve">2027-06-11</t>
         </is>
       </c>
       <c r="D113" t="inlineStr" s="3">
@@ -10966,7 +10966,7 @@
       </c>
       <c r="E113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">High School</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F113" t="inlineStr" s="2">
@@ -10986,22 +10986,22 @@
       </c>
       <c r="I113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT Test #7</t>
+          <t xml:space="preserve">Last Day of Clubs</t>
         </is>
       </c>
       <c r="J113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SAT試験 第7回</t>
+          <t xml:space="preserve">クラブ活動最終日</t>
         </is>
       </c>
       <c r="K113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">An internationally recognized university entrance exam. Our school is an official SAT test center, and both Enishi students and external students are welcome to take the test on campus.</t>
+          <t xml:space="preserve">The last day of after-school clubs for this school year. Bus reminder: the afternoon Red bus runs only on club days, so after today it no longer runs. Please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
         </is>
       </c>
       <c r="L113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国際的に認められた大学入学試験です。本校はSAT公式試験会場であり、本校生徒・外部生徒ともに校内で受験できます。</t>
+          <t xml:space="preserve">今年度の放課後クラブ活動の最終日です。【バスについて】午後の赤バスはクラブ活動がある日のみ運行するため、本日で運行を終了します。明日以降、午後の下校時は青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
         </is>
       </c>
       <c r="M113" t="inlineStr" s="2">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="O113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-05-sat-test-7.webp</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="P113" t="inlineStr" s="2">
@@ -11043,17 +11043,17 @@
     <row r="114">
       <c r="A114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-11-last-day-of-clubs</t>
+          <t xml:space="preserve">2027-06-17-eagle-bucks-store</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-11</t>
+          <t xml:space="preserve">2027-06-17</t>
         </is>
       </c>
       <c r="C114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-11</t>
+          <t xml:space="preserve">2027-06-17</t>
         </is>
       </c>
       <c r="D114" t="inlineStr" s="3">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="E114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Whole School</t>
+          <t xml:space="preserve">Primary, ELC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr" s="2">
@@ -11083,22 +11083,22 @@
       </c>
       <c r="I114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Last Day of Clubs</t>
+          <t xml:space="preserve">Eagle Bucks Store</t>
         </is>
       </c>
       <c r="J114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">クラブ活動最終日</t>
+          <t xml:space="preserve">イーグルバックス・ストア</t>
         </is>
       </c>
       <c r="K114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">The last day of after-school clubs for this school year. Bus reminder: the afternoon Red bus runs only on club days, so after today it no longer runs. Please check the Blue and Green bus schedules for afternoon pick-up. The morning Red bus runs as usual.</t>
+          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
         </is>
       </c>
       <c r="L114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">今年度の放課後クラブ活動の最終日です。【バスについて】午後の赤バスはクラブ活動がある日のみ運行するため、本日で運行を終了します。明日以降、午後の下校時は青バス・緑バスの時刻表をご確認ください。朝の赤バスは通常どおり運行します。</t>
+          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
         </is>
       </c>
       <c r="M114" t="inlineStr" s="2">
@@ -11113,7 +11113,7 @@
       </c>
       <c r="O114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">compass/images/events/2027-06-17-eagle-bucks-store.webp</t>
         </is>
       </c>
       <c r="P114" t="inlineStr" s="2">
@@ -11140,17 +11140,17 @@
     <row r="115">
       <c r="A115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-17-eagle-bucks-store</t>
+          <t xml:space="preserve">2027-06-18-kindergarten-and-grade-5-graduation</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-17</t>
+          <t xml:space="preserve">2027-06-18</t>
         </is>
       </c>
       <c r="C115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-17</t>
+          <t xml:space="preserve">2027-06-18</t>
         </is>
       </c>
       <c r="D115" t="inlineStr" s="3">
@@ -11165,7 +11165,7 @@
       </c>
       <c r="F115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G115" t="inlineStr" s="2">
@@ -11180,22 +11180,22 @@
       </c>
       <c r="I115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Eagle Bucks Store</t>
+          <t xml:space="preserve">Kindergarten and Grade 5 Graduation</t>
         </is>
       </c>
       <c r="J115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">イーグルバックス・ストア</t>
+          <t xml:space="preserve">幼稚部・5年生卒業式</t>
         </is>
       </c>
       <c r="K115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students can use their earned Eagle Bucks to purchase rewards and special items. The store reinforces positive behavior, responsibility, and goal-setting.</t>
+          <t xml:space="preserve">Students participate in graduation ceremonies to celebrate important milestones in their educational journey. The events recognize student growth, achievements, and readiness for the next stage of learning while bringing together families, staff, and the school community in celebration.</t>
         </is>
       </c>
       <c r="L115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">獲得したイーグルバックスを使って、ごほうびや特別なアイテムと交換できます。前向きな行動、責任感、目標設定を後押しする取り組みです。</t>
+          <t xml:space="preserve">学びの歩みにおける大切な節目を祝う卒業式に参加します。生徒の成長と成果、そして次のステージへの準備が整ったことを、ご家族、教職員、学校コミュニティが一堂に会して祝福します。</t>
         </is>
       </c>
       <c r="M115" t="inlineStr" s="2">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="O115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-17-eagle-bucks-store.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-18-kindergarten-and-grade-5-graduation.webp</t>
         </is>
       </c>
       <c r="P115" t="inlineStr" s="2">
@@ -11237,7 +11237,7 @@
     <row r="116">
       <c r="A116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-18-kindergarten-and-grade-5-graduation</t>
+          <t xml:space="preserve">2027-06-18-primary-elc-year-end-performance</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="3">
@@ -11277,22 +11277,22 @@
       </c>
       <c r="I116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Kindergarten and Grade 5 Graduation</t>
+          <t xml:space="preserve">Primary &amp; ELC Year End Performance</t>
         </is>
       </c>
       <c r="J116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部・5年生卒業式</t>
+          <t xml:space="preserve">小学部・幼稚部年度末発表会</t>
         </is>
       </c>
       <c r="K116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students participate in graduation ceremonies to celebrate important milestones in their educational journey. The events recognize student growth, achievements, and readiness for the next stage of learning while bringing together families, staff, and the school community in celebration.</t>
+          <t xml:space="preserve">Students participate in music, dance, drama, and other performance activities to showcase their learning, creativity, and talents. These performances provide an opportunity to celebrate the school year and share achievements with families and the school community.</t>
         </is>
       </c>
       <c r="L116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">学びの歩みにおける大切な節目を祝う卒業式に参加します。生徒の成長と成果、そして次のステージへの準備が整ったことを、ご家族、教職員、学校コミュニティが一堂に会して祝福します。</t>
+          <t xml:space="preserve">音楽、ダンス、演劇などのパフォーマンスを通して、学び、創造性、才能を披露します。一年の締めくくりを祝い、その成果をご家族や学校コミュニティと分かち合う機会です。</t>
         </is>
       </c>
       <c r="M116" t="inlineStr" s="2">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="O116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-18-kindergarten-and-grade-5-graduation.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-18-primary-elc-year-end-performance.webp</t>
         </is>
       </c>
       <c r="P116" t="inlineStr" s="2">
@@ -11334,17 +11334,17 @@
     <row r="117">
       <c r="A117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-18-primary-elc-year-end-performance</t>
+          <t xml:space="preserve">2027-06-19-end-of-term-3-activity-g6-10</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-18</t>
+          <t xml:space="preserve">2027-06-19</t>
         </is>
       </c>
       <c r="C117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-18</t>
+          <t xml:space="preserve">2027-06-19</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="3">
@@ -11354,12 +11354,12 @@
       </c>
       <c r="E117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary, ELC</t>
+          <t xml:space="preserve">Secondary</t>
         </is>
       </c>
       <c r="F117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G117" t="inlineStr" s="2">
@@ -11374,22 +11374,22 @@
       </c>
       <c r="I117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Primary &amp; ELC Year End Performance</t>
+          <t xml:space="preserve">End of Term 3 Activity: G6-10</t>
         </is>
       </c>
       <c r="J117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小学部・幼稚部年度末発表会</t>
+          <t xml:space="preserve">第3学期末行事：G6–10</t>
         </is>
       </c>
       <c r="K117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students participate in music, dance, drama, and other performance activities to showcase their learning, creativity, and talents. These performances provide an opportunity to celebrate the school year and share achievements with families and the school community.</t>
+          <t xml:space="preserve">Students will take part in an off-campus day trip outside Nagoya to celebrate the end of Term 3.</t>
         </is>
       </c>
       <c r="L117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">音楽、ダンス、演劇などのパフォーマンスを通して、学び、創造性、才能を披露します。一年の締めくくりを祝い、その成果をご家族や学校コミュニティと分かち合う機会です。</t>
+          <t xml:space="preserve">第3学期の終わりを祝い、名古屋近郊への日帰り校外活動に参加します。</t>
         </is>
       </c>
       <c r="M117" t="inlineStr" s="2">
@@ -11404,7 +11404,7 @@
       </c>
       <c r="O117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-18-primary-elc-year-end-performance.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-19-end-of-term-3-activity-g6-10.webp</t>
         </is>
       </c>
       <c r="P117" t="inlineStr" s="2">
@@ -11431,17 +11431,17 @@
     <row r="118">
       <c r="A118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-19-end-of-term-3-activity-g6-10</t>
+          <t xml:space="preserve">2027-06-22-parent-teacher-conferences</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-19</t>
+          <t xml:space="preserve">2027-06-22</t>
         </is>
       </c>
       <c r="C118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-19</t>
+          <t xml:space="preserve">2027-06-23</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="3">
@@ -11451,17 +11451,17 @@
       </c>
       <c r="E118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Secondary</t>
+          <t xml:space="preserve">Whole School</t>
         </is>
       </c>
       <c r="F118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="H118" t="inlineStr" s="2">
@@ -11471,22 +11471,22 @@
       </c>
       <c r="I118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">End of Term 3 Activity: G6-10</t>
+          <t xml:space="preserve">Parent Teacher Conferences</t>
         </is>
       </c>
       <c r="J118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第3学期末行事：G6–10</t>
+          <t xml:space="preserve">保護者面談</t>
         </is>
       </c>
       <c r="K118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Students will take part in an off-campus day trip outside Nagoya to celebrate the end of Term 3.</t>
+          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on these days.</t>
         </is>
       </c>
       <c r="L118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">第3学期の終わりを祝い、名古屋近郊への日帰り校外活動に参加します。</t>
+          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。期間中、生徒は登校しません。</t>
         </is>
       </c>
       <c r="M118" t="inlineStr" s="2">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="O118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-19-end-of-term-3-activity-g6-10.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-22-parent-teacher-conferences.webp</t>
         </is>
       </c>
       <c r="P118" t="inlineStr" s="2">
@@ -11528,17 +11528,17 @@
     <row r="119">
       <c r="A119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-22-parent-teacher-conferences</t>
+          <t xml:space="preserve">2027-06-28-summer-school</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-22</t>
+          <t xml:space="preserve">2027-06-28</t>
         </is>
       </c>
       <c r="C119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-23</t>
+          <t xml:space="preserve">2027-07-18</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="3">
@@ -11553,12 +11553,12 @@
       </c>
       <c r="F119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H119" t="inlineStr" s="2">
@@ -11568,22 +11568,22 @@
       </c>
       <c r="I119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parent Teacher Conferences</t>
+          <t xml:space="preserve">Summer School</t>
         </is>
       </c>
       <c r="J119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者面談</t>
+          <t xml:space="preserve">サマースクール</t>
         </is>
       </c>
       <c r="K119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Parents meet one-on-one with each teacher to discuss their child's progress, strengths, and next steps. The school campus is closed to students on these days.</t>
+          <t xml:space="preserve">Participate in fun English style summer camps that challenge students and help foster friendships and connections with others.</t>
         </is>
       </c>
       <c r="L119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">保護者の皆様が各担当教員と個別に面談し、お子様の成長、強み、今後の課題についてお話しします。期間中、生徒は登校しません。</t>
+          <t xml:space="preserve">英語で楽しく過ごすサマーキャンプに参加し、新たなことに挑戦しながら友情や人とのつながりを育みます。</t>
         </is>
       </c>
       <c r="M119" t="inlineStr" s="2">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="O119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2027-06-22-parent-teacher-conferences.webp</t>
+          <t xml:space="preserve">compass/images/events/2027-06-28-summer-school.webp</t>
         </is>
       </c>
       <c r="P119" t="inlineStr" s="2">
@@ -11625,17 +11625,17 @@
     <row r="120">
       <c r="A120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2027-06-28-summer-school</t>
+          <t xml:space="preserve">2027-07-20-summer-school</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-06-28</t>
+          <t xml:space="preserve">2027-07-20</t>
         </is>
       </c>
       <c r="C120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2027-07-18</t>
+          <t xml:space="preserve">2027-07-24</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="3">
@@ -11714,103 +11714,6 @@
         </is>
       </c>
       <c r="S120" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">2027-07-20-summer-school</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">2027-07-20</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">2027-07-24</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Whole School</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Summer School</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">サマースクール</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Participate in fun English style summer camps that challenge students and help foster friendships and connections with others.</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">英語で楽しく過ごすサマーキャンプに参加し、新たなことに挑戦しながら友情や人とのつながりを育みます。</t>
-        </is>
-      </c>
-      <c r="M121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">compass/images/events/2027-06-28-summer-school.webp</t>
-        </is>
-      </c>
-      <c r="P121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R121" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="S121" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>

--- a/admin/EIS-Compass-events.xlsx
+++ b/admin/EIS-Compass-events.xlsx
@@ -2604,17 +2604,17 @@
     <row r="27">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-21-college-fair</t>
+          <t xml:space="preserve">2026-10-23-nagoya-university-biology-laboratory-visit</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="3">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="F27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G27" t="inlineStr" s="2">
@@ -2639,27 +2639,27 @@
       </c>
       <c r="H27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">changed</t>
         </is>
       </c>
       <c r="I27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">College Fair</t>
+          <t xml:space="preserve">Nagoya University Biology Laboratory Visit</t>
         </is>
       </c>
       <c r="J27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">大学進学フェア</t>
+          <t xml:space="preserve">名古屋大学 生物学研究室訪問</t>
         </is>
       </c>
       <c r="K27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">A special event where representatives from several international and Japanese universities visit our school to introduce their programs and admission opportunities. The fair is open to all students and parents, and students from other international schools in the area are also invited to attend.</t>
+          <t xml:space="preserve">Grade 11 and 12 Biology students will visit Nagoya University for a guided laboratory experience, connecting classroom learning with real-world scientific research.</t>
         </is>
       </c>
       <c r="L27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">国内外の複数の大学の担当者が来校し、各大学のプログラムや入学機会を紹介する特別イベントです。全生徒・保護者が参加でき、近隣のインターナショナルスクールの生徒もご招待しています。</t>
+          <t xml:space="preserve">11・12年生の生物履修者が名古屋大学を訪問し、研究室での体験を通して授業での学びと実際の科学研究を結びつけます。</t>
         </is>
       </c>
       <c r="M27" t="inlineStr" s="2">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="O27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-21-college-fair.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-23-nagoya-university-biology-laboratory-visit.webp</t>
         </is>
       </c>
       <c r="P27" t="inlineStr" s="2">
@@ -2701,17 +2701,17 @@
     <row r="28">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">2026-10-23-nagoya-university-biology-laboratory-visit</t>
+          <t xml:space="preserve">2026-10-21-college-fair</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-23</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2026-10-23</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="3">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="F28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="G28" t="inlineStr" s="2">
@@ -2741,22 +2741,22 @@
       </c>
       <c r="I28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Nagoya University Biology Laboratory Visit</t>
+          <t xml:space="preserve">College Fair</t>
         </is>
       </c>
       <c r="J28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">名古屋大学 生物学研究室訪問</t>
+          <t xml:space="preserve">大学進学フェア</t>
         </is>
       </c>
       <c r="K28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Grade 11 and 12 Biology students will visit Nagoya University for a guided laboratory experience, connecting classroom learning with real-world scientific research.</t>
+          <t xml:space="preserve">A special event where representatives from several international and Japanese universities visit our school to introduce their programs and admission opportunities. The fair is open to all students and parents, and students from other international schools in the area are also invited to attend.</t>
         </is>
       </c>
       <c r="L28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11・12年生の生物履修者が名古屋大学を訪問し、研究室での体験を通して授業での学びと実際の科学研究を結びつけます。</t>
+          <t xml:space="preserve">国内外の複数の大学の担当者が来校し、各大学のプログラムや入学機会を紹介する特別イベントです。全生徒・保護者が参加でき、近隣のインターナショナルスクールの生徒もご招待しています。</t>
         </is>
       </c>
       <c r="M28" t="inlineStr" s="2">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="O28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">compass/images/events/2026-10-23-nagoya-university-biology-laboratory-visit.webp</t>
+          <t xml:space="preserve">compass/images/events/2026-10-21-college-fair.webp</t>
         </is>
       </c>
       <c r="P28" t="inlineStr" s="2">

--- a/admin/EIS-Compass-events.xlsx
+++ b/admin/EIS-Compass-events.xlsx
@@ -4700,7 +4700,7 @@
       </c>
       <c r="D44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">13:10-14:55</t>
+          <t xml:space="preserve">13:10-14:45</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="F44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">ELC to Grade 5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">幼稚部〜小学5年生</t>
         </is>
       </c>
       <c r="H44" t="inlineStr" s="2">
@@ -4735,27 +4735,27 @@
       </c>
       <c r="K44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Gallery Day: ELC &amp; Primary Art Showcase</t>
+          <t xml:space="preserve">ELC &amp; Primary Art Showcase</t>
         </is>
       </c>
       <c r="L44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ギャラリーデー：幼稚部・小学部アート展</t>
+          <t xml:space="preserve">幼稚部・小学部アート展</t>
         </is>
       </c>
       <c r="M44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ELC and Primary students display the artwork they have created with the visual arts teacher. Parents are welcome to view the gallery from 13:10 to 14:55. Students vote for their favourite artworks, and the winners for each grade are announced.</t>
+          <t xml:space="preserve">Enishi’s first-ever Art Showcase! Students from ELC through Grade 5 exhibit the artwork they created during Term 1. Walk through the gallery at your own pace, appreciate the artworks, and feel free to ask students about their creative process and inspiration. Parent viewing: 13:10–14:45 (event 13:05–15:15). Students will vote for their favourite artwork from other grade levels, and one outstanding artwork from each grade will receive a set of art-supply prizes. Voting is for students only — parents and guardians are welcome to enjoy all the artwork, but please do not place voting stickers on any artwork.</t>
         </is>
       </c>
       <c r="N44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">幼稚部・小学部の児童が美術の授業で制作した作品を展示します。保護者の皆さまは13:10～14:55にご鑑賞いただけます。児童による投票を行い、学年ごとの受賞作品を発表します。</t>
+          <t xml:space="preserve">本校初のアート展を開催します！幼稚部から小学5年生までの子どもたちが、1学期に制作した作品を展示します。会場内はご自身のペースで自由にご覧いただけます。作品をじっくり鑑賞しながら、制作の過程や着想について、ぜひ子どもたちにお尋ねください。保護者鑑賞時間：13:10～14:45（開催時間 13:05～15:15）。子どもたちは他学年の作品の中からお気に入りの作品に投票し、各学年から優秀作品を1点ずつ選出して、受賞者には画材セットを贈呈します。投票は子どもたちのみを対象としています。保護者の皆様もぜひすべての作品をお楽しみください。ただし、作品に投票用シールを貼ることはご遠慮ください。</t>
         </is>
       </c>
       <c r="O44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Gym</t>
+          <t xml:space="preserve">School Gym</t>
         </is>
       </c>
       <c r="P44" t="inlineStr" s="2">

--- a/admin/EIS-Compass-events.xlsx
+++ b/admin/EIS-Compass-events.xlsx
@@ -3486,12 +3486,12 @@
       </c>
       <c r="R32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Event brochure (English) | イベントパンフレット（英語） | https://drive.google.com/file/d/1iK0N-LadmFzOjYjQr4HX23_EzAvgl_oC/view?usp=sharing</t>
         </is>
       </c>
       <c r="S32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Event brochure (Japanese) | イベントパンフレット（日本語） | https://drive.google.com/file/d/19MKvjdYx80BMoxM6uG35rMK8YX3sWpXI/view?usp=sharing</t>
         </is>
       </c>
       <c r="T32" t="inlineStr" s="2">

--- a/admin/EIS-Compass-events.xlsx
+++ b/admin/EIS-Compass-events.xlsx
@@ -3416,7 +3416,7 @@
       </c>
       <c r="D32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">10:00-14:00</t>
+          <t xml:space="preserve">9:45-13:50</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -3461,22 +3461,22 @@
       </c>
       <c r="M32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">This year’s theme is “Festivals and Holidays Around the World”. A Saturday family event celebrating traditions, cultures, stories, arts, music and celebrations from around the world, with student activities, cultural displays, performances, arts and crafts, and interactive booths. Clean-up runs from 14:00 to 15:00, and community members are welcome to help. ELC and Primary students must attend with a parent or guardian and may not be dropped off. School buses will not operate. More details will be shared soon.</t>
+          <t xml:space="preserve">This year’s theme is “Festivals and Holidays Around the World” — a celebration of the many traditions, celebrations and cultures in our school community. Gates open at 9:45 and the festival begins at 10:00. From 10:00 to 13:00, teachers and students run three booth sessions with games, crafts, cultural activities and hands-on experiences from around the world. The Haunted House is open from 10:00 to 12:00, and there will be a costume parade: students may wear traditional or cultural clothing, an outfit representing a festival or holiday, or a Halloween costume (dressing up is optional — regular clothes are very welcome). Food trucks and food prepared and sold by school parents will be available. From 13:00 to 13:50, everyone moves to the gym for the final event with games and dances. Please note that IMF is not a normal school day: ELC and Primary students must be accompanied and supervised by a parent or guardian throughout their visit and may not be dropped off and collected later. School buses will not operate.</t>
         </is>
       </c>
       <c r="N32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">今年のテーマは「世界の祭りと祝日」です。世界各地の伝統、文化、物語、芸術、音楽、お祝いを紹介する、土曜日のご家族参加型イベントです。児童・生徒の活動、文化展示、パフォーマンス、工作、体験型ブースをお楽しみいただけます。午後2時～3時に片付けを行います（学校コミュニティの皆さまのご協力も歓迎します）。幼稚部・小学部の児童は必ず保護者同伴でご参加ください（お子さまだけを送り届けることはできません）。当日はスクールバスの運行はありません。詳細は近日中にお知らせします。</t>
+          <t xml:space="preserve">今年のテーマは「世界の祝日とお祭り」です。学校コミュニティのさまざまな伝統、行事、文化をみんなで楽しくお祝いする一日です。9:45開門、10:00にフェスティバルが始まります。10:00～13:00には、教職員や生徒によるゲーム、クラフト、文化体験など、世界各地にちなんだ体験型ブースセッションを3回行います。お化け屋敷は10:00～12:00。仮装パレードでは、伝統衣装や民族衣装、祝日やお祭りを表す衣装、ハロウィンの仮装で参加できます（仮装は自由参加です。普段着での参加ももちろん歓迎します）。フードトラックの出店や、保護者の皆様による食べ物の販売もあります。13:00～13:50は体育館に移動し、ゲームやダンスの最終イベントを行います。IMFは通常の登校日ではありません。幼稚部・小学部の児童は、参加している間、必ず保護者または付き添いの大人と一緒に行動してください。お子様だけを学校に送り、後からお迎えに来ることはできません。当日はスクールバスの運行はありません。</t>
         </is>
       </c>
       <c r="O32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Enishi International School</t>
         </is>
       </c>
       <c r="P32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">エニシインターナショナルスクール</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr" s="2">
